--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="150">
   <si>
     <t xml:space="preserve">Station_1</t>
   </si>
@@ -222,13 +222,233 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">10-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-6 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">could be 212 or 272 for Azimuth_B. Large question mark at bottom of sheet and 3 tree entries crossed out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-4 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-4 circled. Big question mark at bottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B17S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B16. No tree entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B15. No tree entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,06</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">50ft 88</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">° approx 30ft circle 5 dead trees. 12-4 circled</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-6 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02,06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-4 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-4 circled. i.e. B032-02-06-272-087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-2 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">question mark by 28-4 station3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azimuth</t>
   </si>
   <si>
     <t xml:space="preserve">Dist (ft)</t>
   </si>
   <si>
-    <t xml:space="preserve">Down</t>
+    <t xml:space="preserve">Spec_SD</t>
   </si>
   <si>
     <t xml:space="preserve">Age</t>
@@ -268,6 +488,21 @@
   </si>
   <si>
     <t xml:space="preserve">NP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i.e. T020-340-077-DF-15-00SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-WH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i.e. T033-204-55-DF-04-00LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i.e. T033-218-070-ST-24-99DS</t>
   </si>
 </sst>
 </file>
@@ -348,7 +583,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -358,6 +593,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -378,7 +617,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.2"/>
@@ -931,24 +1170,1146 @@
         <v>60</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="AB8" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="AC8" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="R9" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA9" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="AB9" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC9" s="0" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>262</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>172</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA10" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="AB10" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC10" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P11" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q11" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC11" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>261</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q12" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="S12" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="U12" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V12" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="W12" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P13" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <v>260</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC13" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P14" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="S14" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="T14" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="U14" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V14" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="W14" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="X14" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P15" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="S15" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="T15" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V15" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="W15" s="0" t="n">
+        <v>172</v>
+      </c>
+      <c r="X15" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC15" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="A16" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
+      <c r="S16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="X16" s="1"/>
+      <c r="Y16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC16" s="0" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="O17" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P17" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="S17" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V17" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="W17" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC17" s="0" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>136</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="K18" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="O18" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P18" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q18" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="S18" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="T18" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="U18" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V18" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="W18" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC18" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="O19" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P19" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="T19" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V19" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="W19" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA19" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB19" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC19" s="0" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="L20" s="0" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P20" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="T20" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="U20" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V20" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="W20" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA20" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB20" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC20" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="R21" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA21" s="0" t="n">
+        <v>183</v>
+      </c>
+      <c r="AB21" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="AC21" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="S22" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V22" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="W22" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA22" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="AB22" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="AC22" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="S23" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="T23" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="U23" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V23" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="W23" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA23" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="AB23" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC23" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>293</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC24" s="0" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -966,7 +2327,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.52"/>
@@ -977,22 +2338,22 @@
         <v>24</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1006,10 +2367,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>6</v>
@@ -1026,7 +2387,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>5</v>
@@ -1046,7 +2407,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>10</v>
@@ -1066,7 +2427,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>4</v>
@@ -1086,10 +2447,10 @@
         <v>30</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>11</v>
@@ -1106,10 +2467,10 @@
         <v>63</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
@@ -1126,7 +2487,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>4</v>
@@ -1146,7 +2507,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>10</v>
@@ -1166,10 +2527,10 @@
         <v>14</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>25</v>
@@ -1186,7 +2547,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>6</v>
@@ -1206,10 +2567,10 @@
         <v>52</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>24</v>
@@ -1226,7 +2587,7 @@
         <v>49</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>5</v>
@@ -1246,7 +2607,7 @@
         <v>80</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>8</v>
@@ -1266,7 +2627,7 @@
         <v>64</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>5</v>
@@ -1286,7 +2647,7 @@
         <v>61</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>6</v>
@@ -1306,10 +2667,10 @@
         <v>85</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>10</v>
@@ -1326,7 +2687,7 @@
         <v>46</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>8</v>
@@ -1346,10 +2707,10 @@
         <v>48</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>6</v>
@@ -1366,10 +2727,10 @@
         <v>54</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>14</v>
@@ -1386,7 +2747,7 @@
         <v>64</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>10</v>
@@ -1406,7 +2767,7 @@
         <v>52</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>5</v>
@@ -1426,7 +2787,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>10</v>
@@ -1446,10 +2807,10 @@
         <v>46</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>14</v>
@@ -1466,7 +2827,7 @@
         <v>82</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>3</v>
@@ -1486,10 +2847,10 @@
         <v>76</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>8</v>
@@ -1506,7 +2867,7 @@
         <v>47</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>4</v>
@@ -1526,7 +2887,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>3</v>
@@ -1546,10 +2907,10 @@
         <v>61</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>6</v>
@@ -1566,10 +2927,10 @@
         <v>53</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>8</v>
@@ -1586,7 +2947,7 @@
         <v>52</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>10</v>
@@ -1606,10 +2967,10 @@
         <v>77</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>6</v>
@@ -1626,10 +2987,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>6</v>
@@ -1646,10 +3007,10 @@
         <v>80</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F34" s="0" t="n">
         <v>7</v>
@@ -1666,7 +3027,7 @@
         <v>86</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>8</v>
@@ -1686,10 +3047,10 @@
         <v>89</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>8</v>
@@ -1706,10 +3067,10 @@
         <v>141</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F37" s="0" t="n">
         <v>6</v>
@@ -1726,7 +3087,7 @@
         <v>67</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>5</v>
@@ -1746,10 +3107,10 @@
         <v>53</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F39" s="0" t="n">
         <v>9</v>
@@ -1766,10 +3127,10 @@
         <v>44</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F40" s="0" t="n">
         <v>14</v>
@@ -1786,7 +3147,7 @@
         <v>38</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>4</v>
@@ -1806,10 +3167,10 @@
         <v>45</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F42" s="0" t="n">
         <v>10</v>
@@ -1826,10 +3187,10 @@
         <v>45</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F43" s="0" t="n">
         <v>12</v>
@@ -1846,10 +3207,10 @@
         <v>24</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F44" s="0" t="n">
         <v>10</v>
@@ -1866,7 +3227,7 @@
         <v>33</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E45" s="0" t="n">
         <v>3</v>
@@ -1886,10 +3247,10 @@
         <v>55</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F46" s="0" t="n">
         <v>7</v>
@@ -1906,7 +3267,7 @@
         <v>43</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>0</v>
@@ -1915,7 +3276,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1929,10 +3290,10 @@
         <v>86</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F48" s="0" t="n">
         <v>14</v>
@@ -1949,10 +3310,10 @@
         <v>39</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F49" s="0" t="n">
         <v>18</v>
@@ -1969,7 +3330,7 @@
         <v>41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>4</v>
@@ -1989,7 +3350,7 @@
         <v>107</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>10</v>
@@ -2009,7 +3370,7 @@
         <v>107</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>1</v>
@@ -2029,10 +3390,10 @@
         <v>127</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F53" s="0" t="n">
         <v>6</v>
@@ -2049,7 +3410,7 @@
         <v>117</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>6</v>
@@ -2069,10 +3430,10 @@
         <v>129</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>12</v>
@@ -2089,10 +3450,10 @@
         <v>67</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F56" s="0" t="n">
         <v>9</v>
@@ -2109,10 +3470,10 @@
         <v>64</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F57" s="0" t="n">
         <v>10</v>
@@ -2129,10 +3490,10 @@
         <v>48</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F58" s="0" t="n">
         <v>6</v>
@@ -2149,10 +3510,10 @@
         <v>61</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F59" s="0" t="n">
         <v>8</v>
@@ -2169,7 +3530,4731 @@
         <v>50</v>
       </c>
       <c r="D60" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F69" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>332</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>339</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>332</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E75" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E76" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F77" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>293</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>313</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E79" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E80" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F81" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F83" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F85" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>306</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E86" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E87" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E88" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>153</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>153</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F90" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F91" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B92" s="0" t="n">
+        <v>220</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F92" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E93" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B94" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E94" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E95" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>127</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F97" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E98" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F98" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F100" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E101" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F102" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E103" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>254</v>
+      </c>
+      <c r="C104" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E104" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F104" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E105" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F105" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="C106" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F106" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E107" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F107" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C108" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E108" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B109" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="C109" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E109" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C110" s="0" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F110" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E111" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B112" s="0" t="n">
+        <v>341</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B113" s="0" t="n">
+        <v>340</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F113" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="G113" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E114" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="E115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="E117" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B118" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E118" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B119" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F119" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B120" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E120" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F120" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B121" s="0" t="n">
+        <v>237</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E121" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B122" s="0" t="n">
+        <v>216</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E122" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B123" s="0" t="n">
+        <v>203</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E123" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B124" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F124" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B125" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E125" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
         <v>76</v>
+      </c>
+      <c r="B126" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F126" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B127" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="C127" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F127" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B128" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="C128" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E128" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B129" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C129" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E129" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F129" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B130" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C130" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E130" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B131" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="C131" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E131" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F131" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B132" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E132" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B133" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F133" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B134" s="0" t="n">
+        <v>214</v>
+      </c>
+      <c r="C134" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D134" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F134" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B135" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="C135" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D135" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F135" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B136" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="C136" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="D136" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E136" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B137" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C137" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D137" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E137" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B138" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C138" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D138" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E138" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B139" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="C139" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F139" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B140" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="C140" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F140" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B141" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="C141" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F141" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B142" s="0" t="n">
+        <v>161</v>
+      </c>
+      <c r="C142" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F142" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B143" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="C143" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E143" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F143" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B144" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="C144" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F144" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B145" s="0" t="n">
+        <v>136</v>
+      </c>
+      <c r="C145" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E145" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F145" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B146" s="0" t="n">
+        <v>128</v>
+      </c>
+      <c r="C146" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E146" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B147" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C147" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F147" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B148" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="C148" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F148" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B149" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="C149" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F149" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B150" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C150" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F150" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B151" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C151" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D151" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F151" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B152" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C152" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D152" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F152" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B153" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="C153" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D153" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E153" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F153" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B154" s="0" t="n">
+        <v>119</v>
+      </c>
+      <c r="C154" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="D154" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F154" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B155" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="C155" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F155" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B156" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C156" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E156" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B157" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="C157" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F157" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B158" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C158" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E158" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F158" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B159" s="0" t="n">
+        <v>277</v>
+      </c>
+      <c r="C159" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D159" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="F159" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B160" s="0" t="n">
+        <v>277</v>
+      </c>
+      <c r="C160" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D160" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E160" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F160" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B161" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="C161" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D161" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E161" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B162" s="0" t="n">
+        <v>281</v>
+      </c>
+      <c r="C162" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="D162" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E162" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F162" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B163" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="C163" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D163" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E163" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F163" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B164" s="0" t="n">
+        <v>345</v>
+      </c>
+      <c r="C164" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D164" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E164" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F164" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B165" s="0" t="n">
+        <v>342</v>
+      </c>
+      <c r="C165" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D165" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E165" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F165" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B166" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="C166" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D166" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E166" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B167" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="C167" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="D167" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E167" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F167" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B168" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="C168" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D168" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E168" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F168" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B169" s="0" t="n">
+        <v>152</v>
+      </c>
+      <c r="C169" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D169" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E169" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F169" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B170" s="0" t="n">
+        <v>163</v>
+      </c>
+      <c r="C170" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D170" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E170" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F170" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B171" s="0" t="n">
+        <v>262</v>
+      </c>
+      <c r="C171" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D171" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E171" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F171" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B172" s="0" t="n">
+        <v>249</v>
+      </c>
+      <c r="C172" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="D172" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E172" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F172" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B173" s="0" t="n">
+        <v>249</v>
+      </c>
+      <c r="C173" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="D173" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E173" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F173" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B174" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="C174" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D174" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E174" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B175" s="0" t="n">
+        <v>230</v>
+      </c>
+      <c r="C175" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D175" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F175" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B176" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="C176" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D176" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B177" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="C177" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D177" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E177" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F177" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B178" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="C178" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="D178" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E178" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F178" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>176</v>
+      </c>
+      <c r="C179" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D179" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E179" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F179" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B180" s="0" t="n">
+        <v>176</v>
+      </c>
+      <c r="C180" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D180" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E180" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F180" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B181" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="C181" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D181" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B182" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="C182" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D182" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E182" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F182" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B183" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C183" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D183" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E183" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F183" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B184" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C184" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D184" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E184" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F184" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B185" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="C185" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D185" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E185" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F185" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B186" s="0" t="n">
+        <v>242</v>
+      </c>
+      <c r="C186" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D186" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E186" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F186" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B187" s="0" t="n">
+        <v>255</v>
+      </c>
+      <c r="C187" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="D187" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E187" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F187" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B188" s="0" t="n">
+        <v>341</v>
+      </c>
+      <c r="C188" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="D188" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E188" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F188" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B189" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C189" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="D189" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E189" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B190" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="C190" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D190" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E190" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F190" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B191" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C191" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D191" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E191" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F191" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B192" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="C192" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D192" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E192" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B193" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="C193" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D193" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E193" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F193" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B194" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C194" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D194" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E194" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F194" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B195" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C195" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D195" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E195" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F195" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B196" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="C196" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D196" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E196" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F196" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B197" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C197" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D197" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E197" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F197" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B198" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C198" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="D198" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E198" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F198" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B199" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="C199" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D199" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E199" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F199" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B200" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="C200" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="D200" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E200" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F200" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B201" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="C201" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D201" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E201" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C202" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D202" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E202" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F202" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C203" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D203" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E203" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F203" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C204" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D204" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E204" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C205" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D205" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E205" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="C206" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D206" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E206" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F206" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C207" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D207" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E207" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="C208" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D208" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E208" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F208" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="C209" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D209" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E209" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F209" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="C210" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D210" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E210" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F210" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="C211" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D211" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E211" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F211" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B212" s="0" t="n">
+        <v>334</v>
+      </c>
+      <c r="C212" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D212" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E212" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F212" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B213" s="0" t="n">
+        <v>334</v>
+      </c>
+      <c r="C213" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D213" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E213" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F213" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B214" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="C214" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="D214" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E214" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B215" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="C215" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D215" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E215" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F215" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B216" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="D216" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E216" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B217" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C217" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D217" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E217" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F217" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B218" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="C218" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="D218" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E218" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F218" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B219" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C219" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="D219" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E219" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F219" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B220" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="C220" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="D220" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E220" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F220" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B221" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="C221" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="D221" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E221" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F221" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B222" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C222" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D222" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E222" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F222" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B223" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="C223" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D223" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E223" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F223" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B224" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="C224" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D224" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E224" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F224" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B225" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="C225" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D225" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E225" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F225" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B226" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C226" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D226" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E226" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F226" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B227" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="C227" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="D227" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E227" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F227" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B228" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="C228" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D228" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E228" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F228" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B229" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C229" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D229" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E229" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F229" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B230" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C230" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D230" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E230" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B231" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C231" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D231" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E231" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F231" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B232" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="C232" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D232" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E232" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B233" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C233" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D233" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E233" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F233" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B234" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C234" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D234" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E234" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F234" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B235" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C235" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D235" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E235" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F235" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B236" s="0" t="n">
+        <v>331</v>
+      </c>
+      <c r="C236" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D236" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="E236" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F236" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B237" s="0" t="n">
+        <v>331</v>
+      </c>
+      <c r="C237" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D237" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="E237" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F237" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B238" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="C238" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D238" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E238" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F238" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B239" s="0" t="n">
+        <v>235</v>
+      </c>
+      <c r="C239" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D239" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E239" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B240" s="0" t="n">
+        <v>217</v>
+      </c>
+      <c r="C240" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D240" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E240" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F240" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B241" s="0" t="n">
+        <v>217</v>
+      </c>
+      <c r="C241" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="D241" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E241" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F241" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B242" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C242" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D242" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E242" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F242" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B243" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="C243" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D243" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E243" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F243" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B244" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="C244" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D244" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E244" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F244" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B245" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="C245" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D245" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="F245" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B246" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="C246" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D246" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E246" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F246" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B247" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="C247" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="D247" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E247" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F247" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B248" s="0" t="n">
+        <v>343</v>
+      </c>
+      <c r="C248" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="D248" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E248" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F248" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B249" s="0" t="n">
+        <v>289</v>
+      </c>
+      <c r="C249" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D249" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E249" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F249" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B250" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C250" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="D250" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E250" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F250" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B251" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="C251" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="D251" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E251" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F251" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B252" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C252" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D252" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E252" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F252" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B253" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C253" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D253" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E253" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F253" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B254" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="C254" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D254" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E254" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F254" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B255" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="C255" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D255" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E255" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F255" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B256" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="C256" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="D256" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E256" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F256" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B257" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C257" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D257" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E257" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F257" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B258" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="C258" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D258" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E258" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F258" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B259" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C259" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D259" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E259" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F259" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B260" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C260" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D260" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E260" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F260" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B261" s="0" t="n">
+        <v>255</v>
+      </c>
+      <c r="C261" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D261" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B262" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="C262" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="D262" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E262" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B263" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C263" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="D263" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E263" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F263" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B264" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="C264" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D264" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E264" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F264" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B265" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="C265" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D265" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E265" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="F265" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G265" s="0" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B266" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="C266" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="D266" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E266" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F266" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B267" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C267" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D267" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E267" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F267" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B268" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="C268" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D268" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E268" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F268" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B269" s="0" t="n">
+        <v>218</v>
+      </c>
+      <c r="C269" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D269" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="F269" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="G269" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B270" s="0" t="n">
+        <v>223</v>
+      </c>
+      <c r="C270" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="D270" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E270" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F270" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B271" s="0" t="n">
+        <v>228</v>
+      </c>
+      <c r="C271" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="D271" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E271" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F271" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B272" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="C272" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D272" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E272" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F272" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B273" s="0" t="n">
+        <v>243</v>
+      </c>
+      <c r="C273" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D273" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E273" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F273" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B274" s="0" t="n">
+        <v>273</v>
+      </c>
+      <c r="C274" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D274" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E274" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F274" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B275" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C275" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D275" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E275" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F275" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B276" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="C276" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="D276" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E276" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F276" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B277" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="C277" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="D277" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E277" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F277" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B278" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="C278" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="D278" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E278" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F278" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B279" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C279" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="D279" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E279" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F279" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B280" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="C280" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="D280" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E280" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F280" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B281" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C281" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="D281" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E281" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F281" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B282" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="C282" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D282" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E282" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F282" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B283" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="C283" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D283" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E283" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F283" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B284" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C284" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D284" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E284" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F284" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B285" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C285" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="D285" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E285" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F285" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B286" s="0" t="n">
+        <v>147</v>
+      </c>
+      <c r="C286" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D286" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E286" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F286" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B287" s="0" t="n">
+        <v>147</v>
+      </c>
+      <c r="C287" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D287" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E287" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F287" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B288" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="C288" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D288" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E288" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F288" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B289" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C289" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D289" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E289" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F289" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B290" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="C290" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D290" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E290" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F290" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B291" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="C291" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D291" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E291" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F291" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B292" s="0" t="n">
+        <v>202</v>
+      </c>
+      <c r="C292" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D292" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E292" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F292" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B293" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="C293" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D293" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E293" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F293" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B294" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="C294" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="D294" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E294" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F294" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B295" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="C295" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D295" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E295" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F295" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B296" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="C296" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="D296" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E296" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F296" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B297" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="C297" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D297" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E297" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F297" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B298" s="0" t="n">
+        <v>219</v>
+      </c>
+      <c r="C298" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D298" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E298" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F298" s="0" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="291">
   <si>
     <t xml:space="preserve">Station_1</t>
   </si>
@@ -782,6 +782,93 @@
   </si>
   <si>
     <t xml:space="preserve">B58. 12+2 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B59. 10C circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B29. West half of plot is open. No tree entries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B30. No tree entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B31. 22+4 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B32. 20+2 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B33. 16+4 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B34. 16+2 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B60. 14+2 circled</t>
   </si>
   <si>
     <t xml:space="preserve">Azimuth</t>
@@ -977,7 +1064,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.2"/>
@@ -4769,6 +4856,580 @@
         <v>234</v>
       </c>
     </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y54" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z54" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA54" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB54" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC54" s="0" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="N55" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="O55" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q55" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="S55" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="T55" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V55" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="W55" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="Y55" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC55" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="M56" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="N56" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q56" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="S56" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="T56" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="U56" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V56" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="W56" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC56" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="M57" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="O57" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q57" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="S57" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="T57" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V57" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="W57" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y57" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AA57" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB57" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC57" s="0" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>183</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="N58" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q58" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="S58" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="T58" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V58" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="W58" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="X58" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y58" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z58" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA58" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="AB58" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="AC58" s="0" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="N59" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="O59" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q59" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="R59" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="S59" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="T59" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V59" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="W59" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="X59" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Z59" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AA59" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB59" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="AC59" s="0" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>174</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="L60" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="N60" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q60" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="R60" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="S60" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="T60" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V60" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="W60" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="X60" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y60" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z60" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA60" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="AB60" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC60" s="0" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="L61" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y61" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z61" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AA61" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="AB61" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="AC61" s="0" t="s">
+        <v>263</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -4785,7 +5446,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G525"/>
+  <dimension ref="A1:G623"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.52"/>
@@ -4796,22 +5457,22 @@
         <v>24</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4825,10 +5486,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>6</v>
@@ -4845,7 +5506,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>5</v>
@@ -4865,7 +5526,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>10</v>
@@ -4885,7 +5546,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>4</v>
@@ -4905,10 +5566,10 @@
         <v>30</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>11</v>
@@ -4925,10 +5586,10 @@
         <v>63</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
@@ -4945,7 +5606,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>4</v>
@@ -4965,7 +5626,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>10</v>
@@ -4985,10 +5646,10 @@
         <v>14</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>25</v>
@@ -5005,7 +5666,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>6</v>
@@ -5025,10 +5686,10 @@
         <v>52</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>24</v>
@@ -5045,7 +5706,7 @@
         <v>49</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>5</v>
@@ -5065,7 +5726,7 @@
         <v>80</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>8</v>
@@ -5085,7 +5746,7 @@
         <v>64</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>5</v>
@@ -5105,7 +5766,7 @@
         <v>61</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>6</v>
@@ -5125,10 +5786,10 @@
         <v>85</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>10</v>
@@ -5145,7 +5806,7 @@
         <v>46</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>8</v>
@@ -5165,10 +5826,10 @@
         <v>48</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>6</v>
@@ -5185,10 +5846,10 @@
         <v>54</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>14</v>
@@ -5205,7 +5866,7 @@
         <v>64</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>10</v>
@@ -5225,7 +5886,7 @@
         <v>52</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>5</v>
@@ -5245,7 +5906,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>10</v>
@@ -5265,10 +5926,10 @@
         <v>46</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>14</v>
@@ -5285,7 +5946,7 @@
         <v>82</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>3</v>
@@ -5305,10 +5966,10 @@
         <v>76</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>8</v>
@@ -5325,7 +5986,7 @@
         <v>47</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>4</v>
@@ -5345,7 +6006,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>3</v>
@@ -5365,10 +6026,10 @@
         <v>61</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>6</v>
@@ -5385,10 +6046,10 @@
         <v>53</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>8</v>
@@ -5405,7 +6066,7 @@
         <v>52</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>10</v>
@@ -5425,10 +6086,10 @@
         <v>77</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>6</v>
@@ -5445,10 +6106,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>6</v>
@@ -5465,10 +6126,10 @@
         <v>80</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F34" s="0" t="n">
         <v>7</v>
@@ -5485,7 +6146,7 @@
         <v>86</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>8</v>
@@ -5505,10 +6166,10 @@
         <v>89</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>8</v>
@@ -5525,10 +6186,10 @@
         <v>141</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F37" s="0" t="n">
         <v>6</v>
@@ -5545,7 +6206,7 @@
         <v>67</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>5</v>
@@ -5565,10 +6226,10 @@
         <v>53</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F39" s="0" t="n">
         <v>9</v>
@@ -5585,10 +6246,10 @@
         <v>44</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F40" s="0" t="n">
         <v>14</v>
@@ -5605,7 +6266,7 @@
         <v>38</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>4</v>
@@ -5625,10 +6286,10 @@
         <v>45</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F42" s="0" t="n">
         <v>10</v>
@@ -5645,10 +6306,10 @@
         <v>45</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F43" s="0" t="n">
         <v>12</v>
@@ -5665,10 +6326,10 @@
         <v>24</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F44" s="0" t="n">
         <v>10</v>
@@ -5685,7 +6346,7 @@
         <v>33</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E45" s="0" t="n">
         <v>3</v>
@@ -5705,10 +6366,10 @@
         <v>55</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F46" s="0" t="n">
         <v>7</v>
@@ -5725,7 +6386,7 @@
         <v>43</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>0</v>
@@ -5734,7 +6395,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5748,10 +6409,10 @@
         <v>86</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F48" s="0" t="n">
         <v>14</v>
@@ -5768,10 +6429,10 @@
         <v>39</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F49" s="0" t="n">
         <v>18</v>
@@ -5788,7 +6449,7 @@
         <v>41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>4</v>
@@ -5808,7 +6469,7 @@
         <v>107</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>10</v>
@@ -5828,7 +6489,7 @@
         <v>107</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>1</v>
@@ -5848,10 +6509,10 @@
         <v>127</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F53" s="0" t="n">
         <v>6</v>
@@ -5868,7 +6529,7 @@
         <v>117</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>6</v>
@@ -5888,10 +6549,10 @@
         <v>129</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>12</v>
@@ -5908,10 +6569,10 @@
         <v>67</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F56" s="0" t="n">
         <v>9</v>
@@ -5928,10 +6589,10 @@
         <v>64</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F57" s="0" t="n">
         <v>10</v>
@@ -5948,10 +6609,10 @@
         <v>48</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F58" s="0" t="n">
         <v>6</v>
@@ -5968,10 +6629,10 @@
         <v>61</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F59" s="0" t="n">
         <v>8</v>
@@ -5988,7 +6649,7 @@
         <v>50</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6002,7 +6663,7 @@
         <v>68</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E61" s="0" t="n">
         <v>1</v>
@@ -6022,7 +6683,7 @@
         <v>58</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E62" s="0" t="n">
         <v>2</v>
@@ -6042,10 +6703,10 @@
         <v>21</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F63" s="0" t="n">
         <v>10</v>
@@ -6062,7 +6723,7 @@
         <v>18</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E64" s="0" t="n">
         <v>10</v>
@@ -6082,7 +6743,7 @@
         <v>31</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E65" s="0" t="n">
         <v>8</v>
@@ -6102,10 +6763,10 @@
         <v>69</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F66" s="0" t="n">
         <v>4</v>
@@ -6122,10 +6783,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F67" s="0" t="n">
         <v>4</v>
@@ -6142,10 +6803,10 @@
         <v>63</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F68" s="0" t="n">
         <v>4</v>
@@ -6162,10 +6823,10 @@
         <v>80</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F69" s="0" t="n">
         <v>5</v>
@@ -6182,10 +6843,10 @@
         <v>80</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F70" s="0" t="n">
         <v>5</v>
@@ -6202,10 +6863,10 @@
         <v>59</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F71" s="0" t="n">
         <v>8</v>
@@ -6222,10 +6883,10 @@
         <v>38</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F72" s="0" t="n">
         <v>6</v>
@@ -6242,10 +6903,10 @@
         <v>37</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F73" s="0" t="n">
         <v>10</v>
@@ -6262,7 +6923,7 @@
         <v>27</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E74" s="0" t="n">
         <v>2</v>
@@ -6282,7 +6943,7 @@
         <v>60</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E75" s="0" t="n">
         <v>7</v>
@@ -6302,7 +6963,7 @@
         <v>64</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E76" s="0" t="n">
         <v>7</v>
@@ -6322,10 +6983,10 @@
         <v>36</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F77" s="0" t="n">
         <v>4</v>
@@ -6342,10 +7003,10 @@
         <v>22</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F78" s="0" t="n">
         <v>6</v>
@@ -6362,7 +7023,7 @@
         <v>45</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E79" s="0" t="n">
         <v>6</v>
@@ -6382,7 +7043,7 @@
         <v>24</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E80" s="0" t="n">
         <v>3</v>
@@ -6402,10 +7063,10 @@
         <v>49</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F81" s="0" t="n">
         <v>6</v>
@@ -6422,7 +7083,7 @@
         <v>50</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6436,10 +7097,10 @@
         <v>42</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F83" s="0" t="n">
         <v>5</v>
@@ -6456,7 +7117,7 @@
         <v>48</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E84" s="0" t="n">
         <v>10</v>
@@ -6476,10 +7137,10 @@
         <v>44</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F85" s="0" t="n">
         <v>6</v>
@@ -6496,7 +7157,7 @@
         <v>61</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E86" s="0" t="n">
         <v>2</v>
@@ -6516,7 +7177,7 @@
         <v>30</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E87" s="0" t="n">
         <v>2</v>
@@ -6536,7 +7197,7 @@
         <v>58</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E88" s="0" t="n">
         <v>2</v>
@@ -6556,7 +7217,7 @@
         <v>31</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E89" s="0" t="n">
         <v>3</v>
@@ -6576,10 +7237,10 @@
         <v>69</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F90" s="0" t="n">
         <v>6</v>
@@ -6596,10 +7257,10 @@
         <v>24</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F91" s="0" t="n">
         <v>20</v>
@@ -6616,10 +7277,10 @@
         <v>34</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F92" s="0" t="n">
         <v>15</v>
@@ -6636,7 +7297,7 @@
         <v>53</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E93" s="0" t="n">
         <v>5</v>
@@ -6656,7 +7317,7 @@
         <v>85</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E94" s="0" t="n">
         <v>2</v>
@@ -6676,7 +7337,7 @@
         <v>89</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E95" s="0" t="n">
         <v>5</v>
@@ -6696,7 +7357,7 @@
         <v>16</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E96" s="0" t="n">
         <v>0</v>
@@ -6716,10 +7377,10 @@
         <v>74</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F97" s="0" t="n">
         <v>8</v>
@@ -6736,7 +7397,7 @@
         <v>53</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E98" s="0" t="n">
         <v>6</v>
@@ -6756,7 +7417,7 @@
         <v>65</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E99" s="0" t="n">
         <v>0</v>
@@ -6776,10 +7437,10 @@
         <v>55</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F100" s="0" t="n">
         <v>8</v>
@@ -6796,7 +7457,7 @@
         <v>63</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E101" s="0" t="n">
         <v>4</v>
@@ -6816,10 +7477,10 @@
         <v>83</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F102" s="0" t="n">
         <v>8</v>
@@ -6836,7 +7497,7 @@
         <v>46</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E103" s="0" t="n">
         <v>7</v>
@@ -6856,7 +7517,7 @@
         <v>40</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E104" s="0" t="n">
         <v>5</v>
@@ -6876,7 +7537,7 @@
         <v>64</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E105" s="0" t="n">
         <v>8</v>
@@ -6896,10 +7557,10 @@
         <v>61</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F106" s="0" t="n">
         <v>15</v>
@@ -6916,7 +7577,7 @@
         <v>59</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E107" s="0" t="n">
         <v>10</v>
@@ -6936,7 +7597,7 @@
         <v>30</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E108" s="0" t="n">
         <v>4</v>
@@ -6956,7 +7617,7 @@
         <v>64</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E109" s="0" t="n">
         <v>2</v>
@@ -6976,10 +7637,10 @@
         <v>85.5</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F110" s="0" t="n">
         <v>8</v>
@@ -6996,7 +7657,7 @@
         <v>65</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E111" s="0" t="n">
         <v>4</v>
@@ -7016,7 +7677,7 @@
         <v>66</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E112" s="0" t="n">
         <v>1</v>
@@ -7036,16 +7697,16 @@
         <v>77</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F113" s="0" t="n">
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7059,7 +7720,7 @@
         <v>66</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E114" s="0" t="n">
         <v>1</v>
@@ -7079,7 +7740,7 @@
         <v>70</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E115" s="0" t="n">
         <v>0</v>
@@ -7099,10 +7760,10 @@
         <v>6</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F116" s="0" t="n">
         <v>14</v>
@@ -7119,7 +7780,7 @@
         <v>75</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E117" s="0" t="n">
         <v>4</v>
@@ -7139,7 +7800,7 @@
         <v>66</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E118" s="0" t="n">
         <v>3</v>
@@ -7159,10 +7820,10 @@
         <v>11</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F119" s="0" t="n">
         <v>10</v>
@@ -7179,7 +7840,7 @@
         <v>54</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E120" s="0" t="n">
         <v>10</v>
@@ -7199,7 +7860,7 @@
         <v>54</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E121" s="0" t="n">
         <v>5</v>
@@ -7219,7 +7880,7 @@
         <v>54</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E122" s="0" t="n">
         <v>10</v>
@@ -7239,7 +7900,7 @@
         <v>77</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E123" s="0" t="n">
         <v>1</v>
@@ -7259,10 +7920,10 @@
         <v>68</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F124" s="0" t="n">
         <v>16</v>
@@ -7279,7 +7940,7 @@
         <v>26</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="E125" s="0" t="n">
         <v>1</v>
@@ -7299,10 +7960,10 @@
         <v>69</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F126" s="0" t="n">
         <v>10</v>
@@ -7319,10 +7980,10 @@
         <v>39</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F127" s="0" t="n">
         <v>4</v>
@@ -7339,7 +8000,7 @@
         <v>23</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E128" s="0" t="n">
         <v>1</v>
@@ -7359,7 +8020,7 @@
         <v>45</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E129" s="0" t="n">
         <v>7</v>
@@ -7379,7 +8040,7 @@
         <v>30</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E130" s="0" t="n">
         <v>7</v>
@@ -7399,7 +8060,7 @@
         <v>45</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E131" s="0" t="n">
         <v>9</v>
@@ -7419,7 +8080,7 @@
         <v>31</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E132" s="0" t="n">
         <v>4</v>
@@ -7439,10 +8100,10 @@
         <v>40</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F133" s="0" t="n">
         <v>4</v>
@@ -7459,10 +8120,10 @@
         <v>67</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F134" s="0" t="n">
         <v>10</v>
@@ -7479,10 +8140,10 @@
         <v>69</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F135" s="0" t="n">
         <v>13</v>
@@ -7499,7 +8160,7 @@
         <v>43</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E136" s="0" t="n">
         <v>1</v>
@@ -7519,7 +8180,7 @@
         <v>39</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E137" s="0" t="n">
         <v>1</v>
@@ -7539,7 +8200,7 @@
         <v>69</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E138" s="0" t="n">
         <v>1</v>
@@ -7559,10 +8220,10 @@
         <v>72</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F139" s="0" t="n">
         <v>16</v>
@@ -7579,10 +8240,10 @@
         <v>69</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F140" s="0" t="n">
         <v>6</v>
@@ -7599,10 +8260,10 @@
         <v>67</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F141" s="0" t="n">
         <v>13</v>
@@ -7619,10 +8280,10 @@
         <v>52</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F142" s="0" t="n">
         <v>6</v>
@@ -7639,7 +8300,7 @@
         <v>67</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E143" s="0" t="n">
         <v>7</v>
@@ -7659,10 +8320,10 @@
         <v>47</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F144" s="0" t="n">
         <v>4</v>
@@ -7679,7 +8340,7 @@
         <v>60</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E145" s="0" t="n">
         <v>4</v>
@@ -7699,7 +8360,7 @@
         <v>55</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E146" s="0" t="n">
         <v>1</v>
@@ -7719,10 +8380,10 @@
         <v>59</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F147" s="0" t="n">
         <v>12</v>
@@ -7739,10 +8400,10 @@
         <v>12</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F148" s="0" t="n">
         <v>8</v>
@@ -7759,10 +8420,10 @@
         <v>77</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F149" s="0" t="n">
         <v>8</v>
@@ -7779,10 +8440,10 @@
         <v>49</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F150" s="0" t="n">
         <v>10</v>
@@ -7799,10 +8460,10 @@
         <v>49</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F151" s="0" t="n">
         <v>9</v>
@@ -7819,10 +8480,10 @@
         <v>53</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F152" s="0" t="n">
         <v>15</v>
@@ -7839,7 +8500,7 @@
         <v>94</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E153" s="0" t="n">
         <v>3</v>
@@ -7859,10 +8520,10 @@
         <v>72</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F154" s="0" t="n">
         <v>10</v>
@@ -7879,10 +8540,10 @@
         <v>34</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F155" s="0" t="n">
         <v>8</v>
@@ -7899,7 +8560,7 @@
         <v>96</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E156" s="0" t="n">
         <v>2</v>
@@ -7919,10 +8580,10 @@
         <v>39</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F157" s="0" t="n">
         <v>10</v>
@@ -7939,7 +8600,7 @@
         <v>78</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E158" s="0" t="n">
         <v>6</v>
@@ -7959,7 +8620,7 @@
         <v>66</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="F159" s="0" t="n">
         <v>4</v>
@@ -7976,10 +8637,10 @@
         <v>66</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F160" s="0" t="n">
         <v>10</v>
@@ -7996,7 +8657,7 @@
         <v>40</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E161" s="0" t="n">
         <v>2</v>
@@ -8016,10 +8677,10 @@
         <v>56</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F162" s="0" t="n">
         <v>8</v>
@@ -8036,7 +8697,7 @@
         <v>60</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E163" s="0" t="n">
         <v>3</v>
@@ -8056,7 +8717,7 @@
         <v>39</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E164" s="0" t="n">
         <v>4</v>
@@ -8076,10 +8737,10 @@
         <v>30</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F165" s="0" t="n">
         <v>7</v>
@@ -8096,7 +8757,7 @@
         <v>84</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E166" s="0" t="n">
         <v>6</v>
@@ -8116,10 +8777,10 @@
         <v>43</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F167" s="0" t="n">
         <v>4</v>
@@ -8136,10 +8797,10 @@
         <v>38</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F168" s="0" t="n">
         <v>8</v>
@@ -8156,7 +8817,7 @@
         <v>24</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E169" s="0" t="n">
         <v>8</v>
@@ -8176,10 +8837,10 @@
         <v>21</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E170" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F170" s="0" t="n">
         <v>6</v>
@@ -8196,10 +8857,10 @@
         <v>68</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F171" s="0" t="n">
         <v>10</v>
@@ -8216,10 +8877,10 @@
         <v>79</v>
       </c>
       <c r="D172" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F172" s="0" t="n">
         <v>14</v>
@@ -8236,10 +8897,10 @@
         <v>79</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F173" s="0" t="n">
         <v>14</v>
@@ -8256,10 +8917,10 @@
         <v>48</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8273,7 +8934,7 @@
         <v>58</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E175" s="0" t="n">
         <v>5</v>
@@ -8293,7 +8954,7 @@
         <v>39</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E176" s="0" t="n">
         <v>2</v>
@@ -8313,7 +8974,7 @@
         <v>39</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E177" s="0" t="n">
         <v>6</v>
@@ -8333,10 +8994,10 @@
         <v>52</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F178" s="0" t="n">
         <v>10</v>
@@ -8353,10 +9014,10 @@
         <v>68</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F179" s="0" t="n">
         <v>10</v>
@@ -8373,7 +9034,7 @@
         <v>40</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E180" s="0" t="n">
         <v>7</v>
@@ -8393,7 +9054,7 @@
         <v>53</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E181" s="0" t="n">
         <v>2</v>
@@ -8413,10 +9074,10 @@
         <v>53</v>
       </c>
       <c r="D182" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F182" s="0" t="n">
         <v>4</v>
@@ -8433,10 +9094,10 @@
         <v>18</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F183" s="0" t="n">
         <v>9</v>
@@ -8453,7 +9114,7 @@
         <v>25</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E184" s="0" t="n">
         <v>5</v>
@@ -8473,7 +9134,7 @@
         <v>40</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E185" s="0" t="n">
         <v>6</v>
@@ -8493,7 +9154,7 @@
         <v>17</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E186" s="0" t="n">
         <v>8</v>
@@ -8513,10 +9174,10 @@
         <v>26</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F187" s="0" t="n">
         <v>6</v>
@@ -8533,10 +9194,10 @@
         <v>72</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F188" s="0" t="n">
         <v>8</v>
@@ -8553,7 +9214,7 @@
         <v>72</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E189" s="0" t="n">
         <v>2</v>
@@ -8573,7 +9234,7 @@
         <v>71</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E190" s="0" t="n">
         <v>3</v>
@@ -8593,7 +9254,7 @@
         <v>38</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E191" s="0" t="n">
         <v>10</v>
@@ -8613,10 +9274,10 @@
         <v>62</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8630,10 +9291,10 @@
         <v>69</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F193" s="0" t="n">
         <v>6</v>
@@ -8650,10 +9311,10 @@
         <v>67</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F194" s="0" t="n">
         <v>5</v>
@@ -8670,10 +9331,10 @@
         <v>64</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F195" s="0" t="n">
         <v>5</v>
@@ -8690,7 +9351,7 @@
         <v>67</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E196" s="0" t="n">
         <v>10</v>
@@ -8710,10 +9371,10 @@
         <v>62</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F197" s="0" t="n">
         <v>7</v>
@@ -8730,10 +9391,10 @@
         <v>56</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F198" s="0" t="n">
         <v>5</v>
@@ -8750,7 +9411,7 @@
         <v>46</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E199" s="0" t="n">
         <v>4</v>
@@ -8770,7 +9431,7 @@
         <v>27</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E200" s="0" t="n">
         <v>3</v>
@@ -8790,7 +9451,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E201" s="0" t="n">
         <v>5</v>
@@ -8807,10 +9468,10 @@
         <v>8</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F202" s="0" t="n">
         <v>5</v>
@@ -8827,10 +9488,10 @@
         <v>13</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F203" s="0" t="n">
         <v>3</v>
@@ -8847,10 +9508,10 @@
         <v>69</v>
       </c>
       <c r="D204" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8864,7 +9525,7 @@
         <v>77</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E205" s="0" t="n">
         <v>8</v>
@@ -8881,10 +9542,10 @@
         <v>77</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F206" s="0" t="n">
         <v>8</v>
@@ -8901,10 +9562,10 @@
         <v>77</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8918,7 +9579,7 @@
         <v>61</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E208" s="0" t="n">
         <v>10</v>
@@ -8938,10 +9599,10 @@
         <v>31</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F209" s="0" t="n">
         <v>6</v>
@@ -8958,10 +9619,10 @@
         <v>71</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F210" s="0" t="n">
         <v>6</v>
@@ -8978,7 +9639,7 @@
         <v>39</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E211" s="0" t="n">
         <v>8</v>
@@ -8998,10 +9659,10 @@
         <v>74</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F212" s="0" t="n">
         <v>4</v>
@@ -9018,10 +9679,10 @@
         <v>25</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F213" s="0" t="n">
         <v>6</v>
@@ -9038,10 +9699,10 @@
         <v>79</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9055,7 +9716,7 @@
         <v>37</v>
       </c>
       <c r="D215" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E215" s="0" t="n">
         <v>5</v>
@@ -9075,7 +9736,7 @@
         <v>97</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E216" s="0" t="n">
         <v>2</v>
@@ -9095,10 +9756,10 @@
         <v>74</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F217" s="0" t="n">
         <v>17</v>
@@ -9115,10 +9776,10 @@
         <v>87</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F218" s="0" t="n">
         <v>10</v>
@@ -9135,10 +9796,10 @@
         <v>76</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F219" s="0" t="n">
         <v>20</v>
@@ -9155,7 +9816,7 @@
         <v>106</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E220" s="0" t="n">
         <v>6</v>
@@ -9175,10 +9836,10 @@
         <v>109</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F221" s="0" t="n">
         <v>6</v>
@@ -9195,10 +9856,10 @@
         <v>74</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F222" s="0" t="n">
         <v>6</v>
@@ -9215,7 +9876,7 @@
         <v>22</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E223" s="0" t="n">
         <v>5</v>
@@ -9235,7 +9896,7 @@
         <v>19</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E224" s="0" t="n">
         <v>3</v>
@@ -9255,10 +9916,10 @@
         <v>31</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F225" s="0" t="n">
         <v>12</v>
@@ -9275,10 +9936,10 @@
         <v>31</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F226" s="0" t="n">
         <v>5</v>
@@ -9295,10 +9956,10 @@
         <v>32</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F227" s="0" t="n">
         <v>8</v>
@@ -9315,10 +9976,10 @@
         <v>25</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F228" s="0" t="n">
         <v>8</v>
@@ -9335,7 +9996,7 @@
         <v>55</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E229" s="0" t="n">
         <v>3</v>
@@ -9355,10 +10016,10 @@
         <v>55</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9372,7 +10033,7 @@
         <v>68</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E231" s="0" t="n">
         <v>4</v>
@@ -9392,7 +10053,7 @@
         <v>13</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E232" s="0" t="n">
         <v>1</v>
@@ -9412,7 +10073,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E233" s="0" t="n">
         <v>2</v>
@@ -9432,7 +10093,7 @@
         <v>7</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E234" s="0" t="n">
         <v>2</v>
@@ -9452,7 +10113,7 @@
         <v>5</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E235" s="0" t="n">
         <v>2</v>
@@ -9472,10 +10133,10 @@
         <v>54</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F236" s="0" t="n">
         <v>17</v>
@@ -9492,10 +10153,10 @@
         <v>66</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F237" s="0" t="n">
         <v>19</v>
@@ -9512,10 +10173,10 @@
         <v>24</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F238" s="0" t="n">
         <v>19</v>
@@ -9532,7 +10193,7 @@
         <v>24</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E239" s="0" t="n">
         <v>1</v>
@@ -9552,10 +10213,10 @@
         <v>25</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F240" s="0" t="n">
         <v>8</v>
@@ -9572,10 +10233,10 @@
         <v>35</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F241" s="0" t="n">
         <v>12</v>
@@ -9592,7 +10253,7 @@
         <v>48</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E242" s="0" t="n">
         <v>5</v>
@@ -9612,7 +10273,7 @@
         <v>57</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E243" s="0" t="n">
         <v>10</v>
@@ -9632,7 +10293,7 @@
         <v>71</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E244" s="0" t="n">
         <v>3</v>
@@ -9652,7 +10313,7 @@
         <v>24</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="F245" s="0" t="n">
         <v>28</v>
@@ -9669,10 +10330,10 @@
         <v>41</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F246" s="0" t="n">
         <v>8</v>
@@ -9689,7 +10350,7 @@
         <v>52</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E247" s="0" t="n">
         <v>6</v>
@@ -9709,7 +10370,7 @@
         <v>44</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E248" s="0" t="n">
         <v>4</v>
@@ -9729,7 +10390,7 @@
         <v>58</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E249" s="0" t="n">
         <v>3</v>
@@ -9749,10 +10410,10 @@
         <v>83</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F250" s="0" t="n">
         <v>10</v>
@@ -9769,7 +10430,7 @@
         <v>79</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E251" s="0" t="n">
         <v>2</v>
@@ -9789,7 +10450,7 @@
         <v>70</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E252" s="0" t="n">
         <v>2</v>
@@ -9809,7 +10470,7 @@
         <v>68</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E253" s="0" t="n">
         <v>6</v>
@@ -9829,7 +10490,7 @@
         <v>68</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E254" s="0" t="n">
         <v>10</v>
@@ -9849,10 +10510,10 @@
         <v>57</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F255" s="0" t="n">
         <v>12</v>
@@ -9869,7 +10530,7 @@
         <v>52</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E256" s="0" t="n">
         <v>10</v>
@@ -9889,10 +10550,10 @@
         <v>49</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F257" s="0" t="n">
         <v>10</v>
@@ -9909,7 +10570,7 @@
         <v>22</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E258" s="0" t="n">
         <v>6</v>
@@ -9929,7 +10590,7 @@
         <v>25</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E259" s="0" t="n">
         <v>9</v>
@@ -9949,10 +10610,10 @@
         <v>12</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F260" s="0" t="n">
         <v>8</v>
@@ -9969,7 +10630,7 @@
         <v>8</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9983,7 +10644,7 @@
         <v>91</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E262" s="0" t="n">
         <v>0</v>
@@ -10003,7 +10664,7 @@
         <v>97</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E263" s="0" t="n">
         <v>2</v>
@@ -10023,10 +10684,10 @@
         <v>55</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F264" s="0" t="n">
         <v>10</v>
@@ -10043,16 +10704,16 @@
         <v>55</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F265" s="0" t="n">
         <v>4</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10066,10 +10727,10 @@
         <v>87</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F266" s="0" t="n">
         <v>9</v>
@@ -10086,7 +10747,7 @@
         <v>53</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E267" s="0" t="n">
         <v>6</v>
@@ -10106,7 +10767,7 @@
         <v>51</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E268" s="0" t="n">
         <v>5</v>
@@ -10126,13 +10787,13 @@
         <v>70</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="F269" s="0" t="n">
         <v>24</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10146,7 +10807,7 @@
         <v>73</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E270" s="0" t="n">
         <v>8</v>
@@ -10166,10 +10827,10 @@
         <v>75</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F271" s="0" t="n">
         <v>10</v>
@@ -10186,7 +10847,7 @@
         <v>62</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E272" s="0" t="n">
         <v>4</v>
@@ -10206,7 +10867,7 @@
         <v>57</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E273" s="0" t="n">
         <v>6</v>
@@ -10226,10 +10887,10 @@
         <v>23</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F274" s="0" t="n">
         <v>14</v>
@@ -10246,10 +10907,10 @@
         <v>18</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F275" s="0" t="n">
         <v>10</v>
@@ -10266,10 +10927,10 @@
         <v>83</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F276" s="0" t="n">
         <v>10</v>
@@ -10286,7 +10947,7 @@
         <v>103</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E277" s="0" t="n">
         <v>1</v>
@@ -10306,7 +10967,7 @@
         <v>92</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E278" s="0" t="n">
         <v>4</v>
@@ -10326,10 +10987,10 @@
         <v>120</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F279" s="0" t="n">
         <v>10</v>
@@ -10346,7 +11007,7 @@
         <v>120</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E280" s="0" t="n">
         <v>8</v>
@@ -10366,7 +11027,7 @@
         <v>121</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E281" s="0" t="n">
         <v>7</v>
@@ -10386,7 +11047,7 @@
         <v>62</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="E282" s="0" t="n">
         <v>2</v>
@@ -10406,7 +11067,7 @@
         <v>57</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E283" s="0" t="n">
         <v>4</v>
@@ -10426,7 +11087,7 @@
         <v>49</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E284" s="0" t="n">
         <v>5</v>
@@ -10446,7 +11107,7 @@
         <v>42</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E285" s="0" t="n">
         <v>6</v>
@@ -10466,7 +11127,7 @@
         <v>31</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E286" s="0" t="n">
         <v>8</v>
@@ -10486,7 +11147,7 @@
         <v>31</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E287" s="0" t="n">
         <v>4</v>
@@ -10506,7 +11167,7 @@
         <v>31</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E288" s="0" t="n">
         <v>2</v>
@@ -10526,10 +11187,10 @@
         <v>71</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F289" s="0" t="n">
         <v>14</v>
@@ -10546,10 +11207,10 @@
         <v>60</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F290" s="0" t="n">
         <v>40</v>
@@ -10566,10 +11227,10 @@
         <v>62</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F291" s="0" t="n">
         <v>18</v>
@@ -10586,7 +11247,7 @@
         <v>60</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E292" s="0" t="n">
         <v>3</v>
@@ -10606,7 +11267,7 @@
         <v>74</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E293" s="0" t="n">
         <v>3</v>
@@ -10626,10 +11287,10 @@
         <v>108</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F294" s="0" t="n">
         <v>14</v>
@@ -10646,10 +11307,10 @@
         <v>68</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F295" s="0" t="n">
         <v>8</v>
@@ -10666,7 +11327,7 @@
         <v>73</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E296" s="0" t="n">
         <v>4</v>
@@ -10686,10 +11347,10 @@
         <v>63</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F297" s="0" t="n">
         <v>6</v>
@@ -10706,10 +11367,10 @@
         <v>10</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F298" s="0" t="n">
         <v>8</v>
@@ -10726,7 +11387,7 @@
         <v>70</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E299" s="0" t="n">
         <v>4</v>
@@ -10746,10 +11407,10 @@
         <v>45</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F300" s="0" t="n">
         <v>14</v>
@@ -10766,7 +11427,7 @@
         <v>99</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E301" s="0" t="n">
         <v>2</v>
@@ -10786,10 +11447,10 @@
         <v>47</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F302" s="0" t="n">
         <v>9</v>
@@ -10806,7 +11467,7 @@
         <v>64</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E303" s="0" t="n">
         <v>4</v>
@@ -10826,7 +11487,7 @@
         <v>6</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E304" s="0" t="n">
         <v>2</v>
@@ -10846,10 +11507,10 @@
         <v>13</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F305" s="0" t="n">
         <v>14</v>
@@ -10866,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E306" s="0" t="n">
         <v>2</v>
@@ -10886,10 +11547,10 @@
         <v>20</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F307" s="0" t="n">
         <v>8</v>
@@ -10906,7 +11567,7 @@
         <v>37</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E308" s="0" t="n">
         <v>1</v>
@@ -10926,7 +11587,7 @@
         <v>37</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E309" s="0" t="n">
         <v>3</v>
@@ -10946,10 +11607,10 @@
         <v>51</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F310" s="0" t="n">
         <v>18</v>
@@ -10966,10 +11627,10 @@
         <v>62</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F311" s="0" t="n">
         <v>14</v>
@@ -10986,10 +11647,10 @@
         <v>32</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F312" s="0" t="n">
         <v>6</v>
@@ -11018,7 +11679,7 @@
         <v>61</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E314" s="0" t="n">
         <v>5</v>
@@ -11038,7 +11699,7 @@
         <v>55</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E315" s="0" t="n">
         <v>2</v>
@@ -11058,7 +11719,7 @@
         <v>58</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E316" s="0" t="n">
         <v>3</v>
@@ -11078,10 +11739,10 @@
         <v>42</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F317" s="0" t="n">
         <v>9</v>
@@ -11098,10 +11759,10 @@
         <v>42</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F318" s="0" t="n">
         <v>9</v>
@@ -11118,10 +11779,10 @@
         <v>56</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F319" s="0" t="n">
         <v>6</v>
@@ -11138,7 +11799,7 @@
         <v>73</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E320" s="0" t="n">
         <v>10</v>
@@ -11158,7 +11819,7 @@
         <v>75</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E321" s="0" t="n">
         <v>3</v>
@@ -11178,7 +11839,7 @@
         <v>42</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E322" s="0" t="n">
         <v>4</v>
@@ -11198,7 +11859,7 @@
         <v>44</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E323" s="0" t="n">
         <v>2</v>
@@ -11218,7 +11879,7 @@
         <v>64</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E324" s="0" t="n">
         <v>2</v>
@@ -11238,7 +11899,7 @@
         <v>25</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E325" s="0" t="n">
         <v>5</v>
@@ -11258,7 +11919,7 @@
         <v>39</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E326" s="0" t="n">
         <v>10</v>
@@ -11278,7 +11939,7 @@
         <v>61</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E327" s="0" t="n">
         <v>10</v>
@@ -11298,7 +11959,7 @@
         <v>58</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E328" s="0" t="n">
         <v>5</v>
@@ -11318,10 +11979,10 @@
         <v>48</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F329" s="0" t="n">
         <v>6</v>
@@ -11338,7 +11999,7 @@
         <v>52</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E330" s="0" t="n">
         <v>4</v>
@@ -11358,10 +12019,10 @@
         <v>45</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F331" s="0" t="n">
         <v>6</v>
@@ -11378,7 +12039,7 @@
         <v>36</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E332" s="0" t="n">
         <v>8</v>
@@ -11398,10 +12059,10 @@
         <v>36</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F333" s="0" t="n">
         <v>4</v>
@@ -11418,10 +12079,10 @@
         <v>31</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F334" s="0" t="n">
         <v>3</v>
@@ -11438,10 +12099,10 @@
         <v>39</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F335" s="0" t="n">
         <v>3</v>
@@ -11458,7 +12119,7 @@
         <v>49</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E336" s="0" t="n">
         <v>2</v>
@@ -11478,7 +12139,7 @@
         <v>56</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E337" s="0" t="n">
         <v>1</v>
@@ -11498,7 +12159,7 @@
         <v>54</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E338" s="0" t="n">
         <v>2</v>
@@ -11518,10 +12179,10 @@
         <v>124</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E339" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F339" s="0" t="n">
         <v>3</v>
@@ -11538,10 +12199,10 @@
         <v>75</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F340" s="0" t="n">
         <v>10</v>
@@ -11558,7 +12219,7 @@
         <v>71</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E341" s="0" t="n">
         <v>5</v>
@@ -11578,10 +12239,10 @@
         <v>71</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F342" s="0" t="n">
         <v>7</v>
@@ -11598,7 +12259,7 @@
         <v>63</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E343" s="0" t="n">
         <v>1</v>
@@ -11618,10 +12279,10 @@
         <v>63</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F344" s="0" t="n">
         <v>2</v>
@@ -11638,10 +12299,10 @@
         <v>60</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F345" s="0" t="n">
         <v>8</v>
@@ -11658,7 +12319,7 @@
         <v>51</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E346" s="0" t="n">
         <v>2</v>
@@ -11678,7 +12339,7 @@
         <v>85</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E347" s="0" t="n">
         <v>3</v>
@@ -11698,7 +12359,7 @@
         <v>82</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E348" s="0" t="n">
         <v>2</v>
@@ -11718,7 +12379,7 @@
         <v>86</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E349" s="0" t="n">
         <v>8</v>
@@ -11738,7 +12399,7 @@
         <v>78</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E350" s="0" t="n">
         <v>8</v>
@@ -11758,7 +12419,7 @@
         <v>59</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E351" s="0" t="n">
         <v>1</v>
@@ -11778,7 +12439,7 @@
         <v>18</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E352" s="0" t="n">
         <v>8</v>
@@ -11798,7 +12459,7 @@
         <v>18</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E353" s="0" t="n">
         <v>5</v>
@@ -11818,10 +12479,10 @@
         <v>59</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F354" s="0" t="n">
         <v>14</v>
@@ -11838,10 +12499,10 @@
         <v>16</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F355" s="0" t="n">
         <v>12</v>
@@ -11858,7 +12519,7 @@
         <v>70</v>
       </c>
       <c r="D356" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E356" s="0" t="n">
         <v>2</v>
@@ -11878,10 +12539,10 @@
         <v>61</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F357" s="0" t="n">
         <v>9</v>
@@ -11898,10 +12559,10 @@
         <v>62</v>
       </c>
       <c r="D358" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F358" s="0" t="n">
         <v>6</v>
@@ -11918,10 +12579,10 @@
         <v>69</v>
       </c>
       <c r="D359" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E359" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F359" s="0" t="n">
         <v>8</v>
@@ -11938,10 +12599,10 @@
         <v>52</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F360" s="0" t="n">
         <v>8</v>
@@ -11958,7 +12619,7 @@
         <v>31</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E361" s="0" t="n">
         <v>3</v>
@@ -11978,7 +12639,7 @@
         <v>29</v>
       </c>
       <c r="D362" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E362" s="0" t="n">
         <v>1</v>
@@ -11998,10 +12659,10 @@
         <v>52.5</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F363" s="0" t="n">
         <v>13</v>
@@ -12018,7 +12679,7 @@
         <v>9</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E364" s="0" t="n">
         <v>2</v>
@@ -12038,10 +12699,10 @@
         <v>93</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F365" s="0" t="n">
         <v>5</v>
@@ -12058,16 +12719,16 @@
         <v>70</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F366" s="0" t="n">
         <v>14</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12081,7 +12742,7 @@
         <v>73</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E367" s="0" t="n">
         <v>8</v>
@@ -12101,10 +12762,10 @@
         <v>70</v>
       </c>
       <c r="D368" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F368" s="0" t="n">
         <v>14</v>
@@ -12121,10 +12782,10 @@
         <v>58</v>
       </c>
       <c r="D369" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E369" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F369" s="0" t="n">
         <v>20</v>
@@ -12141,10 +12802,10 @@
         <v>56</v>
       </c>
       <c r="D370" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F370" s="0" t="n">
         <v>9</v>
@@ -12161,10 +12822,10 @@
         <v>22</v>
       </c>
       <c r="D371" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E371" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F371" s="0" t="n">
         <v>15</v>
@@ -12181,7 +12842,7 @@
         <v>75</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E372" s="0" t="n">
         <v>2</v>
@@ -12201,7 +12862,7 @@
         <v>81</v>
       </c>
       <c r="D373" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E373" s="0" t="n">
         <v>2</v>
@@ -12221,10 +12882,10 @@
         <v>56</v>
       </c>
       <c r="D374" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F374" s="0" t="n">
         <v>22</v>
@@ -12241,10 +12902,10 @@
         <v>56</v>
       </c>
       <c r="D375" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E375" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F375" s="0" t="n">
         <v>14</v>
@@ -12261,7 +12922,7 @@
         <v>21</v>
       </c>
       <c r="D376" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E376" s="0" t="n">
         <v>8</v>
@@ -12281,7 +12942,7 @@
         <v>42</v>
       </c>
       <c r="D377" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E377" s="0" t="n">
         <v>5</v>
@@ -12301,10 +12962,10 @@
         <v>44</v>
       </c>
       <c r="D378" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F378" s="0" t="n">
         <v>8</v>
@@ -12321,7 +12982,7 @@
         <v>52</v>
       </c>
       <c r="D379" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E379" s="0" t="n">
         <v>2</v>
@@ -12341,10 +13002,10 @@
         <v>25</v>
       </c>
       <c r="D380" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F380" s="0" t="n">
         <v>12</v>
@@ -12361,10 +13022,10 @@
         <v>25</v>
       </c>
       <c r="D381" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F381" s="0" t="n">
         <v>10</v>
@@ -12381,7 +13042,7 @@
         <v>19</v>
       </c>
       <c r="D382" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E382" s="0" t="n">
         <v>1</v>
@@ -12401,10 +13062,10 @@
         <v>30</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F383" s="0" t="n">
         <v>6</v>
@@ -12421,10 +13082,10 @@
         <v>35</v>
       </c>
       <c r="D384" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E384" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F384" s="0" t="n">
         <v>8</v>
@@ -12441,10 +13102,10 @@
         <v>75</v>
       </c>
       <c r="D385" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F385" s="0" t="n">
         <v>6</v>
@@ -12461,10 +13122,10 @@
         <v>88</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F386" s="0" t="n">
         <v>8</v>
@@ -12481,16 +13142,16 @@
         <v>88</v>
       </c>
       <c r="D387" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F387" s="0" t="n">
         <v>6</v>
       </c>
       <c r="G387" s="0" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12504,7 +13165,7 @@
         <v>98</v>
       </c>
       <c r="D388" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E388" s="0" t="n">
         <v>6</v>
@@ -12524,7 +13185,7 @@
         <v>39</v>
       </c>
       <c r="D389" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E389" s="0" t="n">
         <v>3</v>
@@ -12544,7 +13205,7 @@
         <v>55</v>
       </c>
       <c r="D390" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E390" s="0" t="n">
         <v>9</v>
@@ -12564,7 +13225,7 @@
         <v>32</v>
       </c>
       <c r="D391" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E391" s="0" t="n">
         <v>3</v>
@@ -12584,7 +13245,7 @@
         <v>35</v>
       </c>
       <c r="D392" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E392" s="0" t="n">
         <v>6</v>
@@ -12604,10 +13265,10 @@
         <v>20</v>
       </c>
       <c r="D393" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F393" s="0" t="n">
         <v>10</v>
@@ -12624,10 +13285,10 @@
         <v>32</v>
       </c>
       <c r="D394" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F394" s="0" t="n">
         <v>10</v>
@@ -12644,7 +13305,7 @@
         <v>42</v>
       </c>
       <c r="D395" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="F395" s="0" t="n">
         <v>10</v>
@@ -12661,10 +13322,10 @@
         <v>63</v>
       </c>
       <c r="D396" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F396" s="0" t="n">
         <v>8</v>
@@ -12681,10 +13342,10 @@
         <v>69</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F397" s="0" t="n">
         <v>15</v>
@@ -12701,16 +13362,16 @@
         <v>18</v>
       </c>
       <c r="D398" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F398" s="0" t="n">
         <v>11</v>
       </c>
       <c r="G398" s="0" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12724,10 +13385,10 @@
         <v>32</v>
       </c>
       <c r="D399" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E399" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F399" s="0" t="n">
         <v>28</v>
@@ -12744,10 +13405,10 @@
         <v>45</v>
       </c>
       <c r="D400" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F400" s="0" t="n">
         <v>28</v>
@@ -12764,10 +13425,10 @@
         <v>40</v>
       </c>
       <c r="D401" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F401" s="0" t="n">
         <v>28</v>
@@ -12784,7 +13445,7 @@
         <v>68</v>
       </c>
       <c r="D402" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E402" s="0" t="n">
         <v>5</v>
@@ -12804,7 +13465,7 @@
         <v>68</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E403" s="0" t="n">
         <v>5</v>
@@ -12824,7 +13485,7 @@
         <v>57</v>
       </c>
       <c r="D404" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E404" s="0" t="n">
         <v>3</v>
@@ -12844,7 +13505,7 @@
         <v>60</v>
       </c>
       <c r="D405" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E405" s="0" t="n">
         <v>5</v>
@@ -12864,7 +13525,7 @@
         <v>14</v>
       </c>
       <c r="D406" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E406" s="0" t="n">
         <v>3</v>
@@ -12884,10 +13545,10 @@
         <v>63</v>
       </c>
       <c r="D407" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E407" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F407" s="0" t="n">
         <v>8</v>
@@ -12904,7 +13565,7 @@
         <v>81</v>
       </c>
       <c r="D408" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E408" s="0" t="n">
         <v>3</v>
@@ -12913,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="G408" s="0" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12927,16 +13588,16 @@
         <v>82</v>
       </c>
       <c r="D409" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F409" s="0" t="n">
         <v>3</v>
       </c>
       <c r="G409" s="0" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12950,16 +13611,16 @@
         <v>102</v>
       </c>
       <c r="D410" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E410" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F410" s="0" t="n">
         <v>4</v>
       </c>
       <c r="G410" s="0" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12973,16 +13634,16 @@
         <v>99</v>
       </c>
       <c r="D411" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F411" s="0" t="n">
         <v>48</v>
       </c>
       <c r="G411" s="0" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12996,10 +13657,10 @@
         <v>94</v>
       </c>
       <c r="D412" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F412" s="0" t="n">
         <v>4</v>
@@ -13016,10 +13677,10 @@
         <v>94</v>
       </c>
       <c r="D413" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F413" s="0" t="n">
         <v>4</v>
@@ -13036,10 +13697,10 @@
         <v>98</v>
       </c>
       <c r="D414" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E414" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F414" s="0" t="n">
         <v>3</v>
@@ -13056,7 +13717,7 @@
         <v>49</v>
       </c>
       <c r="D415" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E415" s="0" t="n">
         <v>5</v>
@@ -13076,7 +13737,7 @@
         <v>56</v>
       </c>
       <c r="D416" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E416" s="0" t="n">
         <v>5</v>
@@ -13096,10 +13757,10 @@
         <v>71</v>
       </c>
       <c r="D417" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E417" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F417" s="0" t="n">
         <v>5</v>
@@ -13116,7 +13777,7 @@
         <v>50</v>
       </c>
       <c r="D418" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E418" s="0" t="n">
         <v>4</v>
@@ -13136,7 +13797,7 @@
         <v>43</v>
       </c>
       <c r="D419" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E419" s="0" t="n">
         <v>5</v>
@@ -13156,10 +13817,10 @@
         <v>74</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F420" s="0" t="n">
         <v>48</v>
@@ -13176,10 +13837,10 @@
         <v>73</v>
       </c>
       <c r="D421" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E421" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F421" s="0" t="n">
         <v>10</v>
@@ -13196,10 +13857,10 @@
         <v>52</v>
       </c>
       <c r="D422" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E422" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F422" s="0" t="n">
         <v>6</v>
@@ -13216,10 +13877,10 @@
         <v>78</v>
       </c>
       <c r="D423" s="0" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="E423" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F423" s="0" t="n">
         <v>6</v>
@@ -13236,7 +13897,7 @@
         <v>80</v>
       </c>
       <c r="D424" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E424" s="0" t="n">
         <v>3</v>
@@ -13256,7 +13917,7 @@
         <v>91</v>
       </c>
       <c r="D425" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E425" s="0" t="n">
         <v>7</v>
@@ -13276,10 +13937,10 @@
         <v>85</v>
       </c>
       <c r="D426" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F426" s="0" t="n">
         <v>30</v>
@@ -13296,10 +13957,10 @@
         <v>91</v>
       </c>
       <c r="D427" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E427" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F427" s="0" t="n">
         <v>12</v>
@@ -13316,10 +13977,10 @@
         <v>57</v>
       </c>
       <c r="D428" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F428" s="0" t="n">
         <v>48</v>
@@ -13336,7 +13997,7 @@
         <v>63</v>
       </c>
       <c r="D429" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E429" s="0" t="n">
         <v>4</v>
@@ -13356,7 +14017,7 @@
         <v>74</v>
       </c>
       <c r="D430" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E430" s="0" t="n">
         <v>2</v>
@@ -13376,10 +14037,10 @@
         <v>43</v>
       </c>
       <c r="D431" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F431" s="0" t="n">
         <v>8</v>
@@ -13396,10 +14057,10 @@
         <v>81</v>
       </c>
       <c r="D432" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F432" s="0" t="n">
         <v>6</v>
@@ -13416,10 +14077,10 @@
         <v>85</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F433" s="0" t="n">
         <v>6</v>
@@ -13436,10 +14097,10 @@
         <v>95</v>
       </c>
       <c r="D434" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F434" s="0" t="n">
         <v>12</v>
@@ -13456,7 +14117,7 @@
         <v>44</v>
       </c>
       <c r="D435" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E435" s="0" t="n">
         <v>5</v>
@@ -13476,10 +14137,10 @@
         <v>46</v>
       </c>
       <c r="D436" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F436" s="0" t="n">
         <v>6</v>
@@ -13496,7 +14157,7 @@
         <v>59</v>
       </c>
       <c r="D437" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E437" s="0" t="n">
         <v>5</v>
@@ -13516,10 +14177,10 @@
         <v>59</v>
       </c>
       <c r="D438" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F438" s="0" t="n">
         <v>3</v>
@@ -13536,10 +14197,10 @@
         <v>57</v>
       </c>
       <c r="D439" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E439" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F439" s="0" t="n">
         <v>3</v>
@@ -13556,10 +14217,10 @@
         <v>60</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F440" s="0" t="n">
         <v>3</v>
@@ -13576,7 +14237,7 @@
         <v>57</v>
       </c>
       <c r="D441" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E441" s="0" t="n">
         <v>2</v>
@@ -13596,7 +14257,7 @@
         <v>78</v>
       </c>
       <c r="D442" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E442" s="0" t="n">
         <v>3</v>
@@ -13616,10 +14277,10 @@
         <v>90</v>
       </c>
       <c r="D443" s="0" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F443" s="0" t="n">
         <v>10</v>
@@ -13636,7 +14297,7 @@
         <v>76</v>
       </c>
       <c r="D444" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E444" s="0" t="n">
         <v>4</v>
@@ -13656,10 +14317,10 @@
         <v>12</v>
       </c>
       <c r="D445" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E445" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F445" s="0" t="n">
         <v>5</v>
@@ -13676,10 +14337,10 @@
         <v>8</v>
       </c>
       <c r="D446" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E446" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F446" s="0" t="n">
         <v>3</v>
@@ -13696,7 +14357,7 @@
         <v>52</v>
       </c>
       <c r="D447" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E447" s="0" t="n">
         <v>6</v>
@@ -13716,10 +14377,10 @@
         <v>5</v>
       </c>
       <c r="D448" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F448" s="0" t="n">
         <v>4</v>
@@ -13736,10 +14397,10 @@
         <v>7</v>
       </c>
       <c r="D449" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F449" s="0" t="n">
         <v>5</v>
@@ -13756,10 +14417,10 @@
         <v>5</v>
       </c>
       <c r="D450" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F450" s="0" t="n">
         <v>4</v>
@@ -13776,10 +14437,10 @@
         <v>5</v>
       </c>
       <c r="D451" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E451" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13793,10 +14454,10 @@
         <v>19</v>
       </c>
       <c r="D452" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F452" s="0" t="n">
         <v>6</v>
@@ -13813,10 +14474,10 @@
         <v>17</v>
       </c>
       <c r="D453" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E453" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F453" s="0" t="n">
         <v>6</v>
@@ -13833,7 +14494,7 @@
         <v>35</v>
       </c>
       <c r="D454" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E454" s="0" t="n">
         <v>4</v>
@@ -13853,10 +14514,10 @@
         <v>28</v>
       </c>
       <c r="D455" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F455" s="0" t="n">
         <v>6</v>
@@ -13873,10 +14534,10 @@
         <v>25</v>
       </c>
       <c r="D456" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F456" s="0" t="n">
         <v>10</v>
@@ -13893,7 +14554,7 @@
         <v>75</v>
       </c>
       <c r="D457" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E457" s="0" t="n">
         <v>1</v>
@@ -13913,10 +14574,10 @@
         <v>72</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F458" s="0" t="n">
         <v>14</v>
@@ -13933,7 +14594,7 @@
         <v>54</v>
       </c>
       <c r="D459" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E459" s="0" t="n">
         <v>2</v>
@@ -13953,7 +14614,7 @@
         <v>30</v>
       </c>
       <c r="D460" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E460" s="0" t="n">
         <v>3</v>
@@ -13973,10 +14634,10 @@
         <v>35</v>
       </c>
       <c r="D461" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F461" s="0" t="n">
         <v>4</v>
@@ -13993,7 +14654,7 @@
         <v>23</v>
       </c>
       <c r="D462" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E462" s="0" t="n">
         <v>3</v>
@@ -14013,10 +14674,10 @@
         <v>70</v>
       </c>
       <c r="D463" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E463" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F463" s="0" t="n">
         <v>14</v>
@@ -14033,10 +14694,10 @@
         <v>24</v>
       </c>
       <c r="D464" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F464" s="0" t="n">
         <v>6</v>
@@ -14053,7 +14714,7 @@
         <v>67</v>
       </c>
       <c r="D465" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E465" s="0" t="n">
         <v>4</v>
@@ -14073,10 +14734,10 @@
         <v>85</v>
       </c>
       <c r="D466" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F466" s="0" t="n">
         <v>18</v>
@@ -14093,10 +14754,10 @@
         <v>85</v>
       </c>
       <c r="D467" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E467" s="0" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F467" s="0" t="n">
         <v>14</v>
@@ -14113,7 +14774,7 @@
         <v>53</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E468" s="0" t="n">
         <v>1</v>
@@ -14133,10 +14794,10 @@
         <v>82</v>
       </c>
       <c r="D469" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F469" s="0" t="n">
         <v>6</v>
@@ -14153,10 +14814,10 @@
         <v>88</v>
       </c>
       <c r="D470" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F470" s="0" t="n">
         <v>10</v>
@@ -14173,7 +14834,7 @@
         <v>81</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E471" s="0" t="n">
         <v>6</v>
@@ -14193,10 +14854,10 @@
         <v>76</v>
       </c>
       <c r="D472" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E472" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F472" s="0" t="n">
         <v>4</v>
@@ -14213,7 +14874,7 @@
         <v>83</v>
       </c>
       <c r="D473" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E473" s="0" t="n">
         <v>7</v>
@@ -14233,10 +14894,10 @@
         <v>84</v>
       </c>
       <c r="D474" s="0" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F474" s="0" t="n">
         <v>52</v>
@@ -14253,10 +14914,10 @@
         <v>75</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F475" s="0" t="n">
         <v>12</v>
@@ -14273,10 +14934,10 @@
         <v>83</v>
       </c>
       <c r="D476" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E476" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F476" s="0" t="n">
         <v>6</v>
@@ -14293,7 +14954,7 @@
         <v>87</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E477" s="0" t="n">
         <v>6</v>
@@ -14313,10 +14974,10 @@
         <v>78</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F478" s="0" t="n">
         <v>12</v>
@@ -14333,7 +14994,7 @@
         <v>93</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E479" s="0" t="n">
         <v>1</v>
@@ -14353,7 +15014,7 @@
         <v>44</v>
       </c>
       <c r="D480" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E480" s="0" t="n">
         <v>7</v>
@@ -14373,10 +15034,10 @@
         <v>51</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F481" s="0" t="n">
         <v>6</v>
@@ -14393,10 +15054,10 @@
         <v>55</v>
       </c>
       <c r="D482" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F482" s="0" t="n">
         <v>9</v>
@@ -14413,10 +15074,10 @@
         <v>55</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F483" s="0" t="n">
         <v>6</v>
@@ -14433,10 +15094,10 @@
         <v>54</v>
       </c>
       <c r="D484" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E484" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F484" s="0" t="n">
         <v>4</v>
@@ -14453,10 +15114,10 @@
         <v>61</v>
       </c>
       <c r="D485" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F485" s="0" t="n">
         <v>12</v>
@@ -14473,7 +15134,7 @@
         <v>71</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E486" s="0" t="n">
         <v>2</v>
@@ -14493,7 +15154,7 @@
         <v>75</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E487" s="0" t="n">
         <v>7</v>
@@ -14513,10 +15174,10 @@
         <v>69</v>
       </c>
       <c r="D488" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E488" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F488" s="0" t="n">
         <v>6</v>
@@ -14533,10 +15194,10 @@
         <v>69</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F489" s="0" t="n">
         <v>8</v>
@@ -14553,7 +15214,7 @@
         <v>70</v>
       </c>
       <c r="D490" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E490" s="0" t="n">
         <v>6</v>
@@ -14573,10 +15234,10 @@
         <v>66</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F491" s="0" t="n">
         <v>7</v>
@@ -14593,10 +15254,10 @@
         <v>36</v>
       </c>
       <c r="D492" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F492" s="0" t="n">
         <v>6</v>
@@ -14613,7 +15274,7 @@
         <v>40</v>
       </c>
       <c r="D493" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E493" s="0" t="n">
         <v>3</v>
@@ -14633,10 +15294,10 @@
         <v>95</v>
       </c>
       <c r="D494" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F494" s="0" t="n">
         <v>12</v>
@@ -14653,7 +15314,7 @@
         <v>45</v>
       </c>
       <c r="D495" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E495" s="0" t="n">
         <v>7</v>
@@ -14673,7 +15334,7 @@
         <v>54</v>
       </c>
       <c r="D496" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E496" s="0" t="n">
         <v>4</v>
@@ -14693,10 +15354,10 @@
         <v>59</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F497" s="0" t="n">
         <v>5</v>
@@ -14713,10 +15374,10 @@
         <v>86</v>
       </c>
       <c r="D498" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F498" s="0" t="n">
         <v>8</v>
@@ -14733,7 +15394,7 @@
         <v>68</v>
       </c>
       <c r="D499" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E499" s="0" t="n">
         <v>2</v>
@@ -14753,7 +15414,7 @@
         <v>40</v>
       </c>
       <c r="D500" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E500" s="0" t="n">
         <v>1</v>
@@ -14773,10 +15434,10 @@
         <v>43</v>
       </c>
       <c r="D501" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E501" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F501" s="0" t="n">
         <v>6</v>
@@ -14793,7 +15454,7 @@
         <v>57</v>
       </c>
       <c r="D502" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E502" s="0" t="n">
         <v>5</v>
@@ -14813,7 +15474,7 @@
         <v>57</v>
       </c>
       <c r="D503" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E503" s="0" t="n">
         <v>5</v>
@@ -14833,7 +15494,7 @@
         <v>75</v>
       </c>
       <c r="D504" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E504" s="0" t="n">
         <v>5</v>
@@ -14853,10 +15514,10 @@
         <v>69</v>
       </c>
       <c r="D505" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E505" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F505" s="0" t="n">
         <v>4</v>
@@ -14873,10 +15534,10 @@
         <v>69</v>
       </c>
       <c r="D506" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E506" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F506" s="0" t="n">
         <v>4</v>
@@ -14893,10 +15554,10 @@
         <v>54</v>
       </c>
       <c r="D507" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E507" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F507" s="0" t="n">
         <v>6</v>
@@ -14913,10 +15574,10 @@
         <v>63</v>
       </c>
       <c r="D508" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E508" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F508" s="0" t="n">
         <v>14</v>
@@ -14933,7 +15594,7 @@
         <v>32</v>
       </c>
       <c r="D509" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E509" s="0" t="n">
         <v>6</v>
@@ -14953,10 +15614,10 @@
         <v>74</v>
       </c>
       <c r="D510" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E510" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F510" s="0" t="n">
         <v>6</v>
@@ -14973,10 +15634,10 @@
         <v>78</v>
       </c>
       <c r="D511" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E511" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F511" s="0" t="n">
         <v>8</v>
@@ -14993,10 +15654,10 @@
         <v>80</v>
       </c>
       <c r="D512" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E512" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F512" s="0" t="n">
         <v>6</v>
@@ -15013,7 +15674,7 @@
         <v>78</v>
       </c>
       <c r="D513" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E513" s="0" t="n">
         <v>5</v>
@@ -15033,7 +15694,7 @@
         <v>52</v>
       </c>
       <c r="D514" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E514" s="0" t="n">
         <v>10</v>
@@ -15053,7 +15714,7 @@
         <v>18</v>
       </c>
       <c r="D515" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E515" s="0" t="n">
         <v>5</v>
@@ -15073,7 +15734,7 @@
         <v>25</v>
       </c>
       <c r="D516" s="0" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E516" s="0" t="n">
         <v>2</v>
@@ -15093,10 +15754,10 @@
         <v>13</v>
       </c>
       <c r="D517" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E517" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F517" s="0" t="n">
         <v>9</v>
@@ -15113,10 +15774,10 @@
         <v>14</v>
       </c>
       <c r="D518" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E518" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F518" s="0" t="n">
         <v>9</v>
@@ -15133,7 +15794,7 @@
         <v>33</v>
       </c>
       <c r="D519" s="0" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E519" s="0" t="n">
         <v>2</v>
@@ -15153,10 +15814,10 @@
         <v>63</v>
       </c>
       <c r="D520" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E520" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F520" s="0" t="n">
         <v>2</v>
@@ -15173,7 +15834,7 @@
         <v>77</v>
       </c>
       <c r="D521" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E521" s="0" t="n">
         <v>10</v>
@@ -15193,7 +15854,7 @@
         <v>72</v>
       </c>
       <c r="D522" s="0" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E522" s="0" t="n">
         <v>8</v>
@@ -15213,10 +15874,10 @@
         <v>70</v>
       </c>
       <c r="D523" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E523" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F523" s="0" t="n">
         <v>3</v>
@@ -15233,10 +15894,10 @@
         <v>70</v>
       </c>
       <c r="D524" s="0" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E524" s="0" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F524" s="0" t="n">
         <v>4</v>
@@ -15253,10 +15914,1967 @@
         <v>45</v>
       </c>
       <c r="D525" s="0" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="G525" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A526" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B526" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="C526" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D526" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E526" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F526" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A527" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B527" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C527" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D527" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E527" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F527" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A528" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B528" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C528" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D528" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E528" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F528" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A529" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B529" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="C529" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D529" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E529" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F529" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A530" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B530" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="C530" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D530" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E530" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F530" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A531" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B531" s="0" t="n">
+        <v>161</v>
+      </c>
+      <c r="C531" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D531" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E531" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F531" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B532" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="C532" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="D532" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E532" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F532" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B533" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="C533" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="D533" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E533" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F533" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A534" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B534" s="0" t="n">
+        <v>131</v>
+      </c>
+      <c r="C534" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D534" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E534" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F534" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A535" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B535" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="C535" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D535" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E535" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F535" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A536" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B536" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C536" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D536" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E536" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F536" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A537" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B537" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="C537" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="D537" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E537" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F537" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A538" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B538" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="C538" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D538" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E538" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F538" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A539" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B539" s="0" t="n">
+        <v>378</v>
+      </c>
+      <c r="C539" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D539" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E539" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F539" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A540" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B540" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="C540" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D540" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E540" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F540" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A541" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B541" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="C541" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D541" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E541" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F541" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A542" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B542" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="C542" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D542" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E542" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F542" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A543" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B543" s="0" t="n">
+        <v>326</v>
+      </c>
+      <c r="C543" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D543" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E543" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F543" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A544" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B544" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C544" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D544" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E544" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F544" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A545" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B545" s="0" t="n">
+        <v>309</v>
+      </c>
+      <c r="C545" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="D545" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E545" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F545" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A546" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B546" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C546" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D546" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E546" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F546" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A547" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B547" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="C547" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="D547" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E547" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F547" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A548" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B548" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C548" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D548" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E548" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F548" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A549" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B549" s="0" t="n">
+        <v>292</v>
+      </c>
+      <c r="C549" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D549" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E549" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F549" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A550" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B550" s="0" t="n">
+        <v>292</v>
+      </c>
+      <c r="C550" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D550" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E550" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F550" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A551" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B551" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="C551" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D551" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E551" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F551" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A552" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B552" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C552" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D552" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E552" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F552" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A553" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B553" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C553" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D553" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E553" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F553" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A554" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B554" s="0" t="n">
+        <v>309</v>
+      </c>
+      <c r="C554" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D554" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="E554" s="0" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A555" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B555" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="C555" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D555" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E555" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F555" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A556" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B556" s="0" t="n">
+        <v>315</v>
+      </c>
+      <c r="C556" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D556" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E556" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F556" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A557" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B557" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C557" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D557" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E557" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F557" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A558" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B558" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C558" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D558" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E558" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F558" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A559" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B559" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C559" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D559" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E559" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F559" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A560" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B560" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="C560" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D560" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E560" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F560" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A561" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B561" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="C561" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D561" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E561" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F561" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A562" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B562" s="0" t="n">
+        <v>171</v>
+      </c>
+      <c r="C562" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D562" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E562" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F562" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A563" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B563" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="C563" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D563" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E563" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F563" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A564" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B564" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="C564" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D564" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E564" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F564" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A565" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B565" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C565" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D565" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E565" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F565" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A566" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B566" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C566" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="D566" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E566" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F566" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A567" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B567" s="0" t="n">
+        <v>310</v>
+      </c>
+      <c r="C567" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D567" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E567" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F567" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A568" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B568" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="C568" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D568" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E568" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F568" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A569" s="1" t="s">
         <v>261</v>
+      </c>
+      <c r="B569" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="C569" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D569" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E569" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F569" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A570" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B570" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="C570" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D570" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E570" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F570" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A571" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B571" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="C571" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D571" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E571" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F571" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A572" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B572" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C572" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D572" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E572" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F572" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A573" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B573" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C573" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D573" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E573" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F573" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A574" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B574" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C574" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D574" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E574" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F574" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A575" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B575" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C575" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="D575" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E575" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F575" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A576" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B576" s="0" t="n">
+        <v>334</v>
+      </c>
+      <c r="C576" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="D576" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="E576" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F576" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A577" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B577" s="0" t="n">
+        <v>331</v>
+      </c>
+      <c r="C577" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D577" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E577" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F577" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A578" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B578" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C578" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D578" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E578" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F578" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A579" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B579" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C579" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D579" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E579" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F579" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A580" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B580" s="0" t="n">
+        <v>322</v>
+      </c>
+      <c r="C580" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D580" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E580" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F580" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A581" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B581" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C581" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D581" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E581" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F581" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A582" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B582" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C582" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D582" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E582" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F582" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A583" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B583" s="0" t="n">
+        <v>319</v>
+      </c>
+      <c r="C583" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D583" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E583" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F583" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A584" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B584" s="0" t="n">
+        <v>323</v>
+      </c>
+      <c r="C584" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D584" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E584" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F584" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A585" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B585" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="C585" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D585" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E585" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F585" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A586" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B586" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C586" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D586" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E586" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F586" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A587" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B587" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C587" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="D587" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E587" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F587" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A588" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B588" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="C588" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="D588" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E588" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F588" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A589" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B589" s="0" t="n">
+        <v>310</v>
+      </c>
+      <c r="C589" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D589" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E589" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F589" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A590" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B590" s="0" t="n">
+        <v>306</v>
+      </c>
+      <c r="C590" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="D590" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E590" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F590" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A591" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B591" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C591" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D591" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E591" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F591" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A592" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B592" s="0" t="n">
+        <v>294</v>
+      </c>
+      <c r="C592" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D592" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E592" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F592" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A593" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B593" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="C593" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D593" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E593" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F593" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A594" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B594" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="C594" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="D594" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E594" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F594" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A595" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B595" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C595" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D595" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E595" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F595" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A596" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B596" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C596" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D596" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E596" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F596" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A597" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B597" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="C597" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D597" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E597" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F597" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A598" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B598" s="0" t="n">
+        <v>282</v>
+      </c>
+      <c r="C598" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D598" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E598" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F598" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A599" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B599" s="0" t="n">
+        <v>291</v>
+      </c>
+      <c r="C599" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="D599" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E599" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F599" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A600" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B600" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="C600" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="D600" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E600" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F600" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A601" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B601" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="C601" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="D601" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E601" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F601" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A602" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B602" s="0" t="n">
+        <v>282</v>
+      </c>
+      <c r="C602" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D602" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E602" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F602" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A603" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B603" s="0" t="n">
+        <v>282</v>
+      </c>
+      <c r="C603" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D603" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="E603" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F603" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A604" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B604" s="0" t="n">
+        <v>292</v>
+      </c>
+      <c r="C604" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D604" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E604" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F604" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A605" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B605" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C605" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D605" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E605" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F605" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A606" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B606" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C606" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D606" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E606" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F606" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A607" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B607" s="0" t="n">
+        <v>292</v>
+      </c>
+      <c r="C607" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D607" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="E607" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F607" s="0" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A608" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B608" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C608" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D608" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E608" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F608" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A609" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B609" s="0" t="n">
+        <v>220</v>
+      </c>
+      <c r="C609" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="D609" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E609" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F609" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A610" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B610" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="C610" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D610" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E610" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F610" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A611" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B611" s="0" t="n">
+        <v>229</v>
+      </c>
+      <c r="C611" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D611" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E611" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F611" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A612" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B612" s="0" t="n">
+        <v>230</v>
+      </c>
+      <c r="C612" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D612" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E612" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F612" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A613" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B613" s="0" t="n">
+        <v>308</v>
+      </c>
+      <c r="C613" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D613" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E613" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F613" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A614" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B614" s="0" t="n">
+        <v>183</v>
+      </c>
+      <c r="C614" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D614" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E614" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F614" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A615" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B615" s="0" t="n">
+        <v>328</v>
+      </c>
+      <c r="C615" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D615" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="E615" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F615" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A616" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B616" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C616" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D616" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E616" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F616" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A617" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B617" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C617" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D617" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E617" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F617" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A618" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B618" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="C618" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D618" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="E618" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F618" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A619" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B619" s="0" t="n">
+        <v>139</v>
+      </c>
+      <c r="C619" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D619" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E619" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F619" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A620" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B620" s="0" t="n">
+        <v>148</v>
+      </c>
+      <c r="C620" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D620" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E620" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F620" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A621" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B621" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C621" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D621" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E621" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F621" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A622" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B622" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C622" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D622" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E622" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F622" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A623" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B623" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C623" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D623" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="E623" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F623" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="337">
   <si>
     <t xml:space="preserve">Station_1</t>
   </si>
@@ -871,6 +871,173 @@
     <t xml:space="preserve">B60. 14+2 circled</t>
   </si>
   <si>
+    <t xml:space="preserve">12+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">B63. 10+2 circled. Touching SW corner, hole in stand 100-150’ in diameter 290</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">° from compass</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">26+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B41. 2 large alder trees east of 26+6. No tree entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B40. No tree entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B39. No tree entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B38. No tree entries. Big alder 45’ west of center. Alder pocket in north corner. 1 alder at station. 8 alder at 20+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">B37. 18+6 circled. 3 alders at 20+6. 2 Alders ~ 5’ 81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">° of center</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">16+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B36. 18+6 circled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B35. 14+4 circled. Large question mark over block info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B61. Note Block 81 has two compass locations relative to 12+4 and 12+6. Noted as “skip for now”. 12+4 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B61. Note Block 81 has two compass locations relative to 12+4 and 12+6. Noted as “skip for now”. 12+6 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12+6.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B62. 12+6.18 circled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28+8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26+8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B42. No tree entries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24+8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B43. No tree entries. Alder pocket on line from 26+8 to 24+8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azimuth</t>
   </si>
   <si>
@@ -950,6 +1117,9 @@
   </si>
   <si>
     <t xml:space="preserve">red alder, not diseased tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1234,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.2"/>
@@ -5430,6 +5600,842 @@
         <v>263</v>
       </c>
     </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="K62" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="L62" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y62" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z62" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA62" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="AB62" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC62" s="0" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="K63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="N63" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="O63" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q63" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="S63" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="T63" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V63" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="W63" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y63" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC63" s="0" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>359</v>
+      </c>
+      <c r="M64" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="N64" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="O64" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P64" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q64" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="S64" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="T64" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="U64" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V64" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="W64" s="0" t="n">
+        <v>181</v>
+      </c>
+      <c r="Y64" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="AC64" s="0" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M65" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="N65" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="O65" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q65" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="S65" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="T65" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V65" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="W65" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="Y65" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC65" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I66" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="K66" s="0" t="n">
+        <v>354</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="N66" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="O66" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P66" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q66" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="S66" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="T66" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="U66" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V66" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="W66" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="Y66" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AC66" s="0" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="E67" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I67" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="K67" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="L67" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="M67" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="N67" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="O67" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="P67" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="S67" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="T67" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="U67" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V67" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="W67" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="X67" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y67" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z67" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA67" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB67" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="AC67" s="0" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="I68" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="K68" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="L68" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="M68" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="N68" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="O68" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="P68" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q68" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="R68" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="S68" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="T68" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="U68" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V68" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="W68" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="X68" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y68" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z68" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA68" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="AB68" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC68" s="0" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="E69" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I69" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="K69" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="L69" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="M69" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="N69" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="O69" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="P69" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q69" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="R69" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="S69" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="T69" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="U69" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V69" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="W69" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="X69" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y69" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Z69" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA69" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="AB69" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC69" s="0" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y70" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC70" s="0" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>288</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="H71" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I71" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K71" s="0" t="n">
+        <v>183</v>
+      </c>
+      <c r="Y71" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AC71" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I72" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="K72" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="M72" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="N72" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="O72" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P72" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q72" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="R72" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y72" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Z72" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA72" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB72" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC72" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="I73" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="K73" s="0" t="n">
+        <v>174</v>
+      </c>
+      <c r="M73" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="N73" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="O73" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q73" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="S73" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="T73" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="U73" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V73" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="W73" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y73" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="AC73" s="0" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="H74" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I74" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="K74" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="M74" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="N74" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="O74" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="P74" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q74" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="R74" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y74" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC74" s="0" t="s">
+        <v>308</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5446,7 +6452,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G623"/>
+  <dimension ref="A1:G687"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.52"/>
@@ -5457,22 +6463,22 @@
         <v>24</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5486,10 +6492,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>6</v>
@@ -5506,7 +6512,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>5</v>
@@ -5526,7 +6532,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>10</v>
@@ -5546,7 +6552,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>4</v>
@@ -5566,10 +6572,10 @@
         <v>30</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>11</v>
@@ -5586,10 +6592,10 @@
         <v>63</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
@@ -5606,7 +6612,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>4</v>
@@ -5626,7 +6632,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>10</v>
@@ -5646,10 +6652,10 @@
         <v>14</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>25</v>
@@ -5666,7 +6672,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>6</v>
@@ -5686,10 +6692,10 @@
         <v>52</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>24</v>
@@ -5706,7 +6712,7 @@
         <v>49</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>5</v>
@@ -5726,7 +6732,7 @@
         <v>80</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>8</v>
@@ -5746,7 +6752,7 @@
         <v>64</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>5</v>
@@ -5766,7 +6772,7 @@
         <v>61</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>6</v>
@@ -5786,10 +6792,10 @@
         <v>85</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>10</v>
@@ -5806,7 +6812,7 @@
         <v>46</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>8</v>
@@ -5826,10 +6832,10 @@
         <v>48</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>6</v>
@@ -5846,10 +6852,10 @@
         <v>54</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>14</v>
@@ -5866,7 +6872,7 @@
         <v>64</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>10</v>
@@ -5886,7 +6892,7 @@
         <v>52</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>5</v>
@@ -5906,7 +6912,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>10</v>
@@ -5926,10 +6932,10 @@
         <v>46</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>14</v>
@@ -5946,7 +6952,7 @@
         <v>82</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>3</v>
@@ -5966,10 +6972,10 @@
         <v>76</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>8</v>
@@ -5986,7 +6992,7 @@
         <v>47</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>4</v>
@@ -6006,7 +7012,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>3</v>
@@ -6026,10 +7032,10 @@
         <v>61</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>6</v>
@@ -6046,10 +7052,10 @@
         <v>53</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>8</v>
@@ -6066,7 +7072,7 @@
         <v>52</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>10</v>
@@ -6086,10 +7092,10 @@
         <v>77</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>6</v>
@@ -6106,10 +7112,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>6</v>
@@ -6126,10 +7132,10 @@
         <v>80</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F34" s="0" t="n">
         <v>7</v>
@@ -6146,7 +7152,7 @@
         <v>86</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>8</v>
@@ -6166,10 +7172,10 @@
         <v>89</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>8</v>
@@ -6186,10 +7192,10 @@
         <v>141</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F37" s="0" t="n">
         <v>6</v>
@@ -6206,7 +7212,7 @@
         <v>67</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>5</v>
@@ -6226,10 +7232,10 @@
         <v>53</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F39" s="0" t="n">
         <v>9</v>
@@ -6246,10 +7252,10 @@
         <v>44</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F40" s="0" t="n">
         <v>14</v>
@@ -6266,7 +7272,7 @@
         <v>38</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>4</v>
@@ -6286,10 +7292,10 @@
         <v>45</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F42" s="0" t="n">
         <v>10</v>
@@ -6306,10 +7312,10 @@
         <v>45</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F43" s="0" t="n">
         <v>12</v>
@@ -6326,10 +7332,10 @@
         <v>24</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F44" s="0" t="n">
         <v>10</v>
@@ -6346,7 +7352,7 @@
         <v>33</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E45" s="0" t="n">
         <v>3</v>
@@ -6366,10 +7372,10 @@
         <v>55</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F46" s="0" t="n">
         <v>7</v>
@@ -6386,7 +7392,7 @@
         <v>43</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>0</v>
@@ -6395,7 +7401,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6409,10 +7415,10 @@
         <v>86</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F48" s="0" t="n">
         <v>14</v>
@@ -6429,10 +7435,10 @@
         <v>39</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F49" s="0" t="n">
         <v>18</v>
@@ -6449,7 +7455,7 @@
         <v>41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>4</v>
@@ -6469,7 +7475,7 @@
         <v>107</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>10</v>
@@ -6489,7 +7495,7 @@
         <v>107</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>1</v>
@@ -6509,10 +7515,10 @@
         <v>127</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F53" s="0" t="n">
         <v>6</v>
@@ -6529,7 +7535,7 @@
         <v>117</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>6</v>
@@ -6549,10 +7555,10 @@
         <v>129</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>12</v>
@@ -6569,10 +7575,10 @@
         <v>67</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F56" s="0" t="n">
         <v>9</v>
@@ -6589,10 +7595,10 @@
         <v>64</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F57" s="0" t="n">
         <v>10</v>
@@ -6609,10 +7615,10 @@
         <v>48</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F58" s="0" t="n">
         <v>6</v>
@@ -6629,10 +7635,10 @@
         <v>61</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F59" s="0" t="n">
         <v>8</v>
@@ -6649,7 +7655,7 @@
         <v>50</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6663,7 +7669,7 @@
         <v>68</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E61" s="0" t="n">
         <v>1</v>
@@ -6683,7 +7689,7 @@
         <v>58</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E62" s="0" t="n">
         <v>2</v>
@@ -6703,10 +7709,10 @@
         <v>21</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F63" s="0" t="n">
         <v>10</v>
@@ -6723,7 +7729,7 @@
         <v>18</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E64" s="0" t="n">
         <v>10</v>
@@ -6743,7 +7749,7 @@
         <v>31</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E65" s="0" t="n">
         <v>8</v>
@@ -6763,10 +7769,10 @@
         <v>69</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F66" s="0" t="n">
         <v>4</v>
@@ -6783,10 +7789,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F67" s="0" t="n">
         <v>4</v>
@@ -6803,10 +7809,10 @@
         <v>63</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F68" s="0" t="n">
         <v>4</v>
@@ -6823,10 +7829,10 @@
         <v>80</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F69" s="0" t="n">
         <v>5</v>
@@ -6843,10 +7849,10 @@
         <v>80</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F70" s="0" t="n">
         <v>5</v>
@@ -6863,10 +7869,10 @@
         <v>59</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F71" s="0" t="n">
         <v>8</v>
@@ -6883,10 +7889,10 @@
         <v>38</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F72" s="0" t="n">
         <v>6</v>
@@ -6903,10 +7909,10 @@
         <v>37</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F73" s="0" t="n">
         <v>10</v>
@@ -6923,7 +7929,7 @@
         <v>27</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E74" s="0" t="n">
         <v>2</v>
@@ -6943,7 +7949,7 @@
         <v>60</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E75" s="0" t="n">
         <v>7</v>
@@ -6963,7 +7969,7 @@
         <v>64</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E76" s="0" t="n">
         <v>7</v>
@@ -6983,10 +7989,10 @@
         <v>36</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F77" s="0" t="n">
         <v>4</v>
@@ -7003,10 +8009,10 @@
         <v>22</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F78" s="0" t="n">
         <v>6</v>
@@ -7023,7 +8029,7 @@
         <v>45</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E79" s="0" t="n">
         <v>6</v>
@@ -7043,7 +8049,7 @@
         <v>24</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E80" s="0" t="n">
         <v>3</v>
@@ -7063,10 +8069,10 @@
         <v>49</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F81" s="0" t="n">
         <v>6</v>
@@ -7083,7 +8089,7 @@
         <v>50</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7097,10 +8103,10 @@
         <v>42</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F83" s="0" t="n">
         <v>5</v>
@@ -7117,7 +8123,7 @@
         <v>48</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E84" s="0" t="n">
         <v>10</v>
@@ -7137,10 +8143,10 @@
         <v>44</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F85" s="0" t="n">
         <v>6</v>
@@ -7157,7 +8163,7 @@
         <v>61</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E86" s="0" t="n">
         <v>2</v>
@@ -7177,7 +8183,7 @@
         <v>30</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E87" s="0" t="n">
         <v>2</v>
@@ -7197,7 +8203,7 @@
         <v>58</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E88" s="0" t="n">
         <v>2</v>
@@ -7217,7 +8223,7 @@
         <v>31</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E89" s="0" t="n">
         <v>3</v>
@@ -7237,10 +8243,10 @@
         <v>69</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F90" s="0" t="n">
         <v>6</v>
@@ -7257,10 +8263,10 @@
         <v>24</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F91" s="0" t="n">
         <v>20</v>
@@ -7277,10 +8283,10 @@
         <v>34</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F92" s="0" t="n">
         <v>15</v>
@@ -7297,7 +8303,7 @@
         <v>53</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E93" s="0" t="n">
         <v>5</v>
@@ -7317,7 +8323,7 @@
         <v>85</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E94" s="0" t="n">
         <v>2</v>
@@ -7337,7 +8343,7 @@
         <v>89</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E95" s="0" t="n">
         <v>5</v>
@@ -7357,7 +8363,7 @@
         <v>16</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E96" s="0" t="n">
         <v>0</v>
@@ -7377,10 +8383,10 @@
         <v>74</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F97" s="0" t="n">
         <v>8</v>
@@ -7397,7 +8403,7 @@
         <v>53</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E98" s="0" t="n">
         <v>6</v>
@@ -7417,7 +8423,7 @@
         <v>65</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E99" s="0" t="n">
         <v>0</v>
@@ -7437,10 +8443,10 @@
         <v>55</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F100" s="0" t="n">
         <v>8</v>
@@ -7457,7 +8463,7 @@
         <v>63</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E101" s="0" t="n">
         <v>4</v>
@@ -7477,10 +8483,10 @@
         <v>83</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F102" s="0" t="n">
         <v>8</v>
@@ -7497,7 +8503,7 @@
         <v>46</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E103" s="0" t="n">
         <v>7</v>
@@ -7517,7 +8523,7 @@
         <v>40</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E104" s="0" t="n">
         <v>5</v>
@@ -7537,7 +8543,7 @@
         <v>64</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E105" s="0" t="n">
         <v>8</v>
@@ -7557,10 +8563,10 @@
         <v>61</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F106" s="0" t="n">
         <v>15</v>
@@ -7577,7 +8583,7 @@
         <v>59</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E107" s="0" t="n">
         <v>10</v>
@@ -7597,7 +8603,7 @@
         <v>30</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E108" s="0" t="n">
         <v>4</v>
@@ -7617,7 +8623,7 @@
         <v>64</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E109" s="0" t="n">
         <v>2</v>
@@ -7637,10 +8643,10 @@
         <v>85.5</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F110" s="0" t="n">
         <v>8</v>
@@ -7657,7 +8663,7 @@
         <v>65</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E111" s="0" t="n">
         <v>4</v>
@@ -7677,7 +8683,7 @@
         <v>66</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E112" s="0" t="n">
         <v>1</v>
@@ -7697,16 +8703,16 @@
         <v>77</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F113" s="0" t="n">
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7720,7 +8726,7 @@
         <v>66</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E114" s="0" t="n">
         <v>1</v>
@@ -7740,7 +8746,7 @@
         <v>70</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E115" s="0" t="n">
         <v>0</v>
@@ -7760,10 +8766,10 @@
         <v>6</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F116" s="0" t="n">
         <v>14</v>
@@ -7780,7 +8786,7 @@
         <v>75</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E117" s="0" t="n">
         <v>4</v>
@@ -7800,7 +8806,7 @@
         <v>66</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E118" s="0" t="n">
         <v>3</v>
@@ -7820,10 +8826,10 @@
         <v>11</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F119" s="0" t="n">
         <v>10</v>
@@ -7840,7 +8846,7 @@
         <v>54</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E120" s="0" t="n">
         <v>10</v>
@@ -7860,7 +8866,7 @@
         <v>54</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E121" s="0" t="n">
         <v>5</v>
@@ -7880,7 +8886,7 @@
         <v>54</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E122" s="0" t="n">
         <v>10</v>
@@ -7900,7 +8906,7 @@
         <v>77</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E123" s="0" t="n">
         <v>1</v>
@@ -7920,10 +8926,10 @@
         <v>68</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F124" s="0" t="n">
         <v>16</v>
@@ -7940,7 +8946,7 @@
         <v>26</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="E125" s="0" t="n">
         <v>1</v>
@@ -7960,10 +8966,10 @@
         <v>69</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F126" s="0" t="n">
         <v>10</v>
@@ -7980,10 +8986,10 @@
         <v>39</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F127" s="0" t="n">
         <v>4</v>
@@ -8000,7 +9006,7 @@
         <v>23</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E128" s="0" t="n">
         <v>1</v>
@@ -8020,7 +9026,7 @@
         <v>45</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E129" s="0" t="n">
         <v>7</v>
@@ -8040,7 +9046,7 @@
         <v>30</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E130" s="0" t="n">
         <v>7</v>
@@ -8060,7 +9066,7 @@
         <v>45</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E131" s="0" t="n">
         <v>9</v>
@@ -8080,7 +9086,7 @@
         <v>31</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E132" s="0" t="n">
         <v>4</v>
@@ -8100,10 +9106,10 @@
         <v>40</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F133" s="0" t="n">
         <v>4</v>
@@ -8120,10 +9126,10 @@
         <v>67</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F134" s="0" t="n">
         <v>10</v>
@@ -8140,10 +9146,10 @@
         <v>69</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F135" s="0" t="n">
         <v>13</v>
@@ -8160,7 +9166,7 @@
         <v>43</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E136" s="0" t="n">
         <v>1</v>
@@ -8180,7 +9186,7 @@
         <v>39</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E137" s="0" t="n">
         <v>1</v>
@@ -8200,7 +9206,7 @@
         <v>69</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E138" s="0" t="n">
         <v>1</v>
@@ -8220,10 +9226,10 @@
         <v>72</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F139" s="0" t="n">
         <v>16</v>
@@ -8240,10 +9246,10 @@
         <v>69</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F140" s="0" t="n">
         <v>6</v>
@@ -8260,10 +9266,10 @@
         <v>67</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F141" s="0" t="n">
         <v>13</v>
@@ -8280,10 +9286,10 @@
         <v>52</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F142" s="0" t="n">
         <v>6</v>
@@ -8300,7 +9306,7 @@
         <v>67</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E143" s="0" t="n">
         <v>7</v>
@@ -8320,10 +9326,10 @@
         <v>47</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F144" s="0" t="n">
         <v>4</v>
@@ -8340,7 +9346,7 @@
         <v>60</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E145" s="0" t="n">
         <v>4</v>
@@ -8360,7 +9366,7 @@
         <v>55</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E146" s="0" t="n">
         <v>1</v>
@@ -8380,10 +9386,10 @@
         <v>59</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F147" s="0" t="n">
         <v>12</v>
@@ -8400,10 +9406,10 @@
         <v>12</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F148" s="0" t="n">
         <v>8</v>
@@ -8420,10 +9426,10 @@
         <v>77</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F149" s="0" t="n">
         <v>8</v>
@@ -8440,10 +9446,10 @@
         <v>49</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F150" s="0" t="n">
         <v>10</v>
@@ -8460,10 +9466,10 @@
         <v>49</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F151" s="0" t="n">
         <v>9</v>
@@ -8480,10 +9486,10 @@
         <v>53</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F152" s="0" t="n">
         <v>15</v>
@@ -8500,7 +9506,7 @@
         <v>94</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E153" s="0" t="n">
         <v>3</v>
@@ -8520,10 +9526,10 @@
         <v>72</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F154" s="0" t="n">
         <v>10</v>
@@ -8540,10 +9546,10 @@
         <v>34</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F155" s="0" t="n">
         <v>8</v>
@@ -8560,7 +9566,7 @@
         <v>96</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E156" s="0" t="n">
         <v>2</v>
@@ -8580,10 +9586,10 @@
         <v>39</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F157" s="0" t="n">
         <v>10</v>
@@ -8600,7 +9606,7 @@
         <v>78</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E158" s="0" t="n">
         <v>6</v>
@@ -8620,7 +9626,7 @@
         <v>66</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="F159" s="0" t="n">
         <v>4</v>
@@ -8637,10 +9643,10 @@
         <v>66</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F160" s="0" t="n">
         <v>10</v>
@@ -8657,7 +9663,7 @@
         <v>40</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E161" s="0" t="n">
         <v>2</v>
@@ -8677,10 +9683,10 @@
         <v>56</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F162" s="0" t="n">
         <v>8</v>
@@ -8697,7 +9703,7 @@
         <v>60</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E163" s="0" t="n">
         <v>3</v>
@@ -8717,7 +9723,7 @@
         <v>39</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E164" s="0" t="n">
         <v>4</v>
@@ -8737,10 +9743,10 @@
         <v>30</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F165" s="0" t="n">
         <v>7</v>
@@ -8757,7 +9763,7 @@
         <v>84</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E166" s="0" t="n">
         <v>6</v>
@@ -8777,10 +9783,10 @@
         <v>43</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F167" s="0" t="n">
         <v>4</v>
@@ -8797,10 +9803,10 @@
         <v>38</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F168" s="0" t="n">
         <v>8</v>
@@ -8817,7 +9823,7 @@
         <v>24</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E169" s="0" t="n">
         <v>8</v>
@@ -8837,10 +9843,10 @@
         <v>21</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E170" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F170" s="0" t="n">
         <v>6</v>
@@ -8857,10 +9863,10 @@
         <v>68</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F171" s="0" t="n">
         <v>10</v>
@@ -8877,10 +9883,10 @@
         <v>79</v>
       </c>
       <c r="D172" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F172" s="0" t="n">
         <v>14</v>
@@ -8897,10 +9903,10 @@
         <v>79</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F173" s="0" t="n">
         <v>14</v>
@@ -8917,10 +9923,10 @@
         <v>48</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8934,7 +9940,7 @@
         <v>58</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E175" s="0" t="n">
         <v>5</v>
@@ -8954,7 +9960,7 @@
         <v>39</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E176" s="0" t="n">
         <v>2</v>
@@ -8974,7 +9980,7 @@
         <v>39</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E177" s="0" t="n">
         <v>6</v>
@@ -8994,10 +10000,10 @@
         <v>52</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F178" s="0" t="n">
         <v>10</v>
@@ -9014,10 +10020,10 @@
         <v>68</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F179" s="0" t="n">
         <v>10</v>
@@ -9034,7 +10040,7 @@
         <v>40</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E180" s="0" t="n">
         <v>7</v>
@@ -9054,7 +10060,7 @@
         <v>53</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E181" s="0" t="n">
         <v>2</v>
@@ -9074,10 +10080,10 @@
         <v>53</v>
       </c>
       <c r="D182" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F182" s="0" t="n">
         <v>4</v>
@@ -9094,10 +10100,10 @@
         <v>18</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F183" s="0" t="n">
         <v>9</v>
@@ -9114,7 +10120,7 @@
         <v>25</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E184" s="0" t="n">
         <v>5</v>
@@ -9134,7 +10140,7 @@
         <v>40</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E185" s="0" t="n">
         <v>6</v>
@@ -9154,7 +10160,7 @@
         <v>17</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E186" s="0" t="n">
         <v>8</v>
@@ -9174,10 +10180,10 @@
         <v>26</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F187" s="0" t="n">
         <v>6</v>
@@ -9194,10 +10200,10 @@
         <v>72</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F188" s="0" t="n">
         <v>8</v>
@@ -9214,7 +10220,7 @@
         <v>72</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E189" s="0" t="n">
         <v>2</v>
@@ -9234,7 +10240,7 @@
         <v>71</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E190" s="0" t="n">
         <v>3</v>
@@ -9254,7 +10260,7 @@
         <v>38</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E191" s="0" t="n">
         <v>10</v>
@@ -9274,10 +10280,10 @@
         <v>62</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9291,10 +10297,10 @@
         <v>69</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F193" s="0" t="n">
         <v>6</v>
@@ -9311,10 +10317,10 @@
         <v>67</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F194" s="0" t="n">
         <v>5</v>
@@ -9331,10 +10337,10 @@
         <v>64</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F195" s="0" t="n">
         <v>5</v>
@@ -9351,7 +10357,7 @@
         <v>67</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E196" s="0" t="n">
         <v>10</v>
@@ -9371,10 +10377,10 @@
         <v>62</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F197" s="0" t="n">
         <v>7</v>
@@ -9391,10 +10397,10 @@
         <v>56</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F198" s="0" t="n">
         <v>5</v>
@@ -9411,7 +10417,7 @@
         <v>46</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E199" s="0" t="n">
         <v>4</v>
@@ -9431,7 +10437,7 @@
         <v>27</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E200" s="0" t="n">
         <v>3</v>
@@ -9451,7 +10457,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E201" s="0" t="n">
         <v>5</v>
@@ -9468,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F202" s="0" t="n">
         <v>5</v>
@@ -9488,10 +10494,10 @@
         <v>13</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F203" s="0" t="n">
         <v>3</v>
@@ -9508,10 +10514,10 @@
         <v>69</v>
       </c>
       <c r="D204" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9525,7 +10531,7 @@
         <v>77</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E205" s="0" t="n">
         <v>8</v>
@@ -9542,10 +10548,10 @@
         <v>77</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F206" s="0" t="n">
         <v>8</v>
@@ -9562,10 +10568,10 @@
         <v>77</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,7 +10585,7 @@
         <v>61</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E208" s="0" t="n">
         <v>10</v>
@@ -9599,10 +10605,10 @@
         <v>31</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F209" s="0" t="n">
         <v>6</v>
@@ -9619,10 +10625,10 @@
         <v>71</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F210" s="0" t="n">
         <v>6</v>
@@ -9639,7 +10645,7 @@
         <v>39</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E211" s="0" t="n">
         <v>8</v>
@@ -9659,10 +10665,10 @@
         <v>74</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F212" s="0" t="n">
         <v>4</v>
@@ -9679,10 +10685,10 @@
         <v>25</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F213" s="0" t="n">
         <v>6</v>
@@ -9699,10 +10705,10 @@
         <v>79</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9716,7 +10722,7 @@
         <v>37</v>
       </c>
       <c r="D215" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E215" s="0" t="n">
         <v>5</v>
@@ -9736,7 +10742,7 @@
         <v>97</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E216" s="0" t="n">
         <v>2</v>
@@ -9756,10 +10762,10 @@
         <v>74</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F217" s="0" t="n">
         <v>17</v>
@@ -9776,10 +10782,10 @@
         <v>87</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F218" s="0" t="n">
         <v>10</v>
@@ -9796,10 +10802,10 @@
         <v>76</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F219" s="0" t="n">
         <v>20</v>
@@ -9816,7 +10822,7 @@
         <v>106</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E220" s="0" t="n">
         <v>6</v>
@@ -9836,10 +10842,10 @@
         <v>109</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F221" s="0" t="n">
         <v>6</v>
@@ -9856,10 +10862,10 @@
         <v>74</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F222" s="0" t="n">
         <v>6</v>
@@ -9876,7 +10882,7 @@
         <v>22</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E223" s="0" t="n">
         <v>5</v>
@@ -9896,7 +10902,7 @@
         <v>19</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E224" s="0" t="n">
         <v>3</v>
@@ -9916,10 +10922,10 @@
         <v>31</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F225" s="0" t="n">
         <v>12</v>
@@ -9936,10 +10942,10 @@
         <v>31</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F226" s="0" t="n">
         <v>5</v>
@@ -9956,10 +10962,10 @@
         <v>32</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F227" s="0" t="n">
         <v>8</v>
@@ -9976,10 +10982,10 @@
         <v>25</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F228" s="0" t="n">
         <v>8</v>
@@ -9996,7 +11002,7 @@
         <v>55</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E229" s="0" t="n">
         <v>3</v>
@@ -10016,10 +11022,10 @@
         <v>55</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10033,7 +11039,7 @@
         <v>68</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E231" s="0" t="n">
         <v>4</v>
@@ -10053,7 +11059,7 @@
         <v>13</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E232" s="0" t="n">
         <v>1</v>
@@ -10073,7 +11079,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E233" s="0" t="n">
         <v>2</v>
@@ -10093,7 +11099,7 @@
         <v>7</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E234" s="0" t="n">
         <v>2</v>
@@ -10113,7 +11119,7 @@
         <v>5</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E235" s="0" t="n">
         <v>2</v>
@@ -10133,10 +11139,10 @@
         <v>54</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F236" s="0" t="n">
         <v>17</v>
@@ -10153,10 +11159,10 @@
         <v>66</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F237" s="0" t="n">
         <v>19</v>
@@ -10173,10 +11179,10 @@
         <v>24</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F238" s="0" t="n">
         <v>19</v>
@@ -10193,7 +11199,7 @@
         <v>24</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E239" s="0" t="n">
         <v>1</v>
@@ -10213,10 +11219,10 @@
         <v>25</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F240" s="0" t="n">
         <v>8</v>
@@ -10233,10 +11239,10 @@
         <v>35</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F241" s="0" t="n">
         <v>12</v>
@@ -10253,7 +11259,7 @@
         <v>48</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E242" s="0" t="n">
         <v>5</v>
@@ -10273,7 +11279,7 @@
         <v>57</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E243" s="0" t="n">
         <v>10</v>
@@ -10293,7 +11299,7 @@
         <v>71</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E244" s="0" t="n">
         <v>3</v>
@@ -10313,7 +11319,7 @@
         <v>24</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="F245" s="0" t="n">
         <v>28</v>
@@ -10330,10 +11336,10 @@
         <v>41</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F246" s="0" t="n">
         <v>8</v>
@@ -10350,7 +11356,7 @@
         <v>52</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E247" s="0" t="n">
         <v>6</v>
@@ -10370,7 +11376,7 @@
         <v>44</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E248" s="0" t="n">
         <v>4</v>
@@ -10390,7 +11396,7 @@
         <v>58</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E249" s="0" t="n">
         <v>3</v>
@@ -10410,10 +11416,10 @@
         <v>83</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F250" s="0" t="n">
         <v>10</v>
@@ -10430,7 +11436,7 @@
         <v>79</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E251" s="0" t="n">
         <v>2</v>
@@ -10450,7 +11456,7 @@
         <v>70</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E252" s="0" t="n">
         <v>2</v>
@@ -10470,7 +11476,7 @@
         <v>68</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E253" s="0" t="n">
         <v>6</v>
@@ -10490,7 +11496,7 @@
         <v>68</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E254" s="0" t="n">
         <v>10</v>
@@ -10510,10 +11516,10 @@
         <v>57</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F255" s="0" t="n">
         <v>12</v>
@@ -10530,7 +11536,7 @@
         <v>52</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E256" s="0" t="n">
         <v>10</v>
@@ -10550,10 +11556,10 @@
         <v>49</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F257" s="0" t="n">
         <v>10</v>
@@ -10570,7 +11576,7 @@
         <v>22</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E258" s="0" t="n">
         <v>6</v>
@@ -10590,7 +11596,7 @@
         <v>25</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E259" s="0" t="n">
         <v>9</v>
@@ -10610,10 +11616,10 @@
         <v>12</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F260" s="0" t="n">
         <v>8</v>
@@ -10630,7 +11636,7 @@
         <v>8</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10644,7 +11650,7 @@
         <v>91</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E262" s="0" t="n">
         <v>0</v>
@@ -10664,7 +11670,7 @@
         <v>97</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E263" s="0" t="n">
         <v>2</v>
@@ -10684,10 +11690,10 @@
         <v>55</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F264" s="0" t="n">
         <v>10</v>
@@ -10704,16 +11710,16 @@
         <v>55</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F265" s="0" t="n">
         <v>4</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10727,10 +11733,10 @@
         <v>87</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F266" s="0" t="n">
         <v>9</v>
@@ -10747,7 +11753,7 @@
         <v>53</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E267" s="0" t="n">
         <v>6</v>
@@ -10767,7 +11773,7 @@
         <v>51</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E268" s="0" t="n">
         <v>5</v>
@@ -10787,13 +11793,13 @@
         <v>70</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="F269" s="0" t="n">
         <v>24</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10807,7 +11813,7 @@
         <v>73</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E270" s="0" t="n">
         <v>8</v>
@@ -10827,10 +11833,10 @@
         <v>75</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F271" s="0" t="n">
         <v>10</v>
@@ -10847,7 +11853,7 @@
         <v>62</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E272" s="0" t="n">
         <v>4</v>
@@ -10867,7 +11873,7 @@
         <v>57</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E273" s="0" t="n">
         <v>6</v>
@@ -10887,10 +11893,10 @@
         <v>23</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F274" s="0" t="n">
         <v>14</v>
@@ -10907,10 +11913,10 @@
         <v>18</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F275" s="0" t="n">
         <v>10</v>
@@ -10927,10 +11933,10 @@
         <v>83</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F276" s="0" t="n">
         <v>10</v>
@@ -10947,7 +11953,7 @@
         <v>103</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E277" s="0" t="n">
         <v>1</v>
@@ -10967,7 +11973,7 @@
         <v>92</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E278" s="0" t="n">
         <v>4</v>
@@ -10987,10 +11993,10 @@
         <v>120</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F279" s="0" t="n">
         <v>10</v>
@@ -11007,7 +12013,7 @@
         <v>120</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E280" s="0" t="n">
         <v>8</v>
@@ -11027,7 +12033,7 @@
         <v>121</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E281" s="0" t="n">
         <v>7</v>
@@ -11047,7 +12053,7 @@
         <v>62</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="E282" s="0" t="n">
         <v>2</v>
@@ -11067,7 +12073,7 @@
         <v>57</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E283" s="0" t="n">
         <v>4</v>
@@ -11087,7 +12093,7 @@
         <v>49</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E284" s="0" t="n">
         <v>5</v>
@@ -11107,7 +12113,7 @@
         <v>42</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E285" s="0" t="n">
         <v>6</v>
@@ -11127,7 +12133,7 @@
         <v>31</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E286" s="0" t="n">
         <v>8</v>
@@ -11147,7 +12153,7 @@
         <v>31</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E287" s="0" t="n">
         <v>4</v>
@@ -11167,7 +12173,7 @@
         <v>31</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E288" s="0" t="n">
         <v>2</v>
@@ -11187,10 +12193,10 @@
         <v>71</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F289" s="0" t="n">
         <v>14</v>
@@ -11207,10 +12213,10 @@
         <v>60</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F290" s="0" t="n">
         <v>40</v>
@@ -11227,10 +12233,10 @@
         <v>62</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F291" s="0" t="n">
         <v>18</v>
@@ -11247,7 +12253,7 @@
         <v>60</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E292" s="0" t="n">
         <v>3</v>
@@ -11267,7 +12273,7 @@
         <v>74</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E293" s="0" t="n">
         <v>3</v>
@@ -11287,10 +12293,10 @@
         <v>108</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F294" s="0" t="n">
         <v>14</v>
@@ -11307,10 +12313,10 @@
         <v>68</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F295" s="0" t="n">
         <v>8</v>
@@ -11327,7 +12333,7 @@
         <v>73</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E296" s="0" t="n">
         <v>4</v>
@@ -11347,10 +12353,10 @@
         <v>63</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F297" s="0" t="n">
         <v>6</v>
@@ -11367,10 +12373,10 @@
         <v>10</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F298" s="0" t="n">
         <v>8</v>
@@ -11387,7 +12393,7 @@
         <v>70</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E299" s="0" t="n">
         <v>4</v>
@@ -11407,10 +12413,10 @@
         <v>45</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F300" s="0" t="n">
         <v>14</v>
@@ -11427,7 +12433,7 @@
         <v>99</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E301" s="0" t="n">
         <v>2</v>
@@ -11447,10 +12453,10 @@
         <v>47</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F302" s="0" t="n">
         <v>9</v>
@@ -11467,7 +12473,7 @@
         <v>64</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E303" s="0" t="n">
         <v>4</v>
@@ -11487,7 +12493,7 @@
         <v>6</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E304" s="0" t="n">
         <v>2</v>
@@ -11507,10 +12513,10 @@
         <v>13</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F305" s="0" t="n">
         <v>14</v>
@@ -11527,7 +12533,7 @@
         <v>12</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E306" s="0" t="n">
         <v>2</v>
@@ -11547,10 +12553,10 @@
         <v>20</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F307" s="0" t="n">
         <v>8</v>
@@ -11567,7 +12573,7 @@
         <v>37</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E308" s="0" t="n">
         <v>1</v>
@@ -11587,7 +12593,7 @@
         <v>37</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E309" s="0" t="n">
         <v>3</v>
@@ -11607,10 +12613,10 @@
         <v>51</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F310" s="0" t="n">
         <v>18</v>
@@ -11627,10 +12633,10 @@
         <v>62</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F311" s="0" t="n">
         <v>14</v>
@@ -11647,10 +12653,10 @@
         <v>32</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F312" s="0" t="n">
         <v>6</v>
@@ -11679,7 +12685,7 @@
         <v>61</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E314" s="0" t="n">
         <v>5</v>
@@ -11699,7 +12705,7 @@
         <v>55</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E315" s="0" t="n">
         <v>2</v>
@@ -11719,7 +12725,7 @@
         <v>58</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E316" s="0" t="n">
         <v>3</v>
@@ -11739,10 +12745,10 @@
         <v>42</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F317" s="0" t="n">
         <v>9</v>
@@ -11759,10 +12765,10 @@
         <v>42</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F318" s="0" t="n">
         <v>9</v>
@@ -11779,10 +12785,10 @@
         <v>56</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F319" s="0" t="n">
         <v>6</v>
@@ -11799,7 +12805,7 @@
         <v>73</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E320" s="0" t="n">
         <v>10</v>
@@ -11819,7 +12825,7 @@
         <v>75</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E321" s="0" t="n">
         <v>3</v>
@@ -11839,7 +12845,7 @@
         <v>42</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E322" s="0" t="n">
         <v>4</v>
@@ -11859,7 +12865,7 @@
         <v>44</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E323" s="0" t="n">
         <v>2</v>
@@ -11879,7 +12885,7 @@
         <v>64</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E324" s="0" t="n">
         <v>2</v>
@@ -11899,7 +12905,7 @@
         <v>25</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E325" s="0" t="n">
         <v>5</v>
@@ -11919,7 +12925,7 @@
         <v>39</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E326" s="0" t="n">
         <v>10</v>
@@ -11939,7 +12945,7 @@
         <v>61</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E327" s="0" t="n">
         <v>10</v>
@@ -11959,7 +12965,7 @@
         <v>58</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E328" s="0" t="n">
         <v>5</v>
@@ -11979,10 +12985,10 @@
         <v>48</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F329" s="0" t="n">
         <v>6</v>
@@ -11999,7 +13005,7 @@
         <v>52</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E330" s="0" t="n">
         <v>4</v>
@@ -12019,10 +13025,10 @@
         <v>45</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F331" s="0" t="n">
         <v>6</v>
@@ -12039,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E332" s="0" t="n">
         <v>8</v>
@@ -12059,10 +13065,10 @@
         <v>36</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F333" s="0" t="n">
         <v>4</v>
@@ -12079,10 +13085,10 @@
         <v>31</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F334" s="0" t="n">
         <v>3</v>
@@ -12099,10 +13105,10 @@
         <v>39</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F335" s="0" t="n">
         <v>3</v>
@@ -12119,7 +13125,7 @@
         <v>49</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E336" s="0" t="n">
         <v>2</v>
@@ -12139,7 +13145,7 @@
         <v>56</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E337" s="0" t="n">
         <v>1</v>
@@ -12159,7 +13165,7 @@
         <v>54</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E338" s="0" t="n">
         <v>2</v>
@@ -12179,10 +13185,10 @@
         <v>124</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E339" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F339" s="0" t="n">
         <v>3</v>
@@ -12199,10 +13205,10 @@
         <v>75</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F340" s="0" t="n">
         <v>10</v>
@@ -12219,7 +13225,7 @@
         <v>71</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E341" s="0" t="n">
         <v>5</v>
@@ -12239,10 +13245,10 @@
         <v>71</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F342" s="0" t="n">
         <v>7</v>
@@ -12259,7 +13265,7 @@
         <v>63</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E343" s="0" t="n">
         <v>1</v>
@@ -12279,10 +13285,10 @@
         <v>63</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F344" s="0" t="n">
         <v>2</v>
@@ -12299,10 +13305,10 @@
         <v>60</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F345" s="0" t="n">
         <v>8</v>
@@ -12319,7 +13325,7 @@
         <v>51</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E346" s="0" t="n">
         <v>2</v>
@@ -12339,7 +13345,7 @@
         <v>85</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E347" s="0" t="n">
         <v>3</v>
@@ -12359,7 +13365,7 @@
         <v>82</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E348" s="0" t="n">
         <v>2</v>
@@ -12379,7 +13385,7 @@
         <v>86</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E349" s="0" t="n">
         <v>8</v>
@@ -12399,7 +13405,7 @@
         <v>78</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E350" s="0" t="n">
         <v>8</v>
@@ -12419,7 +13425,7 @@
         <v>59</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E351" s="0" t="n">
         <v>1</v>
@@ -12439,7 +13445,7 @@
         <v>18</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E352" s="0" t="n">
         <v>8</v>
@@ -12459,7 +13465,7 @@
         <v>18</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E353" s="0" t="n">
         <v>5</v>
@@ -12479,10 +13485,10 @@
         <v>59</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F354" s="0" t="n">
         <v>14</v>
@@ -12499,10 +13505,10 @@
         <v>16</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F355" s="0" t="n">
         <v>12</v>
@@ -12519,7 +13525,7 @@
         <v>70</v>
       </c>
       <c r="D356" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E356" s="0" t="n">
         <v>2</v>
@@ -12539,10 +13545,10 @@
         <v>61</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F357" s="0" t="n">
         <v>9</v>
@@ -12559,10 +13565,10 @@
         <v>62</v>
       </c>
       <c r="D358" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F358" s="0" t="n">
         <v>6</v>
@@ -12579,10 +13585,10 @@
         <v>69</v>
       </c>
       <c r="D359" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E359" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F359" s="0" t="n">
         <v>8</v>
@@ -12599,10 +13605,10 @@
         <v>52</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F360" s="0" t="n">
         <v>8</v>
@@ -12619,7 +13625,7 @@
         <v>31</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E361" s="0" t="n">
         <v>3</v>
@@ -12639,7 +13645,7 @@
         <v>29</v>
       </c>
       <c r="D362" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E362" s="0" t="n">
         <v>1</v>
@@ -12659,10 +13665,10 @@
         <v>52.5</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F363" s="0" t="n">
         <v>13</v>
@@ -12679,7 +13685,7 @@
         <v>9</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E364" s="0" t="n">
         <v>2</v>
@@ -12699,10 +13705,10 @@
         <v>93</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F365" s="0" t="n">
         <v>5</v>
@@ -12719,16 +13725,16 @@
         <v>70</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F366" s="0" t="n">
         <v>14</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12742,7 +13748,7 @@
         <v>73</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E367" s="0" t="n">
         <v>8</v>
@@ -12762,10 +13768,10 @@
         <v>70</v>
       </c>
       <c r="D368" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F368" s="0" t="n">
         <v>14</v>
@@ -12782,10 +13788,10 @@
         <v>58</v>
       </c>
       <c r="D369" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E369" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F369" s="0" t="n">
         <v>20</v>
@@ -12802,10 +13808,10 @@
         <v>56</v>
       </c>
       <c r="D370" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F370" s="0" t="n">
         <v>9</v>
@@ -12822,10 +13828,10 @@
         <v>22</v>
       </c>
       <c r="D371" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E371" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F371" s="0" t="n">
         <v>15</v>
@@ -12842,7 +13848,7 @@
         <v>75</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E372" s="0" t="n">
         <v>2</v>
@@ -12862,7 +13868,7 @@
         <v>81</v>
       </c>
       <c r="D373" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E373" s="0" t="n">
         <v>2</v>
@@ -12882,10 +13888,10 @@
         <v>56</v>
       </c>
       <c r="D374" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F374" s="0" t="n">
         <v>22</v>
@@ -12902,10 +13908,10 @@
         <v>56</v>
       </c>
       <c r="D375" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E375" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F375" s="0" t="n">
         <v>14</v>
@@ -12922,7 +13928,7 @@
         <v>21</v>
       </c>
       <c r="D376" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E376" s="0" t="n">
         <v>8</v>
@@ -12942,7 +13948,7 @@
         <v>42</v>
       </c>
       <c r="D377" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E377" s="0" t="n">
         <v>5</v>
@@ -12962,10 +13968,10 @@
         <v>44</v>
       </c>
       <c r="D378" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F378" s="0" t="n">
         <v>8</v>
@@ -12982,7 +13988,7 @@
         <v>52</v>
       </c>
       <c r="D379" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E379" s="0" t="n">
         <v>2</v>
@@ -13002,10 +14008,10 @@
         <v>25</v>
       </c>
       <c r="D380" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F380" s="0" t="n">
         <v>12</v>
@@ -13022,10 +14028,10 @@
         <v>25</v>
       </c>
       <c r="D381" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F381" s="0" t="n">
         <v>10</v>
@@ -13042,7 +14048,7 @@
         <v>19</v>
       </c>
       <c r="D382" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E382" s="0" t="n">
         <v>1</v>
@@ -13062,10 +14068,10 @@
         <v>30</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F383" s="0" t="n">
         <v>6</v>
@@ -13082,10 +14088,10 @@
         <v>35</v>
       </c>
       <c r="D384" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E384" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F384" s="0" t="n">
         <v>8</v>
@@ -13102,10 +14108,10 @@
         <v>75</v>
       </c>
       <c r="D385" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F385" s="0" t="n">
         <v>6</v>
@@ -13122,10 +14128,10 @@
         <v>88</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F386" s="0" t="n">
         <v>8</v>
@@ -13142,16 +14148,16 @@
         <v>88</v>
       </c>
       <c r="D387" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F387" s="0" t="n">
         <v>6</v>
       </c>
       <c r="G387" s="0" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13165,7 +14171,7 @@
         <v>98</v>
       </c>
       <c r="D388" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E388" s="0" t="n">
         <v>6</v>
@@ -13185,7 +14191,7 @@
         <v>39</v>
       </c>
       <c r="D389" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E389" s="0" t="n">
         <v>3</v>
@@ -13205,7 +14211,7 @@
         <v>55</v>
       </c>
       <c r="D390" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E390" s="0" t="n">
         <v>9</v>
@@ -13225,7 +14231,7 @@
         <v>32</v>
       </c>
       <c r="D391" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E391" s="0" t="n">
         <v>3</v>
@@ -13245,7 +14251,7 @@
         <v>35</v>
       </c>
       <c r="D392" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E392" s="0" t="n">
         <v>6</v>
@@ -13265,10 +14271,10 @@
         <v>20</v>
       </c>
       <c r="D393" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F393" s="0" t="n">
         <v>10</v>
@@ -13285,10 +14291,10 @@
         <v>32</v>
       </c>
       <c r="D394" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F394" s="0" t="n">
         <v>10</v>
@@ -13305,7 +14311,7 @@
         <v>42</v>
       </c>
       <c r="D395" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="F395" s="0" t="n">
         <v>10</v>
@@ -13322,10 +14328,10 @@
         <v>63</v>
       </c>
       <c r="D396" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F396" s="0" t="n">
         <v>8</v>
@@ -13342,10 +14348,10 @@
         <v>69</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F397" s="0" t="n">
         <v>15</v>
@@ -13362,16 +14368,16 @@
         <v>18</v>
       </c>
       <c r="D398" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F398" s="0" t="n">
         <v>11</v>
       </c>
       <c r="G398" s="0" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13385,10 +14391,10 @@
         <v>32</v>
       </c>
       <c r="D399" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E399" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F399" s="0" t="n">
         <v>28</v>
@@ -13405,10 +14411,10 @@
         <v>45</v>
       </c>
       <c r="D400" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F400" s="0" t="n">
         <v>28</v>
@@ -13425,10 +14431,10 @@
         <v>40</v>
       </c>
       <c r="D401" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F401" s="0" t="n">
         <v>28</v>
@@ -13445,7 +14451,7 @@
         <v>68</v>
       </c>
       <c r="D402" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E402" s="0" t="n">
         <v>5</v>
@@ -13465,7 +14471,7 @@
         <v>68</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E403" s="0" t="n">
         <v>5</v>
@@ -13485,7 +14491,7 @@
         <v>57</v>
       </c>
       <c r="D404" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E404" s="0" t="n">
         <v>3</v>
@@ -13505,7 +14511,7 @@
         <v>60</v>
       </c>
       <c r="D405" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E405" s="0" t="n">
         <v>5</v>
@@ -13525,7 +14531,7 @@
         <v>14</v>
       </c>
       <c r="D406" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E406" s="0" t="n">
         <v>3</v>
@@ -13545,10 +14551,10 @@
         <v>63</v>
       </c>
       <c r="D407" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E407" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F407" s="0" t="n">
         <v>8</v>
@@ -13565,7 +14571,7 @@
         <v>81</v>
       </c>
       <c r="D408" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E408" s="0" t="n">
         <v>3</v>
@@ -13574,7 +14580,7 @@
         <v>6</v>
       </c>
       <c r="G408" s="0" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13588,16 +14594,16 @@
         <v>82</v>
       </c>
       <c r="D409" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F409" s="0" t="n">
         <v>3</v>
       </c>
       <c r="G409" s="0" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13611,16 +14617,16 @@
         <v>102</v>
       </c>
       <c r="D410" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E410" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F410" s="0" t="n">
         <v>4</v>
       </c>
       <c r="G410" s="0" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13634,16 +14640,16 @@
         <v>99</v>
       </c>
       <c r="D411" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F411" s="0" t="n">
         <v>48</v>
       </c>
       <c r="G411" s="0" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13657,10 +14663,10 @@
         <v>94</v>
       </c>
       <c r="D412" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F412" s="0" t="n">
         <v>4</v>
@@ -13677,10 +14683,10 @@
         <v>94</v>
       </c>
       <c r="D413" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F413" s="0" t="n">
         <v>4</v>
@@ -13697,10 +14703,10 @@
         <v>98</v>
       </c>
       <c r="D414" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E414" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F414" s="0" t="n">
         <v>3</v>
@@ -13717,7 +14723,7 @@
         <v>49</v>
       </c>
       <c r="D415" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E415" s="0" t="n">
         <v>5</v>
@@ -13737,7 +14743,7 @@
         <v>56</v>
       </c>
       <c r="D416" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E416" s="0" t="n">
         <v>5</v>
@@ -13757,10 +14763,10 @@
         <v>71</v>
       </c>
       <c r="D417" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E417" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F417" s="0" t="n">
         <v>5</v>
@@ -13777,7 +14783,7 @@
         <v>50</v>
       </c>
       <c r="D418" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E418" s="0" t="n">
         <v>4</v>
@@ -13797,7 +14803,7 @@
         <v>43</v>
       </c>
       <c r="D419" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E419" s="0" t="n">
         <v>5</v>
@@ -13817,10 +14823,10 @@
         <v>74</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F420" s="0" t="n">
         <v>48</v>
@@ -13837,10 +14843,10 @@
         <v>73</v>
       </c>
       <c r="D421" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E421" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F421" s="0" t="n">
         <v>10</v>
@@ -13857,10 +14863,10 @@
         <v>52</v>
       </c>
       <c r="D422" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E422" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F422" s="0" t="n">
         <v>6</v>
@@ -13877,10 +14883,10 @@
         <v>78</v>
       </c>
       <c r="D423" s="0" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="E423" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F423" s="0" t="n">
         <v>6</v>
@@ -13897,7 +14903,7 @@
         <v>80</v>
       </c>
       <c r="D424" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E424" s="0" t="n">
         <v>3</v>
@@ -13917,7 +14923,7 @@
         <v>91</v>
       </c>
       <c r="D425" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E425" s="0" t="n">
         <v>7</v>
@@ -13937,10 +14943,10 @@
         <v>85</v>
       </c>
       <c r="D426" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F426" s="0" t="n">
         <v>30</v>
@@ -13957,10 +14963,10 @@
         <v>91</v>
       </c>
       <c r="D427" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E427" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F427" s="0" t="n">
         <v>12</v>
@@ -13977,10 +14983,10 @@
         <v>57</v>
       </c>
       <c r="D428" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F428" s="0" t="n">
         <v>48</v>
@@ -13997,7 +15003,7 @@
         <v>63</v>
       </c>
       <c r="D429" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E429" s="0" t="n">
         <v>4</v>
@@ -14017,7 +15023,7 @@
         <v>74</v>
       </c>
       <c r="D430" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E430" s="0" t="n">
         <v>2</v>
@@ -14037,10 +15043,10 @@
         <v>43</v>
       </c>
       <c r="D431" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F431" s="0" t="n">
         <v>8</v>
@@ -14057,10 +15063,10 @@
         <v>81</v>
       </c>
       <c r="D432" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F432" s="0" t="n">
         <v>6</v>
@@ -14077,10 +15083,10 @@
         <v>85</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F433" s="0" t="n">
         <v>6</v>
@@ -14097,10 +15103,10 @@
         <v>95</v>
       </c>
       <c r="D434" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F434" s="0" t="n">
         <v>12</v>
@@ -14117,7 +15123,7 @@
         <v>44</v>
       </c>
       <c r="D435" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E435" s="0" t="n">
         <v>5</v>
@@ -14137,10 +15143,10 @@
         <v>46</v>
       </c>
       <c r="D436" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F436" s="0" t="n">
         <v>6</v>
@@ -14157,7 +15163,7 @@
         <v>59</v>
       </c>
       <c r="D437" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E437" s="0" t="n">
         <v>5</v>
@@ -14177,10 +15183,10 @@
         <v>59</v>
       </c>
       <c r="D438" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F438" s="0" t="n">
         <v>3</v>
@@ -14197,10 +15203,10 @@
         <v>57</v>
       </c>
       <c r="D439" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E439" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F439" s="0" t="n">
         <v>3</v>
@@ -14217,10 +15223,10 @@
         <v>60</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F440" s="0" t="n">
         <v>3</v>
@@ -14237,7 +15243,7 @@
         <v>57</v>
       </c>
       <c r="D441" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E441" s="0" t="n">
         <v>2</v>
@@ -14257,7 +15263,7 @@
         <v>78</v>
       </c>
       <c r="D442" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E442" s="0" t="n">
         <v>3</v>
@@ -14277,10 +15283,10 @@
         <v>90</v>
       </c>
       <c r="D443" s="0" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F443" s="0" t="n">
         <v>10</v>
@@ -14297,7 +15303,7 @@
         <v>76</v>
       </c>
       <c r="D444" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E444" s="0" t="n">
         <v>4</v>
@@ -14317,10 +15323,10 @@
         <v>12</v>
       </c>
       <c r="D445" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E445" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F445" s="0" t="n">
         <v>5</v>
@@ -14337,10 +15343,10 @@
         <v>8</v>
       </c>
       <c r="D446" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E446" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F446" s="0" t="n">
         <v>3</v>
@@ -14357,7 +15363,7 @@
         <v>52</v>
       </c>
       <c r="D447" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E447" s="0" t="n">
         <v>6</v>
@@ -14377,10 +15383,10 @@
         <v>5</v>
       </c>
       <c r="D448" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F448" s="0" t="n">
         <v>4</v>
@@ -14397,10 +15403,10 @@
         <v>7</v>
       </c>
       <c r="D449" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F449" s="0" t="n">
         <v>5</v>
@@ -14417,10 +15423,10 @@
         <v>5</v>
       </c>
       <c r="D450" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F450" s="0" t="n">
         <v>4</v>
@@ -14437,10 +15443,10 @@
         <v>5</v>
       </c>
       <c r="D451" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E451" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14454,10 +15460,10 @@
         <v>19</v>
       </c>
       <c r="D452" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F452" s="0" t="n">
         <v>6</v>
@@ -14474,10 +15480,10 @@
         <v>17</v>
       </c>
       <c r="D453" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E453" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F453" s="0" t="n">
         <v>6</v>
@@ -14494,7 +15500,7 @@
         <v>35</v>
       </c>
       <c r="D454" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E454" s="0" t="n">
         <v>4</v>
@@ -14514,10 +15520,10 @@
         <v>28</v>
       </c>
       <c r="D455" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F455" s="0" t="n">
         <v>6</v>
@@ -14534,10 +15540,10 @@
         <v>25</v>
       </c>
       <c r="D456" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F456" s="0" t="n">
         <v>10</v>
@@ -14554,7 +15560,7 @@
         <v>75</v>
       </c>
       <c r="D457" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E457" s="0" t="n">
         <v>1</v>
@@ -14574,10 +15580,10 @@
         <v>72</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F458" s="0" t="n">
         <v>14</v>
@@ -14594,7 +15600,7 @@
         <v>54</v>
       </c>
       <c r="D459" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E459" s="0" t="n">
         <v>2</v>
@@ -14614,7 +15620,7 @@
         <v>30</v>
       </c>
       <c r="D460" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E460" s="0" t="n">
         <v>3</v>
@@ -14634,10 +15640,10 @@
         <v>35</v>
       </c>
       <c r="D461" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F461" s="0" t="n">
         <v>4</v>
@@ -14654,7 +15660,7 @@
         <v>23</v>
       </c>
       <c r="D462" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E462" s="0" t="n">
         <v>3</v>
@@ -14674,10 +15680,10 @@
         <v>70</v>
       </c>
       <c r="D463" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E463" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F463" s="0" t="n">
         <v>14</v>
@@ -14694,10 +15700,10 @@
         <v>24</v>
       </c>
       <c r="D464" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F464" s="0" t="n">
         <v>6</v>
@@ -14714,7 +15720,7 @@
         <v>67</v>
       </c>
       <c r="D465" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E465" s="0" t="n">
         <v>4</v>
@@ -14734,10 +15740,10 @@
         <v>85</v>
       </c>
       <c r="D466" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F466" s="0" t="n">
         <v>18</v>
@@ -14754,10 +15760,10 @@
         <v>85</v>
       </c>
       <c r="D467" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E467" s="0" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="F467" s="0" t="n">
         <v>14</v>
@@ -14774,7 +15780,7 @@
         <v>53</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E468" s="0" t="n">
         <v>1</v>
@@ -14794,10 +15800,10 @@
         <v>82</v>
       </c>
       <c r="D469" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F469" s="0" t="n">
         <v>6</v>
@@ -14814,10 +15820,10 @@
         <v>88</v>
       </c>
       <c r="D470" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F470" s="0" t="n">
         <v>10</v>
@@ -14834,7 +15840,7 @@
         <v>81</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E471" s="0" t="n">
         <v>6</v>
@@ -14854,10 +15860,10 @@
         <v>76</v>
       </c>
       <c r="D472" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E472" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F472" s="0" t="n">
         <v>4</v>
@@ -14874,7 +15880,7 @@
         <v>83</v>
       </c>
       <c r="D473" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E473" s="0" t="n">
         <v>7</v>
@@ -14894,10 +15900,10 @@
         <v>84</v>
       </c>
       <c r="D474" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F474" s="0" t="n">
         <v>52</v>
@@ -14914,10 +15920,10 @@
         <v>75</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F475" s="0" t="n">
         <v>12</v>
@@ -14934,10 +15940,10 @@
         <v>83</v>
       </c>
       <c r="D476" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E476" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F476" s="0" t="n">
         <v>6</v>
@@ -14954,7 +15960,7 @@
         <v>87</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E477" s="0" t="n">
         <v>6</v>
@@ -14974,10 +15980,10 @@
         <v>78</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F478" s="0" t="n">
         <v>12</v>
@@ -14994,7 +16000,7 @@
         <v>93</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E479" s="0" t="n">
         <v>1</v>
@@ -15014,7 +16020,7 @@
         <v>44</v>
       </c>
       <c r="D480" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E480" s="0" t="n">
         <v>7</v>
@@ -15034,10 +16040,10 @@
         <v>51</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F481" s="0" t="n">
         <v>6</v>
@@ -15054,10 +16060,10 @@
         <v>55</v>
       </c>
       <c r="D482" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F482" s="0" t="n">
         <v>9</v>
@@ -15074,10 +16080,10 @@
         <v>55</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F483" s="0" t="n">
         <v>6</v>
@@ -15094,10 +16100,10 @@
         <v>54</v>
       </c>
       <c r="D484" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E484" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F484" s="0" t="n">
         <v>4</v>
@@ -15114,10 +16120,10 @@
         <v>61</v>
       </c>
       <c r="D485" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F485" s="0" t="n">
         <v>12</v>
@@ -15134,7 +16140,7 @@
         <v>71</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E486" s="0" t="n">
         <v>2</v>
@@ -15154,7 +16160,7 @@
         <v>75</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E487" s="0" t="n">
         <v>7</v>
@@ -15174,10 +16180,10 @@
         <v>69</v>
       </c>
       <c r="D488" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E488" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F488" s="0" t="n">
         <v>6</v>
@@ -15194,10 +16200,10 @@
         <v>69</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F489" s="0" t="n">
         <v>8</v>
@@ -15214,7 +16220,7 @@
         <v>70</v>
       </c>
       <c r="D490" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E490" s="0" t="n">
         <v>6</v>
@@ -15234,10 +16240,10 @@
         <v>66</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F491" s="0" t="n">
         <v>7</v>
@@ -15254,10 +16260,10 @@
         <v>36</v>
       </c>
       <c r="D492" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F492" s="0" t="n">
         <v>6</v>
@@ -15274,7 +16280,7 @@
         <v>40</v>
       </c>
       <c r="D493" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E493" s="0" t="n">
         <v>3</v>
@@ -15294,10 +16300,10 @@
         <v>95</v>
       </c>
       <c r="D494" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F494" s="0" t="n">
         <v>12</v>
@@ -15314,7 +16320,7 @@
         <v>45</v>
       </c>
       <c r="D495" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E495" s="0" t="n">
         <v>7</v>
@@ -15334,7 +16340,7 @@
         <v>54</v>
       </c>
       <c r="D496" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E496" s="0" t="n">
         <v>4</v>
@@ -15354,10 +16360,10 @@
         <v>59</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F497" s="0" t="n">
         <v>5</v>
@@ -15374,10 +16380,10 @@
         <v>86</v>
       </c>
       <c r="D498" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F498" s="0" t="n">
         <v>8</v>
@@ -15394,7 +16400,7 @@
         <v>68</v>
       </c>
       <c r="D499" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E499" s="0" t="n">
         <v>2</v>
@@ -15414,7 +16420,7 @@
         <v>40</v>
       </c>
       <c r="D500" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E500" s="0" t="n">
         <v>1</v>
@@ -15434,10 +16440,10 @@
         <v>43</v>
       </c>
       <c r="D501" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E501" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F501" s="0" t="n">
         <v>6</v>
@@ -15454,7 +16460,7 @@
         <v>57</v>
       </c>
       <c r="D502" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E502" s="0" t="n">
         <v>5</v>
@@ -15474,7 +16480,7 @@
         <v>57</v>
       </c>
       <c r="D503" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E503" s="0" t="n">
         <v>5</v>
@@ -15494,7 +16500,7 @@
         <v>75</v>
       </c>
       <c r="D504" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E504" s="0" t="n">
         <v>5</v>
@@ -15514,10 +16520,10 @@
         <v>69</v>
       </c>
       <c r="D505" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E505" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F505" s="0" t="n">
         <v>4</v>
@@ -15534,10 +16540,10 @@
         <v>69</v>
       </c>
       <c r="D506" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E506" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F506" s="0" t="n">
         <v>4</v>
@@ -15554,10 +16560,10 @@
         <v>54</v>
       </c>
       <c r="D507" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E507" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F507" s="0" t="n">
         <v>6</v>
@@ -15574,10 +16580,10 @@
         <v>63</v>
       </c>
       <c r="D508" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E508" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F508" s="0" t="n">
         <v>14</v>
@@ -15594,7 +16600,7 @@
         <v>32</v>
       </c>
       <c r="D509" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E509" s="0" t="n">
         <v>6</v>
@@ -15614,10 +16620,10 @@
         <v>74</v>
       </c>
       <c r="D510" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E510" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F510" s="0" t="n">
         <v>6</v>
@@ -15634,10 +16640,10 @@
         <v>78</v>
       </c>
       <c r="D511" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E511" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F511" s="0" t="n">
         <v>8</v>
@@ -15654,10 +16660,10 @@
         <v>80</v>
       </c>
       <c r="D512" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E512" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F512" s="0" t="n">
         <v>6</v>
@@ -15674,7 +16680,7 @@
         <v>78</v>
       </c>
       <c r="D513" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E513" s="0" t="n">
         <v>5</v>
@@ -15694,7 +16700,7 @@
         <v>52</v>
       </c>
       <c r="D514" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E514" s="0" t="n">
         <v>10</v>
@@ -15714,7 +16720,7 @@
         <v>18</v>
       </c>
       <c r="D515" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E515" s="0" t="n">
         <v>5</v>
@@ -15734,7 +16740,7 @@
         <v>25</v>
       </c>
       <c r="D516" s="0" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E516" s="0" t="n">
         <v>2</v>
@@ -15754,10 +16760,10 @@
         <v>13</v>
       </c>
       <c r="D517" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E517" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F517" s="0" t="n">
         <v>9</v>
@@ -15774,10 +16780,10 @@
         <v>14</v>
       </c>
       <c r="D518" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E518" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F518" s="0" t="n">
         <v>9</v>
@@ -15794,7 +16800,7 @@
         <v>33</v>
       </c>
       <c r="D519" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E519" s="0" t="n">
         <v>2</v>
@@ -15814,10 +16820,10 @@
         <v>63</v>
       </c>
       <c r="D520" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E520" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F520" s="0" t="n">
         <v>2</v>
@@ -15834,7 +16840,7 @@
         <v>77</v>
       </c>
       <c r="D521" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E521" s="0" t="n">
         <v>10</v>
@@ -15854,7 +16860,7 @@
         <v>72</v>
       </c>
       <c r="D522" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E522" s="0" t="n">
         <v>8</v>
@@ -15874,10 +16880,10 @@
         <v>70</v>
       </c>
       <c r="D523" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E523" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F523" s="0" t="n">
         <v>3</v>
@@ -15894,10 +16900,10 @@
         <v>70</v>
       </c>
       <c r="D524" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E524" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F524" s="0" t="n">
         <v>4</v>
@@ -15914,10 +16920,10 @@
         <v>45</v>
       </c>
       <c r="D525" s="0" t="s">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="G525" s="0" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15931,10 +16937,10 @@
         <v>24</v>
       </c>
       <c r="D526" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E526" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F526" s="0" t="n">
         <v>8</v>
@@ -15951,7 +16957,7 @@
         <v>38</v>
       </c>
       <c r="D527" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E527" s="0" t="n">
         <v>3</v>
@@ -15971,7 +16977,7 @@
         <v>45</v>
       </c>
       <c r="D528" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E528" s="0" t="n">
         <v>2</v>
@@ -15991,7 +16997,7 @@
         <v>20</v>
       </c>
       <c r="D529" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E529" s="0" t="n">
         <v>3</v>
@@ -16011,7 +17017,7 @@
         <v>45</v>
       </c>
       <c r="D530" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E530" s="0" t="n">
         <v>2</v>
@@ -16031,7 +17037,7 @@
         <v>45</v>
       </c>
       <c r="D531" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E531" s="0" t="n">
         <v>1</v>
@@ -16051,10 +17057,10 @@
         <v>35</v>
       </c>
       <c r="D532" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E532" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F532" s="0" t="n">
         <v>6</v>
@@ -16071,7 +17077,7 @@
         <v>42</v>
       </c>
       <c r="D533" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E533" s="0" t="n">
         <v>4</v>
@@ -16091,7 +17097,7 @@
         <v>39</v>
       </c>
       <c r="D534" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E534" s="0" t="n">
         <v>8</v>
@@ -16111,7 +17117,7 @@
         <v>2</v>
       </c>
       <c r="D535" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E535" s="0" t="n">
         <v>3</v>
@@ -16131,7 +17137,7 @@
         <v>41</v>
       </c>
       <c r="D536" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E536" s="0" t="n">
         <v>10</v>
@@ -16151,10 +17157,10 @@
         <v>16</v>
       </c>
       <c r="D537" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E537" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F537" s="0" t="n">
         <v>6</v>
@@ -16171,7 +17177,7 @@
         <v>10</v>
       </c>
       <c r="D538" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E538" s="0" t="n">
         <v>10</v>
@@ -16191,7 +17197,7 @@
         <v>19</v>
       </c>
       <c r="D539" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E539" s="0" t="n">
         <v>3</v>
@@ -16211,7 +17217,7 @@
         <v>31</v>
       </c>
       <c r="D540" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E540" s="0" t="n">
         <v>10</v>
@@ -16231,7 +17237,7 @@
         <v>28</v>
       </c>
       <c r="D541" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E541" s="0" t="n">
         <v>10</v>
@@ -16251,10 +17257,10 @@
         <v>23</v>
       </c>
       <c r="D542" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E542" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F542" s="0" t="n">
         <v>7</v>
@@ -16271,7 +17277,7 @@
         <v>5</v>
       </c>
       <c r="D543" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E543" s="0" t="n">
         <v>6</v>
@@ -16291,7 +17297,7 @@
         <v>36</v>
       </c>
       <c r="D544" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E544" s="0" t="n">
         <v>7</v>
@@ -16311,7 +17317,7 @@
         <v>32</v>
       </c>
       <c r="D545" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E545" s="0" t="n">
         <v>4</v>
@@ -16331,10 +17337,10 @@
         <v>54</v>
       </c>
       <c r="D546" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E546" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F546" s="0" t="n">
         <v>14</v>
@@ -16351,7 +17357,7 @@
         <v>35</v>
       </c>
       <c r="D547" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E547" s="0" t="n">
         <v>2</v>
@@ -16371,10 +17377,10 @@
         <v>49</v>
       </c>
       <c r="D548" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E548" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F548" s="0" t="n">
         <v>10</v>
@@ -16391,7 +17397,7 @@
         <v>61</v>
       </c>
       <c r="D549" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E549" s="0" t="n">
         <v>3</v>
@@ -16411,7 +17417,7 @@
         <v>63</v>
       </c>
       <c r="D550" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E550" s="0" t="n">
         <v>3</v>
@@ -16431,7 +17437,7 @@
         <v>68</v>
       </c>
       <c r="D551" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E551" s="0" t="n">
         <v>4</v>
@@ -16451,10 +17457,10 @@
         <v>63</v>
       </c>
       <c r="D552" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E552" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F552" s="0" t="n">
         <v>8</v>
@@ -16471,10 +17477,10 @@
         <v>54</v>
       </c>
       <c r="D553" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E553" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F553" s="0" t="n">
         <v>6</v>
@@ -16491,10 +17497,10 @@
         <v>68</v>
       </c>
       <c r="D554" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E554" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16508,10 +17514,10 @@
         <v>53</v>
       </c>
       <c r="D555" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E555" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F555" s="0" t="n">
         <v>4</v>
@@ -16528,10 +17534,10 @@
         <v>57</v>
       </c>
       <c r="D556" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E556" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F556" s="0" t="n">
         <v>10</v>
@@ -16548,10 +17554,10 @@
         <v>36</v>
       </c>
       <c r="D557" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E557" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F557" s="0" t="n">
         <v>9</v>
@@ -16568,10 +17574,10 @@
         <v>36</v>
       </c>
       <c r="D558" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E558" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F558" s="0" t="n">
         <v>6</v>
@@ -16588,7 +17594,7 @@
         <v>57</v>
       </c>
       <c r="D559" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E559" s="0" t="n">
         <v>8</v>
@@ -16608,10 +17614,10 @@
         <v>53</v>
       </c>
       <c r="D560" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E560" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F560" s="0" t="n">
         <v>6</v>
@@ -16628,7 +17634,7 @@
         <v>53</v>
       </c>
       <c r="D561" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E561" s="0" t="n">
         <v>4</v>
@@ -16648,10 +17654,10 @@
         <v>63</v>
       </c>
       <c r="D562" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E562" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F562" s="0" t="n">
         <v>10</v>
@@ -16668,10 +17674,10 @@
         <v>63</v>
       </c>
       <c r="D563" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E563" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F563" s="0" t="n">
         <v>7</v>
@@ -16688,10 +17694,10 @@
         <v>60</v>
       </c>
       <c r="D564" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E564" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F564" s="0" t="n">
         <v>8</v>
@@ -16708,10 +17714,10 @@
         <v>39</v>
       </c>
       <c r="D565" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E565" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F565" s="0" t="n">
         <v>5</v>
@@ -16728,7 +17734,7 @@
         <v>43</v>
       </c>
       <c r="D566" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E566" s="0" t="n">
         <v>0</v>
@@ -16748,7 +17754,7 @@
         <v>55</v>
       </c>
       <c r="D567" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E567" s="0" t="n">
         <v>0</v>
@@ -16768,10 +17774,10 @@
         <v>39</v>
       </c>
       <c r="D568" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E568" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F568" s="0" t="n">
         <v>9</v>
@@ -16788,7 +17794,7 @@
         <v>51</v>
       </c>
       <c r="D569" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E569" s="0" t="n">
         <v>5</v>
@@ -16808,10 +17814,10 @@
         <v>49</v>
       </c>
       <c r="D570" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E570" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F570" s="0" t="n">
         <v>8</v>
@@ -16828,7 +17834,7 @@
         <v>77</v>
       </c>
       <c r="D571" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E571" s="0" t="n">
         <v>10</v>
@@ -16848,7 +17854,7 @@
         <v>77</v>
       </c>
       <c r="D572" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E572" s="0" t="n">
         <v>10</v>
@@ -16868,10 +17874,10 @@
         <v>90</v>
       </c>
       <c r="D573" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E573" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F573" s="0" t="n">
         <v>5</v>
@@ -16888,10 +17894,10 @@
         <v>74</v>
       </c>
       <c r="D574" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E574" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F574" s="0" t="n">
         <v>4</v>
@@ -16908,10 +17914,10 @@
         <v>92</v>
       </c>
       <c r="D575" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E575" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F575" s="0" t="n">
         <v>7</v>
@@ -16928,10 +17934,10 @@
         <v>92</v>
       </c>
       <c r="D576" s="0" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="E576" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F576" s="0" t="n">
         <v>4</v>
@@ -16948,7 +17954,7 @@
         <v>84</v>
       </c>
       <c r="D577" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E577" s="0" t="n">
         <v>10</v>
@@ -16968,10 +17974,10 @@
         <v>94</v>
       </c>
       <c r="D578" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E578" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F578" s="0" t="n">
         <v>3</v>
@@ -16988,7 +17994,7 @@
         <v>66</v>
       </c>
       <c r="D579" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E579" s="0" t="n">
         <v>8</v>
@@ -17008,7 +18014,7 @@
         <v>63</v>
       </c>
       <c r="D580" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E580" s="0" t="n">
         <v>10</v>
@@ -17028,10 +18034,10 @@
         <v>64</v>
       </c>
       <c r="D581" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E581" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F581" s="0" t="n">
         <v>3</v>
@@ -17048,10 +18054,10 @@
         <v>64</v>
       </c>
       <c r="D582" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E582" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F582" s="0" t="n">
         <v>8</v>
@@ -17068,7 +18074,7 @@
         <v>66</v>
       </c>
       <c r="D583" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E583" s="0" t="n">
         <v>2</v>
@@ -17088,7 +18094,7 @@
         <v>77</v>
       </c>
       <c r="D584" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E584" s="0" t="n">
         <v>10</v>
@@ -17108,10 +18114,10 @@
         <v>64</v>
       </c>
       <c r="D585" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E585" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F585" s="0" t="n">
         <v>2</v>
@@ -17128,10 +18134,10 @@
         <v>68</v>
       </c>
       <c r="D586" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E586" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F586" s="0" t="n">
         <v>5</v>
@@ -17148,10 +18154,10 @@
         <v>98</v>
       </c>
       <c r="D587" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E587" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F587" s="0" t="n">
         <v>5</v>
@@ -17168,10 +18174,10 @@
         <v>103</v>
       </c>
       <c r="D588" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E588" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F588" s="0" t="n">
         <v>5</v>
@@ -17188,7 +18194,7 @@
         <v>54</v>
       </c>
       <c r="D589" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E589" s="0" t="n">
         <v>8</v>
@@ -17208,7 +18214,7 @@
         <v>93</v>
       </c>
       <c r="D590" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E590" s="0" t="n">
         <v>10</v>
@@ -17228,7 +18234,7 @@
         <v>70</v>
       </c>
       <c r="D591" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E591" s="0" t="n">
         <v>2</v>
@@ -17248,7 +18254,7 @@
         <v>51</v>
       </c>
       <c r="D592" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E592" s="0" t="n">
         <v>8</v>
@@ -17268,10 +18274,10 @@
         <v>94</v>
       </c>
       <c r="D593" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E593" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F593" s="0" t="n">
         <v>8</v>
@@ -17288,10 +18294,10 @@
         <v>47</v>
       </c>
       <c r="D594" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E594" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F594" s="0" t="n">
         <v>2</v>
@@ -17308,10 +18314,10 @@
         <v>57</v>
       </c>
       <c r="D595" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E595" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F595" s="0" t="n">
         <v>7</v>
@@ -17328,10 +18334,10 @@
         <v>57</v>
       </c>
       <c r="D596" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E596" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F596" s="0" t="n">
         <v>5</v>
@@ -17348,10 +18354,10 @@
         <v>100</v>
       </c>
       <c r="D597" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E597" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F597" s="0" t="n">
         <v>8</v>
@@ -17368,7 +18374,7 @@
         <v>46</v>
       </c>
       <c r="D598" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E598" s="0" t="n">
         <v>8</v>
@@ -17388,10 +18394,10 @@
         <v>106</v>
       </c>
       <c r="D599" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E599" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F599" s="0" t="n">
         <v>5</v>
@@ -17408,10 +18414,10 @@
         <v>98</v>
       </c>
       <c r="D600" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E600" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F600" s="0" t="n">
         <v>6</v>
@@ -17428,7 +18434,7 @@
         <v>95</v>
       </c>
       <c r="D601" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E601" s="0" t="n">
         <v>10</v>
@@ -17448,10 +18454,10 @@
         <v>67</v>
       </c>
       <c r="D602" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E602" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F602" s="0" t="n">
         <v>3</v>
@@ -17468,10 +18474,10 @@
         <v>67</v>
       </c>
       <c r="D603" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E603" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F603" s="0" t="n">
         <v>18</v>
@@ -17488,10 +18494,10 @@
         <v>90</v>
       </c>
       <c r="D604" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E604" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F604" s="0" t="n">
         <v>8</v>
@@ -17508,10 +18514,10 @@
         <v>68</v>
       </c>
       <c r="D605" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E605" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F605" s="0" t="n">
         <v>6</v>
@@ -17528,10 +18534,10 @@
         <v>71</v>
       </c>
       <c r="D606" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E606" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F606" s="0" t="n">
         <v>4</v>
@@ -17548,10 +18554,10 @@
         <v>77</v>
       </c>
       <c r="D607" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E607" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F607" s="0" t="n">
         <v>48</v>
@@ -17568,10 +18574,10 @@
         <v>69</v>
       </c>
       <c r="D608" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E608" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F608" s="0" t="n">
         <v>6</v>
@@ -17588,7 +18594,7 @@
         <v>65</v>
       </c>
       <c r="D609" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E609" s="0" t="n">
         <v>3</v>
@@ -17608,7 +18614,7 @@
         <v>68</v>
       </c>
       <c r="D610" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E610" s="0" t="n">
         <v>8</v>
@@ -17628,7 +18634,7 @@
         <v>29</v>
       </c>
       <c r="D611" s="0" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="E611" s="0" t="n">
         <v>2</v>
@@ -17648,7 +18654,7 @@
         <v>29</v>
       </c>
       <c r="D612" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E612" s="0" t="n">
         <v>4</v>
@@ -17668,7 +18674,7 @@
         <v>5</v>
       </c>
       <c r="D613" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E613" s="0" t="n">
         <v>6</v>
@@ -17688,7 +18694,7 @@
         <v>40</v>
       </c>
       <c r="D614" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E614" s="0" t="n">
         <v>10</v>
@@ -17708,10 +18714,10 @@
         <v>8</v>
       </c>
       <c r="D615" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E615" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F615" s="0" t="n">
         <v>24</v>
@@ -17728,7 +18734,7 @@
         <v>67</v>
       </c>
       <c r="D616" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E616" s="0" t="n">
         <v>10</v>
@@ -17748,7 +18754,7 @@
         <v>60</v>
       </c>
       <c r="D617" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E617" s="0" t="n">
         <v>10</v>
@@ -17768,10 +18774,10 @@
         <v>49</v>
       </c>
       <c r="D618" s="0" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="E618" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F618" s="0" t="n">
         <v>28</v>
@@ -17788,7 +18794,7 @@
         <v>18</v>
       </c>
       <c r="D619" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E619" s="0" t="n">
         <v>5</v>
@@ -17808,10 +18814,10 @@
         <v>13</v>
       </c>
       <c r="D620" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E620" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F620" s="0" t="n">
         <v>8</v>
@@ -17828,10 +18834,10 @@
         <v>18</v>
       </c>
       <c r="D621" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E621" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F621" s="0" t="n">
         <v>4</v>
@@ -17848,10 +18854,10 @@
         <v>40</v>
       </c>
       <c r="D622" s="0" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E622" s="0" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F622" s="0" t="n">
         <v>4</v>
@@ -17868,13 +18874,1293 @@
         <v>20</v>
       </c>
       <c r="D623" s="0" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="E623" s="0" t="n">
         <v>4</v>
       </c>
       <c r="F623" s="0" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A624" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B624" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="C624" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D624" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E624" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F624" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A625" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B625" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="C625" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D625" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E625" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F625" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A626" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B626" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C626" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D626" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E626" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F626" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A627" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B627" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C627" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D627" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E627" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F627" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A628" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B628" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C628" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D628" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="E628" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F628" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A629" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B629" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C629" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="D629" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E629" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F629" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A630" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B630" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C630" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D630" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E630" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F630" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A631" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B631" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="C631" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D631" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E631" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F631" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A632" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B632" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C632" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D632" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E632" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F632" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A633" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B633" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="C633" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="D633" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E633" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F633" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A634" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B634" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C634" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D634" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E634" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F634" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A635" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B635" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C635" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D635" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E635" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F635" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A636" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B636" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="C636" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D636" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E636" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F636" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A637" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B637" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C637" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D637" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E637" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F637" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A638" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B638" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="C638" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D638" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="E638" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F638" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A639" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B639" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C639" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D639" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E639" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F639" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A640" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B640" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C640" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D640" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="E640" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F640" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A641" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B641" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="C641" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D641" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E641" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F641" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A642" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B642" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="C642" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="D642" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E642" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F642" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A643" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B643" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="C643" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D643" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E643" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F643" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A644" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B644" s="0" t="n">
+        <v>346</v>
+      </c>
+      <c r="C644" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="D644" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E644" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F644" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A645" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B645" s="0" t="n">
+        <v>346</v>
+      </c>
+      <c r="C645" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="D645" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E645" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F645" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A646" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B646" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C646" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D646" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E646" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F646" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A647" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B647" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C647" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D647" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E647" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F647" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A648" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B648" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="C648" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="D648" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E648" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F648" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A649" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B649" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="C649" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D649" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E649" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F649" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A650" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B650" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="C650" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D650" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E650" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F650" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A651" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B651" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="C651" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="D651" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E651" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F651" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A652" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B652" s="0" t="n">
+        <v>339</v>
+      </c>
+      <c r="C652" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D652" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E652" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F652" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A653" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B653" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C653" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D653" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E653" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F653" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A654" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B654" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C654" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D654" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E654" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F654" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A655" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B655" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="C655" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D655" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E655" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F655" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A656" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B656" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="C656" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="D656" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E656" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F656" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A657" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B657" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C657" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D657" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E657" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F657" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A658" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B658" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C658" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="D658" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E658" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F658" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A659" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B659" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C659" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D659" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E659" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F659" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A660" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B660" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="C660" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D660" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E660" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F660" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A661" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B661" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="C661" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="D661" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E661" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F661" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A662" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B662" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="C662" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="D662" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E662" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F662" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A663" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B663" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="C663" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="D663" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E663" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F663" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A664" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B664" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="C664" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="D664" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E664" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F664" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A665" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B665" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="C665" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D665" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E665" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F665" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A666" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B666" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="C666" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D666" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E666" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F666" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A667" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B667" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C667" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="D667" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E667" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F667" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A668" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B668" s="0" t="n">
+        <v>332</v>
+      </c>
+      <c r="C668" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D668" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E668" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F668" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A669" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B669" s="0" t="n">
+        <v>328</v>
+      </c>
+      <c r="C669" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D669" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="E669" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F669" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A670" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B670" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C670" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D670" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E670" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F670" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A671" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B671" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C671" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D671" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E671" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F671" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A672" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B672" s="0" t="n">
+        <v>1388</v>
+      </c>
+      <c r="C672" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D672" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E672" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F672" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A673" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B673" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C673" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="D673" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E673" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F673" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A674" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B674" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="C674" s="0" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D674" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E674" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F674" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A675" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B675" s="0" t="n">
+        <v>193</v>
+      </c>
+      <c r="C675" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="D675" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E675" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F675" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A676" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B676" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="C676" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="D676" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E676" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F676" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A677" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B677" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="C677" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D677" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E677" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F677" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A678" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B678" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="C678" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D678" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E678" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F678" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A679" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B679" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C679" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D679" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E679" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F679" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A680" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B680" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C680" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D680" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E680" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F680" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A681" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B681" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="C681" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D681" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E681" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F681" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A682" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B682" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="C682" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D682" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="E682" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F682" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A683" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B683" s="0" t="n">
+        <v>346</v>
+      </c>
+      <c r="C683" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D683" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E683" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F683" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A684" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B684" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="C684" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="D684" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E684" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F684" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A685" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B685" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C685" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D685" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E685" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F685" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A686" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B686" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C686" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="D686" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E686" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F686" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A687" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B687" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C687" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="D687" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E687" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F687" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Cut_stump_compass_points" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Cut_stump_trees" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Plot_corners" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="map" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="map_chain" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="491">
   <si>
     <t xml:space="preserve">Station_1</t>
   </si>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Block</t>
   </si>
   <si>
-    <t xml:space="preserve">Grid</t>
+    <t xml:space="preserve">Code?</t>
   </si>
   <si>
     <t xml:space="preserve">Azimuth_B</t>
@@ -1199,6 +1199,12 @@
     <t xml:space="preserve">NP</t>
   </si>
   <si>
+    <t xml:space="preserve">not poria, uncertain cause. 3 trees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not poria, uncertain cause.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS</t>
   </si>
   <si>
@@ -1239,6 +1245,9 @@
   </si>
   <si>
     <t xml:space="preserve">alder, not diseased tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid</t>
   </si>
   <si>
     <t xml:space="preserve">None</t>
@@ -1578,70 +1587,37 @@
     <t xml:space="preserve">E corner (north) BI</t>
   </si>
   <si>
-    <t xml:space="preserve">0
-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 
-                                                +12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65
-                                          C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44
-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56
-                                          -2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31
-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43
-                                          -4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18
-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30
-                                          -6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5
-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17
-                                          -8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0/34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1
-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2
-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3
-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4
-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10                                             -10</t>
+    <t xml:space="preserve">Grid Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survey Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-harvest count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-harvest not old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-harvest count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 chain lengths (132’)</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1628,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1679,16 +1655,61 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA6A6"/>
+        <bgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="25">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1698,9 +1719,170 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
       <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thick"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thick"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom style="thick"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom style="thick"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1729,7 +1911,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1746,32 +1928,192 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1783,7 +2125,147 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFB4C7DC"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFFA6A6"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>146880</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>317160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>11520</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>286560</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2700000">
+          <a:off x="26359560" y="8871480"/>
+          <a:ext cx="1693440" cy="426600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="0" t="0" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="4706" h="1188">
+              <a:moveTo>
+                <a:pt x="0" y="296"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="3528" y="296"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="3528" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4705" y="593"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="3528" y="1187"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="3528" y="890"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="889"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="296"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="ffffff"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8826,6 +9308,9 @@
       <c r="D60" s="0" t="s">
         <v>355</v>
       </c>
+      <c r="G60" s="0" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
@@ -9260,6 +9745,9 @@
       <c r="D82" s="0" t="s">
         <v>355</v>
       </c>
+      <c r="G82" s="0" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
@@ -9412,7 +9900,7 @@
         <v>69</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E90" s="0" t="s">
         <v>352</v>
@@ -9432,7 +9920,7 @@
         <v>24</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E91" s="0" t="s">
         <v>352</v>
@@ -9881,7 +10369,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10115,7 +10603,7 @@
         <v>26</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E125" s="0" t="n">
         <v>1</v>
@@ -12308,7 +12796,7 @@
         <v>54</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E236" s="0" t="s">
         <v>352</v>
@@ -12328,7 +12816,7 @@
         <v>66</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E237" s="0" t="s">
         <v>352</v>
@@ -12888,7 +13376,7 @@
         <v>4</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12968,7 +13456,7 @@
         <v>24</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14903,7 +15391,7 @@
         <v>14</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15326,7 +15814,7 @@
         <v>6</v>
       </c>
       <c r="G387" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15546,7 +16034,7 @@
         <v>11</v>
       </c>
       <c r="G398" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15749,7 +16237,7 @@
         <v>6</v>
       </c>
       <c r="G408" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15772,7 +16260,7 @@
         <v>3</v>
       </c>
       <c r="G409" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15795,7 +16283,7 @@
         <v>4</v>
       </c>
       <c r="G410" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15818,7 +16306,7 @@
         <v>48</v>
       </c>
       <c r="G411" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16452,7 +16940,7 @@
         <v>90</v>
       </c>
       <c r="D443" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E443" s="0" t="s">
         <v>347</v>
@@ -18089,10 +18577,10 @@
         <v>45</v>
       </c>
       <c r="D525" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G525" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20963,7 +21451,7 @@
         <v>62</v>
       </c>
       <c r="D669" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E669" s="0" t="s">
         <v>347</v>
@@ -21452,7 +21940,7 @@
         <v>13</v>
       </c>
       <c r="G693" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22426,10 +22914,10 @@
         <v>49</v>
       </c>
       <c r="D742" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G742" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22894,7 +23382,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>25</v>
+        <v>372</v>
       </c>
       <c r="AA1" s="0" t="s">
         <v>26</v>
@@ -22927,7 +23415,7 @@
       </c>
       <c r="Z2" s="1"/>
       <c r="AC2" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22990,7 +23478,7 @@
         <v>68</v>
       </c>
       <c r="AC5" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23063,7 +23551,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23255,13 +23743,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D1" s="0" t="s">
         <v>28</v>
@@ -23269,7 +23757,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>30</v>
@@ -23278,12 +23766,12 @@
         <v>-8.72</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>30</v>
@@ -23292,12 +23780,12 @@
         <v>-7.48</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>28</v>
@@ -23306,12 +23794,12 @@
         <v>-7.48</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>22.94</v>
@@ -23320,12 +23808,12 @@
         <v>-6.54</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>22.94</v>
@@ -23334,12 +23822,12 @@
         <v>-4.4</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>22.94</v>
@@ -23348,12 +23836,12 @@
         <v>-2.43</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>26</v>
@@ -23362,7 +23850,7 @@
         <v>-4.4</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23378,7 +23866,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>28.55</v>
@@ -23387,12 +23875,12 @@
         <v>-4</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>28.55</v>
@@ -23401,7 +23889,7 @@
         <v>-6</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23417,7 +23905,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>32.56</v>
@@ -23426,12 +23914,12 @@
         <v>-6</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>32.13</v>
@@ -23440,12 +23928,12 @@
         <v>-4</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>26</v>
@@ -23454,12 +23942,12 @@
         <v>-1.29</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>24.2</v>
@@ -23468,12 +23956,12 @@
         <v>0.4</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>22</v>
@@ -23482,12 +23970,12 @@
         <v>0.4</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>19.28</v>
@@ -23496,12 +23984,12 @@
         <v>0.4</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>18</v>
@@ -23512,7 +24000,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>16.5</v>
@@ -23521,12 +24009,12 @@
         <v>0.4</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>14.55</v>
@@ -23535,12 +24023,12 @@
         <v>0.4</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>13.61</v>
@@ -23549,12 +24037,12 @@
         <v>0.4</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>12</v>
@@ -23563,7 +24051,7 @@
         <v>0.4</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23577,7 +24065,7 @@
         <v>159</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23591,12 +24079,12 @@
         <v>159</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>9.24</v>
@@ -23605,12 +24093,12 @@
         <v>-2</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>13.62</v>
@@ -23619,7 +24107,7 @@
         <v>-2</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23633,12 +24121,12 @@
         <v>-2</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>16.5</v>
@@ -23647,12 +24135,12 @@
         <v>-2.43</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>16.73</v>
@@ -23661,12 +24149,12 @@
         <v>-2.43</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>19.28</v>
@@ -23675,12 +24163,12 @@
         <v>-2.43</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>20</v>
@@ -23689,12 +24177,12 @@
         <v>-2.43</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>16.73</v>
@@ -23703,7 +24191,7 @@
         <v>-4</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23717,7 +24205,7 @@
         <v>-4</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23731,12 +24219,12 @@
         <v>-4</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>9.55</v>
@@ -23747,7 +24235,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>9.12</v>
@@ -23756,7 +24244,7 @@
         <v>-6</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23770,12 +24258,12 @@
         <v>-6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>14</v>
@@ -23784,12 +24272,12 @@
         <v>-7.66</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>16.73</v>
@@ -23798,12 +24286,12 @@
         <v>-7.4</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>8</v>
@@ -23812,7 +24300,7 @@
         <v>2</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23826,12 +24314,12 @@
         <v>2</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>12.49</v>
@@ -23840,12 +24328,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>12.49</v>
@@ -23854,12 +24342,12 @@
         <v>4</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>8</v>
@@ -23868,7 +24356,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23882,12 +24370,12 @@
         <v>4</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>14.55</v>
@@ -23896,12 +24384,12 @@
         <v>3.54</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>14.55</v>
@@ -23910,12 +24398,12 @@
         <v>2.41</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>17.04</v>
@@ -23924,12 +24412,12 @@
         <v>2.41</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>18</v>
@@ -23938,12 +24426,12 @@
         <v>2.41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>22</v>
@@ -23952,12 +24440,12 @@
         <v>2.41</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>22</v>
@@ -23966,12 +24454,12 @@
         <v>4.37</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>18.65</v>
@@ -23980,12 +24468,12 @@
         <v>4.37</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>17.04</v>
@@ -23994,12 +24482,12 @@
         <v>4.26</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>16.23</v>
@@ -24008,12 +24496,12 @@
         <v>4.26</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>16.23</v>
@@ -24022,12 +24510,12 @@
         <v>4.9</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>14</v>
@@ -24036,12 +24524,12 @@
         <v>4.9</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>14</v>
@@ -24050,12 +24538,12 @@
         <v>6.06</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>18.65</v>
@@ -24075,7 +24563,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24089,12 +24577,12 @@
         <v>8</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>25.5</v>
@@ -24103,7 +24591,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -24122,462 +24610,4916 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C3:P14"/>
+  <dimension ref="A3:BS50"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="3" style="0" width="25.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="3.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="3" style="0" width="6.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="56" style="0" width="6.48"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="D3" s="5" t="n">
+    <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="7"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="6"/>
+      <c r="AU3" s="4"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="6"/>
+      <c r="AY3" s="4"/>
+      <c r="AZ3" s="5"/>
+      <c r="BA3" s="5"/>
+      <c r="BB3" s="6"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BH3" s="10"/>
+      <c r="BI3" s="10"/>
+      <c r="BJ3" s="10"/>
+      <c r="BK3" s="10"/>
+      <c r="BL3" s="10"/>
+      <c r="BM3" s="10"/>
+      <c r="BN3" s="10"/>
+      <c r="BO3" s="10"/>
+      <c r="BP3" s="11"/>
+      <c r="BQ3" s="11"/>
+      <c r="BR3" s="11"/>
+      <c r="BS3" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="13"/>
+      <c r="AG4" s="13"/>
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="13"/>
+      <c r="AK4" s="13"/>
+      <c r="AL4" s="14"/>
+      <c r="AM4" s="12"/>
+      <c r="AN4" s="13"/>
+      <c r="AO4" s="13"/>
+      <c r="AP4" s="15"/>
+      <c r="AQ4" s="16"/>
+      <c r="AR4" s="13"/>
+      <c r="AS4" s="13"/>
+      <c r="AT4" s="14"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="13"/>
+      <c r="AW4" s="13"/>
+      <c r="AX4" s="14"/>
+      <c r="AY4" s="12"/>
+      <c r="AZ4" s="13"/>
+      <c r="BA4" s="13"/>
+      <c r="BB4" s="14"/>
+      <c r="BD4" s="9"/>
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="9"/>
+      <c r="BH4" s="10"/>
+      <c r="BI4" s="10"/>
+      <c r="BJ4" s="10"/>
+      <c r="BK4" s="10"/>
+      <c r="BL4" s="10"/>
+      <c r="BM4" s="10"/>
+      <c r="BN4" s="10"/>
+      <c r="BO4" s="10"/>
+      <c r="BP4" s="11"/>
+      <c r="BQ4" s="11"/>
+      <c r="BR4" s="11"/>
+      <c r="BS4" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="13"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="AJ5" s="13"/>
+      <c r="AK5" s="13"/>
+      <c r="AL5" s="14"/>
+      <c r="AM5" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="AN5" s="13"/>
+      <c r="AO5" s="13"/>
+      <c r="AP5" s="15"/>
+      <c r="AQ5" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="13"/>
+      <c r="AT5" s="14"/>
+      <c r="AU5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="P3" s="7" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8" t="n">
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="13"/>
+      <c r="AX5" s="14"/>
+      <c r="AY5" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ5" s="13"/>
+      <c r="BA5" s="13"/>
+      <c r="BB5" s="14"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="10"/>
+      <c r="BI5" s="10"/>
+      <c r="BJ5" s="10"/>
+      <c r="BK5" s="10"/>
+      <c r="BL5" s="10"/>
+      <c r="BM5" s="10"/>
+      <c r="BN5" s="10"/>
+      <c r="BO5" s="10"/>
+      <c r="BP5" s="11"/>
+      <c r="BQ5" s="11"/>
+      <c r="BR5" s="11"/>
+      <c r="BS5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C6" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S6" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T6" s="20"/>
+      <c r="U6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI6" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ6" s="20"/>
+      <c r="AK6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM6" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP6" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ6" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" s="20"/>
+      <c r="AS6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV6" s="20"/>
+      <c r="AW6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C5" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="8" t="n">
-        <v>7</v>
-      </c>
+      <c r="AZ6" s="20"/>
+      <c r="BA6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB6" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="10"/>
+      <c r="BI6" s="10"/>
+      <c r="BJ6" s="10"/>
+      <c r="BK6" s="10"/>
+      <c r="BL6" s="10"/>
+      <c r="BM6" s="10"/>
+      <c r="BN6" s="10"/>
+      <c r="BO6" s="10"/>
+      <c r="BP6" s="11"/>
+      <c r="BQ6" s="11"/>
+      <c r="BR6" s="11"/>
+      <c r="BS6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C7" s="4"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="4"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="4"/>
+      <c r="AN7" s="5"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="8"/>
+      <c r="AR7" s="5"/>
+      <c r="AS7" s="5"/>
+      <c r="AT7" s="6"/>
+      <c r="AU7" s="4"/>
+      <c r="AV7" s="5"/>
+      <c r="AW7" s="5"/>
+      <c r="AX7" s="6"/>
+      <c r="AY7" s="4"/>
+      <c r="AZ7" s="5"/>
+      <c r="BA7" s="5"/>
+      <c r="BB7" s="6"/>
+      <c r="BD7" s="25"/>
+      <c r="BE7" s="25"/>
+      <c r="BF7" s="25"/>
+      <c r="BG7" s="25"/>
+      <c r="BH7" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="BI7" s="26"/>
+      <c r="BJ7" s="26"/>
+      <c r="BK7" s="26"/>
+      <c r="BL7" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="BM7" s="27"/>
+      <c r="BN7" s="27"/>
+      <c r="BO7" s="27"/>
+      <c r="BP7" s="28"/>
+      <c r="BQ7" s="28"/>
+      <c r="BR7" s="28"/>
+      <c r="BS7" s="28"/>
+    </row>
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="29" t="n">
+        <v>98</v>
+      </c>
+      <c r="U8" s="13"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="13"/>
+      <c r="AK8" s="13"/>
+      <c r="AL8" s="14"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="13"/>
+      <c r="AO8" s="13"/>
+      <c r="AP8" s="15"/>
+      <c r="AQ8" s="16"/>
+      <c r="AR8" s="13"/>
+      <c r="AS8" s="13"/>
+      <c r="AT8" s="14"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="13"/>
+      <c r="AW8" s="13"/>
+      <c r="AX8" s="14"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="13"/>
+      <c r="BA8" s="13"/>
+      <c r="BB8" s="14"/>
+      <c r="BD8" s="25"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="25"/>
+      <c r="BG8" s="25"/>
+      <c r="BH8" s="26"/>
+      <c r="BI8" s="26"/>
+      <c r="BJ8" s="26"/>
+      <c r="BK8" s="26"/>
+      <c r="BL8" s="27"/>
+      <c r="BM8" s="27"/>
+      <c r="BN8" s="27"/>
+      <c r="BO8" s="27"/>
+      <c r="BP8" s="28"/>
+      <c r="BQ8" s="28"/>
+      <c r="BR8" s="28"/>
+      <c r="BS8" s="28"/>
+    </row>
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ9" s="13"/>
+      <c r="AK9" s="13"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="13"/>
+      <c r="AP9" s="15"/>
+      <c r="AQ9" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="13"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV9" s="13"/>
+      <c r="AW9" s="13"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" s="13"/>
+      <c r="BA9" s="13"/>
+      <c r="BB9" s="14"/>
+      <c r="BD9" s="25"/>
+      <c r="BE9" s="25"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
+      <c r="BJ9" s="26"/>
+      <c r="BK9" s="26"/>
+      <c r="BL9" s="27"/>
+      <c r="BM9" s="27"/>
+      <c r="BN9" s="27"/>
+      <c r="BO9" s="27"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+    </row>
+    <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L10" s="20"/>
+      <c r="M10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T10" s="20"/>
+      <c r="U10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE10" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI10" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ10" s="20"/>
+      <c r="AK10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM10" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN10" s="20"/>
+      <c r="AO10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP10" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" s="20"/>
+      <c r="AS10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV10" s="20"/>
+      <c r="AW10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" s="20"/>
+      <c r="BA10" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD10" s="25"/>
+      <c r="BE10" s="25"/>
+      <c r="BF10" s="25"/>
+      <c r="BG10" s="25"/>
+      <c r="BH10" s="26"/>
+      <c r="BI10" s="26"/>
+      <c r="BJ10" s="26"/>
+      <c r="BK10" s="26"/>
+      <c r="BL10" s="27"/>
+      <c r="BM10" s="27"/>
+      <c r="BN10" s="27"/>
+      <c r="BO10" s="27"/>
+      <c r="BP10" s="28"/>
+      <c r="BQ10" s="28"/>
+      <c r="BR10" s="28"/>
+      <c r="BS10" s="28"/>
+    </row>
+    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="5"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="5"/>
+      <c r="AP11" s="7"/>
+      <c r="AQ11" s="8"/>
+      <c r="AR11" s="5"/>
+      <c r="AS11" s="5"/>
+      <c r="AT11" s="6"/>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="6"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="5"/>
+      <c r="BA11" s="5"/>
+      <c r="BB11" s="6"/>
+      <c r="BD11" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="BE11" s="30"/>
+      <c r="BF11" s="30"/>
+      <c r="BG11" s="30"/>
+      <c r="BH11" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="BI11" s="27"/>
+      <c r="BJ11" s="27"/>
+      <c r="BK11" s="27"/>
+      <c r="BL11" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="BM11" s="27"/>
+      <c r="BN11" s="27"/>
+      <c r="BO11" s="27"/>
+      <c r="BP11" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="BQ11" s="28"/>
+      <c r="BR11" s="28"/>
+      <c r="BS11" s="28"/>
+    </row>
+    <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="29" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="R12" s="14"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="U12" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="V12" s="14"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="29" t="n">
+        <v>93</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="12"/>
+      <c r="AB12" s="29" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC12" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="12"/>
+      <c r="AF12" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AG12" s="13"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="29" t="n">
+        <v>96</v>
+      </c>
+      <c r="AK12" s="13"/>
+      <c r="AL12" s="14"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="13"/>
+      <c r="AO12" s="13"/>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="16"/>
+      <c r="AR12" s="13"/>
+      <c r="AS12" s="13"/>
+      <c r="AT12" s="14"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="13"/>
+      <c r="AW12" s="13"/>
+      <c r="AX12" s="14"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="13"/>
+      <c r="BA12" s="13"/>
+      <c r="BB12" s="14"/>
+      <c r="BD12" s="30"/>
+      <c r="BE12" s="30"/>
+      <c r="BF12" s="30"/>
+      <c r="BG12" s="30"/>
+      <c r="BH12" s="27"/>
+      <c r="BI12" s="27"/>
+      <c r="BJ12" s="27"/>
+      <c r="BK12" s="27"/>
+      <c r="BL12" s="27"/>
+      <c r="BM12" s="27"/>
+      <c r="BN12" s="27"/>
+      <c r="BO12" s="27"/>
+      <c r="BP12" s="28"/>
+      <c r="BQ12" s="28"/>
+      <c r="BR12" s="28"/>
+      <c r="BS12" s="28"/>
+    </row>
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="14"/>
+      <c r="S13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="14"/>
+      <c r="W13" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" s="13"/>
+      <c r="AK13" s="13"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN13" s="13"/>
+      <c r="AO13" s="13"/>
+      <c r="AP13" s="15"/>
+      <c r="AQ13" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" s="13"/>
+      <c r="AS13" s="13"/>
+      <c r="AT13" s="14"/>
+      <c r="AU13" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV13" s="13"/>
+      <c r="AW13" s="13"/>
+      <c r="AX13" s="14"/>
+      <c r="AY13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" s="13"/>
+      <c r="BA13" s="13"/>
+      <c r="BB13" s="14"/>
+      <c r="BD13" s="30"/>
+      <c r="BE13" s="30"/>
+      <c r="BF13" s="30"/>
+      <c r="BG13" s="30"/>
+      <c r="BH13" s="27"/>
+      <c r="BI13" s="27"/>
+      <c r="BJ13" s="27"/>
+      <c r="BK13" s="27"/>
+      <c r="BL13" s="27"/>
+      <c r="BM13" s="27"/>
+      <c r="BN13" s="27"/>
+      <c r="BO13" s="27"/>
+      <c r="BP13" s="28"/>
+      <c r="BQ13" s="28"/>
+      <c r="BR13" s="28"/>
+      <c r="BS13" s="28"/>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C14" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T14" s="20"/>
+      <c r="U14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="V14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ14" s="20"/>
+      <c r="AK14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN14" s="20"/>
+      <c r="AO14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP14" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ14" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" s="20"/>
+      <c r="AS14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV14" s="20"/>
+      <c r="AW14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" s="20"/>
+      <c r="BA14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD14" s="30"/>
+      <c r="BE14" s="30"/>
+      <c r="BF14" s="30"/>
+      <c r="BG14" s="30"/>
+      <c r="BH14" s="27"/>
+      <c r="BI14" s="27"/>
+      <c r="BJ14" s="27"/>
+      <c r="BK14" s="27"/>
+      <c r="BL14" s="27"/>
+      <c r="BM14" s="27"/>
+      <c r="BN14" s="27"/>
+      <c r="BO14" s="27"/>
+      <c r="BP14" s="28"/>
+      <c r="BQ14" s="28"/>
+      <c r="BR14" s="28"/>
+      <c r="BS14" s="28"/>
+    </row>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="4"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="4"/>
+      <c r="AJ15" s="5"/>
+      <c r="AK15" s="5"/>
+      <c r="AL15" s="6"/>
+      <c r="AM15" s="4"/>
+      <c r="AN15" s="5"/>
+      <c r="AO15" s="5"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="8"/>
+      <c r="AR15" s="5"/>
+      <c r="AS15" s="5"/>
+      <c r="AT15" s="6"/>
+      <c r="AU15" s="4"/>
+      <c r="AV15" s="5"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="6"/>
+      <c r="AY15" s="4"/>
+      <c r="AZ15" s="5"/>
+      <c r="BA15" s="5"/>
+      <c r="BB15" s="6"/>
+      <c r="BD15" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="BE15" s="31"/>
+      <c r="BF15" s="31"/>
+      <c r="BG15" s="31"/>
+      <c r="BH15" s="32"/>
+      <c r="BI15" s="32"/>
+      <c r="BJ15" s="32"/>
+      <c r="BK15" s="32"/>
+      <c r="BL15" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="BM15" s="33"/>
+      <c r="BN15" s="33"/>
+      <c r="BO15" s="33"/>
+      <c r="BP15" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="BQ15" s="34"/>
+      <c r="BR15" s="34"/>
+      <c r="BS15" s="34"/>
+    </row>
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="29" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q16" s="35" t="n">
+        <v>42</v>
+      </c>
+      <c r="R16" s="14"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="29" t="n">
+        <v>84</v>
+      </c>
+      <c r="U16" s="35" t="n">
+        <v>43</v>
+      </c>
+      <c r="V16" s="14"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="29" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="29" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC16" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD16" s="14"/>
+      <c r="AE16" s="12"/>
+      <c r="AF16" s="29" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG16" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH16" s="14"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="29" t="n">
+        <v>88</v>
+      </c>
+      <c r="AK16" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="AL16" s="14"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="29" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO16" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="AP16" s="15"/>
+      <c r="AQ16" s="16"/>
+      <c r="AR16" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS16" s="35"/>
+      <c r="AT16" s="14"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="13"/>
+      <c r="AW16" s="13"/>
+      <c r="AX16" s="14"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="13"/>
+      <c r="BA16" s="13"/>
+      <c r="BB16" s="14"/>
+      <c r="BD16" s="31"/>
+      <c r="BE16" s="31"/>
+      <c r="BF16" s="31"/>
+      <c r="BG16" s="31"/>
+      <c r="BH16" s="32"/>
+      <c r="BI16" s="32"/>
+      <c r="BJ16" s="32"/>
+      <c r="BK16" s="32"/>
+      <c r="BL16" s="33"/>
+      <c r="BM16" s="33"/>
+      <c r="BN16" s="33"/>
+      <c r="BO16" s="33"/>
+      <c r="BP16" s="34"/>
+      <c r="BQ16" s="34"/>
+      <c r="BR16" s="34"/>
+      <c r="BS16" s="34"/>
+    </row>
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="14"/>
+      <c r="S17" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="14"/>
+      <c r="W17" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF17" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG17" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH17" s="14"/>
+      <c r="AI17" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ17" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK17" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL17" s="14"/>
+      <c r="AM17" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" s="13"/>
+      <c r="AS17" s="35"/>
+      <c r="AT17" s="14"/>
+      <c r="AU17" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV17" s="13"/>
+      <c r="AW17" s="13"/>
+      <c r="AX17" s="14"/>
+      <c r="AY17" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ17" s="13"/>
+      <c r="BA17" s="13"/>
+      <c r="BB17" s="14"/>
+      <c r="BD17" s="31"/>
+      <c r="BE17" s="31"/>
+      <c r="BF17" s="31"/>
+      <c r="BG17" s="31"/>
+      <c r="BH17" s="32"/>
+      <c r="BI17" s="32"/>
+      <c r="BJ17" s="32"/>
+      <c r="BK17" s="32"/>
+      <c r="BL17" s="33"/>
+      <c r="BM17" s="33"/>
+      <c r="BN17" s="33"/>
+      <c r="BO17" s="33"/>
+      <c r="BP17" s="34"/>
+      <c r="BQ17" s="34"/>
+      <c r="BR17" s="34"/>
+      <c r="BS17" s="34"/>
+    </row>
+    <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L18" s="20"/>
+      <c r="M18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="S18" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T18" s="20"/>
+      <c r="U18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA18" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE18" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI18" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ18" s="20"/>
+      <c r="AK18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM18" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN18" s="20"/>
+      <c r="AO18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP18" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ18" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR18" s="20"/>
+      <c r="AS18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU18" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV18" s="20"/>
+      <c r="AW18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" s="20"/>
+      <c r="BA18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD18" s="31"/>
+      <c r="BE18" s="31"/>
+      <c r="BF18" s="31"/>
+      <c r="BG18" s="31"/>
+      <c r="BH18" s="32"/>
+      <c r="BI18" s="32"/>
+      <c r="BJ18" s="32"/>
+      <c r="BK18" s="32"/>
+      <c r="BL18" s="33"/>
+      <c r="BM18" s="33"/>
+      <c r="BN18" s="33"/>
+      <c r="BO18" s="33"/>
+      <c r="BP18" s="34"/>
+      <c r="BQ18" s="34"/>
+      <c r="BR18" s="34"/>
+      <c r="BS18" s="34"/>
+    </row>
+    <row r="19" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="4"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="6"/>
+      <c r="AI19" s="4"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="5"/>
+      <c r="AL19" s="6"/>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="5"/>
+      <c r="AO19" s="5"/>
+      <c r="AP19" s="7"/>
+      <c r="AQ19" s="8"/>
+      <c r="AR19" s="5"/>
+      <c r="AS19" s="5"/>
+      <c r="AT19" s="6"/>
+      <c r="AU19" s="4"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="6"/>
+      <c r="AY19" s="4"/>
+      <c r="AZ19" s="5"/>
+      <c r="BA19" s="5"/>
+      <c r="BB19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="29" t="n">
         <v>74</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="Q20" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="R20" s="14"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="29" t="n">
         <v>75</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="U20" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="V20" s="14"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="29" t="n">
         <v>76</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="Y20" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="29" t="n">
         <v>77</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="AC20" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD20" s="14"/>
+      <c r="AE20" s="12"/>
+      <c r="AF20" s="29" t="n">
         <v>78</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="AG20" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="AH20" s="14"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="29" t="n">
         <v>79</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="AK20" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL20" s="14"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="AO20" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="AP20" s="15"/>
+      <c r="AQ20" s="16"/>
+      <c r="AR20" s="29" t="n">
         <v>81</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="AS20" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AT20" s="14"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="29" t="n">
         <v>82</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="AW20" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="AX20" s="14"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="13"/>
+      <c r="BA20" s="13"/>
+      <c r="BB20" s="14"/>
+      <c r="BD20" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="BE20" s="36"/>
+      <c r="BF20" s="36"/>
+      <c r="BG20" s="36"/>
+      <c r="BH20" s="36"/>
+    </row>
+    <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="14"/>
+      <c r="S21" s="17" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="8" t="n">
+      <c r="T21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="14"/>
+      <c r="W21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="n">
+      <c r="AB21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="14"/>
+      <c r="AI21" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL21" s="14"/>
+      <c r="AM21" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN21" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP21" s="15"/>
+      <c r="AQ21" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS21" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT21" s="14"/>
+      <c r="AU21" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV21" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW21" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX21" s="14"/>
+      <c r="AY21" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ21" s="13"/>
+      <c r="BA21" s="13"/>
+      <c r="BB21" s="14"/>
+      <c r="BD21" s="36"/>
+      <c r="BE21" s="36"/>
+      <c r="BF21" s="36"/>
+      <c r="BG21" s="36"/>
+      <c r="BH21" s="36"/>
+    </row>
+    <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="C22" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L22" s="20"/>
+      <c r="M22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T22" s="20"/>
+      <c r="U22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="V22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="W22" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI22" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ22" s="20"/>
+      <c r="AK22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN22" s="20"/>
+      <c r="AO22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP22" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ22" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" s="20"/>
+      <c r="AS22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU22" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV22" s="20"/>
+      <c r="AW22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY22" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" s="20"/>
+      <c r="BA22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD22" s="36"/>
+      <c r="BE22" s="36"/>
+      <c r="BF22" s="36"/>
+      <c r="BG22" s="36"/>
+      <c r="BH22" s="36"/>
+    </row>
+    <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="5"/>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="5"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="5"/>
+      <c r="AO23" s="5"/>
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="8"/>
+      <c r="AR23" s="5"/>
+      <c r="AS23" s="5"/>
+      <c r="AT23" s="6"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="5"/>
+      <c r="AW23" s="5"/>
+      <c r="AX23" s="6"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="5"/>
+      <c r="BA23" s="5"/>
+      <c r="BB23" s="6"/>
+      <c r="BD23" s="36"/>
+      <c r="BE23" s="36"/>
+      <c r="BF23" s="36"/>
+      <c r="BG23" s="36"/>
+      <c r="BH23" s="36"/>
+    </row>
+    <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="29" t="n">
         <v>66</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="U24" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="V24" s="14"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="29" t="n">
         <v>67</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="Y24" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="12"/>
+      <c r="AB24" s="29" t="n">
         <v>68</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="AC24" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD24" s="14"/>
+      <c r="AE24" s="12"/>
+      <c r="AF24" s="29" t="n">
         <v>69</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="AG24" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH24" s="14"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="29" t="n">
         <v>70</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="AK24" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="AL24" s="14"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="29" t="n">
         <v>71</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="AO24" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="16"/>
+      <c r="AR24" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="AS24" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT24" s="14"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="29" t="n">
         <v>73</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="AW24" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="AX24" s="14"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="13"/>
+      <c r="BA24" s="13"/>
+      <c r="BB24" s="14"/>
+      <c r="BD24" s="36"/>
+      <c r="BE24" s="36"/>
+      <c r="BF24" s="36"/>
+      <c r="BG24" s="36"/>
+      <c r="BH24" s="36"/>
+    </row>
+    <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="17" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C9" s="8" t="n">
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="14"/>
+      <c r="W25" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="n">
+      <c r="X25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB25" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD25" s="14"/>
+      <c r="AE25" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF25" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG25" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH25" s="14"/>
+      <c r="AI25" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL25" s="14"/>
+      <c r="AM25" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="15"/>
+      <c r="AQ25" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR25" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS25" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT25" s="14"/>
+      <c r="AU25" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV25" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW25" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX25" s="14"/>
+      <c r="AY25" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ25" s="13"/>
+      <c r="BA25" s="13"/>
+      <c r="BB25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C26" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L26" s="20"/>
+      <c r="M26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T26" s="20"/>
+      <c r="U26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE26" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI26" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ26" s="20"/>
+      <c r="AK26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM26" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN26" s="20"/>
+      <c r="AO26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP26" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ26" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR26" s="20"/>
+      <c r="AS26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU26" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV26" s="20"/>
+      <c r="AW26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY26" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" s="20"/>
+      <c r="BA26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD26" s="38"/>
+      <c r="BE26" s="38"/>
+      <c r="BF26" s="38"/>
+      <c r="BG26" s="38"/>
+    </row>
+    <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="4"/>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AH27" s="6"/>
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="5"/>
+      <c r="AL27" s="6"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="5"/>
+      <c r="AP27" s="7"/>
+      <c r="AQ27" s="8"/>
+      <c r="AR27" s="5"/>
+      <c r="AS27" s="5"/>
+      <c r="AT27" s="6"/>
+      <c r="AU27" s="4"/>
+      <c r="AV27" s="5"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="6"/>
+      <c r="AY27" s="4"/>
+      <c r="AZ27" s="5"/>
+      <c r="BA27" s="5"/>
+      <c r="BB27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="29" t="n">
         <v>57</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="U28" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="V28" s="14"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="29" t="n">
         <v>58</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="Y28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="12"/>
+      <c r="AB28" s="29" t="n">
         <v>59</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="AC28" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="12"/>
+      <c r="AF28" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="AG28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH28" s="14"/>
+      <c r="AI28" s="12"/>
+      <c r="AJ28" s="29" t="n">
         <v>61</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="AK28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" s="14"/>
+      <c r="AM28" s="12"/>
+      <c r="AN28" s="29" t="n">
         <v>62</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="AO28" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP28" s="15"/>
+      <c r="AQ28" s="16"/>
+      <c r="AR28" s="29" t="n">
         <v>63</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="AS28" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="AT28" s="14"/>
+      <c r="AU28" s="12"/>
+      <c r="AV28" s="29" t="n">
         <v>64</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="AW28" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="AX28" s="14"/>
+      <c r="AY28" s="12"/>
+      <c r="AZ28" s="29" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA28" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB28" s="14"/>
+      <c r="BD28" s="39" t="s">
+        <v>490</v>
+      </c>
+      <c r="BE28" s="39"/>
+      <c r="BF28" s="39"/>
+      <c r="BG28" s="39"/>
+      <c r="BH28" s="39"/>
+      <c r="BI28" s="39"/>
+      <c r="BJ28" s="39"/>
+      <c r="BK28" s="39"/>
+      <c r="BL28" s="39"/>
+      <c r="BM28" s="39"/>
+      <c r="BN28" s="39"/>
+      <c r="BO28" s="39"/>
+      <c r="BP28" s="39"/>
+      <c r="BQ28" s="39"/>
+      <c r="BR28" s="39"/>
+      <c r="BS28" s="39"/>
+    </row>
+    <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="U29" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="V29" s="14"/>
+      <c r="W29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB29" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF29" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="14"/>
+      <c r="AI29" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL29" s="14"/>
+      <c r="AM29" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN29" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO29" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP29" s="15"/>
+      <c r="AQ29" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT29" s="14"/>
+      <c r="AU29" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV29" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX29" s="14"/>
+      <c r="AY29" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ29" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA29" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB29" s="14"/>
+      <c r="BD29" s="39"/>
+      <c r="BE29" s="39"/>
+      <c r="BF29" s="39"/>
+      <c r="BG29" s="39"/>
+      <c r="BH29" s="39"/>
+      <c r="BI29" s="39"/>
+      <c r="BJ29" s="39"/>
+      <c r="BK29" s="39"/>
+      <c r="BL29" s="39"/>
+      <c r="BM29" s="39"/>
+      <c r="BN29" s="39"/>
+      <c r="BO29" s="39"/>
+      <c r="BP29" s="39"/>
+      <c r="BQ29" s="39"/>
+      <c r="BR29" s="39"/>
+      <c r="BS29" s="39"/>
+    </row>
+    <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C30" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="G30" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="K30" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="L30" s="41"/>
+      <c r="M30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="S30" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="W30" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA30" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE30" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI30" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ30" s="41"/>
+      <c r="AK30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM30" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN30" s="41"/>
+      <c r="AO30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP30" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="AQ30" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR30" s="41"/>
+      <c r="AS30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="AU30" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV30" s="41"/>
+      <c r="AW30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY30" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" s="41"/>
+      <c r="BA30" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB30" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C31" s="46"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="47"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="47"/>
+      <c r="U31" s="47"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="47"/>
+      <c r="Y31" s="47"/>
+      <c r="Z31" s="48"/>
+      <c r="AA31" s="46"/>
+      <c r="AB31" s="47"/>
+      <c r="AC31" s="47"/>
+      <c r="AD31" s="48"/>
+      <c r="AE31" s="46"/>
+      <c r="AF31" s="47"/>
+      <c r="AG31" s="47"/>
+      <c r="AH31" s="48"/>
+      <c r="AI31" s="46"/>
+      <c r="AJ31" s="47"/>
+      <c r="AK31" s="47"/>
+      <c r="AL31" s="48"/>
+      <c r="AM31" s="46"/>
+      <c r="AN31" s="47"/>
+      <c r="AO31" s="47"/>
+      <c r="AP31" s="49"/>
+      <c r="AQ31" s="50"/>
+      <c r="AR31" s="47"/>
+      <c r="AS31" s="47"/>
+      <c r="AT31" s="48"/>
+      <c r="AU31" s="46"/>
+      <c r="AV31" s="47"/>
+      <c r="AW31" s="47"/>
+      <c r="AX31" s="48"/>
+      <c r="AY31" s="46"/>
+      <c r="AZ31" s="47"/>
+      <c r="BA31" s="47"/>
+      <c r="BB31" s="48"/>
+    </row>
+    <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C32" s="12"/>
+      <c r="D32" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="I32" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="29" t="n">
         <v>46</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="M32" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="N32" s="14"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="29" t="n">
         <v>47</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="Q32" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="R32" s="14"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="U32" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="14"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="29" t="n">
         <v>49</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="Y32" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="AC32" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="12"/>
+      <c r="AF32" s="29" t="n">
         <v>51</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="AG32" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH32" s="14"/>
+      <c r="AI32" s="12"/>
+      <c r="AJ32" s="29" t="n">
         <v>52</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="AK32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL32" s="14"/>
+      <c r="AM32" s="12"/>
+      <c r="AN32" s="29" t="n">
         <v>53</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="AO32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" s="15"/>
+      <c r="AQ32" s="16"/>
+      <c r="AR32" s="29" t="n">
         <v>54</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="AS32" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT32" s="14"/>
+      <c r="AU32" s="12"/>
+      <c r="AV32" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C11" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="AW32" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="AX32" s="14"/>
+      <c r="AY32" s="12"/>
+      <c r="AZ32" s="29" t="n">
+        <v>56</v>
+      </c>
+      <c r="BA32" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="14"/>
+      <c r="K33" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="N33" s="14"/>
+      <c r="O33" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="R33" s="14"/>
+      <c r="S33" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="14"/>
+      <c r="W33" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF33" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG33" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH33" s="14"/>
+      <c r="AI33" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ33" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK33" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL33" s="14"/>
+      <c r="AM33" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN33" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP33" s="15"/>
+      <c r="AQ33" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR33" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT33" s="14"/>
+      <c r="AU33" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV33" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX33" s="14"/>
+      <c r="AY33" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G34" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="H34" s="20"/>
+      <c r="I34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L34" s="20"/>
+      <c r="M34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O34" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S34" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T34" s="20"/>
+      <c r="U34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W34" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA34" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE34" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF34" s="20"/>
+      <c r="AG34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI34" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ34" s="20"/>
+      <c r="AK34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AM34" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN34" s="20"/>
+      <c r="AO34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP34" s="23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AQ34" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR34" s="20"/>
+      <c r="AS34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU34" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV34" s="20"/>
+      <c r="AW34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX34" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AY34" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ34" s="20"/>
+      <c r="BA34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB34" s="22" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="6"/>
+      <c r="W35" s="4"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="5"/>
+      <c r="AC35" s="5"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="4"/>
+      <c r="AF35" s="5"/>
+      <c r="AG35" s="5"/>
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="4"/>
+      <c r="AJ35" s="5"/>
+      <c r="AK35" s="5"/>
+      <c r="AL35" s="6"/>
+      <c r="AM35" s="4"/>
+      <c r="AN35" s="5"/>
+      <c r="AO35" s="5"/>
+      <c r="AP35" s="7"/>
+      <c r="AQ35" s="8"/>
+      <c r="AR35" s="5"/>
+      <c r="AS35" s="5"/>
+      <c r="AT35" s="6"/>
+      <c r="AU35" s="4"/>
+      <c r="AV35" s="5"/>
+      <c r="AW35" s="5"/>
+      <c r="AX35" s="6"/>
+      <c r="AY35" s="4"/>
+      <c r="AZ35" s="5"/>
+      <c r="BA35" s="5"/>
+      <c r="BB35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="12"/>
+      <c r="D36" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="J36" s="14"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="29" t="n">
         <v>33</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="M36" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="N36" s="14"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="Q36" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" s="14"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="U36" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V36" s="14"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="Y36" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="29" t="n">
         <v>37</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="AC36" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="12"/>
+      <c r="AF36" s="29" t="n">
         <v>38</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="AG36" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH36" s="14"/>
+      <c r="AI36" s="12"/>
+      <c r="AJ36" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="AK36" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL36" s="14"/>
+      <c r="AM36" s="12"/>
+      <c r="AN36" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="AO36" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP36" s="15"/>
+      <c r="AQ36" s="16"/>
+      <c r="AR36" s="29" t="n">
         <v>41</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="AS36" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="AT36" s="14"/>
+      <c r="AU36" s="12"/>
+      <c r="AV36" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="AW36" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="AX36" s="14"/>
+      <c r="AY36" s="12"/>
+      <c r="AZ36" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="BA36" s="13"/>
+      <c r="BB36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="N37" s="14"/>
+      <c r="O37" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q37" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="R37" s="14"/>
+      <c r="S37" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="14"/>
+      <c r="W37" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X37" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y37" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB37" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="14"/>
+      <c r="AI37" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ37" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK37" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL37" s="14"/>
+      <c r="AM37" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN37" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO37" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP37" s="15"/>
+      <c r="AQ37" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR37" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS37" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT37" s="14"/>
+      <c r="AU37" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV37" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW37" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX37" s="14"/>
+      <c r="AY37" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ37" s="13"/>
+      <c r="BA37" s="13"/>
+      <c r="BB37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C38" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H38" s="20"/>
+      <c r="I38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L38" s="20"/>
+      <c r="M38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O38" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S38" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T38" s="20"/>
+      <c r="U38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W38" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA38" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE38" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF38" s="20"/>
+      <c r="AG38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI38" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ38" s="20"/>
+      <c r="AK38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM38" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN38" s="20"/>
+      <c r="AO38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP38" s="23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AQ38" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR38" s="20"/>
+      <c r="AS38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AU38" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV38" s="20"/>
+      <c r="AW38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX38" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AY38" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ38" s="20"/>
+      <c r="BA38" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB38" s="22" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="5"/>
+      <c r="AC39" s="5"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="5"/>
+      <c r="AG39" s="5"/>
+      <c r="AH39" s="6"/>
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="5"/>
+      <c r="AK39" s="5"/>
+      <c r="AL39" s="6"/>
+      <c r="AM39" s="4"/>
+      <c r="AN39" s="5"/>
+      <c r="AO39" s="5"/>
+      <c r="AP39" s="7"/>
+      <c r="AQ39" s="8"/>
+      <c r="AR39" s="5"/>
+      <c r="AS39" s="5"/>
+      <c r="AT39" s="6"/>
+      <c r="AU39" s="4"/>
+      <c r="AV39" s="5"/>
+      <c r="AW39" s="5"/>
+      <c r="AX39" s="6"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="5"/>
+      <c r="BB39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C40" s="12"/>
+      <c r="D40" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="I40" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="J40" s="14"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="M40" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="N40" s="14"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="29" t="n">
         <v>21</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="Q40" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="R40" s="14"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="U40" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="V40" s="14"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="Y40" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z40" s="14"/>
+      <c r="AA40" s="12"/>
+      <c r="AB40" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="AC40" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD40" s="14"/>
+      <c r="AE40" s="12"/>
+      <c r="AF40" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="AG40" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH40" s="14"/>
+      <c r="AI40" s="12"/>
+      <c r="AJ40" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="AK40" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL40" s="14"/>
+      <c r="AM40" s="12"/>
+      <c r="AN40" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="AO40" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP40" s="15"/>
+      <c r="AQ40" s="16"/>
+      <c r="AR40" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="AS40" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="AT40" s="14"/>
+      <c r="AU40" s="12"/>
+      <c r="AV40" s="29" t="n">
         <v>29</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C13" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="AW40" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="AX40" s="14"/>
+      <c r="AY40" s="12"/>
+      <c r="AZ40" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA40" s="13"/>
+      <c r="BB40" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="14"/>
+      <c r="K41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="N41" s="14"/>
+      <c r="O41" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P41" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q41" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R41" s="14"/>
+      <c r="S41" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="U41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V41" s="14"/>
+      <c r="W41" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X41" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y41" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" s="14"/>
+      <c r="AE41" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="AF41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="14"/>
+      <c r="AI41" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="AJ41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="14"/>
+      <c r="AM41" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="AN41" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO41" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP41" s="15"/>
+      <c r="AQ41" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="AR41" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS41" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT41" s="14"/>
+      <c r="AU41" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="AV41" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW41" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX41" s="14"/>
+      <c r="AY41" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="AZ41" s="13"/>
+      <c r="BA41" s="13"/>
+      <c r="BB41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C42" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D42" s="20"/>
+      <c r="E42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H42" s="20"/>
+      <c r="I42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L42" s="20"/>
+      <c r="M42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O42" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="S42" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T42" s="20"/>
+      <c r="U42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W42" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AA42" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AE42" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF42" s="20"/>
+      <c r="AG42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI42" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ42" s="20"/>
+      <c r="AK42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AM42" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN42" s="20"/>
+      <c r="AO42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP42" s="23" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AQ42" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR42" s="20"/>
+      <c r="AS42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AU42" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV42" s="20"/>
+      <c r="AW42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX42" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AY42" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ42" s="20"/>
+      <c r="BA42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB42" s="22" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="5"/>
+      <c r="AC43" s="5"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="5"/>
+      <c r="AG43" s="5"/>
+      <c r="AH43" s="6"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="5"/>
+      <c r="AK43" s="5"/>
+      <c r="AL43" s="6"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="5"/>
+      <c r="AO43" s="5"/>
+      <c r="AP43" s="7"/>
+      <c r="AQ43" s="8"/>
+      <c r="AR43" s="5"/>
+      <c r="AS43" s="5"/>
+      <c r="AT43" s="6"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="5"/>
+      <c r="AW43" s="5"/>
+      <c r="AX43" s="6"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="5"/>
+      <c r="BB43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C44" s="12"/>
+      <c r="D44" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="J44" s="14"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="N44" s="14"/>
+      <c r="O44" s="12"/>
+      <c r="P44" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="R44" s="14"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="U44" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="V44" s="14"/>
+      <c r="W44" s="12"/>
+      <c r="X44" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y44" s="13"/>
+      <c r="Z44" s="14"/>
+      <c r="AA44" s="12"/>
+      <c r="AB44" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC44" s="13"/>
+      <c r="AD44" s="14"/>
+      <c r="AE44" s="12"/>
+      <c r="AF44" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG44" s="13"/>
+      <c r="AH44" s="14"/>
+      <c r="AI44" s="12"/>
+      <c r="AJ44" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="AK44" s="13"/>
+      <c r="AL44" s="14"/>
+      <c r="AM44" s="12"/>
+      <c r="AN44" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="AO44" s="13"/>
+      <c r="AP44" s="15"/>
+      <c r="AQ44" s="16"/>
+      <c r="AR44" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="AS44" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="AT44" s="14"/>
+      <c r="AU44" s="12"/>
+      <c r="AV44" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="AW44" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX44" s="14"/>
+      <c r="AY44" s="12"/>
+      <c r="AZ44" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA44" s="13"/>
+      <c r="BB44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J45" s="14"/>
+      <c r="K45" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N45" s="14"/>
+      <c r="O45" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P45" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" s="14"/>
+      <c r="S45" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="14"/>
+      <c r="W45" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="14"/>
+      <c r="AA45" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="14"/>
+      <c r="AE45" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="14"/>
+      <c r="AI45" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="14"/>
+      <c r="AM45" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="15"/>
+      <c r="AQ45" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="14"/>
+      <c r="AU45" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV45" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW45" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX45" s="14"/>
+      <c r="AY45" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ45" s="13"/>
+      <c r="BA45" s="13"/>
+      <c r="BB45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C46" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D46" s="20"/>
+      <c r="E46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H46" s="20"/>
+      <c r="I46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L46" s="20"/>
+      <c r="M46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O46" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="S46" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T46" s="20"/>
+      <c r="U46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="W46" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="X46" s="20"/>
+      <c r="Y46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA46" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="AB46" s="20"/>
+      <c r="AC46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AE46" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="AF46" s="20"/>
+      <c r="AG46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AI46" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="AJ46" s="20"/>
+      <c r="AK46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AM46" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="AN46" s="20"/>
+      <c r="AO46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" s="23" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AQ46" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="AR46" s="20"/>
+      <c r="AS46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AU46" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="P14" s="10" t="n">
+      <c r="AV46" s="20"/>
+      <c r="AW46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AY46" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ46" s="20"/>
+      <c r="BA46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB46" s="22" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="6"/>
+      <c r="W47" s="4"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="5"/>
+      <c r="AC47" s="5"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="4"/>
+      <c r="AF47" s="5"/>
+      <c r="AG47" s="5"/>
+      <c r="AH47" s="6"/>
+      <c r="AI47" s="4"/>
+      <c r="AJ47" s="5"/>
+      <c r="AK47" s="5"/>
+      <c r="AL47" s="6"/>
+      <c r="AM47" s="4"/>
+      <c r="AN47" s="5"/>
+      <c r="AO47" s="5"/>
+      <c r="AP47" s="7"/>
+      <c r="AQ47" s="8"/>
+      <c r="AR47" s="5"/>
+      <c r="AS47" s="5"/>
+      <c r="AT47" s="6"/>
+      <c r="AU47" s="4"/>
+      <c r="AV47" s="5"/>
+      <c r="AW47" s="5"/>
+      <c r="AX47" s="6"/>
+      <c r="AY47" s="4"/>
+      <c r="AZ47" s="5"/>
+      <c r="BA47" s="5"/>
+      <c r="BB47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C48" s="12"/>
+      <c r="D48" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="13"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="13"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="12"/>
+      <c r="P48" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="14"/>
+      <c r="S48" s="12"/>
+      <c r="T48" s="37"/>
+      <c r="U48" s="13"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="12"/>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="13"/>
+      <c r="Z48" s="14"/>
+      <c r="AA48" s="12"/>
+      <c r="AB48" s="13"/>
+      <c r="AC48" s="13"/>
+      <c r="AD48" s="14"/>
+      <c r="AE48" s="12"/>
+      <c r="AF48" s="13"/>
+      <c r="AG48" s="13"/>
+      <c r="AH48" s="14"/>
+      <c r="AI48" s="12"/>
+      <c r="AJ48" s="13"/>
+      <c r="AK48" s="13"/>
+      <c r="AL48" s="14"/>
+      <c r="AM48" s="12"/>
+      <c r="AN48" s="13"/>
+      <c r="AO48" s="13"/>
+      <c r="AP48" s="15"/>
+      <c r="AQ48" s="16"/>
+      <c r="AR48" s="13"/>
+      <c r="AS48" s="13"/>
+      <c r="AT48" s="14"/>
+      <c r="AU48" s="12"/>
+      <c r="AV48" s="13"/>
+      <c r="AW48" s="13"/>
+      <c r="AX48" s="14"/>
+      <c r="AY48" s="12"/>
+      <c r="AZ48" s="13"/>
+      <c r="BA48" s="13"/>
+      <c r="BB48" s="14"/>
+    </row>
+    <row r="49" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" s="13"/>
+      <c r="U49" s="13"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="13"/>
+      <c r="Z49" s="14"/>
+      <c r="AA49" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB49" s="13"/>
+      <c r="AC49" s="13"/>
+      <c r="AD49" s="14"/>
+      <c r="AE49" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF49" s="13"/>
+      <c r="AG49" s="13"/>
+      <c r="AH49" s="14"/>
+      <c r="AI49" s="17" t="n">
         <v>8</v>
       </c>
+      <c r="AJ49" s="13"/>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="14"/>
+      <c r="AM49" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN49" s="13"/>
+      <c r="AO49" s="13"/>
+      <c r="AP49" s="15"/>
+      <c r="AQ49" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR49" s="13"/>
+      <c r="AS49" s="13"/>
+      <c r="AT49" s="14"/>
+      <c r="AU49" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV49" s="13"/>
+      <c r="AW49" s="13"/>
+      <c r="AX49" s="14"/>
+      <c r="AY49" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ49" s="13"/>
+      <c r="BA49" s="13"/>
+      <c r="BB49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C50" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D50" s="20"/>
+      <c r="E50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H50" s="20"/>
+      <c r="I50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L50" s="20"/>
+      <c r="M50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O50" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="S50" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T50" s="20"/>
+      <c r="U50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="W50" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AA50" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AE50" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF50" s="20"/>
+      <c r="AG50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AI50" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ50" s="20"/>
+      <c r="AK50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AM50" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN50" s="20"/>
+      <c r="AO50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AQ50" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR50" s="20"/>
+      <c r="AS50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AU50" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV50" s="20"/>
+      <c r="AW50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AY50" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ50" s="20"/>
+      <c r="BA50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" s="22" t="n">
+        <v>-10</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="BD3:BG6"/>
+    <mergeCell ref="BH3:BK6"/>
+    <mergeCell ref="BL3:BO6"/>
+    <mergeCell ref="BP3:BS6"/>
+    <mergeCell ref="BD7:BG10"/>
+    <mergeCell ref="BH7:BK10"/>
+    <mergeCell ref="BL7:BO10"/>
+    <mergeCell ref="BP7:BS10"/>
+    <mergeCell ref="BD11:BG14"/>
+    <mergeCell ref="BH11:BK14"/>
+    <mergeCell ref="BL11:BO14"/>
+    <mergeCell ref="BP11:BS14"/>
+    <mergeCell ref="BD15:BG18"/>
+    <mergeCell ref="BH15:BK18"/>
+    <mergeCell ref="BL15:BO18"/>
+    <mergeCell ref="BP15:BS18"/>
+    <mergeCell ref="BD20:BH24"/>
+    <mergeCell ref="BD28:BS29"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -24585,5 +29527,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="494">
   <si>
     <t xml:space="preserve">Station_1</t>
   </si>
@@ -1247,16 +1247,25 @@
     <t xml:space="preserve">alder, not diseased tree</t>
   </si>
   <si>
-    <t xml:space="preserve">Grid</t>
-  </si>
-  <si>
     <t xml:space="preserve">None</t>
   </si>
   <si>
     <t xml:space="preserve">none</t>
   </si>
   <si>
+    <t xml:space="preserve">“done other book” not found</t>
+  </si>
+  <si>
     <t xml:space="preserve">hemlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">partially disturbed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">might be duplicated in plot 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fungi?</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
@@ -23276,33 +23285,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="4.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="4.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="5.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="4.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="9.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="0" width="4.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="10.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="5.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="6.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="10.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="6.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="15.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23321,76 +23312,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="AA1" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="0" t="s">
         <v>28</v>
       </c>
     </row>
@@ -23410,12 +23335,11 @@
       <c r="E2" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="Z2" s="1"/>
-      <c r="AC2" s="0" t="s">
-        <v>373</v>
+      <c r="G2" s="0" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23434,7 +23358,7 @@
       <c r="E3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" s="0" t="n">
+      <c r="F3" s="0" t="n">
         <v>64</v>
       </c>
     </row>
@@ -23454,7 +23378,7 @@
       <c r="E4" s="0" t="n">
         <v>264</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="F4" s="0" t="n">
         <v>65</v>
       </c>
     </row>
@@ -23474,11 +23398,11 @@
       <c r="E5" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="F5" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="AC5" s="0" t="s">
-        <v>374</v>
+      <c r="G5" s="0" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23497,8 +23421,774 @@
       <c r="E6" s="0" t="n">
         <v>267</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="F6" s="0" t="n">
         <v>69</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F39" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -23517,7 +24207,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23720,6 +24410,2364 @@
       </c>
       <c r="D14" s="0" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>194</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>234</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>235</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>354</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>346</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>357</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>149</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>337</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>119</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>281</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>216</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>191</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>199</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>273</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>288</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B92" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B93" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B94" s="0" t="n">
+        <v>306</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>323</v>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>344</v>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C104" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C106" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="C108" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B109" s="0" t="n">
+        <v>318</v>
+      </c>
+      <c r="C109" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="C110" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B112" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B113" s="0" t="n">
+        <v>294</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>337</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>217</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B118" s="0" t="n">
+        <v>191</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B119" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B120" s="0" t="n">
+        <v>154</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B122" s="0" t="n">
+        <v>310</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B123" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B124" s="0" t="n">
+        <v>263</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B125" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B126" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B127" s="0" t="n">
+        <v>323</v>
+      </c>
+      <c r="C127" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B128" s="0" t="n">
+        <v>354</v>
+      </c>
+      <c r="C128" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B129" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C129" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B130" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="C130" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B131" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="C131" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D131" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B132" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="B133" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B134" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="C134" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B135" s="0" t="n">
+        <v>334</v>
+      </c>
+      <c r="C135" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D135" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B136" s="0" t="n">
+        <v>256</v>
+      </c>
+      <c r="C136" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="D136" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B137" s="0" t="n">
+        <v>244</v>
+      </c>
+      <c r="C137" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D137" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B138" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="C138" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B139" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="C139" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D139" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B140" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="C140" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D140" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B141" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C141" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D141" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B142" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="C142" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="D142" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B143" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="C143" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="D143" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B144" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="C144" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D144" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B145" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="C145" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D145" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B146" s="0" t="n">
+        <v>149</v>
+      </c>
+      <c r="C146" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="D146" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B147" s="0" t="n">
+        <v>128</v>
+      </c>
+      <c r="C147" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D147" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B148" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="C148" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D148" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B149" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="C149" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D149" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B150" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="C150" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D150" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B151" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="C151" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D151" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B152" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="C152" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D152" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B153" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="C153" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D153" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B154" s="0" t="n">
+        <v>314</v>
+      </c>
+      <c r="C154" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="D154" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B155" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C155" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D155" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B156" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="C156" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="D156" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B157" s="0" t="n">
+        <v>341</v>
+      </c>
+      <c r="C157" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D157" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B158" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="C158" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="D158" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B159" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C159" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="D159" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B160" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="D160" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B161" s="0" t="n">
+        <v>343</v>
+      </c>
+      <c r="C161" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D161" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B162" s="0" t="n">
+        <v>315</v>
+      </c>
+      <c r="C162" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="D162" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B163" s="0" t="n">
+        <v>260</v>
+      </c>
+      <c r="C163" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="D163" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B164" s="0" t="n">
+        <v>181</v>
+      </c>
+      <c r="C164" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="D164" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="B165" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C165" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D165" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E165" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="B166" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C166" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D166" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="B167" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="D167" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="B168" s="0" t="n">
+        <v>196</v>
+      </c>
+      <c r="C168" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="D168" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="B169" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="C169" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="D169" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="B170" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="C170" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D170" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="B171" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C171" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D171" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B172" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C172" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="D172" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B173" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="C173" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="D173" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B174" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="C174" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D174" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B175" s="0" t="n">
+        <v>238</v>
+      </c>
+      <c r="C175" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="D175" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B176" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="C176" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="D176" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="B177" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C177" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="D177" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="B178" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C178" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D178" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C179" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -23743,13 +26791,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D1" s="0" t="s">
         <v>28</v>
@@ -23757,7 +26805,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>30</v>
@@ -23766,12 +26814,12 @@
         <v>-8.72</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>30</v>
@@ -23780,12 +26828,12 @@
         <v>-7.48</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>28</v>
@@ -23794,12 +26842,12 @@
         <v>-7.48</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>22.94</v>
@@ -23808,12 +26856,12 @@
         <v>-6.54</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>22.94</v>
@@ -23822,12 +26870,12 @@
         <v>-4.4</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>22.94</v>
@@ -23836,12 +26884,12 @@
         <v>-2.43</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>26</v>
@@ -23850,7 +26898,7 @@
         <v>-4.4</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23866,7 +26914,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>28.55</v>
@@ -23875,12 +26923,12 @@
         <v>-4</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>28.55</v>
@@ -23889,7 +26937,7 @@
         <v>-6</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23905,7 +26953,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>32.56</v>
@@ -23914,12 +26962,12 @@
         <v>-6</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>32.13</v>
@@ -23928,12 +26976,12 @@
         <v>-4</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>26</v>
@@ -23942,12 +26990,12 @@
         <v>-1.29</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>24.2</v>
@@ -23956,12 +27004,12 @@
         <v>0.4</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>22</v>
@@ -23970,12 +27018,12 @@
         <v>0.4</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>19.28</v>
@@ -23984,12 +27032,12 @@
         <v>0.4</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>18</v>
@@ -24000,7 +27048,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>16.5</v>
@@ -24009,12 +27057,12 @@
         <v>0.4</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>14.55</v>
@@ -24023,12 +27071,12 @@
         <v>0.4</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>13.61</v>
@@ -24037,12 +27085,12 @@
         <v>0.4</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>12</v>
@@ -24051,7 +27099,7 @@
         <v>0.4</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24065,7 +27113,7 @@
         <v>159</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24079,12 +27127,12 @@
         <v>159</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>9.24</v>
@@ -24093,12 +27141,12 @@
         <v>-2</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>13.62</v>
@@ -24107,7 +27155,7 @@
         <v>-2</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24121,12 +27169,12 @@
         <v>-2</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>16.5</v>
@@ -24135,12 +27183,12 @@
         <v>-2.43</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>16.73</v>
@@ -24149,12 +27197,12 @@
         <v>-2.43</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>19.28</v>
@@ -24163,12 +27211,12 @@
         <v>-2.43</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>20</v>
@@ -24177,12 +27225,12 @@
         <v>-2.43</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>16.73</v>
@@ -24191,7 +27239,7 @@
         <v>-4</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24205,7 +27253,7 @@
         <v>-4</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24219,12 +27267,12 @@
         <v>-4</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>9.55</v>
@@ -24235,7 +27283,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>9.12</v>
@@ -24244,7 +27292,7 @@
         <v>-6</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24258,12 +27306,12 @@
         <v>-6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>14</v>
@@ -24272,12 +27320,12 @@
         <v>-7.66</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>16.73</v>
@@ -24286,12 +27334,12 @@
         <v>-7.4</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>8</v>
@@ -24300,7 +27348,7 @@
         <v>2</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24314,12 +27362,12 @@
         <v>2</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>12.49</v>
@@ -24328,12 +27376,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>12.49</v>
@@ -24342,12 +27390,12 @@
         <v>4</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>8</v>
@@ -24356,7 +27404,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24370,12 +27418,12 @@
         <v>4</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>14.55</v>
@@ -24384,12 +27432,12 @@
         <v>3.54</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>14.55</v>
@@ -24398,12 +27446,12 @@
         <v>2.41</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>17.04</v>
@@ -24412,12 +27460,12 @@
         <v>2.41</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>18</v>
@@ -24426,12 +27474,12 @@
         <v>2.41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>22</v>
@@ -24440,12 +27488,12 @@
         <v>2.41</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>22</v>
@@ -24454,12 +27502,12 @@
         <v>4.37</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>18.65</v>
@@ -24468,12 +27516,12 @@
         <v>4.37</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>17.04</v>
@@ -24482,12 +27530,12 @@
         <v>4.26</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>16.23</v>
@@ -24496,12 +27544,12 @@
         <v>4.26</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>16.23</v>
@@ -24510,12 +27558,12 @@
         <v>4.9</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>14</v>
@@ -24524,12 +27572,12 @@
         <v>4.9</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>14</v>
@@ -24538,12 +27586,12 @@
         <v>6.06</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>18.65</v>
@@ -24563,7 +27611,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24577,12 +27625,12 @@
         <v>8</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>25.5</v>
@@ -24591,7 +27639,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -25059,13 +28107,13 @@
       <c r="BF7" s="25"/>
       <c r="BG7" s="25"/>
       <c r="BH7" s="26" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="BI7" s="26"/>
       <c r="BJ7" s="26"/>
       <c r="BK7" s="26"/>
       <c r="BL7" s="27" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="BM7" s="27"/>
       <c r="BN7" s="27"/>
@@ -25171,15 +28219,27 @@
       <c r="O9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="14"/>
+      <c r="P9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="14"/>
+      <c r="T9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="W9" s="17" t="n">
         <v>5</v>
       </c>
@@ -25447,25 +28507,25 @@
       <c r="BA11" s="5"/>
       <c r="BB11" s="6"/>
       <c r="BD11" s="30" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="BE11" s="30"/>
       <c r="BF11" s="30"/>
       <c r="BG11" s="30"/>
       <c r="BH11" s="27" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="BI11" s="27"/>
       <c r="BJ11" s="27"/>
       <c r="BK11" s="27"/>
       <c r="BL11" s="27" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="BM11" s="27"/>
       <c r="BN11" s="27"/>
       <c r="BO11" s="27"/>
       <c r="BP11" s="28" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="BQ11" s="28"/>
       <c r="BR11" s="28"/>
@@ -25589,17 +28649,21 @@
       <c r="Q13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="14"/>
+      <c r="R13" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="S13" s="17" t="n">
         <v>4</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="14"/>
+      <c r="V13" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="W13" s="17" t="n">
         <v>5</v>
       </c>
@@ -25609,7 +28673,9 @@
       <c r="Y13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" s="14"/>
+      <c r="Z13" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="AA13" s="17" t="n">
         <v>6</v>
       </c>
@@ -25619,19 +28685,33 @@
       <c r="AC13" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="AD13" s="14"/>
+      <c r="AD13" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="AE13" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="14"/>
+      <c r="AF13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AI13" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="AJ13" s="13"/>
-      <c r="AK13" s="13"/>
-      <c r="AL13" s="14"/>
+      <c r="AJ13" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AM13" s="17" t="n">
         <v>9</v>
       </c>
@@ -25875,7 +28955,7 @@
       <c r="BA15" s="5"/>
       <c r="BB15" s="6"/>
       <c r="BD15" s="31" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="BE15" s="31"/>
       <c r="BF15" s="31"/>
@@ -25885,13 +28965,13 @@
       <c r="BJ15" s="32"/>
       <c r="BK15" s="32"/>
       <c r="BL15" s="33" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="BM15" s="33"/>
       <c r="BN15" s="33"/>
       <c r="BO15" s="33"/>
       <c r="BP15" s="34" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="BQ15" s="34"/>
       <c r="BR15" s="34"/>
@@ -26025,7 +29105,9 @@
       <c r="Q17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="R17" s="14"/>
+      <c r="R17" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="S17" s="17" t="n">
         <v>4</v>
       </c>
@@ -26035,7 +29117,9 @@
       <c r="U17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="14"/>
+      <c r="V17" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="W17" s="17" t="n">
         <v>5</v>
       </c>
@@ -26045,7 +29129,9 @@
       <c r="Y17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" s="14"/>
+      <c r="Z17" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AA17" s="17" t="n">
         <v>6</v>
       </c>
@@ -26060,22 +29146,26 @@
         <v>7</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH17" s="14"/>
+        <v>7</v>
+      </c>
+      <c r="AH17" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="AI17" s="17" t="n">
         <v>8</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL17" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="AL17" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="AM17" s="17" t="n">
         <v>9</v>
       </c>
@@ -26085,13 +29175,21 @@
       <c r="AO17" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AP17" s="15"/>
+      <c r="AP17" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ17" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="AR17" s="13"/>
-      <c r="AS17" s="35"/>
-      <c r="AT17" s="14"/>
+      <c r="AR17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS17" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AU17" s="17" t="n">
         <v>11</v>
       </c>
@@ -26413,7 +29511,7 @@
       <c r="BA20" s="13"/>
       <c r="BB20" s="14"/>
       <c r="BD20" s="36" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="BE20" s="36"/>
       <c r="BF20" s="36"/>
@@ -26478,7 +29576,9 @@
       <c r="AC21" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="14"/>
+      <c r="AD21" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AE21" s="17" t="n">
         <v>7</v>
       </c>
@@ -26488,7 +29588,9 @@
       <c r="AG21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="AH21" s="14"/>
+      <c r="AH21" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="AI21" s="17" t="n">
         <v>8</v>
       </c>
@@ -26498,7 +29600,9 @@
       <c r="AK21" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="AL21" s="14"/>
+      <c r="AL21" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="AM21" s="17" t="n">
         <v>9</v>
       </c>
@@ -26508,17 +29612,21 @@
       <c r="AO21" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AP21" s="15"/>
+      <c r="AP21" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="AQ21" s="18" t="n">
         <v>10</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT21" s="14"/>
+        <v>7</v>
+      </c>
+      <c r="AT21" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AU21" s="17" t="n">
         <v>11</v>
       </c>
@@ -26528,7 +29636,9 @@
       <c r="AW21" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AX21" s="14"/>
+      <c r="AX21" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="AY21" s="17" t="n">
         <v>12</v>
       </c>
@@ -26863,7 +29973,9 @@
       <c r="U25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="14"/>
+      <c r="V25" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="W25" s="17" t="n">
         <v>5</v>
       </c>
@@ -26873,7 +29985,9 @@
       <c r="Y25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="14"/>
+      <c r="Z25" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AA25" s="17" t="n">
         <v>6</v>
       </c>
@@ -26883,7 +29997,9 @@
       <c r="AC25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AD25" s="14"/>
+      <c r="AD25" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AE25" s="17" t="n">
         <v>7</v>
       </c>
@@ -26893,7 +30009,9 @@
       <c r="AG25" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AH25" s="14"/>
+      <c r="AH25" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="AI25" s="17" t="n">
         <v>8</v>
       </c>
@@ -26903,7 +30021,9 @@
       <c r="AK25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AL25" s="14"/>
+      <c r="AL25" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="AM25" s="17" t="n">
         <v>9</v>
       </c>
@@ -26913,7 +30033,9 @@
       <c r="AO25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AP25" s="15"/>
+      <c r="AP25" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="AQ25" s="18" t="n">
         <v>10</v>
       </c>
@@ -26923,7 +30045,9 @@
       <c r="AS25" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="AT25" s="14"/>
+      <c r="AT25" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="AU25" s="17" t="n">
         <v>11</v>
       </c>
@@ -26933,7 +30057,9 @@
       <c r="AW25" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="AX25" s="14"/>
+      <c r="AX25" s="14" t="n">
+        <v>12</v>
+      </c>
       <c r="AY25" s="17" t="n">
         <v>12</v>
       </c>
@@ -27221,7 +30347,7 @@
       </c>
       <c r="BB28" s="14"/>
       <c r="BD28" s="39" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="BE28" s="39"/>
       <c r="BF28" s="39"/>
@@ -27273,7 +30399,9 @@
       <c r="U29" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="V29" s="14"/>
+      <c r="V29" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="W29" s="17" t="n">
         <v>5</v>
       </c>
@@ -27283,7 +30411,9 @@
       <c r="Y29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" s="14"/>
+      <c r="Z29" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AA29" s="17" t="n">
         <v>6</v>
       </c>
@@ -27293,7 +30423,9 @@
       <c r="AC29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AD29" s="14"/>
+      <c r="AD29" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AE29" s="17" t="n">
         <v>7</v>
       </c>
@@ -27303,7 +30435,9 @@
       <c r="AG29" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AH29" s="14"/>
+      <c r="AH29" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="AI29" s="17" t="n">
         <v>8</v>
       </c>
@@ -27313,7 +30447,9 @@
       <c r="AK29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AL29" s="14"/>
+      <c r="AL29" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="AM29" s="17" t="n">
         <v>9</v>
       </c>
@@ -27323,7 +30459,9 @@
       <c r="AO29" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AP29" s="15"/>
+      <c r="AP29" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="AQ29" s="18" t="n">
         <v>10</v>
       </c>
@@ -27333,7 +30471,9 @@
       <c r="AS29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AT29" s="14"/>
+      <c r="AT29" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AU29" s="17" t="n">
         <v>11</v>
       </c>
@@ -27343,7 +30483,9 @@
       <c r="AW29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AX29" s="14"/>
+      <c r="AX29" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AY29" s="17" t="n">
         <v>12</v>
       </c>
@@ -27353,7 +30495,9 @@
       <c r="BA29" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="BB29" s="14"/>
+      <c r="BB29" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="BD29" s="39"/>
       <c r="BE29" s="39"/>
       <c r="BF29" s="39"/>
@@ -27673,7 +30817,9 @@
       <c r="E33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="14"/>
+      <c r="F33" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="17" t="n">
         <v>1</v>
       </c>
@@ -27683,7 +30829,9 @@
       <c r="I33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="14"/>
+      <c r="J33" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="K33" s="17" t="n">
         <v>2</v>
       </c>
@@ -27693,7 +30841,9 @@
       <c r="M33" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="N33" s="14"/>
+      <c r="N33" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="O33" s="17" t="n">
         <v>3</v>
       </c>
@@ -27703,7 +30853,9 @@
       <c r="Q33" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="R33" s="14"/>
+      <c r="R33" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="S33" s="17" t="n">
         <v>4</v>
       </c>
@@ -27713,7 +30865,9 @@
       <c r="U33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="14"/>
+      <c r="V33" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="W33" s="17" t="n">
         <v>5</v>
       </c>
@@ -27723,7 +30877,9 @@
       <c r="Y33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="14"/>
+      <c r="Z33" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AA33" s="17" t="n">
         <v>6</v>
       </c>
@@ -27733,7 +30889,9 @@
       <c r="AC33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" s="14"/>
+      <c r="AD33" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AE33" s="17" t="n">
         <v>7</v>
       </c>
@@ -27743,7 +30901,9 @@
       <c r="AG33" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="AH33" s="14"/>
+      <c r="AH33" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="AI33" s="17" t="n">
         <v>8</v>
       </c>
@@ -27753,7 +30913,9 @@
       <c r="AK33" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="AL33" s="14"/>
+      <c r="AL33" s="14" t="n">
+        <v>12</v>
+      </c>
       <c r="AM33" s="17" t="n">
         <v>9</v>
       </c>
@@ -27763,7 +30925,9 @@
       <c r="AO33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AP33" s="15"/>
+      <c r="AP33" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="AQ33" s="18" t="n">
         <v>10</v>
       </c>
@@ -27773,7 +30937,9 @@
       <c r="AS33" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AT33" s="14"/>
+      <c r="AT33" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="AU33" s="17" t="n">
         <v>11</v>
       </c>
@@ -27783,7 +30949,9 @@
       <c r="AW33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AX33" s="14"/>
+      <c r="AX33" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="AY33" s="17" t="n">
         <v>12</v>
       </c>
@@ -28095,7 +31263,9 @@
       <c r="E37" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="F37" s="14"/>
+      <c r="F37" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="17" t="n">
         <v>1</v>
       </c>
@@ -28105,7 +31275,9 @@
       <c r="I37" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="J37" s="14"/>
+      <c r="J37" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" s="17" t="n">
         <v>2</v>
       </c>
@@ -28115,7 +31287,9 @@
       <c r="M37" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="N37" s="14"/>
+      <c r="N37" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="O37" s="17" t="n">
         <v>3</v>
       </c>
@@ -28125,7 +31299,9 @@
       <c r="Q37" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="R37" s="14"/>
+      <c r="R37" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="S37" s="17" t="n">
         <v>4</v>
       </c>
@@ -28135,7 +31311,9 @@
       <c r="U37" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="14"/>
+      <c r="V37" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="W37" s="17" t="n">
         <v>5</v>
       </c>
@@ -28145,7 +31323,9 @@
       <c r="Y37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="Z37" s="14"/>
+      <c r="Z37" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AA37" s="17" t="n">
         <v>6</v>
       </c>
@@ -28155,7 +31335,9 @@
       <c r="AC37" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AD37" s="14"/>
+      <c r="AD37" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="AE37" s="17" t="n">
         <v>7</v>
       </c>
@@ -28165,7 +31347,9 @@
       <c r="AG37" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AH37" s="14"/>
+      <c r="AH37" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AI37" s="17" t="n">
         <v>8</v>
       </c>
@@ -28175,7 +31359,9 @@
       <c r="AK37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AL37" s="14"/>
+      <c r="AL37" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AM37" s="17" t="n">
         <v>9</v>
       </c>
@@ -28185,7 +31371,9 @@
       <c r="AO37" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="AP37" s="15"/>
+      <c r="AP37" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="AQ37" s="18" t="n">
         <v>10</v>
       </c>
@@ -28195,7 +31383,9 @@
       <c r="AS37" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="AT37" s="14"/>
+      <c r="AT37" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="AU37" s="17" t="n">
         <v>11</v>
       </c>
@@ -28205,13 +31395,21 @@
       <c r="AW37" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="AX37" s="14"/>
+      <c r="AX37" s="14" t="n">
+        <v>11</v>
+      </c>
       <c r="AY37" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AZ37" s="13"/>
-      <c r="BA37" s="13"/>
-      <c r="BB37" s="14"/>
+      <c r="AZ37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" s="14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C38" s="19" t="n">
@@ -28513,7 +31711,9 @@
       <c r="E41" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="F41" s="14"/>
+      <c r="F41" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="G41" s="17" t="n">
         <v>1</v>
       </c>
@@ -28523,7 +31723,9 @@
       <c r="I41" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="J41" s="14"/>
+      <c r="J41" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="K41" s="17" t="n">
         <v>2</v>
       </c>
@@ -28533,7 +31735,9 @@
       <c r="M41" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="N41" s="14"/>
+      <c r="N41" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="O41" s="17" t="n">
         <v>3</v>
       </c>
@@ -28543,7 +31747,9 @@
       <c r="Q41" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="R41" s="14"/>
+      <c r="R41" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="S41" s="17" t="n">
         <v>4</v>
       </c>
@@ -28553,7 +31759,9 @@
       <c r="U41" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="V41" s="14"/>
+      <c r="V41" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="W41" s="17" t="n">
         <v>5</v>
       </c>
@@ -28563,7 +31771,9 @@
       <c r="Y41" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="Z41" s="14"/>
+      <c r="Z41" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="AA41" s="17" t="n">
         <v>6</v>
       </c>
@@ -28573,7 +31783,9 @@
       <c r="AC41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="AD41" s="14"/>
+      <c r="AD41" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="AE41" s="17" t="n">
         <v>7</v>
       </c>
@@ -28583,7 +31795,9 @@
       <c r="AG41" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AH41" s="14"/>
+      <c r="AH41" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AI41" s="17" t="n">
         <v>8</v>
       </c>
@@ -28593,7 +31807,9 @@
       <c r="AK41" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AL41" s="14"/>
+      <c r="AL41" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AM41" s="17" t="n">
         <v>9</v>
       </c>
@@ -28603,7 +31819,9 @@
       <c r="AO41" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="AP41" s="15"/>
+      <c r="AP41" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="AQ41" s="18" t="n">
         <v>10</v>
       </c>
@@ -28613,23 +31831,33 @@
       <c r="AS41" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AT41" s="14"/>
+      <c r="AT41" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AU41" s="17" t="n">
         <v>11</v>
       </c>
       <c r="AV41" s="13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AW41" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX41" s="14"/>
+        <v>8</v>
+      </c>
+      <c r="AX41" s="14" t="n">
+        <v>24</v>
+      </c>
       <c r="AY41" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AZ41" s="13"/>
-      <c r="BA41" s="13"/>
-      <c r="BB41" s="14"/>
+      <c r="AZ41" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB41" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C42" s="19" t="n">
@@ -28921,37 +32149,45 @@
       <c r="E45" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="14"/>
+      <c r="F45" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="G45" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J45" s="14"/>
+        <v>13</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="K45" s="17" t="n">
         <v>2</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="14"/>
+        <v>5</v>
+      </c>
+      <c r="N45" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="O45" s="17" t="n">
         <v>3</v>
       </c>
       <c r="P45" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q45" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="14"/>
+      <c r="R45" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="S45" s="17" t="n">
         <v>4</v>
       </c>
@@ -28961,7 +32197,9 @@
       <c r="U45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="14"/>
+      <c r="V45" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="W45" s="17" t="n">
         <v>5</v>
       </c>
@@ -28971,7 +32209,9 @@
       <c r="Y45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="14"/>
+      <c r="Z45" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AA45" s="17" t="n">
         <v>6</v>
       </c>
@@ -28981,7 +32221,9 @@
       <c r="AC45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AD45" s="14"/>
+      <c r="AD45" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AE45" s="17" t="n">
         <v>7</v>
       </c>
@@ -28991,7 +32233,9 @@
       <c r="AG45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AH45" s="14"/>
+      <c r="AH45" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AI45" s="17" t="n">
         <v>8</v>
       </c>
@@ -29001,7 +32245,9 @@
       <c r="AK45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AL45" s="14"/>
+      <c r="AL45" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AM45" s="17" t="n">
         <v>9</v>
       </c>
@@ -29011,7 +32257,9 @@
       <c r="AO45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AP45" s="15"/>
+      <c r="AP45" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="AQ45" s="18" t="n">
         <v>10</v>
       </c>
@@ -29021,7 +32269,9 @@
       <c r="AS45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AT45" s="14"/>
+      <c r="AT45" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="AU45" s="17" t="n">
         <v>11</v>
       </c>
@@ -29031,13 +32281,21 @@
       <c r="AW45" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="AX45" s="14"/>
+      <c r="AX45" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="AY45" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AZ45" s="13"/>
-      <c r="BA45" s="13"/>
-      <c r="BB45" s="14"/>
+      <c r="AZ45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C46" s="19" t="n">
@@ -29291,27 +32549,51 @@
       <c r="C49" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="14"/>
+      <c r="D49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="G49" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="14"/>
+      <c r="H49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="K49" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="14"/>
+      <c r="L49" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="O49" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="14"/>
+      <c r="P49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="S49" s="17" t="n">
         <v>4</v>
       </c>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,6 +14,7 @@
     <sheet name="Cut_stump_trees" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Plot_corners" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="map_chain" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Lat_long" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="509">
   <si>
     <t xml:space="preserve">Station_1</t>
   </si>
@@ -1627,6 +1628,51 @@
   </si>
   <si>
     <t xml:space="preserve">2 chain lengths (132’)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain_X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain_Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid_X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid_Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lat_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lat_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34+14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8+14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-10</t>
   </si>
 </sst>
 </file>
@@ -32811,4 +32857,192 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="12.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>46.00122516</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-123.07626975</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0.006396625</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0.009046875</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0.00051173</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0.00072375</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>45.99815481</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>-123.08061225</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>46.001481055</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>-123.085316625</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>46.004551435</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-123.080974125</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">$F$2+0.5*($D6*$J$2)-0.5*($E6*$K$2)</f>
+        <v>46.001974435</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <f aca="false">$G$2-0.5*($E6*$J$2)-0.5*($D6*$K$2)</f>
+        <v>-123.081167825</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\showalt_d\Documents\GitHub\Apiary_LRR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACF233E-74BD-49EA-A0EE-38B5C2FB0B73}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123C79B0-1AB3-4CFB-9EDA-9458C73CFF43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4196" uniqueCount="718">
   <si>
     <t>Block</t>
   </si>
@@ -1576,9 +1576,6 @@
   </si>
   <si>
     <t>17.04+4.26</t>
-  </si>
-  <si>
-    <t>W corner DII</t>
   </si>
   <si>
     <t>16.23+4.26</t>
@@ -2070,6 +2067,129 @@
   </si>
   <si>
     <t>43</t>
+  </si>
+  <si>
+    <t>26+10</t>
+  </si>
+  <si>
+    <t>BIII</t>
+  </si>
+  <si>
+    <t>EII</t>
+  </si>
+  <si>
+    <t>CIII</t>
+  </si>
+  <si>
+    <t>AIV</t>
+  </si>
+  <si>
+    <t>EI</t>
+  </si>
+  <si>
+    <t>AII</t>
+  </si>
+  <si>
+    <t>CII</t>
+  </si>
+  <si>
+    <t>AIII</t>
+  </si>
+  <si>
+    <t>EIII</t>
+  </si>
+  <si>
+    <t>EIV</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>CIV</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>E0</t>
+  </si>
+  <si>
+    <t>22.94-6</t>
+  </si>
+  <si>
+    <t>vx_1</t>
+  </si>
+  <si>
+    <t>vx_2</t>
+  </si>
+  <si>
+    <t>vx_3</t>
+  </si>
+  <si>
+    <t>vy_1</t>
+  </si>
+  <si>
+    <t>vy_2</t>
+  </si>
+  <si>
+    <t>vy_3</t>
+  </si>
+  <si>
+    <t>vx_4</t>
+  </si>
+  <si>
+    <t>vy_4</t>
+  </si>
+  <si>
+    <t>vx_5</t>
+  </si>
+  <si>
+    <t>vy_5</t>
+  </si>
+  <si>
+    <t>vx_6</t>
+  </si>
+  <si>
+    <t>vy_6</t>
+  </si>
+  <si>
+    <t>vx_7</t>
+  </si>
+  <si>
+    <t>vy_7</t>
+  </si>
+  <si>
+    <t>vx_8</t>
+  </si>
+  <si>
+    <t>vy_8</t>
+  </si>
+  <si>
+    <t>BIV</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>DIII</t>
+  </si>
+  <si>
+    <t>DIV</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>BI</t>
+  </si>
+  <si>
+    <t>BII</t>
+  </si>
+  <si>
+    <t>DII</t>
+  </si>
+  <si>
+    <t>W corner DIII</t>
   </si>
 </sst>
 </file>
@@ -2501,33 +2621,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2541,6 +2634,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6872,7 +6992,7 @@
         <v>63</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>64</v>
@@ -6895,7 +7015,7 @@
         <v>63</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AA16" s="1" t="s">
         <v>64</v>
@@ -6918,7 +7038,7 @@
         <v>60</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AJ16" s="1" t="s">
         <v>64</v>
@@ -9929,7 +10049,7 @@
         <v>96</v>
       </c>
       <c r="AH51" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AI51">
         <v>88.5</v>
@@ -10162,6 +10282,9 @@
       <c r="AN54">
         <v>96</v>
       </c>
+      <c r="AO54" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="AP54" t="s">
         <v>252</v>
       </c>
@@ -10182,8 +10305,14 @@
       <c r="E55">
         <v>91</v>
       </c>
-      <c r="F55">
-        <v>177</v>
+      <c r="G55" t="s">
+        <v>60</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55" t="s">
+        <v>64</v>
       </c>
       <c r="K55" t="s">
         <v>254</v>
@@ -10197,8 +10326,14 @@
       <c r="N55">
         <v>101</v>
       </c>
-      <c r="O55">
-        <v>179</v>
+      <c r="P55" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q55">
+        <v>0.5</v>
+      </c>
+      <c r="R55" t="s">
+        <v>64</v>
       </c>
       <c r="T55" t="s">
         <v>255</v>
@@ -10212,8 +10347,14 @@
       <c r="W55">
         <v>94</v>
       </c>
-      <c r="X55">
-        <v>265</v>
+      <c r="Y55" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z55">
+        <v>85</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>61</v>
       </c>
       <c r="AC55" t="s">
         <v>221</v>
@@ -10227,8 +10368,14 @@
       <c r="AF55">
         <v>87</v>
       </c>
-      <c r="AG55">
-        <v>358</v>
+      <c r="AH55" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI55">
+        <v>2</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>61</v>
       </c>
       <c r="AP55" t="s">
         <v>256</v>
@@ -10250,8 +10397,14 @@
       <c r="E56">
         <v>117</v>
       </c>
-      <c r="F56">
-        <v>93</v>
+      <c r="G56" t="s">
+        <v>60</v>
+      </c>
+      <c r="H56">
+        <v>87.5</v>
+      </c>
+      <c r="I56" t="s">
+        <v>64</v>
       </c>
       <c r="K56" t="s">
         <v>255</v>
@@ -10265,8 +10418,14 @@
       <c r="N56">
         <v>103</v>
       </c>
-      <c r="O56">
-        <v>166</v>
+      <c r="P56" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q56">
+        <v>14.5</v>
+      </c>
+      <c r="R56" t="s">
+        <v>64</v>
       </c>
       <c r="T56" t="s">
         <v>258</v>
@@ -10280,8 +10439,14 @@
       <c r="W56">
         <v>68</v>
       </c>
-      <c r="X56">
-        <v>264</v>
+      <c r="Y56" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z56">
+        <v>84</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>61</v>
       </c>
       <c r="AC56" t="s">
         <v>226</v>
@@ -10295,8 +10460,14 @@
       <c r="AF56">
         <v>92</v>
       </c>
-      <c r="AG56">
-        <v>12</v>
+      <c r="AH56" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI56">
+        <v>12.5</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>64</v>
       </c>
       <c r="AP56" t="s">
         <v>259</v>
@@ -10318,8 +10489,14 @@
       <c r="E57">
         <v>75</v>
       </c>
-      <c r="F57">
-        <v>92</v>
+      <c r="G57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H57">
+        <v>88</v>
+      </c>
+      <c r="I57" t="s">
+        <v>64</v>
       </c>
       <c r="K57" t="s">
         <v>229</v>
@@ -10333,8 +10510,14 @@
       <c r="N57">
         <v>92</v>
       </c>
-      <c r="O57">
-        <v>348</v>
+      <c r="P57" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q57">
+        <v>12.5</v>
+      </c>
+      <c r="R57" t="s">
+        <v>61</v>
       </c>
       <c r="T57" t="s">
         <v>258</v>
@@ -10348,8 +10531,14 @@
       <c r="W57">
         <v>99</v>
       </c>
-      <c r="X57">
-        <v>190</v>
+      <c r="Y57" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z57">
+        <v>10</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>61</v>
       </c>
       <c r="AC57" t="s">
         <v>261</v>
@@ -10363,8 +10552,14 @@
       <c r="AF57">
         <v>111</v>
       </c>
-      <c r="AG57">
-        <v>267</v>
+      <c r="AH57" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI57">
+        <v>87</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>61</v>
       </c>
       <c r="AL57" s="1" t="s">
         <v>262</v>
@@ -10374,6 +10569,9 @@
       </c>
       <c r="AN57">
         <v>99</v>
+      </c>
+      <c r="AO57" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="AP57" t="s">
         <v>263</v>
@@ -10395,8 +10593,14 @@
       <c r="E58">
         <v>91</v>
       </c>
-      <c r="F58">
-        <v>183</v>
+      <c r="G58" t="s">
+        <v>60</v>
+      </c>
+      <c r="H58">
+        <v>3.5</v>
+      </c>
+      <c r="I58" t="s">
+        <v>61</v>
       </c>
       <c r="J58">
         <v>26</v>
@@ -10413,8 +10617,14 @@
       <c r="N58">
         <v>87</v>
       </c>
-      <c r="O58">
+      <c r="P58" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q58">
         <v>87</v>
+      </c>
+      <c r="R58" t="s">
+        <v>64</v>
       </c>
       <c r="T58" t="s">
         <v>265</v>
@@ -10428,8 +10638,17 @@
       <c r="W58">
         <v>102</v>
       </c>
-      <c r="X58">
-        <v>272</v>
+      <c r="Y58" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z58">
+        <v>88.5</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB58">
+        <v>19</v>
       </c>
       <c r="AC58" t="s">
         <v>233</v>
@@ -10443,8 +10662,14 @@
       <c r="AF58">
         <v>102</v>
       </c>
-      <c r="AG58">
-        <v>356</v>
+      <c r="AH58" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI58">
+        <v>4</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>61</v>
       </c>
       <c r="AK58">
         <v>28</v>
@@ -10457,6 +10682,9 @@
       </c>
       <c r="AN58">
         <v>87</v>
+      </c>
+      <c r="AO58" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="AP58" t="s">
         <v>267</v>
@@ -10478,8 +10706,14 @@
       <c r="E59">
         <v>94</v>
       </c>
-      <c r="F59">
-        <v>180</v>
+      <c r="G59" t="s">
+        <v>60</v>
+      </c>
+      <c r="H59">
+        <v>0.5</v>
+      </c>
+      <c r="I59" t="s">
+        <v>64</v>
       </c>
       <c r="J59">
         <v>32</v>
@@ -10496,8 +10730,14 @@
       <c r="N59">
         <v>97</v>
       </c>
-      <c r="O59">
-        <v>86</v>
+      <c r="P59" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q59">
+        <v>86.5</v>
+      </c>
+      <c r="R59" t="s">
+        <v>64</v>
       </c>
       <c r="T59" t="s">
         <v>237</v>
@@ -10511,8 +10751,14 @@
       <c r="W59">
         <v>100</v>
       </c>
-      <c r="X59">
+      <c r="Y59" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z59">
         <v>6</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>64</v>
       </c>
       <c r="AB59">
         <v>22</v>
@@ -10529,8 +10775,14 @@
       <c r="AF59">
         <v>96</v>
       </c>
-      <c r="AG59">
-        <v>271</v>
+      <c r="AH59" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI59">
+        <v>89</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>61</v>
       </c>
       <c r="AK59">
         <v>28</v>
@@ -10543,6 +10795,9 @@
       </c>
       <c r="AN59">
         <v>93</v>
+      </c>
+      <c r="AO59" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="AP59" t="s">
         <v>271</v>
@@ -10564,8 +10819,14 @@
       <c r="E60">
         <v>91</v>
       </c>
-      <c r="F60">
-        <v>174</v>
+      <c r="G60" t="s">
+        <v>60</v>
+      </c>
+      <c r="H60">
+        <v>6</v>
+      </c>
+      <c r="I60" t="s">
+        <v>64</v>
       </c>
       <c r="J60">
         <v>30</v>
@@ -10582,8 +10843,14 @@
       <c r="N60">
         <v>92</v>
       </c>
-      <c r="O60">
-        <v>271</v>
+      <c r="P60" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q60">
+        <v>89</v>
+      </c>
+      <c r="R60" t="s">
+        <v>61</v>
       </c>
       <c r="S60">
         <v>44</v>
@@ -10600,8 +10867,14 @@
       <c r="W60">
         <v>106</v>
       </c>
-      <c r="X60">
-        <v>4</v>
+      <c r="Y60" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z60">
+        <v>4.5</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>64</v>
       </c>
       <c r="AB60">
         <v>25</v>
@@ -10618,8 +10891,14 @@
       <c r="AF60">
         <v>103</v>
       </c>
-      <c r="AG60">
+      <c r="AH60" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI60">
         <v>86</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>64</v>
       </c>
       <c r="AK60">
         <v>24</v>
@@ -10632,6 +10911,9 @@
       </c>
       <c r="AN60">
         <v>100</v>
+      </c>
+      <c r="AO60" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="AP60" t="s">
         <v>275</v>
@@ -10686,6 +10968,9 @@
       <c r="AN61">
         <v>82</v>
       </c>
+      <c r="AO61" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="AP61" t="s">
         <v>278</v>
       </c>
@@ -10739,6 +11024,9 @@
       <c r="AN62">
         <v>101</v>
       </c>
+      <c r="AO62" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="AP62" t="s">
         <v>282</v>
       </c>
@@ -10759,8 +11047,14 @@
       <c r="E63">
         <v>95</v>
       </c>
-      <c r="F63">
-        <v>266</v>
+      <c r="G63" t="s">
+        <v>60</v>
+      </c>
+      <c r="H63">
+        <v>88</v>
+      </c>
+      <c r="I63" t="s">
+        <v>61</v>
       </c>
       <c r="K63" t="s">
         <v>254</v>
@@ -10774,8 +11068,14 @@
       <c r="N63">
         <v>90</v>
       </c>
-      <c r="O63">
+      <c r="P63" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q63">
         <v>0</v>
+      </c>
+      <c r="R63" t="s">
+        <v>64</v>
       </c>
       <c r="T63" t="s">
         <v>285</v>
@@ -10789,8 +11089,14 @@
       <c r="W63">
         <v>93</v>
       </c>
-      <c r="X63">
-        <v>91</v>
+      <c r="Y63" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z63">
+        <v>89</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>64</v>
       </c>
       <c r="AC63" t="s">
         <v>286</v>
@@ -10804,8 +11110,14 @@
       <c r="AF63">
         <v>95</v>
       </c>
-      <c r="AG63">
-        <v>180</v>
+      <c r="AH63" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI63">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>61</v>
       </c>
       <c r="AP63" t="s">
         <v>287</v>
@@ -10827,8 +11139,14 @@
       <c r="E64">
         <v>94</v>
       </c>
-      <c r="F64">
-        <v>269</v>
+      <c r="G64" t="s">
+        <v>60</v>
+      </c>
+      <c r="H64">
+        <v>89</v>
+      </c>
+      <c r="I64" t="s">
+        <v>61</v>
       </c>
       <c r="K64" t="s">
         <v>255</v>
@@ -10842,8 +11160,14 @@
       <c r="N64">
         <v>84</v>
       </c>
-      <c r="O64">
-        <v>359</v>
+      <c r="P64" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+      <c r="R64" t="s">
+        <v>61</v>
       </c>
       <c r="T64" t="s">
         <v>254</v>
@@ -10857,8 +11181,14 @@
       <c r="W64">
         <v>95</v>
       </c>
-      <c r="X64">
-        <v>91</v>
+      <c r="Y64" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z64">
+        <v>89</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>64</v>
       </c>
       <c r="AC64" t="s">
         <v>284</v>
@@ -10872,8 +11202,14 @@
       <c r="AF64">
         <v>94</v>
       </c>
-      <c r="AG64">
-        <v>181</v>
+      <c r="AH64" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI64">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>61</v>
       </c>
       <c r="AP64" t="s">
         <v>290</v>
@@ -10895,8 +11231,14 @@
       <c r="E65">
         <v>85</v>
       </c>
-      <c r="F65">
-        <v>267</v>
+      <c r="G65" t="s">
+        <v>60</v>
+      </c>
+      <c r="H65">
+        <v>87.5</v>
+      </c>
+      <c r="I65" t="s">
+        <v>61</v>
       </c>
       <c r="K65" t="s">
         <v>258</v>
@@ -10910,8 +11252,14 @@
       <c r="N65">
         <v>91</v>
       </c>
-      <c r="O65">
+      <c r="P65" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q65">
         <v>5</v>
+      </c>
+      <c r="R65" t="s">
+        <v>64</v>
       </c>
       <c r="T65" t="s">
         <v>255</v>
@@ -10925,8 +11273,14 @@
       <c r="W65">
         <v>103</v>
       </c>
-      <c r="X65">
-        <v>93</v>
+      <c r="Y65" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z65">
+        <v>87.5</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>64</v>
       </c>
       <c r="AC65" t="s">
         <v>289</v>
@@ -10940,8 +11294,14 @@
       <c r="AF65">
         <v>96</v>
       </c>
-      <c r="AG65">
-        <v>175</v>
+      <c r="AH65" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI65">
+        <v>5</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>64</v>
       </c>
       <c r="AP65" t="s">
         <v>293</v>
@@ -10963,8 +11323,14 @@
       <c r="E66">
         <v>106</v>
       </c>
-      <c r="F66">
-        <v>275</v>
+      <c r="G66" t="s">
+        <v>63</v>
+      </c>
+      <c r="H66">
+        <v>85</v>
+      </c>
+      <c r="I66" t="s">
+        <v>61</v>
       </c>
       <c r="K66" t="s">
         <v>261</v>
@@ -10978,8 +11344,14 @@
       <c r="N66">
         <v>105</v>
       </c>
-      <c r="O66">
-        <v>354</v>
+      <c r="P66" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q66">
+        <v>6.5</v>
+      </c>
+      <c r="R66" t="s">
+        <v>61</v>
       </c>
       <c r="T66" t="s">
         <v>258</v>
@@ -10993,8 +11365,14 @@
       <c r="W66">
         <v>85</v>
       </c>
-      <c r="X66">
+      <c r="Y66" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z66">
         <v>83</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>64</v>
       </c>
       <c r="AC66" t="s">
         <v>292</v>
@@ -11008,8 +11386,14 @@
       <c r="AF66">
         <v>83</v>
       </c>
-      <c r="AG66">
-        <v>187</v>
+      <c r="AH66" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI66">
+        <v>7</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>61</v>
       </c>
       <c r="AP66" t="s">
         <v>296</v>
@@ -11031,8 +11415,14 @@
       <c r="E67">
         <v>109</v>
       </c>
-      <c r="F67">
+      <c r="G67" t="s">
+        <v>63</v>
+      </c>
+      <c r="H67">
         <v>2</v>
+      </c>
+      <c r="I67" t="s">
+        <v>64</v>
       </c>
       <c r="J67">
         <v>28</v>
@@ -11049,8 +11439,14 @@
       <c r="N67">
         <v>104</v>
       </c>
-      <c r="O67">
-        <v>81</v>
+      <c r="P67" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q67">
+        <v>81.5</v>
+      </c>
+      <c r="R67" t="s">
+        <v>64</v>
       </c>
       <c r="S67">
         <v>28</v>
@@ -11067,8 +11463,14 @@
       <c r="W67">
         <v>79</v>
       </c>
-      <c r="X67">
-        <v>6</v>
+      <c r="Y67" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z67">
+        <v>6.5</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>64</v>
       </c>
       <c r="AC67" t="s">
         <v>298</v>
@@ -11082,8 +11484,14 @@
       <c r="AF67">
         <v>93</v>
       </c>
-      <c r="AG67">
-        <v>278</v>
+      <c r="AH67" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI67">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>61</v>
       </c>
       <c r="AK67">
         <v>30</v>
@@ -11096,6 +11504,9 @@
       </c>
       <c r="AN67">
         <v>89</v>
+      </c>
+      <c r="AO67" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="AP67" t="s">
         <v>300</v>
@@ -11117,8 +11528,14 @@
       <c r="E68">
         <v>100</v>
       </c>
-      <c r="F68">
+      <c r="G68" t="s">
+        <v>63</v>
+      </c>
+      <c r="H68">
         <v>2</v>
+      </c>
+      <c r="I68" t="s">
+        <v>64</v>
       </c>
       <c r="J68">
         <v>26</v>
@@ -11135,8 +11552,14 @@
       <c r="N68">
         <v>97</v>
       </c>
-      <c r="O68">
-        <v>269</v>
+      <c r="P68" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q68">
+        <v>89</v>
+      </c>
+      <c r="R68" t="s">
+        <v>61</v>
       </c>
       <c r="S68">
         <v>28</v>
@@ -11153,8 +11576,14 @@
       <c r="W68">
         <v>93</v>
       </c>
-      <c r="X68">
-        <v>178</v>
+      <c r="Y68" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z68">
+        <v>2</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>64</v>
       </c>
       <c r="AB68">
         <v>26</v>
@@ -11171,8 +11600,14 @@
       <c r="AF68">
         <v>103</v>
       </c>
-      <c r="AG68">
+      <c r="AH68" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI68">
         <v>78</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>64</v>
       </c>
       <c r="AK68">
         <v>36</v>
@@ -11185,6 +11620,9 @@
       </c>
       <c r="AN68">
         <v>90</v>
+      </c>
+      <c r="AO68" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="AP68" t="s">
         <v>303</v>
@@ -11206,8 +11644,14 @@
       <c r="E69">
         <v>86</v>
       </c>
-      <c r="F69">
-        <v>355</v>
+      <c r="G69" t="s">
+        <v>63</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69" t="s">
+        <v>61</v>
       </c>
       <c r="K69" t="s">
         <v>305</v>
@@ -11221,8 +11665,14 @@
       <c r="N69">
         <v>106</v>
       </c>
-      <c r="O69">
-        <v>264</v>
+      <c r="P69" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q69">
+        <v>84.5</v>
+      </c>
+      <c r="R69" t="s">
+        <v>61</v>
       </c>
       <c r="S69">
         <v>27</v>
@@ -11239,8 +11689,14 @@
       <c r="W69">
         <v>106</v>
       </c>
-      <c r="X69">
-        <v>185</v>
+      <c r="Y69" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z69">
+        <v>5</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>61</v>
       </c>
       <c r="AB69">
         <v>28</v>
@@ -11257,8 +11713,14 @@
       <c r="AF69">
         <v>92</v>
       </c>
-      <c r="AG69">
-        <v>175</v>
+      <c r="AH69" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI69">
+        <v>5</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>64</v>
       </c>
       <c r="AK69">
         <v>27</v>
@@ -11271,6 +11733,9 @@
       </c>
       <c r="AN69">
         <v>86</v>
+      </c>
+      <c r="AO69" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="AP69" t="s">
         <v>307</v>
@@ -11298,6 +11763,9 @@
       <c r="J70">
         <v>20</v>
       </c>
+      <c r="AO70" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="AP70" t="s">
         <v>309</v>
       </c>
@@ -11333,6 +11801,9 @@
       <c r="O71">
         <v>183</v>
       </c>
+      <c r="AO71" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="AP71" s="2" t="s">
         <v>312</v>
       </c>
@@ -11401,6 +11872,9 @@
       <c r="AN72">
         <v>90</v>
       </c>
+      <c r="AO72" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="AP72" t="s">
         <v>317</v>
       </c>
@@ -11421,8 +11895,14 @@
       <c r="E73">
         <v>103</v>
       </c>
-      <c r="F73">
-        <v>87</v>
+      <c r="G73" t="s">
+        <v>63</v>
+      </c>
+      <c r="H73">
+        <v>87.5</v>
+      </c>
+      <c r="I73" t="s">
+        <v>64</v>
       </c>
       <c r="K73" t="s">
         <v>319</v>
@@ -11436,8 +11916,14 @@
       <c r="N73">
         <v>90</v>
       </c>
-      <c r="O73">
-        <v>174</v>
+      <c r="P73" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q73">
+        <v>6.5</v>
+      </c>
+      <c r="R73" t="s">
+        <v>64</v>
       </c>
       <c r="T73" t="s">
         <v>320</v>
@@ -11448,8 +11934,14 @@
       <c r="V73">
         <v>8</v>
       </c>
-      <c r="X73">
-        <v>270</v>
+      <c r="Y73" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>63</v>
       </c>
       <c r="AC73" t="s">
         <v>284</v>
@@ -11463,8 +11955,14 @@
       <c r="AF73">
         <v>97</v>
       </c>
-      <c r="AG73">
+      <c r="AH73" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI73">
         <v>3</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>64</v>
       </c>
       <c r="AP73" t="s">
         <v>321</v>
@@ -11486,8 +11984,14 @@
       <c r="E74">
         <v>89</v>
       </c>
-      <c r="F74">
-        <v>93</v>
+      <c r="G74" t="s">
+        <v>60</v>
+      </c>
+      <c r="H74">
+        <v>87.5</v>
+      </c>
+      <c r="I74" t="s">
+        <v>64</v>
       </c>
       <c r="K74" t="s">
         <v>320</v>
@@ -11501,8 +12005,14 @@
       <c r="N74">
         <v>99</v>
       </c>
-      <c r="O74">
-        <v>182</v>
+      <c r="P74" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q74">
+        <v>2.5</v>
+      </c>
+      <c r="R74" t="s">
+        <v>61</v>
       </c>
       <c r="T74" t="s">
         <v>322</v>
@@ -11516,8 +12026,14 @@
       <c r="W74">
         <v>100</v>
       </c>
-      <c r="X74">
-        <v>266</v>
+      <c r="Y74" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z74">
+        <v>86.5</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>61</v>
       </c>
       <c r="AB74">
         <v>28</v>
@@ -11542,8 +12058,14 @@
       <c r="E75">
         <v>92</v>
       </c>
-      <c r="F75">
-        <v>179</v>
+      <c r="G75" t="s">
+        <v>60</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>64</v>
       </c>
       <c r="K75" t="s">
         <v>289</v>
@@ -11557,8 +12079,14 @@
       <c r="N75">
         <v>103</v>
       </c>
-      <c r="O75">
+      <c r="P75" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q75">
         <v>88</v>
+      </c>
+      <c r="R75" t="s">
+        <v>64</v>
       </c>
       <c r="S75">
         <v>22</v>
@@ -11575,8 +12103,14 @@
       <c r="W75">
         <v>90</v>
       </c>
-      <c r="X75">
-        <v>271</v>
+      <c r="Y75" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z75">
+        <v>89</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>61</v>
       </c>
       <c r="AB75">
         <v>26</v>
@@ -11593,8 +12127,14 @@
       <c r="AF75">
         <v>97</v>
       </c>
-      <c r="AG75">
+      <c r="AH75" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI75">
         <v>2</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>64</v>
       </c>
       <c r="AL75" s="1" t="s">
         <v>326</v>
@@ -11604,6 +12144,9 @@
       </c>
       <c r="AN75">
         <v>96</v>
+      </c>
+      <c r="AO75" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="AP75" t="s">
         <v>327</v>
@@ -11625,8 +12168,14 @@
       <c r="E76">
         <v>98</v>
       </c>
-      <c r="F76">
-        <v>88</v>
+      <c r="G76" t="s">
+        <v>63</v>
+      </c>
+      <c r="H76">
+        <v>88.5</v>
+      </c>
+      <c r="I76" t="s">
+        <v>64</v>
       </c>
       <c r="J76">
         <v>25</v>
@@ -11643,8 +12192,14 @@
       <c r="N76">
         <v>91</v>
       </c>
-      <c r="O76">
-        <v>179</v>
+      <c r="P76" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76" t="s">
+        <v>64</v>
       </c>
       <c r="T76" t="s">
         <v>328</v>
@@ -11658,8 +12213,14 @@
       <c r="W76">
         <v>94</v>
       </c>
-      <c r="X76">
-        <v>271</v>
+      <c r="Y76" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z76">
+        <v>89.5</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>61</v>
       </c>
       <c r="AC76" t="s">
         <v>295</v>
@@ -11673,8 +12234,14 @@
       <c r="AF76">
         <v>96</v>
       </c>
-      <c r="AG76">
+      <c r="AH76" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI76">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>64</v>
       </c>
       <c r="AL76" s="1" t="s">
         <v>329</v>
@@ -11684,6 +12251,9 @@
       </c>
       <c r="AN76">
         <v>91</v>
+      </c>
+      <c r="AO76" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="AP76" t="s">
         <v>330</v>
@@ -11765,6 +12335,9 @@
       <c r="AN77">
         <v>95</v>
       </c>
+      <c r="AO77" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="AP77" t="s">
         <v>334</v>
       </c>
@@ -11785,8 +12358,14 @@
       <c r="E78">
         <v>102</v>
       </c>
-      <c r="F78">
-        <v>92</v>
+      <c r="G78" t="s">
+        <v>60</v>
+      </c>
+      <c r="H78">
+        <v>88</v>
+      </c>
+      <c r="I78" t="s">
+        <v>64</v>
       </c>
       <c r="K78" t="s">
         <v>336</v>
@@ -11800,8 +12379,14 @@
       <c r="N78">
         <v>88</v>
       </c>
-      <c r="O78">
-        <v>258</v>
+      <c r="P78" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q78">
+        <v>78.5</v>
+      </c>
+      <c r="R78" t="s">
+        <v>61</v>
       </c>
       <c r="T78" t="s">
         <v>332</v>
@@ -11815,8 +12400,14 @@
       <c r="W78">
         <v>97</v>
       </c>
-      <c r="X78">
-        <v>175</v>
+      <c r="Y78" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z78">
+        <v>5</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>64</v>
       </c>
       <c r="AC78" t="s">
         <v>302</v>
@@ -11830,8 +12421,14 @@
       <c r="AF78">
         <v>88</v>
       </c>
-      <c r="AG78">
-        <v>3</v>
+      <c r="AH78" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI78">
+        <v>3.5</v>
+      </c>
+      <c r="AJ78" t="s">
+        <v>64</v>
       </c>
       <c r="AL78" s="1" t="s">
         <v>337</v>
@@ -11841,6 +12438,9 @@
       </c>
       <c r="AN78">
         <v>97</v>
+      </c>
+      <c r="AO78" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="AP78" t="s">
         <v>338</v>
@@ -11889,6 +12489,9 @@
       <c r="AN79">
         <v>68</v>
       </c>
+      <c r="AO79" s="1" t="s">
+        <v>305</v>
+      </c>
       <c r="AP79" t="s">
         <v>341</v>
       </c>
@@ -11951,6 +12554,9 @@
       <c r="AB80">
         <v>14</v>
       </c>
+      <c r="AO80" s="1" t="s">
+        <v>677</v>
+      </c>
       <c r="AP80" t="s">
         <v>345</v>
       </c>
@@ -12019,6 +12625,9 @@
       <c r="AN81">
         <v>94</v>
       </c>
+      <c r="AO81" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="AP81" t="s">
         <v>349</v>
       </c>
@@ -12087,6 +12696,9 @@
       <c r="AN82">
         <v>102</v>
       </c>
+      <c r="AO82" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="AP82" t="s">
         <v>352</v>
       </c>
@@ -12133,6 +12745,9 @@
       </c>
       <c r="AN83">
         <v>85</v>
+      </c>
+      <c r="AO83" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="AP83" t="s">
         <v>354</v>
@@ -12189,13 +12804,13 @@
         <v>363</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -23258,7 +23873,7 @@
         <v>232</v>
       </c>
       <c r="C478">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D478" t="s">
         <v>60</v>
@@ -23284,7 +23899,7 @@
         <v>232</v>
       </c>
       <c r="C479">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D479" t="s">
         <v>364</v>
@@ -24488,7 +25103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
         <v>250</v>
       </c>
@@ -24508,7 +25123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
         <v>250</v>
       </c>
@@ -24528,7 +25143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
         <v>250</v>
       </c>
@@ -24548,7 +25163,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
         <v>250</v>
       </c>
@@ -24568,7 +25183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
         <v>250</v>
       </c>
@@ -24588,7 +25203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
         <v>250</v>
       </c>
@@ -24608,7 +25223,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
         <v>250</v>
       </c>
@@ -24628,7 +25243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
         <v>250</v>
       </c>
@@ -24648,7 +25263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
         <v>250</v>
       </c>
@@ -24668,7 +25283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
         <v>250</v>
       </c>
@@ -24688,7 +25303,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
         <v>250</v>
       </c>
@@ -24708,7 +25323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" s="1" t="s">
         <v>250</v>
       </c>
@@ -24728,7 +25343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="1" t="s">
         <v>250</v>
       </c>
@@ -24748,7 +25363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" s="1" t="s">
         <v>250</v>
       </c>
@@ -24768,13 +25383,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B543">
-        <v>326</v>
-      </c>
       <c r="C543">
         <v>5</v>
       </c>
@@ -24787,14 +25399,20 @@
       <c r="F543">
         <v>10</v>
       </c>
-    </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K543" t="s">
+        <v>63</v>
+      </c>
+      <c r="L543">
+        <v>34</v>
+      </c>
+      <c r="M543" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B544">
-        <v>325</v>
-      </c>
       <c r="C544">
         <v>36</v>
       </c>
@@ -24807,14 +25425,20 @@
       <c r="F544">
         <v>12</v>
       </c>
-    </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K544" t="s">
+        <v>63</v>
+      </c>
+      <c r="L544">
+        <v>35</v>
+      </c>
+      <c r="M544" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B545">
-        <v>309</v>
-      </c>
       <c r="C545">
         <v>32</v>
       </c>
@@ -24827,14 +25451,20 @@
       <c r="F545">
         <v>4</v>
       </c>
-    </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K545" t="s">
+        <v>63</v>
+      </c>
+      <c r="L545">
+        <v>51.5</v>
+      </c>
+      <c r="M545" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B546">
-        <v>305</v>
-      </c>
       <c r="C546">
         <v>54</v>
       </c>
@@ -24847,14 +25477,20 @@
       <c r="F546">
         <v>14</v>
       </c>
-    </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K546" t="s">
+        <v>63</v>
+      </c>
+      <c r="L546">
+        <v>55</v>
+      </c>
+      <c r="M546" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B547">
-        <v>283</v>
-      </c>
       <c r="C547">
         <v>35</v>
       </c>
@@ -24867,14 +25503,20 @@
       <c r="F547">
         <v>6</v>
       </c>
-    </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K547" t="s">
+        <v>63</v>
+      </c>
+      <c r="L547">
+        <v>77.5</v>
+      </c>
+      <c r="M547" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B548">
-        <v>286</v>
-      </c>
       <c r="C548">
         <v>49</v>
       </c>
@@ -24887,14 +25529,20 @@
       <c r="F548">
         <v>10</v>
       </c>
-    </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K548" t="s">
+        <v>63</v>
+      </c>
+      <c r="L548">
+        <v>74</v>
+      </c>
+      <c r="M548" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B549">
-        <v>292</v>
-      </c>
       <c r="C549">
         <v>61</v>
       </c>
@@ -24907,14 +25555,20 @@
       <c r="F549">
         <v>6</v>
       </c>
-    </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K549" t="s">
+        <v>63</v>
+      </c>
+      <c r="L549">
+        <v>68</v>
+      </c>
+      <c r="M549" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B550">
-        <v>292</v>
-      </c>
       <c r="C550">
         <v>63</v>
       </c>
@@ -24927,14 +25581,20 @@
       <c r="F550">
         <v>7</v>
       </c>
-    </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K550" t="s">
+        <v>63</v>
+      </c>
+      <c r="L550">
+        <v>68</v>
+      </c>
+      <c r="M550" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B551">
-        <v>300</v>
-      </c>
       <c r="C551">
         <v>68</v>
       </c>
@@ -24947,14 +25607,20 @@
       <c r="F551">
         <v>10</v>
       </c>
-    </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K551" t="s">
+        <v>63</v>
+      </c>
+      <c r="L551">
+        <v>60</v>
+      </c>
+      <c r="M551" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B552">
-        <v>305</v>
-      </c>
       <c r="C552">
         <v>63</v>
       </c>
@@ -24967,14 +25633,20 @@
       <c r="F552">
         <v>8</v>
       </c>
-    </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K552" t="s">
+        <v>63</v>
+      </c>
+      <c r="L552">
+        <v>55</v>
+      </c>
+      <c r="M552" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B553">
-        <v>305</v>
-      </c>
       <c r="C553">
         <v>54</v>
       </c>
@@ -24987,14 +25659,20 @@
       <c r="F553">
         <v>6</v>
       </c>
-    </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K553" t="s">
+        <v>63</v>
+      </c>
+      <c r="L553">
+        <v>55</v>
+      </c>
+      <c r="M553" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B554">
-        <v>309</v>
-      </c>
       <c r="C554">
         <v>68</v>
       </c>
@@ -25004,14 +25682,20 @@
       <c r="E554" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K554" t="s">
+        <v>63</v>
+      </c>
+      <c r="L554">
+        <v>51</v>
+      </c>
+      <c r="M554" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B555">
-        <v>300</v>
-      </c>
       <c r="C555">
         <v>53</v>
       </c>
@@ -25024,14 +25708,20 @@
       <c r="F555">
         <v>4</v>
       </c>
-    </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K555" t="s">
+        <v>63</v>
+      </c>
+      <c r="L555">
+        <v>60</v>
+      </c>
+      <c r="M555" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B556">
-        <v>315</v>
-      </c>
       <c r="C556">
         <v>57</v>
       </c>
@@ -25044,16 +25734,22 @@
       <c r="F556">
         <v>10</v>
       </c>
-    </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K556" t="s">
+        <v>63</v>
+      </c>
+      <c r="L556">
+        <v>45</v>
+      </c>
+      <c r="M556" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B557">
-        <v>18</v>
-      </c>
       <c r="C557">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D557" t="s">
         <v>364</v>
@@ -25064,16 +25760,22 @@
       <c r="F557">
         <v>9</v>
       </c>
-    </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K557" t="s">
+        <v>63</v>
+      </c>
+      <c r="L557">
+        <v>18</v>
+      </c>
+      <c r="M557" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B558">
-        <v>18</v>
-      </c>
       <c r="C558">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D558" t="s">
         <v>364</v>
@@ -25084,14 +25786,20 @@
       <c r="F558">
         <v>6</v>
       </c>
-    </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K558" t="s">
+        <v>63</v>
+      </c>
+      <c r="L558">
+        <v>18</v>
+      </c>
+      <c r="M558" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B559">
-        <v>37</v>
-      </c>
       <c r="C559">
         <v>57</v>
       </c>
@@ -25104,14 +25812,20 @@
       <c r="F559">
         <v>6</v>
       </c>
-    </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K559" t="s">
+        <v>63</v>
+      </c>
+      <c r="L559">
+        <v>37.5</v>
+      </c>
+      <c r="M559" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A560" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B560">
-        <v>69</v>
-      </c>
       <c r="C560">
         <v>53</v>
       </c>
@@ -25124,14 +25838,20 @@
       <c r="F560">
         <v>6</v>
       </c>
-    </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K560" t="s">
+        <v>63</v>
+      </c>
+      <c r="L560">
+        <v>69.5</v>
+      </c>
+      <c r="M560" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B561">
-        <v>160</v>
-      </c>
       <c r="C561">
         <v>53</v>
       </c>
@@ -25144,14 +25864,20 @@
       <c r="F561">
         <v>8</v>
       </c>
-    </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K561" t="s">
+        <v>60</v>
+      </c>
+      <c r="L561">
+        <v>20</v>
+      </c>
+      <c r="M561" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A562" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B562">
-        <v>171</v>
-      </c>
       <c r="C562">
         <v>63</v>
       </c>
@@ -25164,14 +25890,20 @@
       <c r="F562">
         <v>10</v>
       </c>
-    </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K562" t="s">
+        <v>60</v>
+      </c>
+      <c r="L562">
+        <v>9</v>
+      </c>
+      <c r="M562" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B563">
-        <v>165</v>
-      </c>
       <c r="C563">
         <v>63</v>
       </c>
@@ -25184,14 +25916,20 @@
       <c r="F563">
         <v>7</v>
       </c>
-    </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K563" t="s">
+        <v>60</v>
+      </c>
+      <c r="L563">
+        <v>15</v>
+      </c>
+      <c r="M563" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B564">
-        <v>130</v>
-      </c>
       <c r="C564">
         <v>60</v>
       </c>
@@ -25204,14 +25942,20 @@
       <c r="F564">
         <v>8</v>
       </c>
-    </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K564" t="s">
+        <v>60</v>
+      </c>
+      <c r="L564">
+        <v>50</v>
+      </c>
+      <c r="M564" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A565" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B565">
-        <v>329</v>
-      </c>
       <c r="C565">
         <v>39</v>
       </c>
@@ -25224,14 +25968,20 @@
       <c r="F565">
         <v>5</v>
       </c>
-    </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K565" t="s">
+        <v>63</v>
+      </c>
+      <c r="L565">
+        <v>31.5</v>
+      </c>
+      <c r="M565" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B566">
-        <v>329</v>
-      </c>
       <c r="C566">
         <v>43</v>
       </c>
@@ -25244,14 +25994,20 @@
       <c r="F566">
         <v>10</v>
       </c>
-    </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K566" t="s">
+        <v>63</v>
+      </c>
+      <c r="L566">
+        <v>31.5</v>
+      </c>
+      <c r="M566" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A567" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B567">
-        <v>310</v>
-      </c>
       <c r="C567">
         <v>55</v>
       </c>
@@ -25264,14 +26020,20 @@
       <c r="F567">
         <v>9</v>
       </c>
-    </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K567" t="s">
+        <v>63</v>
+      </c>
+      <c r="L567">
+        <v>50</v>
+      </c>
+      <c r="M567" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A568" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B568">
-        <v>177</v>
-      </c>
       <c r="C568">
         <v>39</v>
       </c>
@@ -25284,8 +26046,17 @@
       <c r="F568">
         <v>9</v>
       </c>
-    </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K568" t="s">
+        <v>60</v>
+      </c>
+      <c r="L568">
+        <v>3.5</v>
+      </c>
+      <c r="M568" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A569" s="1" t="s">
         <v>276</v>
       </c>
@@ -25305,7 +26076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A570" s="1" t="s">
         <v>276</v>
       </c>
@@ -25325,7 +26096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A571" s="1" t="s">
         <v>276</v>
       </c>
@@ -25345,7 +26116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A572" s="1" t="s">
         <v>276</v>
       </c>
@@ -25365,7 +26136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A573" s="1" t="s">
         <v>276</v>
       </c>
@@ -25385,7 +26156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A574" s="1" t="s">
         <v>276</v>
       </c>
@@ -25405,7 +26176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A575" s="1" t="s">
         <v>276</v>
       </c>
@@ -25425,7 +26196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A576" s="1" t="s">
         <v>276</v>
       </c>
@@ -26725,7 +27496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A641" s="1" t="s">
         <v>279</v>
       </c>
@@ -26745,7 +27516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A642" s="1" t="s">
         <v>279</v>
       </c>
@@ -26765,7 +27536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A643" s="1" t="s">
         <v>279</v>
       </c>
@@ -26785,7 +27556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A644" s="1" t="s">
         <v>279</v>
       </c>
@@ -26805,7 +27576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A645" s="1" t="s">
         <v>279</v>
       </c>
@@ -26825,13 +27596,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B646">
-        <v>16</v>
-      </c>
       <c r="C646">
         <v>28</v>
       </c>
@@ -26844,14 +27612,20 @@
       <c r="F646">
         <v>10</v>
       </c>
-    </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K646" t="s">
+        <v>63</v>
+      </c>
+      <c r="L646">
+        <v>16</v>
+      </c>
+      <c r="M646" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B647">
-        <v>16</v>
-      </c>
       <c r="C647">
         <v>28</v>
       </c>
@@ -26864,14 +27638,20 @@
       <c r="F647">
         <v>5</v>
       </c>
-    </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K647" t="s">
+        <v>63</v>
+      </c>
+      <c r="L647">
+        <v>16</v>
+      </c>
+      <c r="M647" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B648">
-        <v>157</v>
-      </c>
       <c r="C648">
         <v>34</v>
       </c>
@@ -26884,14 +27664,20 @@
       <c r="F648">
         <v>10</v>
       </c>
-    </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K648" t="s">
+        <v>60</v>
+      </c>
+      <c r="L648">
+        <v>23.5</v>
+      </c>
+      <c r="M648" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B649">
-        <v>187</v>
-      </c>
       <c r="C649">
         <v>38</v>
       </c>
@@ -26904,14 +27690,20 @@
       <c r="F649">
         <v>6</v>
       </c>
-    </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K649" t="s">
+        <v>60</v>
+      </c>
+      <c r="L649">
+        <v>7.5</v>
+      </c>
+      <c r="M649" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B650">
-        <v>187</v>
-      </c>
       <c r="C650">
         <v>36</v>
       </c>
@@ -26924,14 +27716,20 @@
       <c r="F650">
         <v>6</v>
       </c>
-    </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K650" t="s">
+        <v>60</v>
+      </c>
+      <c r="L650">
+        <v>7.5</v>
+      </c>
+      <c r="M650" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B651">
-        <v>192</v>
-      </c>
       <c r="C651">
         <v>42</v>
       </c>
@@ -26944,14 +27742,20 @@
       <c r="F651">
         <v>8</v>
       </c>
-    </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K651" t="s">
+        <v>60</v>
+      </c>
+      <c r="L651">
+        <v>12.5</v>
+      </c>
+      <c r="M651" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A652" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B652">
-        <v>339</v>
-      </c>
       <c r="C652">
         <v>46</v>
       </c>
@@ -26964,14 +27768,20 @@
       <c r="F652">
         <v>7</v>
       </c>
-    </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K652" t="s">
+        <v>63</v>
+      </c>
+      <c r="L652">
+        <v>21</v>
+      </c>
+      <c r="M652" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A653" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B653">
-        <v>353</v>
-      </c>
       <c r="C653">
         <v>54</v>
       </c>
@@ -26984,14 +27794,20 @@
       <c r="F653">
         <v>12</v>
       </c>
-    </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K653" t="s">
+        <v>63</v>
+      </c>
+      <c r="L653">
+        <v>7.5</v>
+      </c>
+      <c r="M653" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A654" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B654">
-        <v>20</v>
-      </c>
       <c r="C654">
         <v>37</v>
       </c>
@@ -27004,14 +27820,20 @@
       <c r="F654">
         <v>10</v>
       </c>
-    </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K654" t="s">
+        <v>63</v>
+      </c>
+      <c r="L654">
+        <v>20.5</v>
+      </c>
+      <c r="M654" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A655" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B655">
-        <v>115</v>
-      </c>
       <c r="C655">
         <v>50</v>
       </c>
@@ -27024,14 +27846,20 @@
       <c r="F655">
         <v>14</v>
       </c>
-    </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K655" t="s">
+        <v>60</v>
+      </c>
+      <c r="L655">
+        <v>65</v>
+      </c>
+      <c r="M655" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A656" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B656">
-        <v>121</v>
-      </c>
       <c r="C656">
         <v>32</v>
       </c>
@@ -27044,14 +27872,20 @@
       <c r="F656">
         <v>8</v>
       </c>
-    </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K656" t="s">
+        <v>60</v>
+      </c>
+      <c r="L656">
+        <v>59</v>
+      </c>
+      <c r="M656" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A657" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B657">
-        <v>52</v>
-      </c>
       <c r="C657">
         <v>57</v>
       </c>
@@ -27064,14 +27898,20 @@
       <c r="F657">
         <v>9</v>
       </c>
-    </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K657" t="s">
+        <v>63</v>
+      </c>
+      <c r="L657">
+        <v>52.5</v>
+      </c>
+      <c r="M657" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A658" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B658">
-        <v>44</v>
-      </c>
       <c r="C658">
         <v>59</v>
       </c>
@@ -27084,14 +27924,20 @@
       <c r="F658">
         <v>4</v>
       </c>
-    </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K658" t="s">
+        <v>63</v>
+      </c>
+      <c r="L658">
+        <v>44</v>
+      </c>
+      <c r="M658" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A659" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B659">
-        <v>44</v>
-      </c>
       <c r="C659">
         <v>55</v>
       </c>
@@ -27104,14 +27950,20 @@
       <c r="F659">
         <v>10</v>
       </c>
-    </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K659" t="s">
+        <v>63</v>
+      </c>
+      <c r="L659">
+        <v>44</v>
+      </c>
+      <c r="M659" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B660">
-        <v>39</v>
-      </c>
       <c r="C660">
         <v>55</v>
       </c>
@@ -27124,14 +27976,20 @@
       <c r="F660">
         <v>10</v>
       </c>
-    </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K660" t="s">
+        <v>63</v>
+      </c>
+      <c r="L660">
+        <v>39</v>
+      </c>
+      <c r="M660" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A661" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B661">
-        <v>274</v>
-      </c>
       <c r="C661">
         <v>35</v>
       </c>
@@ -27144,14 +28002,20 @@
       <c r="F661">
         <v>9</v>
       </c>
-    </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K661" t="s">
+        <v>63</v>
+      </c>
+      <c r="L661">
+        <v>86</v>
+      </c>
+      <c r="M661" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A662" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B662">
-        <v>270</v>
-      </c>
       <c r="C662">
         <v>85</v>
       </c>
@@ -27164,14 +28028,20 @@
       <c r="F662">
         <v>8</v>
       </c>
-    </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K662" t="s">
+        <v>61</v>
+      </c>
+      <c r="L662">
+        <v>0</v>
+      </c>
+      <c r="M662" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A663" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B663">
-        <v>270</v>
-      </c>
       <c r="C663">
         <v>85</v>
       </c>
@@ -27184,14 +28054,20 @@
       <c r="F663">
         <v>10</v>
       </c>
-    </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K663" t="s">
+        <v>61</v>
+      </c>
+      <c r="L663">
+        <v>0</v>
+      </c>
+      <c r="M663" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A664" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B664">
-        <v>270</v>
-      </c>
       <c r="C664">
         <v>79</v>
       </c>
@@ -27204,14 +28080,20 @@
       <c r="F664">
         <v>8</v>
       </c>
-    </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K664" t="s">
+        <v>61</v>
+      </c>
+      <c r="L664">
+        <v>0</v>
+      </c>
+      <c r="M664" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B665">
-        <v>111</v>
-      </c>
       <c r="C665">
         <v>53</v>
       </c>
@@ -27224,8 +28106,17 @@
       <c r="F665">
         <v>7</v>
       </c>
-    </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K665" t="s">
+        <v>60</v>
+      </c>
+      <c r="L665">
+        <v>31</v>
+      </c>
+      <c r="M665" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A666" s="1" t="s">
         <v>308</v>
       </c>
@@ -27245,7 +28136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A667" s="1" t="s">
         <v>308</v>
       </c>
@@ -27265,7 +28156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A668" s="1" t="s">
         <v>308</v>
       </c>
@@ -27285,7 +28176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A669" s="1" t="s">
         <v>308</v>
       </c>
@@ -27305,7 +28196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A670" s="1" t="s">
         <v>308</v>
       </c>
@@ -27325,7 +28216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A671" s="1" t="s">
         <v>310</v>
       </c>
@@ -27345,7 +28236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A672" s="1" t="s">
         <v>310</v>
       </c>
@@ -27685,13 +28576,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B689">
-        <v>287</v>
-      </c>
       <c r="C689">
         <v>23</v>
       </c>
@@ -27704,14 +28592,20 @@
       <c r="F689">
         <v>12</v>
       </c>
-    </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K689" t="s">
+        <v>63</v>
+      </c>
+      <c r="L689">
+        <v>73</v>
+      </c>
+      <c r="M689" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A690" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B690">
-        <v>60</v>
-      </c>
       <c r="C690">
         <v>64</v>
       </c>
@@ -27724,14 +28618,20 @@
       <c r="F690">
         <v>8</v>
       </c>
-    </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K690" t="s">
+        <v>63</v>
+      </c>
+      <c r="L690">
+        <v>60.5</v>
+      </c>
+      <c r="M690" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B691">
-        <v>288</v>
-      </c>
       <c r="C691">
         <v>62</v>
       </c>
@@ -27744,14 +28644,20 @@
       <c r="F691">
         <v>4</v>
       </c>
-    </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K691" t="s">
+        <v>63</v>
+      </c>
+      <c r="L691">
+        <v>72</v>
+      </c>
+      <c r="M691" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A692" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B692">
-        <v>318</v>
-      </c>
       <c r="C692">
         <v>63</v>
       </c>
@@ -27764,14 +28670,20 @@
       <c r="F692">
         <v>8</v>
       </c>
-    </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K692" t="s">
+        <v>63</v>
+      </c>
+      <c r="L692">
+        <v>42</v>
+      </c>
+      <c r="M692" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A693" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B693">
-        <v>0</v>
-      </c>
       <c r="C693">
         <v>87</v>
       </c>
@@ -27788,14 +28700,20 @@
         <v>407</v>
       </c>
       <c r="H693" s="4"/>
-    </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K693" t="s">
+        <v>63</v>
+      </c>
+      <c r="L693">
+        <v>0</v>
+      </c>
+      <c r="M693" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A694" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B694">
-        <v>177</v>
-      </c>
       <c r="C694">
         <v>73</v>
       </c>
@@ -27808,14 +28726,20 @@
       <c r="F694">
         <v>12</v>
       </c>
-    </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K694" t="s">
+        <v>60</v>
+      </c>
+      <c r="L694">
+        <v>3</v>
+      </c>
+      <c r="M694" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A695" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B695">
-        <v>162</v>
-      </c>
       <c r="C695">
         <v>81</v>
       </c>
@@ -27828,14 +28752,20 @@
       <c r="F695">
         <v>10</v>
       </c>
-    </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K695" t="s">
+        <v>60</v>
+      </c>
+      <c r="L695">
+        <v>18.5</v>
+      </c>
+      <c r="M695" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A696" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B696">
-        <v>186</v>
-      </c>
       <c r="C696">
         <v>81</v>
       </c>
@@ -27848,14 +28778,20 @@
       <c r="F696">
         <v>12</v>
       </c>
-    </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K696" t="s">
+        <v>60</v>
+      </c>
+      <c r="L696">
+        <v>6.5</v>
+      </c>
+      <c r="M696" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A697" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B697">
-        <v>112</v>
-      </c>
       <c r="C697">
         <v>50</v>
       </c>
@@ -27868,14 +28804,20 @@
       <c r="F697">
         <v>14</v>
       </c>
-    </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K697" t="s">
+        <v>60</v>
+      </c>
+      <c r="L697">
+        <v>68</v>
+      </c>
+      <c r="M697" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B698">
-        <v>112</v>
-      </c>
       <c r="C698">
         <v>53</v>
       </c>
@@ -27888,14 +28830,20 @@
       <c r="F698">
         <v>6</v>
       </c>
-    </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K698" t="s">
+        <v>60</v>
+      </c>
+      <c r="L698">
+        <v>68</v>
+      </c>
+      <c r="M698" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B699">
-        <v>96</v>
-      </c>
       <c r="C699">
         <v>76</v>
       </c>
@@ -27908,14 +28856,20 @@
       <c r="F699">
         <v>7</v>
       </c>
-    </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K699" t="s">
+        <v>60</v>
+      </c>
+      <c r="L699">
+        <v>84</v>
+      </c>
+      <c r="M699" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B700">
-        <v>195</v>
-      </c>
       <c r="C700">
         <v>71</v>
       </c>
@@ -27928,14 +28882,20 @@
       <c r="F700">
         <v>13</v>
       </c>
-    </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K700" t="s">
+        <v>60</v>
+      </c>
+      <c r="L700">
+        <v>15.5</v>
+      </c>
+      <c r="M700" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B701">
-        <v>193</v>
-      </c>
       <c r="C701">
         <v>65</v>
       </c>
@@ -27948,14 +28908,20 @@
       <c r="F701">
         <v>5</v>
       </c>
-    </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K701" t="s">
+        <v>60</v>
+      </c>
+      <c r="L701">
+        <v>13</v>
+      </c>
+      <c r="M701" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B702">
-        <v>207</v>
-      </c>
       <c r="C702">
         <v>68</v>
       </c>
@@ -27968,14 +28934,20 @@
       <c r="F702">
         <v>10</v>
       </c>
-    </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K702" t="s">
+        <v>60</v>
+      </c>
+      <c r="L702">
+        <v>27</v>
+      </c>
+      <c r="M702" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B703">
-        <v>192</v>
-      </c>
       <c r="C703">
         <v>60</v>
       </c>
@@ -27988,14 +28960,20 @@
       <c r="F703">
         <v>14</v>
       </c>
-    </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K703" t="s">
+        <v>60</v>
+      </c>
+      <c r="L703">
+        <v>12</v>
+      </c>
+      <c r="M703" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B704">
-        <v>194</v>
-      </c>
       <c r="C704">
         <v>87</v>
       </c>
@@ -28008,14 +28986,20 @@
       <c r="F704">
         <v>13</v>
       </c>
-    </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K704" t="s">
+        <v>60</v>
+      </c>
+      <c r="L704">
+        <v>14.5</v>
+      </c>
+      <c r="M704" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B705">
-        <v>70</v>
-      </c>
       <c r="C705">
         <v>40</v>
       </c>
@@ -28028,14 +29012,20 @@
       <c r="F705">
         <v>10</v>
       </c>
-    </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K705" t="s">
+        <v>63</v>
+      </c>
+      <c r="L705">
+        <v>70</v>
+      </c>
+      <c r="M705" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B706">
-        <v>116</v>
-      </c>
       <c r="C706">
         <v>68</v>
       </c>
@@ -28049,13 +29039,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B707">
-        <v>99</v>
-      </c>
       <c r="C707">
         <v>63</v>
       </c>
@@ -28068,14 +29055,20 @@
       <c r="F707">
         <v>6</v>
       </c>
-    </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K707" t="s">
+        <v>60</v>
+      </c>
+      <c r="L707">
+        <v>81</v>
+      </c>
+      <c r="M707" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B708">
-        <v>96</v>
-      </c>
       <c r="C708">
         <v>54</v>
       </c>
@@ -28088,14 +29081,20 @@
       <c r="F708">
         <v>10</v>
       </c>
-    </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K708" t="s">
+        <v>60</v>
+      </c>
+      <c r="L708">
+        <v>84</v>
+      </c>
+      <c r="M708" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B709">
-        <v>96</v>
-      </c>
       <c r="C709">
         <v>56</v>
       </c>
@@ -28108,14 +29107,20 @@
       <c r="F709">
         <v>6</v>
       </c>
-    </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K709" t="s">
+        <v>60</v>
+      </c>
+      <c r="L709">
+        <v>84</v>
+      </c>
+      <c r="M709" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B710">
-        <v>244</v>
-      </c>
       <c r="C710">
         <v>61</v>
       </c>
@@ -28128,14 +29133,20 @@
       <c r="F710">
         <v>8</v>
       </c>
-    </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K710" t="s">
+        <v>60</v>
+      </c>
+      <c r="L710">
+        <v>64</v>
+      </c>
+      <c r="M710" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B711">
-        <v>242</v>
-      </c>
       <c r="C711">
         <v>70</v>
       </c>
@@ -28148,14 +29159,20 @@
       <c r="F711">
         <v>13</v>
       </c>
-    </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K711" t="s">
+        <v>60</v>
+      </c>
+      <c r="L711">
+        <v>62.5</v>
+      </c>
+      <c r="M711" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B712">
-        <v>249</v>
-      </c>
       <c r="C712">
         <v>70</v>
       </c>
@@ -28168,14 +29185,20 @@
       <c r="F712">
         <v>5</v>
       </c>
-    </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K712" t="s">
+        <v>60</v>
+      </c>
+      <c r="L712">
+        <v>69</v>
+      </c>
+      <c r="M712" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B713">
-        <v>252</v>
-      </c>
       <c r="C713">
         <v>70</v>
       </c>
@@ -28188,14 +29211,20 @@
       <c r="F713">
         <v>6</v>
       </c>
-    </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K713" t="s">
+        <v>60</v>
+      </c>
+      <c r="L713">
+        <v>71.5</v>
+      </c>
+      <c r="M713" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B714">
-        <v>165</v>
-      </c>
       <c r="C714">
         <v>11</v>
       </c>
@@ -28208,14 +29237,20 @@
       <c r="F714">
         <v>7</v>
       </c>
-    </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K714" t="s">
+        <v>60</v>
+      </c>
+      <c r="L714">
+        <v>25</v>
+      </c>
+      <c r="M714" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B715">
-        <v>242</v>
-      </c>
       <c r="C715">
         <v>87</v>
       </c>
@@ -28228,14 +29263,20 @@
       <c r="F715">
         <v>6</v>
       </c>
-    </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K715" t="s">
+        <v>60</v>
+      </c>
+      <c r="L715">
+        <v>62.5</v>
+      </c>
+      <c r="M715" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B716">
-        <v>247</v>
-      </c>
       <c r="C716">
         <v>78</v>
       </c>
@@ -28248,14 +29289,20 @@
       <c r="F716">
         <v>6</v>
       </c>
-    </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K716" t="s">
+        <v>60</v>
+      </c>
+      <c r="L716">
+        <v>67</v>
+      </c>
+      <c r="M716" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B717">
-        <v>239</v>
-      </c>
       <c r="C717">
         <v>91</v>
       </c>
@@ -28268,14 +29315,20 @@
       <c r="F717">
         <v>5</v>
       </c>
-    </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K717" t="s">
+        <v>60</v>
+      </c>
+      <c r="L717">
+        <v>58.5</v>
+      </c>
+      <c r="M717" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B718">
-        <v>226</v>
-      </c>
       <c r="C718">
         <v>79</v>
       </c>
@@ -28288,14 +29341,20 @@
       <c r="F718">
         <v>7</v>
       </c>
-    </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K718" t="s">
+        <v>60</v>
+      </c>
+      <c r="L718">
+        <v>46</v>
+      </c>
+      <c r="M718" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B719">
-        <v>226</v>
-      </c>
       <c r="C719">
         <v>88</v>
       </c>
@@ -28308,14 +29367,20 @@
       <c r="F719">
         <v>16</v>
       </c>
-    </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K719" t="s">
+        <v>60</v>
+      </c>
+      <c r="L719">
+        <v>46</v>
+      </c>
+      <c r="M719" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B720">
-        <v>23</v>
-      </c>
       <c r="C720">
         <v>88</v>
       </c>
@@ -28328,14 +29393,20 @@
       <c r="F720">
         <v>3</v>
       </c>
-    </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K720" t="s">
+        <v>60</v>
+      </c>
+      <c r="L720">
+        <v>50</v>
+      </c>
+      <c r="M720" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B721">
-        <v>233</v>
-      </c>
       <c r="C721">
         <v>105</v>
       </c>
@@ -28348,14 +29419,20 @@
       <c r="F721">
         <v>12</v>
       </c>
-    </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K721" t="s">
+        <v>60</v>
+      </c>
+      <c r="L721">
+        <v>53.5</v>
+      </c>
+      <c r="M721" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A722" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B722">
-        <v>231</v>
-      </c>
       <c r="C722">
         <v>77</v>
       </c>
@@ -28368,14 +29445,20 @@
       <c r="F722">
         <v>6</v>
       </c>
-    </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K722" t="s">
+        <v>60</v>
+      </c>
+      <c r="L722">
+        <v>51</v>
+      </c>
+      <c r="M722" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A723" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B723">
-        <v>231</v>
-      </c>
       <c r="C723">
         <v>77</v>
       </c>
@@ -28388,14 +29471,20 @@
       <c r="F723">
         <v>8</v>
       </c>
-    </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K723" t="s">
+        <v>60</v>
+      </c>
+      <c r="L723">
+        <v>51</v>
+      </c>
+      <c r="M723" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A724" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B724">
-        <v>244</v>
-      </c>
       <c r="C724">
         <v>77</v>
       </c>
@@ -28408,14 +29497,20 @@
       <c r="F724">
         <v>4</v>
       </c>
-    </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K724" t="s">
+        <v>60</v>
+      </c>
+      <c r="L724">
+        <v>64</v>
+      </c>
+      <c r="M724" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A725" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B725">
-        <v>215</v>
-      </c>
       <c r="C725">
         <v>80</v>
       </c>
@@ -28428,14 +29523,20 @@
       <c r="F725">
         <v>5</v>
       </c>
-    </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K725" t="s">
+        <v>60</v>
+      </c>
+      <c r="L725">
+        <v>35</v>
+      </c>
+      <c r="M725" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B726">
-        <v>259</v>
-      </c>
       <c r="C726">
         <v>62</v>
       </c>
@@ -28448,14 +29549,20 @@
       <c r="F726">
         <v>12</v>
       </c>
-    </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K726" t="s">
+        <v>60</v>
+      </c>
+      <c r="L726">
+        <v>78.5</v>
+      </c>
+      <c r="M726" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B727">
-        <v>270</v>
-      </c>
       <c r="C727">
         <v>54</v>
       </c>
@@ -28468,14 +29575,20 @@
       <c r="F727">
         <v>9</v>
       </c>
-    </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K727" t="s">
+        <v>61</v>
+      </c>
+      <c r="L727">
+        <v>0</v>
+      </c>
+      <c r="M727" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B728">
-        <v>270</v>
-      </c>
       <c r="C728">
         <v>50</v>
       </c>
@@ -28488,14 +29601,20 @@
       <c r="F728">
         <v>6</v>
       </c>
-    </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K728" t="s">
+        <v>61</v>
+      </c>
+      <c r="L728">
+        <v>0</v>
+      </c>
+      <c r="M728" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B729">
-        <v>270</v>
-      </c>
       <c r="C729">
         <v>67</v>
       </c>
@@ -28508,14 +29627,20 @@
       <c r="F729">
         <v>7</v>
       </c>
-    </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K729" t="s">
+        <v>61</v>
+      </c>
+      <c r="L729">
+        <v>0</v>
+      </c>
+      <c r="M729" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A730" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B730">
-        <v>277</v>
-      </c>
       <c r="C730">
         <v>71</v>
       </c>
@@ -28528,14 +29653,20 @@
       <c r="F730">
         <v>8</v>
       </c>
-    </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K730" t="s">
+        <v>63</v>
+      </c>
+      <c r="L730">
+        <v>83</v>
+      </c>
+      <c r="M730" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A731" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B731">
-        <v>310</v>
-      </c>
       <c r="C731">
         <v>62</v>
       </c>
@@ -28548,14 +29679,20 @@
       <c r="F731">
         <v>4</v>
       </c>
-    </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K731" t="s">
+        <v>63</v>
+      </c>
+      <c r="L731">
+        <v>50.5</v>
+      </c>
+      <c r="M731" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A732" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B732">
-        <v>306</v>
-      </c>
       <c r="C732">
         <v>57</v>
       </c>
@@ -28568,14 +29705,20 @@
       <c r="F732">
         <v>10</v>
       </c>
-    </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K732" t="s">
+        <v>63</v>
+      </c>
+      <c r="L732">
+        <v>54</v>
+      </c>
+      <c r="M732" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B733">
-        <v>301</v>
-      </c>
       <c r="C733">
         <v>46</v>
       </c>
@@ -28588,14 +29731,20 @@
       <c r="F733">
         <v>5</v>
       </c>
-    </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K733" t="s">
+        <v>63</v>
+      </c>
+      <c r="L733">
+        <v>59</v>
+      </c>
+      <c r="M733" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B734">
-        <v>41</v>
-      </c>
       <c r="C734">
         <v>58</v>
       </c>
@@ -28608,8 +29757,17 @@
       <c r="F734">
         <v>4</v>
       </c>
-    </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K734" t="s">
+        <v>63</v>
+      </c>
+      <c r="L734">
+        <v>40.5</v>
+      </c>
+      <c r="M734" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A735" s="1" t="s">
         <v>339</v>
       </c>
@@ -28629,7 +29787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" s="1" t="s">
         <v>339</v>
       </c>
@@ -32909,10 +34067,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>425</v>
       </c>
@@ -32925,8 +34083,59 @@
       <c r="D1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" t="s">
+        <v>693</v>
+      </c>
+      <c r="G1" t="s">
+        <v>696</v>
+      </c>
+      <c r="H1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I1" t="s">
+        <v>697</v>
+      </c>
+      <c r="J1" t="s">
+        <v>695</v>
+      </c>
+      <c r="K1" t="s">
+        <v>698</v>
+      </c>
+      <c r="L1" t="s">
+        <v>699</v>
+      </c>
+      <c r="M1" t="s">
+        <v>700</v>
+      </c>
+      <c r="N1" t="s">
+        <v>701</v>
+      </c>
+      <c r="O1" t="s">
+        <v>702</v>
+      </c>
+      <c r="P1" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>704</v>
+      </c>
+      <c r="R1" t="s">
+        <v>705</v>
+      </c>
+      <c r="S1" t="s">
+        <v>706</v>
+      </c>
+      <c r="T1" t="s">
+        <v>707</v>
+      </c>
+      <c r="U1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>428</v>
       </c>
@@ -32939,8 +34148,47 @@
       <c r="D2" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F2">
+        <v>32</v>
+      </c>
+      <c r="G2">
+        <v>-8</v>
+      </c>
+      <c r="H2">
+        <v>32.5</v>
+      </c>
+      <c r="I2">
+        <v>-6</v>
+      </c>
+      <c r="J2">
+        <v>28</v>
+      </c>
+      <c r="K2">
+        <v>-6</v>
+      </c>
+      <c r="L2">
+        <v>28</v>
+      </c>
+      <c r="M2">
+        <v>-7.48</v>
+      </c>
+      <c r="N2">
+        <v>30</v>
+      </c>
+      <c r="O2">
+        <v>-7.48</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2">
+        <v>-8.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>430</v>
       </c>
@@ -32953,8 +34201,59 @@
       <c r="D3" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3">
+        <v>-8.75</v>
+      </c>
+      <c r="H3">
+        <v>26</v>
+      </c>
+      <c r="I3">
+        <v>-8.75</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>-7</v>
+      </c>
+      <c r="L3">
+        <v>22.94</v>
+      </c>
+      <c r="M3">
+        <v>-6.54</v>
+      </c>
+      <c r="N3">
+        <v>22.94</v>
+      </c>
+      <c r="O3">
+        <v>-6</v>
+      </c>
+      <c r="P3">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <v>-6</v>
+      </c>
+      <c r="R3">
+        <v>28</v>
+      </c>
+      <c r="S3">
+        <v>-7.48</v>
+      </c>
+      <c r="T3">
+        <v>30</v>
+      </c>
+      <c r="U3">
+        <v>-7.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>432</v>
       </c>
@@ -32967,8 +34266,41 @@
       <c r="D4" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>690</v>
+      </c>
+      <c r="F4">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>-6</v>
+      </c>
+      <c r="H4">
+        <v>28.55</v>
+      </c>
+      <c r="I4">
+        <v>-6</v>
+      </c>
+      <c r="J4">
+        <v>28.55</v>
+      </c>
+      <c r="K4">
+        <v>-4</v>
+      </c>
+      <c r="L4">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>-4</v>
+      </c>
+      <c r="N4">
+        <v>26</v>
+      </c>
+      <c r="O4">
+        <v>-4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>434</v>
       </c>
@@ -32981,8 +34313,47 @@
       <c r="D5" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F5">
+        <v>28.55</v>
+      </c>
+      <c r="G5">
+        <v>-6</v>
+      </c>
+      <c r="H5">
+        <v>28.55</v>
+      </c>
+      <c r="I5">
+        <v>-4</v>
+      </c>
+      <c r="J5">
+        <v>32.25</v>
+      </c>
+      <c r="K5">
+        <v>-4</v>
+      </c>
+      <c r="L5">
+        <v>32.5</v>
+      </c>
+      <c r="M5">
+        <v>-6</v>
+      </c>
+      <c r="N5">
+        <v>22.94</v>
+      </c>
+      <c r="O5">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="P5">
+        <v>22.94</v>
+      </c>
+      <c r="Q5">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>436</v>
       </c>
@@ -32995,8 +34366,35 @@
       <c r="D6" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>691</v>
+      </c>
+      <c r="F6">
+        <v>32.5</v>
+      </c>
+      <c r="G6">
+        <v>-6</v>
+      </c>
+      <c r="H6">
+        <v>30.5</v>
+      </c>
+      <c r="I6">
+        <v>-2.5</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>-1.29</v>
+      </c>
+      <c r="L6">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>438</v>
       </c>
@@ -33009,760 +34407,1515 @@
       <c r="D7" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>678</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>-6.54</v>
+      </c>
+      <c r="H7">
+        <v>22.94</v>
+      </c>
+      <c r="I7">
+        <v>-6.54</v>
+      </c>
+      <c r="J7">
+        <v>22.94</v>
+      </c>
+      <c r="K7">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
+        <v>-2.4300000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>692</v>
+      </c>
+      <c r="B8">
+        <v>22.94</v>
+      </c>
+      <c r="C8">
+        <v>-6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>679</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>-1.29</v>
+      </c>
+      <c r="J8">
+        <v>24.2</v>
+      </c>
+      <c r="K8">
+        <v>0.4</v>
+      </c>
+      <c r="L8">
+        <v>19.28</v>
+      </c>
+      <c r="M8">
+        <v>0.4</v>
+      </c>
+      <c r="N8">
+        <v>19.28</v>
+      </c>
+      <c r="O8">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="P8">
+        <v>22.94</v>
+      </c>
+      <c r="Q8">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="R8">
+        <v>22.94</v>
+      </c>
+      <c r="S8">
+        <v>-4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>440</v>
-      </c>
-      <c r="B8">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>-4.4000000000000004</v>
-      </c>
-      <c r="D8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>94</v>
       </c>
       <c r="B9">
         <v>26</v>
       </c>
       <c r="C9">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="D9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E9" t="s">
+        <v>681</v>
+      </c>
+      <c r="F9">
+        <v>19.28</v>
+      </c>
+      <c r="G9">
+        <v>0.4</v>
+      </c>
+      <c r="H9">
+        <v>19.28</v>
+      </c>
+      <c r="I9">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="J9">
+        <v>16.5</v>
+      </c>
+      <c r="K9">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="L9">
+        <v>16.5</v>
+      </c>
+      <c r="M9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>94</v>
       </c>
       <c r="B10">
-        <v>28.55</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>-4</v>
       </c>
-      <c r="D10" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>683</v>
+      </c>
+      <c r="F10">
+        <v>16.5</v>
+      </c>
+      <c r="G10">
+        <v>0.4</v>
+      </c>
+      <c r="H10">
+        <v>16.5</v>
+      </c>
+      <c r="I10">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="J10">
+        <v>16.73</v>
+      </c>
+      <c r="K10">
+        <v>-2.4300000000000002</v>
+      </c>
+      <c r="L10">
+        <v>16.73</v>
+      </c>
+      <c r="M10">
+        <v>-4</v>
+      </c>
+      <c r="N10">
+        <v>14</v>
+      </c>
+      <c r="O10">
+        <v>-4</v>
+      </c>
+      <c r="P10">
+        <v>14</v>
+      </c>
+      <c r="Q10">
+        <v>-2</v>
+      </c>
+      <c r="R10">
+        <v>13.62</v>
+      </c>
+      <c r="S10">
+        <v>-2</v>
+      </c>
+      <c r="T10">
+        <v>13.62</v>
+      </c>
+      <c r="U10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B11">
         <v>28.55</v>
       </c>
       <c r="C11">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+      <c r="E11" t="s">
+        <v>688</v>
+      </c>
+      <c r="F11">
+        <v>16.73</v>
+      </c>
+      <c r="G11">
+        <v>-4</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>-4</v>
+      </c>
+      <c r="J11">
+        <v>14</v>
+      </c>
+      <c r="K11">
+        <v>-7.66</v>
+      </c>
+      <c r="L11">
+        <v>16.73</v>
+      </c>
+      <c r="M11">
+        <v>-7.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>443</v>
       </c>
       <c r="B12">
-        <v>28</v>
+        <v>28.55</v>
       </c>
       <c r="C12">
         <v>-6</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>444</v>
+      </c>
+      <c r="E12" t="s">
+        <v>709</v>
+      </c>
+      <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>-4</v>
+      </c>
+      <c r="H12">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>-7.66</v>
+      </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
+      <c r="K12">
+        <v>-7.66</v>
+      </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <v>-7.25</v>
+      </c>
+      <c r="N12">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="O12">
+        <v>-6</v>
+      </c>
+      <c r="P12">
+        <v>12</v>
+      </c>
+      <c r="Q12">
+        <v>-6</v>
+      </c>
+      <c r="R12">
+        <v>12</v>
+      </c>
+      <c r="S12">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>445</v>
+        <v>62</v>
       </c>
       <c r="B13">
-        <v>32.56</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>-6</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>689</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>-4</v>
+      </c>
+      <c r="H13">
+        <v>12</v>
+      </c>
+      <c r="I13">
+        <v>-6</v>
+      </c>
+      <c r="J13">
+        <v>10.5</v>
+      </c>
+      <c r="K13">
+        <v>-6</v>
+      </c>
+      <c r="L13">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="M13">
+        <v>-6</v>
+      </c>
+      <c r="N13">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="O13">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>445</v>
+      </c>
+      <c r="B14">
+        <v>32.56</v>
+      </c>
+      <c r="C14">
+        <v>-6</v>
+      </c>
+      <c r="D14" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="E14" t="s">
+        <v>687</v>
+      </c>
+      <c r="F14">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="G14">
+        <v>-4</v>
+      </c>
+      <c r="H14">
+        <v>9.24</v>
+      </c>
+      <c r="I14">
+        <v>-2</v>
+      </c>
+      <c r="J14">
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <v>-2</v>
+      </c>
+      <c r="L14">
+        <v>14</v>
+      </c>
+      <c r="M14">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>447</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>32.130000000000003</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>-4</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="E15" t="s">
+        <v>686</v>
+      </c>
+      <c r="F15">
+        <v>13.62</v>
+      </c>
+      <c r="G15">
+        <v>-2</v>
+      </c>
+      <c r="H15">
+        <v>9.24</v>
+      </c>
+      <c r="I15">
+        <v>-2</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <v>-1.75</v>
+      </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>12</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>12</v>
+      </c>
+      <c r="Q15">
+        <v>0.4</v>
+      </c>
+      <c r="R15">
+        <v>13.62</v>
+      </c>
+      <c r="S15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>449</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>26</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>-1.29</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="E16" t="s">
+        <v>685</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>12</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>451</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>24.2</v>
-      </c>
-      <c r="C16">
-        <v>0.4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>453</v>
-      </c>
-      <c r="B17">
-        <v>22</v>
       </c>
       <c r="C17">
         <v>0.4</v>
       </c>
       <c r="D17" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+      <c r="E17" t="s">
+        <v>684</v>
+      </c>
+      <c r="F17">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>12</v>
+      </c>
+      <c r="I17">
+        <v>0.4</v>
+      </c>
+      <c r="J17">
+        <v>14.55</v>
+      </c>
+      <c r="K17">
+        <v>0.4</v>
+      </c>
+      <c r="L17">
+        <v>14.55</v>
+      </c>
+      <c r="M17">
+        <v>3.54</v>
+      </c>
+      <c r="N17">
+        <v>14</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
+      </c>
+      <c r="P17">
+        <v>12.49</v>
+      </c>
+      <c r="Q17">
+        <v>4</v>
+      </c>
+      <c r="R17">
+        <v>12.49</v>
+      </c>
+      <c r="S17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B18">
-        <v>19.28</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>0.4</v>
       </c>
       <c r="D18" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+      <c r="E18" t="s">
+        <v>682</v>
+      </c>
+      <c r="F18">
+        <v>14.55</v>
+      </c>
+      <c r="G18">
+        <v>2.41</v>
+      </c>
+      <c r="H18">
+        <v>14.55</v>
+      </c>
+      <c r="I18">
+        <v>0.4</v>
+      </c>
+      <c r="J18">
+        <v>18</v>
+      </c>
+      <c r="K18">
+        <v>0.4</v>
+      </c>
+      <c r="L18">
+        <v>18</v>
+      </c>
+      <c r="M18">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>19.28</v>
       </c>
       <c r="C19">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D19" t="s">
+        <v>456</v>
+      </c>
+      <c r="E19" t="s">
+        <v>680</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+      <c r="G19">
+        <v>0.4</v>
+      </c>
+      <c r="H19">
+        <v>18</v>
+      </c>
+      <c r="I19">
+        <v>2.41</v>
+      </c>
+      <c r="J19">
+        <v>22</v>
+      </c>
+      <c r="K19">
+        <v>0.4</v>
+      </c>
+      <c r="L19">
+        <v>22</v>
+      </c>
+      <c r="M19">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B20">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="C20">
         <v>0.4</v>
       </c>
-      <c r="D20" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>711</v>
+      </c>
+      <c r="F20">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>2.41</v>
+      </c>
+      <c r="H20">
+        <v>22</v>
+      </c>
+      <c r="I20">
+        <v>4.37</v>
+      </c>
+      <c r="J20">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="K20">
+        <v>4.37</v>
+      </c>
+      <c r="L20">
+        <v>17.04</v>
+      </c>
+      <c r="M20">
+        <v>4.26</v>
+      </c>
+      <c r="N20">
+        <v>17.04</v>
+      </c>
+      <c r="O20">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B21">
-        <v>14.55</v>
+        <v>16.5</v>
       </c>
       <c r="C21">
         <v>0.4</v>
       </c>
       <c r="D21" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+      <c r="E21" t="s">
+        <v>710</v>
+      </c>
+      <c r="F21">
+        <v>17.04</v>
+      </c>
+      <c r="G21">
+        <v>2.41</v>
+      </c>
+      <c r="H21">
+        <v>17.04</v>
+      </c>
+      <c r="I21">
+        <v>4.26</v>
+      </c>
+      <c r="J21">
+        <v>16.23</v>
+      </c>
+      <c r="K21">
+        <v>4.26</v>
+      </c>
+      <c r="L21">
+        <v>16.23</v>
+      </c>
+      <c r="M21">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="N21">
+        <v>14</v>
+      </c>
+      <c r="O21">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P21">
+        <v>14</v>
+      </c>
+      <c r="Q21">
+        <v>4</v>
+      </c>
+      <c r="R21">
+        <v>14.55</v>
+      </c>
+      <c r="S21">
+        <v>3.54</v>
+      </c>
+      <c r="T21">
+        <v>14.55</v>
+      </c>
+      <c r="U21">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B22">
-        <v>13.61</v>
+        <v>14.55</v>
       </c>
       <c r="C22">
         <v>0.4</v>
       </c>
       <c r="D22" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+      <c r="E22" t="s">
+        <v>712</v>
+      </c>
+      <c r="F22">
+        <v>12.49</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>12.49</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B23">
-        <v>12</v>
+        <v>13.62</v>
       </c>
       <c r="C23">
         <v>0.4</v>
       </c>
       <c r="D23" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+      <c r="E23" t="s">
+        <v>713</v>
+      </c>
+      <c r="F23">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>8</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>8</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>10</v>
+      </c>
+      <c r="O23">
+        <v>5.5</v>
+      </c>
+      <c r="P23">
+        <v>12</v>
+      </c>
+      <c r="Q23">
+        <v>5.6</v>
+      </c>
+      <c r="R23">
+        <v>14</v>
+      </c>
+      <c r="S23">
+        <v>6</v>
+      </c>
+      <c r="T23">
+        <v>14</v>
+      </c>
+      <c r="U23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>464</v>
       </c>
       <c r="B24">
         <v>12</v>
       </c>
-      <c r="C24" t="s">
-        <v>175</v>
+      <c r="C24">
+        <v>0.4</v>
       </c>
       <c r="D24" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+      <c r="E24" t="s">
+        <v>715</v>
+      </c>
+      <c r="F24">
+        <v>16.23</v>
+      </c>
+      <c r="G24">
+        <v>4.26</v>
+      </c>
+      <c r="H24">
+        <v>16.23</v>
+      </c>
+      <c r="I24">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J24">
+        <v>14</v>
+      </c>
+      <c r="K24">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L24">
+        <v>14</v>
+      </c>
+      <c r="M24">
+        <v>6</v>
+      </c>
+      <c r="N24">
+        <v>18</v>
+      </c>
+      <c r="O24">
+        <v>7.98</v>
+      </c>
+      <c r="P24">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="Q24">
+        <v>7.93</v>
+      </c>
+      <c r="R24">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="S24">
+        <v>4.37</v>
+      </c>
+      <c r="T24">
+        <v>17.04</v>
+      </c>
+      <c r="U24">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
         <v>175</v>
       </c>
       <c r="D25" t="s">
+        <v>466</v>
+      </c>
+      <c r="E25" t="s">
+        <v>716</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>4.37</v>
+      </c>
+      <c r="H25">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="I25">
+        <v>4.37</v>
+      </c>
+      <c r="J25">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="K25">
+        <v>7.93</v>
+      </c>
+      <c r="L25">
+        <v>20</v>
+      </c>
+      <c r="M25">
+        <v>6.75</v>
+      </c>
+      <c r="N25">
+        <v>20</v>
+      </c>
+      <c r="O25">
+        <v>8</v>
+      </c>
+      <c r="P25">
+        <v>22</v>
+      </c>
+      <c r="Q25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="E26" t="s">
+        <v>714</v>
+      </c>
+      <c r="F26">
+        <v>26</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <v>20</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>20.75</v>
+      </c>
+      <c r="K26">
+        <v>9.25</v>
+      </c>
+      <c r="L26">
+        <v>22</v>
+      </c>
+      <c r="M26">
+        <v>9.9</v>
+      </c>
+      <c r="N26">
+        <v>24</v>
+      </c>
+      <c r="O26">
+        <v>9.9</v>
+      </c>
+      <c r="P26">
+        <v>26</v>
+      </c>
+      <c r="Q26">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>468</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>9.24</v>
-      </c>
-      <c r="C26">
-        <v>-2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>470</v>
-      </c>
-      <c r="B27">
-        <v>13.62</v>
       </c>
       <c r="C27">
         <v>-2</v>
       </c>
       <c r="D27" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>470</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>13.62</v>
       </c>
       <c r="C28">
         <v>-2</v>
       </c>
       <c r="D28" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>-2</v>
+      </c>
+      <c r="D29" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>473</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>16.5</v>
-      </c>
-      <c r="C29">
-        <v>-2.4300000000000002</v>
-      </c>
-      <c r="D29" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>475</v>
-      </c>
-      <c r="B30">
-        <v>16.73</v>
       </c>
       <c r="C30">
         <v>-2.4300000000000002</v>
       </c>
       <c r="D30" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B31">
-        <v>19.28</v>
+        <v>16.73</v>
       </c>
       <c r="C31">
         <v>-2.4300000000000002</v>
       </c>
       <c r="D31" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>19.28</v>
       </c>
       <c r="C32">
         <v>-2.4300000000000002</v>
       </c>
       <c r="D32" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B33">
-        <v>16.73</v>
+        <v>20</v>
       </c>
       <c r="C33">
-        <v>-4</v>
+        <v>-2.4300000000000002</v>
       </c>
       <c r="D33" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>480</v>
       </c>
       <c r="B34">
-        <v>14</v>
+        <v>16.73</v>
       </c>
       <c r="C34">
         <v>-4</v>
       </c>
       <c r="D34" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C35">
         <v>-4</v>
       </c>
       <c r="D35" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>484</v>
+        <v>124</v>
       </c>
       <c r="B36">
-        <v>9.5500000000000007</v>
+        <v>12</v>
       </c>
       <c r="C36">
         <v>-4</v>
       </c>
+      <c r="D36" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B37">
-        <v>9.1199999999999992</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C37">
-        <v>-6</v>
-      </c>
-      <c r="D37" t="s">
-        <v>486</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="B38">
-        <v>12</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="C38">
         <v>-6</v>
       </c>
       <c r="D38" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>488</v>
+        <v>75</v>
       </c>
       <c r="B39">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>-7.66</v>
+        <v>-6</v>
       </c>
       <c r="D39" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B40">
-        <v>16.73</v>
+        <v>14</v>
       </c>
       <c r="C40">
-        <v>-7.4</v>
+        <v>-7.66</v>
       </c>
       <c r="D40" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>16.73</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>-7.4</v>
       </c>
       <c r="D41" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>243</v>
+        <v>491</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>494</v>
+        <v>243</v>
       </c>
       <c r="B43">
-        <v>12.49</v>
+        <v>12</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B44">
         <v>12.49</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B45">
-        <v>8</v>
+        <v>12.49</v>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>273</v>
+        <v>498</v>
       </c>
       <c r="B46">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>500</v>
+        <v>273</v>
       </c>
       <c r="B47">
-        <v>14.55</v>
+        <v>14</v>
       </c>
       <c r="C47">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B48">
         <v>14.55</v>
       </c>
       <c r="C48">
-        <v>2.41</v>
+        <v>3.54</v>
       </c>
       <c r="D48" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B49">
-        <v>17.04</v>
+        <v>14.55</v>
       </c>
       <c r="C49">
         <v>2.41</v>
       </c>
       <c r="D49" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B50">
-        <v>18</v>
+        <v>17.04</v>
       </c>
       <c r="C50">
         <v>2.41</v>
       </c>
       <c r="D50" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B51">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C51">
         <v>2.41</v>
       </c>
       <c r="D51" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B52">
         <v>22</v>
       </c>
       <c r="C52">
-        <v>4.37</v>
+        <v>2.41</v>
       </c>
       <c r="D52" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B53">
-        <v>18.649999999999999</v>
+        <v>22</v>
       </c>
       <c r="C53">
         <v>4.37</v>
       </c>
       <c r="D53" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B54">
-        <v>17.04</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="C54">
-        <v>4.26</v>
+        <v>4.37</v>
       </c>
       <c r="D54" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B55">
-        <v>16.23</v>
+        <v>17.04</v>
       </c>
       <c r="C55">
         <v>4.26</v>
       </c>
       <c r="D55" t="s">
-        <v>517</v>
+        <v>717</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B56">
         <v>16.23</v>
       </c>
       <c r="C56">
-        <v>4.9000000000000004</v>
+        <v>4.26</v>
       </c>
       <c r="D56" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>16.23</v>
       </c>
       <c r="C57">
         <v>4.9000000000000004</v>
       </c>
       <c r="D57" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B58">
         <v>14</v>
       </c>
       <c r="C58">
-        <v>6.06</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D58" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B59">
-        <v>18.649999999999999</v>
+        <v>14</v>
       </c>
       <c r="C59">
-        <v>7.93</v>
+        <v>6.06</v>
+      </c>
+      <c r="D59" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>328</v>
+        <v>523</v>
       </c>
       <c r="B60">
-        <v>20</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="C60">
-        <v>8</v>
-      </c>
-      <c r="D60" t="s">
-        <v>525</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B61">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C61">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>527</v>
+        <v>325</v>
       </c>
       <c r="B62">
-        <v>25.5</v>
+        <v>22</v>
       </c>
       <c r="C62">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>528</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>526</v>
+      </c>
+      <c r="B63">
+        <v>25.5</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -33837,22 +35990,22 @@
       <c r="AZ3" s="6"/>
       <c r="BA3" s="6"/>
       <c r="BB3" s="7"/>
-      <c r="BD3" s="47"/>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="47"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="48"/>
-      <c r="BI3" s="48"/>
-      <c r="BJ3" s="48"/>
-      <c r="BK3" s="48"/>
-      <c r="BL3" s="48"/>
-      <c r="BM3" s="48"/>
-      <c r="BN3" s="48"/>
-      <c r="BO3" s="48"/>
-      <c r="BP3" s="49"/>
-      <c r="BQ3" s="49"/>
-      <c r="BR3" s="49"/>
-      <c r="BS3" s="49"/>
+      <c r="BD3" s="38"/>
+      <c r="BE3" s="38"/>
+      <c r="BF3" s="38"/>
+      <c r="BG3" s="38"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="39"/>
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="40"/>
+      <c r="BQ3" s="40"/>
+      <c r="BR3" s="40"/>
+      <c r="BS3" s="40"/>
     </row>
     <row r="4" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="10"/>
@@ -33907,22 +36060,22 @@
       <c r="AZ4" s="11"/>
       <c r="BA4" s="11"/>
       <c r="BB4" s="12"/>
-      <c r="BD4" s="47"/>
-      <c r="BE4" s="47"/>
-      <c r="BF4" s="47"/>
-      <c r="BG4" s="47"/>
-      <c r="BH4" s="48"/>
-      <c r="BI4" s="48"/>
-      <c r="BJ4" s="48"/>
-      <c r="BK4" s="48"/>
-      <c r="BL4" s="48"/>
-      <c r="BM4" s="48"/>
-      <c r="BN4" s="48"/>
-      <c r="BO4" s="48"/>
-      <c r="BP4" s="49"/>
-      <c r="BQ4" s="49"/>
-      <c r="BR4" s="49"/>
-      <c r="BS4" s="49"/>
+      <c r="BD4" s="38"/>
+      <c r="BE4" s="38"/>
+      <c r="BF4" s="38"/>
+      <c r="BG4" s="38"/>
+      <c r="BH4" s="39"/>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="39"/>
+      <c r="BL4" s="39"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="40"/>
+      <c r="BQ4" s="40"/>
+      <c r="BR4" s="40"/>
+      <c r="BS4" s="40"/>
     </row>
     <row r="5" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="15">
@@ -34003,22 +36156,22 @@
       <c r="AZ5" s="11"/>
       <c r="BA5" s="11"/>
       <c r="BB5" s="12"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="47"/>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="48"/>
-      <c r="BJ5" s="48"/>
-      <c r="BK5" s="48"/>
-      <c r="BL5" s="48"/>
-      <c r="BM5" s="48"/>
-      <c r="BN5" s="48"/>
-      <c r="BO5" s="48"/>
-      <c r="BP5" s="49"/>
-      <c r="BQ5" s="49"/>
-      <c r="BR5" s="49"/>
-      <c r="BS5" s="49"/>
+      <c r="BD5" s="38"/>
+      <c r="BE5" s="38"/>
+      <c r="BF5" s="38"/>
+      <c r="BG5" s="38"/>
+      <c r="BH5" s="39"/>
+      <c r="BI5" s="39"/>
+      <c r="BJ5" s="39"/>
+      <c r="BK5" s="39"/>
+      <c r="BL5" s="39"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
+      <c r="BO5" s="39"/>
+      <c r="BP5" s="40"/>
+      <c r="BQ5" s="40"/>
+      <c r="BR5" s="40"/>
+      <c r="BS5" s="40"/>
     </row>
     <row r="6" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="17">
@@ -34151,22 +36304,22 @@
       <c r="BB6" s="20">
         <v>12</v>
       </c>
-      <c r="BD6" s="47"/>
-      <c r="BE6" s="47"/>
-      <c r="BF6" s="47"/>
-      <c r="BG6" s="47"/>
-      <c r="BH6" s="48"/>
-      <c r="BI6" s="48"/>
-      <c r="BJ6" s="48"/>
-      <c r="BK6" s="48"/>
-      <c r="BL6" s="48"/>
-      <c r="BM6" s="48"/>
-      <c r="BN6" s="48"/>
-      <c r="BO6" s="48"/>
-      <c r="BP6" s="49"/>
-      <c r="BQ6" s="49"/>
-      <c r="BR6" s="49"/>
-      <c r="BS6" s="49"/>
+      <c r="BD6" s="38"/>
+      <c r="BE6" s="38"/>
+      <c r="BF6" s="38"/>
+      <c r="BG6" s="38"/>
+      <c r="BH6" s="39"/>
+      <c r="BI6" s="39"/>
+      <c r="BJ6" s="39"/>
+      <c r="BK6" s="39"/>
+      <c r="BL6" s="39"/>
+      <c r="BM6" s="39"/>
+      <c r="BN6" s="39"/>
+      <c r="BO6" s="39"/>
+      <c r="BP6" s="40"/>
+      <c r="BQ6" s="40"/>
+      <c r="BR6" s="40"/>
+      <c r="BS6" s="40"/>
     </row>
     <row r="7" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="5"/>
@@ -34221,26 +36374,26 @@
       <c r="AZ7" s="6"/>
       <c r="BA7" s="6"/>
       <c r="BB7" s="7"/>
-      <c r="BD7" s="50"/>
-      <c r="BE7" s="50"/>
-      <c r="BF7" s="50"/>
-      <c r="BG7" s="50"/>
-      <c r="BH7" s="51" t="s">
+      <c r="BD7" s="41"/>
+      <c r="BE7" s="41"/>
+      <c r="BF7" s="41"/>
+      <c r="BG7" s="41"/>
+      <c r="BH7" s="42" t="s">
+        <v>528</v>
+      </c>
+      <c r="BI7" s="42"/>
+      <c r="BJ7" s="42"/>
+      <c r="BK7" s="42"/>
+      <c r="BL7" s="43" t="s">
         <v>529</v>
       </c>
-      <c r="BI7" s="51"/>
-      <c r="BJ7" s="51"/>
-      <c r="BK7" s="51"/>
-      <c r="BL7" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="BM7" s="41"/>
-      <c r="BN7" s="41"/>
-      <c r="BO7" s="41"/>
-      <c r="BP7" s="42"/>
-      <c r="BQ7" s="42"/>
-      <c r="BR7" s="42"/>
-      <c r="BS7" s="42"/>
+      <c r="BM7" s="43"/>
+      <c r="BN7" s="43"/>
+      <c r="BO7" s="43"/>
+      <c r="BP7" s="44"/>
+      <c r="BQ7" s="44"/>
+      <c r="BR7" s="44"/>
+      <c r="BS7" s="44"/>
     </row>
     <row r="8" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="10"/>
@@ -34299,22 +36452,22 @@
       <c r="AZ8" s="11"/>
       <c r="BA8" s="11"/>
       <c r="BB8" s="12"/>
-      <c r="BD8" s="50"/>
-      <c r="BE8" s="50"/>
-      <c r="BF8" s="50"/>
-      <c r="BG8" s="50"/>
-      <c r="BH8" s="51"/>
-      <c r="BI8" s="51"/>
-      <c r="BJ8" s="51"/>
-      <c r="BK8" s="51"/>
-      <c r="BL8" s="41"/>
-      <c r="BM8" s="41"/>
-      <c r="BN8" s="41"/>
-      <c r="BO8" s="41"/>
-      <c r="BP8" s="42"/>
-      <c r="BQ8" s="42"/>
-      <c r="BR8" s="42"/>
-      <c r="BS8" s="42"/>
+      <c r="BD8" s="41"/>
+      <c r="BE8" s="41"/>
+      <c r="BF8" s="41"/>
+      <c r="BG8" s="41"/>
+      <c r="BH8" s="42"/>
+      <c r="BI8" s="42"/>
+      <c r="BJ8" s="42"/>
+      <c r="BK8" s="42"/>
+      <c r="BL8" s="43"/>
+      <c r="BM8" s="43"/>
+      <c r="BN8" s="43"/>
+      <c r="BO8" s="43"/>
+      <c r="BP8" s="44"/>
+      <c r="BQ8" s="44"/>
+      <c r="BR8" s="44"/>
+      <c r="BS8" s="44"/>
     </row>
     <row r="9" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="15">
@@ -34407,22 +36560,22 @@
       <c r="AZ9" s="11"/>
       <c r="BA9" s="11"/>
       <c r="BB9" s="12"/>
-      <c r="BD9" s="50"/>
-      <c r="BE9" s="50"/>
-      <c r="BF9" s="50"/>
-      <c r="BG9" s="50"/>
-      <c r="BH9" s="51"/>
-      <c r="BI9" s="51"/>
-      <c r="BJ9" s="51"/>
-      <c r="BK9" s="51"/>
-      <c r="BL9" s="41"/>
-      <c r="BM9" s="41"/>
-      <c r="BN9" s="41"/>
-      <c r="BO9" s="41"/>
-      <c r="BP9" s="42"/>
-      <c r="BQ9" s="42"/>
-      <c r="BR9" s="42"/>
-      <c r="BS9" s="42"/>
+      <c r="BD9" s="41"/>
+      <c r="BE9" s="41"/>
+      <c r="BF9" s="41"/>
+      <c r="BG9" s="41"/>
+      <c r="BH9" s="42"/>
+      <c r="BI9" s="42"/>
+      <c r="BJ9" s="42"/>
+      <c r="BK9" s="42"/>
+      <c r="BL9" s="43"/>
+      <c r="BM9" s="43"/>
+      <c r="BN9" s="43"/>
+      <c r="BO9" s="43"/>
+      <c r="BP9" s="44"/>
+      <c r="BQ9" s="44"/>
+      <c r="BR9" s="44"/>
+      <c r="BS9" s="44"/>
     </row>
     <row r="10" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="17">
@@ -34555,22 +36708,22 @@
       <c r="BB10" s="20">
         <v>10</v>
       </c>
-      <c r="BD10" s="50"/>
-      <c r="BE10" s="50"/>
-      <c r="BF10" s="50"/>
-      <c r="BG10" s="50"/>
-      <c r="BH10" s="51"/>
-      <c r="BI10" s="51"/>
-      <c r="BJ10" s="51"/>
-      <c r="BK10" s="51"/>
-      <c r="BL10" s="41"/>
-      <c r="BM10" s="41"/>
-      <c r="BN10" s="41"/>
-      <c r="BO10" s="41"/>
-      <c r="BP10" s="42"/>
-      <c r="BQ10" s="42"/>
-      <c r="BR10" s="42"/>
-      <c r="BS10" s="42"/>
+      <c r="BD10" s="41"/>
+      <c r="BE10" s="41"/>
+      <c r="BF10" s="41"/>
+      <c r="BG10" s="41"/>
+      <c r="BH10" s="42"/>
+      <c r="BI10" s="42"/>
+      <c r="BJ10" s="42"/>
+      <c r="BK10" s="42"/>
+      <c r="BL10" s="43"/>
+      <c r="BM10" s="43"/>
+      <c r="BN10" s="43"/>
+      <c r="BO10" s="43"/>
+      <c r="BP10" s="44"/>
+      <c r="BQ10" s="44"/>
+      <c r="BR10" s="44"/>
+      <c r="BS10" s="44"/>
     </row>
     <row r="11" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="5"/>
@@ -34625,30 +36778,30 @@
       <c r="AZ11" s="6"/>
       <c r="BA11" s="6"/>
       <c r="BB11" s="7"/>
-      <c r="BD11" s="40" t="s">
+      <c r="BD11" s="47" t="s">
+        <v>530</v>
+      </c>
+      <c r="BE11" s="47"/>
+      <c r="BF11" s="47"/>
+      <c r="BG11" s="47"/>
+      <c r="BH11" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="BE11" s="40"/>
-      <c r="BF11" s="40"/>
-      <c r="BG11" s="40"/>
-      <c r="BH11" s="41" t="s">
+      <c r="BI11" s="43"/>
+      <c r="BJ11" s="43"/>
+      <c r="BK11" s="43"/>
+      <c r="BL11" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="BI11" s="41"/>
-      <c r="BJ11" s="41"/>
-      <c r="BK11" s="41"/>
-      <c r="BL11" s="41" t="s">
+      <c r="BM11" s="43"/>
+      <c r="BN11" s="43"/>
+      <c r="BO11" s="43"/>
+      <c r="BP11" s="44" t="s">
         <v>533</v>
       </c>
-      <c r="BM11" s="41"/>
-      <c r="BN11" s="41"/>
-      <c r="BO11" s="41"/>
-      <c r="BP11" s="42" t="s">
-        <v>534</v>
-      </c>
-      <c r="BQ11" s="42"/>
-      <c r="BR11" s="42"/>
-      <c r="BS11" s="42"/>
+      <c r="BQ11" s="44"/>
+      <c r="BR11" s="44"/>
+      <c r="BS11" s="44"/>
     </row>
     <row r="12" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="10"/>
@@ -34723,22 +36876,22 @@
       <c r="AZ12" s="11"/>
       <c r="BA12" s="11"/>
       <c r="BB12" s="12"/>
-      <c r="BD12" s="40"/>
-      <c r="BE12" s="40"/>
-      <c r="BF12" s="40"/>
-      <c r="BG12" s="40"/>
-      <c r="BH12" s="41"/>
-      <c r="BI12" s="41"/>
-      <c r="BJ12" s="41"/>
-      <c r="BK12" s="41"/>
-      <c r="BL12" s="41"/>
-      <c r="BM12" s="41"/>
-      <c r="BN12" s="41"/>
-      <c r="BO12" s="41"/>
-      <c r="BP12" s="42"/>
-      <c r="BQ12" s="42"/>
-      <c r="BR12" s="42"/>
-      <c r="BS12" s="42"/>
+      <c r="BD12" s="47"/>
+      <c r="BE12" s="47"/>
+      <c r="BF12" s="47"/>
+      <c r="BG12" s="47"/>
+      <c r="BH12" s="43"/>
+      <c r="BI12" s="43"/>
+      <c r="BJ12" s="43"/>
+      <c r="BK12" s="43"/>
+      <c r="BL12" s="43"/>
+      <c r="BM12" s="43"/>
+      <c r="BN12" s="43"/>
+      <c r="BO12" s="43"/>
+      <c r="BP12" s="44"/>
+      <c r="BQ12" s="44"/>
+      <c r="BR12" s="44"/>
+      <c r="BS12" s="44"/>
     </row>
     <row r="13" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="15">
@@ -34855,22 +37008,22 @@
       <c r="AZ13" s="11"/>
       <c r="BA13" s="11"/>
       <c r="BB13" s="12"/>
-      <c r="BD13" s="40"/>
-      <c r="BE13" s="40"/>
-      <c r="BF13" s="40"/>
-      <c r="BG13" s="40"/>
-      <c r="BH13" s="41"/>
-      <c r="BI13" s="41"/>
-      <c r="BJ13" s="41"/>
-      <c r="BK13" s="41"/>
-      <c r="BL13" s="41"/>
-      <c r="BM13" s="41"/>
-      <c r="BN13" s="41"/>
-      <c r="BO13" s="41"/>
-      <c r="BP13" s="42"/>
-      <c r="BQ13" s="42"/>
-      <c r="BR13" s="42"/>
-      <c r="BS13" s="42"/>
+      <c r="BD13" s="47"/>
+      <c r="BE13" s="47"/>
+      <c r="BF13" s="47"/>
+      <c r="BG13" s="47"/>
+      <c r="BH13" s="43"/>
+      <c r="BI13" s="43"/>
+      <c r="BJ13" s="43"/>
+      <c r="BK13" s="43"/>
+      <c r="BL13" s="43"/>
+      <c r="BM13" s="43"/>
+      <c r="BN13" s="43"/>
+      <c r="BO13" s="43"/>
+      <c r="BP13" s="44"/>
+      <c r="BQ13" s="44"/>
+      <c r="BR13" s="44"/>
+      <c r="BS13" s="44"/>
     </row>
     <row r="14" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="17">
@@ -35003,22 +37156,22 @@
       <c r="BB14" s="20">
         <v>8</v>
       </c>
-      <c r="BD14" s="40"/>
-      <c r="BE14" s="40"/>
-      <c r="BF14" s="40"/>
-      <c r="BG14" s="40"/>
-      <c r="BH14" s="41"/>
-      <c r="BI14" s="41"/>
-      <c r="BJ14" s="41"/>
-      <c r="BK14" s="41"/>
-      <c r="BL14" s="41"/>
-      <c r="BM14" s="41"/>
-      <c r="BN14" s="41"/>
-      <c r="BO14" s="41"/>
-      <c r="BP14" s="42"/>
-      <c r="BQ14" s="42"/>
-      <c r="BR14" s="42"/>
-      <c r="BS14" s="42"/>
+      <c r="BD14" s="47"/>
+      <c r="BE14" s="47"/>
+      <c r="BF14" s="47"/>
+      <c r="BG14" s="47"/>
+      <c r="BH14" s="43"/>
+      <c r="BI14" s="43"/>
+      <c r="BJ14" s="43"/>
+      <c r="BK14" s="43"/>
+      <c r="BL14" s="43"/>
+      <c r="BM14" s="43"/>
+      <c r="BN14" s="43"/>
+      <c r="BO14" s="43"/>
+      <c r="BP14" s="44"/>
+      <c r="BQ14" s="44"/>
+      <c r="BR14" s="44"/>
+      <c r="BS14" s="44"/>
     </row>
     <row r="15" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5"/>
@@ -35073,28 +37226,28 @@
       <c r="AZ15" s="6"/>
       <c r="BA15" s="6"/>
       <c r="BB15" s="7"/>
-      <c r="BD15" s="43" t="s">
+      <c r="BD15" s="48" t="s">
+        <v>534</v>
+      </c>
+      <c r="BE15" s="48"/>
+      <c r="BF15" s="48"/>
+      <c r="BG15" s="48"/>
+      <c r="BH15" s="49"/>
+      <c r="BI15" s="49"/>
+      <c r="BJ15" s="49"/>
+      <c r="BK15" s="49"/>
+      <c r="BL15" s="50" t="s">
         <v>535</v>
       </c>
-      <c r="BE15" s="43"/>
-      <c r="BF15" s="43"/>
-      <c r="BG15" s="43"/>
-      <c r="BH15" s="44"/>
-      <c r="BI15" s="44"/>
-      <c r="BJ15" s="44"/>
-      <c r="BK15" s="44"/>
-      <c r="BL15" s="45" t="s">
+      <c r="BM15" s="50"/>
+      <c r="BN15" s="50"/>
+      <c r="BO15" s="50"/>
+      <c r="BP15" s="51" t="s">
         <v>536</v>
       </c>
-      <c r="BM15" s="45"/>
-      <c r="BN15" s="45"/>
-      <c r="BO15" s="45"/>
-      <c r="BP15" s="46" t="s">
-        <v>537</v>
-      </c>
-      <c r="BQ15" s="46"/>
-      <c r="BR15" s="46"/>
-      <c r="BS15" s="46"/>
+      <c r="BQ15" s="51"/>
+      <c r="BR15" s="51"/>
+      <c r="BS15" s="51"/>
     </row>
     <row r="16" spans="3:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="10"/>
@@ -35179,22 +37332,22 @@
       <c r="AZ16" s="11"/>
       <c r="BA16" s="11"/>
       <c r="BB16" s="12"/>
-      <c r="BD16" s="43"/>
-      <c r="BE16" s="43"/>
-      <c r="BF16" s="43"/>
-      <c r="BG16" s="43"/>
-      <c r="BH16" s="44"/>
-      <c r="BI16" s="44"/>
-      <c r="BJ16" s="44"/>
-      <c r="BK16" s="44"/>
-      <c r="BL16" s="45"/>
-      <c r="BM16" s="45"/>
-      <c r="BN16" s="45"/>
-      <c r="BO16" s="45"/>
-      <c r="BP16" s="46"/>
-      <c r="BQ16" s="46"/>
-      <c r="BR16" s="46"/>
-      <c r="BS16" s="46"/>
+      <c r="BD16" s="48"/>
+      <c r="BE16" s="48"/>
+      <c r="BF16" s="48"/>
+      <c r="BG16" s="48"/>
+      <c r="BH16" s="49"/>
+      <c r="BI16" s="49"/>
+      <c r="BJ16" s="49"/>
+      <c r="BK16" s="49"/>
+      <c r="BL16" s="50"/>
+      <c r="BM16" s="50"/>
+      <c r="BN16" s="50"/>
+      <c r="BO16" s="50"/>
+      <c r="BP16" s="51"/>
+      <c r="BQ16" s="51"/>
+      <c r="BR16" s="51"/>
+      <c r="BS16" s="51"/>
     </row>
     <row r="17" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="15">
@@ -35321,22 +37474,22 @@
       <c r="AZ17" s="11"/>
       <c r="BA17" s="11"/>
       <c r="BB17" s="12"/>
-      <c r="BD17" s="43"/>
-      <c r="BE17" s="43"/>
-      <c r="BF17" s="43"/>
-      <c r="BG17" s="43"/>
-      <c r="BH17" s="44"/>
-      <c r="BI17" s="44"/>
-      <c r="BJ17" s="44"/>
-      <c r="BK17" s="44"/>
-      <c r="BL17" s="45"/>
-      <c r="BM17" s="45"/>
-      <c r="BN17" s="45"/>
-      <c r="BO17" s="45"/>
-      <c r="BP17" s="46"/>
-      <c r="BQ17" s="46"/>
-      <c r="BR17" s="46"/>
-      <c r="BS17" s="46"/>
+      <c r="BD17" s="48"/>
+      <c r="BE17" s="48"/>
+      <c r="BF17" s="48"/>
+      <c r="BG17" s="48"/>
+      <c r="BH17" s="49"/>
+      <c r="BI17" s="49"/>
+      <c r="BJ17" s="49"/>
+      <c r="BK17" s="49"/>
+      <c r="BL17" s="50"/>
+      <c r="BM17" s="50"/>
+      <c r="BN17" s="50"/>
+      <c r="BO17" s="50"/>
+      <c r="BP17" s="51"/>
+      <c r="BQ17" s="51"/>
+      <c r="BR17" s="51"/>
+      <c r="BS17" s="51"/>
     </row>
     <row r="18" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="17">
@@ -35469,22 +37622,22 @@
       <c r="BB18" s="20">
         <v>6</v>
       </c>
-      <c r="BD18" s="43"/>
-      <c r="BE18" s="43"/>
-      <c r="BF18" s="43"/>
-      <c r="BG18" s="43"/>
-      <c r="BH18" s="44"/>
-      <c r="BI18" s="44"/>
-      <c r="BJ18" s="44"/>
-      <c r="BK18" s="44"/>
-      <c r="BL18" s="45"/>
-      <c r="BM18" s="45"/>
-      <c r="BN18" s="45"/>
-      <c r="BO18" s="45"/>
-      <c r="BP18" s="46"/>
-      <c r="BQ18" s="46"/>
-      <c r="BR18" s="46"/>
-      <c r="BS18" s="46"/>
+      <c r="BD18" s="48"/>
+      <c r="BE18" s="48"/>
+      <c r="BF18" s="48"/>
+      <c r="BG18" s="48"/>
+      <c r="BH18" s="49"/>
+      <c r="BI18" s="49"/>
+      <c r="BJ18" s="49"/>
+      <c r="BK18" s="49"/>
+      <c r="BL18" s="50"/>
+      <c r="BM18" s="50"/>
+      <c r="BN18" s="50"/>
+      <c r="BO18" s="50"/>
+      <c r="BP18" s="51"/>
+      <c r="BQ18" s="51"/>
+      <c r="BR18" s="51"/>
+      <c r="BS18" s="51"/>
     </row>
     <row r="19" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="5"/>
@@ -35629,13 +37782,13 @@
       <c r="AZ20" s="11"/>
       <c r="BA20" s="11"/>
       <c r="BB20" s="12"/>
-      <c r="BD20" s="38" t="s">
+      <c r="BD20" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="BE20" s="38"/>
-      <c r="BF20" s="38"/>
-      <c r="BG20" s="38"/>
-      <c r="BH20" s="38"/>
+      <c r="BE20" s="45"/>
+      <c r="BF20" s="45"/>
+      <c r="BG20" s="45"/>
+      <c r="BH20" s="45"/>
     </row>
     <row r="21" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="15">
@@ -35764,11 +37917,11 @@
       <c r="AZ21" s="11"/>
       <c r="BA21" s="11"/>
       <c r="BB21" s="12"/>
-      <c r="BD21" s="38"/>
-      <c r="BE21" s="38"/>
-      <c r="BF21" s="38"/>
-      <c r="BG21" s="38"/>
-      <c r="BH21" s="38"/>
+      <c r="BD21" s="45"/>
+      <c r="BE21" s="45"/>
+      <c r="BF21" s="45"/>
+      <c r="BG21" s="45"/>
+      <c r="BH21" s="45"/>
     </row>
     <row r="22" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
@@ -35902,11 +38055,11 @@
       <c r="BB22" s="20">
         <v>4</v>
       </c>
-      <c r="BD22" s="38"/>
-      <c r="BE22" s="38"/>
-      <c r="BF22" s="38"/>
-      <c r="BG22" s="38"/>
-      <c r="BH22" s="38"/>
+      <c r="BD22" s="45"/>
+      <c r="BE22" s="45"/>
+      <c r="BF22" s="45"/>
+      <c r="BG22" s="45"/>
+      <c r="BH22" s="45"/>
     </row>
     <row r="23" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="5"/>
@@ -35961,11 +38114,11 @@
       <c r="AZ23" s="6"/>
       <c r="BA23" s="6"/>
       <c r="BB23" s="7"/>
-      <c r="BD23" s="38"/>
-      <c r="BE23" s="38"/>
-      <c r="BF23" s="38"/>
-      <c r="BG23" s="38"/>
-      <c r="BH23" s="38"/>
+      <c r="BD23" s="45"/>
+      <c r="BE23" s="45"/>
+      <c r="BF23" s="45"/>
+      <c r="BG23" s="45"/>
+      <c r="BH23" s="45"/>
     </row>
     <row r="24" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="10"/>
@@ -36052,11 +38205,11 @@
       <c r="AZ24" s="11"/>
       <c r="BA24" s="11"/>
       <c r="BB24" s="12"/>
-      <c r="BD24" s="38"/>
-      <c r="BE24" s="38"/>
-      <c r="BF24" s="38"/>
-      <c r="BG24" s="38"/>
-      <c r="BH24" s="38"/>
+      <c r="BD24" s="45"/>
+      <c r="BE24" s="45"/>
+      <c r="BF24" s="45"/>
+      <c r="BG24" s="45"/>
+      <c r="BH24" s="45"/>
     </row>
     <row r="25" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="15">
@@ -36465,24 +38618,24 @@
         <v>59</v>
       </c>
       <c r="BB28" s="12"/>
-      <c r="BD28" s="39" t="s">
-        <v>538</v>
-      </c>
-      <c r="BE28" s="39"/>
-      <c r="BF28" s="39"/>
-      <c r="BG28" s="39"/>
-      <c r="BH28" s="39"/>
-      <c r="BI28" s="39"/>
-      <c r="BJ28" s="39"/>
-      <c r="BK28" s="39"/>
-      <c r="BL28" s="39"/>
-      <c r="BM28" s="39"/>
-      <c r="BN28" s="39"/>
-      <c r="BO28" s="39"/>
-      <c r="BP28" s="39"/>
-      <c r="BQ28" s="39"/>
-      <c r="BR28" s="39"/>
-      <c r="BS28" s="39"/>
+      <c r="BD28" s="46" t="s">
+        <v>537</v>
+      </c>
+      <c r="BE28" s="46"/>
+      <c r="BF28" s="46"/>
+      <c r="BG28" s="46"/>
+      <c r="BH28" s="46"/>
+      <c r="BI28" s="46"/>
+      <c r="BJ28" s="46"/>
+      <c r="BK28" s="46"/>
+      <c r="BL28" s="46"/>
+      <c r="BM28" s="46"/>
+      <c r="BN28" s="46"/>
+      <c r="BO28" s="46"/>
+      <c r="BP28" s="46"/>
+      <c r="BQ28" s="46"/>
+      <c r="BR28" s="46"/>
+      <c r="BS28" s="46"/>
     </row>
     <row r="29" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="15">
@@ -36617,22 +38770,22 @@
       <c r="BB29" s="12">
         <v>7</v>
       </c>
-      <c r="BD29" s="39"/>
-      <c r="BE29" s="39"/>
-      <c r="BF29" s="39"/>
-      <c r="BG29" s="39"/>
-      <c r="BH29" s="39"/>
-      <c r="BI29" s="39"/>
-      <c r="BJ29" s="39"/>
-      <c r="BK29" s="39"/>
-      <c r="BL29" s="39"/>
-      <c r="BM29" s="39"/>
-      <c r="BN29" s="39"/>
-      <c r="BO29" s="39"/>
-      <c r="BP29" s="39"/>
-      <c r="BQ29" s="39"/>
-      <c r="BR29" s="39"/>
-      <c r="BS29" s="39"/>
+      <c r="BD29" s="46"/>
+      <c r="BE29" s="46"/>
+      <c r="BF29" s="46"/>
+      <c r="BG29" s="46"/>
+      <c r="BH29" s="46"/>
+      <c r="BI29" s="46"/>
+      <c r="BJ29" s="46"/>
+      <c r="BK29" s="46"/>
+      <c r="BL29" s="46"/>
+      <c r="BM29" s="46"/>
+      <c r="BN29" s="46"/>
+      <c r="BO29" s="46"/>
+      <c r="BP29" s="46"/>
+      <c r="BQ29" s="46"/>
+      <c r="BR29" s="46"/>
+      <c r="BS29" s="46"/>
     </row>
     <row r="30" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="26">
@@ -38902,14 +41055,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="BD3:BG6"/>
-    <mergeCell ref="BH3:BK6"/>
-    <mergeCell ref="BL3:BO6"/>
-    <mergeCell ref="BP3:BS6"/>
-    <mergeCell ref="BD7:BG10"/>
-    <mergeCell ref="BH7:BK10"/>
-    <mergeCell ref="BL7:BO10"/>
-    <mergeCell ref="BP7:BS10"/>
     <mergeCell ref="BD20:BH24"/>
     <mergeCell ref="BD28:BS29"/>
     <mergeCell ref="BD11:BG14"/>
@@ -38920,6 +41065,14 @@
     <mergeCell ref="BH15:BK18"/>
     <mergeCell ref="BL15:BO18"/>
     <mergeCell ref="BP15:BS18"/>
+    <mergeCell ref="BD3:BG6"/>
+    <mergeCell ref="BH3:BK6"/>
+    <mergeCell ref="BL3:BO6"/>
+    <mergeCell ref="BP3:BS6"/>
+    <mergeCell ref="BD7:BG10"/>
+    <mergeCell ref="BH7:BK10"/>
+    <mergeCell ref="BL7:BO10"/>
+    <mergeCell ref="BP7:BS10"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -38943,60 +41096,60 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B1" t="s">
         <v>539</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>540</v>
-      </c>
-      <c r="C1" t="s">
-        <v>541</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F1" t="s">
         <v>542</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>543</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>544</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>545</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>546</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>547</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>548</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>549</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>550</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>551</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>552</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>553</v>
-      </c>
-      <c r="S1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B2">
         <v>34</v>
@@ -39031,7 +41184,7 @@
     </row>
     <row r="3" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A3" s="37" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B3">
         <v>34</v>
@@ -39056,7 +41209,7 @@
     </row>
     <row r="4" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="37" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -39081,7 +41234,7 @@
     </row>
     <row r="5" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -39104,7 +41257,7 @@
     </row>
     <row r="6" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B6">
         <v>14</v>
@@ -42160,7 +44313,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K198">
         <v>46.001860000000001</v>
@@ -42171,7 +44324,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K199">
         <v>46.001950000000001</v>
@@ -42182,7 +44335,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K200">
         <v>46.002139999999997</v>
@@ -42193,7 +44346,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K201">
         <v>46.002319999999997</v>
@@ -42204,7 +44357,7 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K202">
         <v>46.002429999999997</v>
@@ -42215,7 +44368,7 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K203">
         <v>46.00271</v>
@@ -42226,7 +44379,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K204">
         <v>46.002560000000003</v>
@@ -42237,7 +44390,7 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K205">
         <v>46.002569999999999</v>
@@ -42248,7 +44401,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K206">
         <v>46.002549999999999</v>
@@ -42259,7 +44412,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K207">
         <v>46.002800000000001</v>
@@ -42270,7 +44423,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K208">
         <v>46.002809999999997</v>
@@ -42281,7 +44434,7 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K209">
         <v>46.002879999999998</v>
@@ -42292,7 +44445,7 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K210">
         <v>46.003050000000002</v>
@@ -42303,7 +44456,7 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K211">
         <v>46.003039999999999</v>
@@ -42314,7 +44467,7 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K212">
         <v>46.003050000000002</v>
@@ -42325,7 +44478,7 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K213">
         <v>46.001989999999999</v>
@@ -42336,7 +44489,7 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K214">
         <v>46.002009999999999</v>
@@ -42347,7 +44500,7 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K215">
         <v>46.002130000000001</v>
@@ -42358,7 +44511,7 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K216">
         <v>46.002189999999999</v>
@@ -42369,7 +44522,7 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K217">
         <v>46.002369999999999</v>
@@ -42380,7 +44533,7 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K218">
         <v>46.001370000000001</v>
@@ -42391,7 +44544,7 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K219">
         <v>46.001460000000002</v>
@@ -42402,7 +44555,7 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K220">
         <v>46.001440000000002</v>
@@ -42413,7 +44566,7 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K221">
         <v>46.001579999999997</v>
@@ -42424,7 +44577,7 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K222">
         <v>46.001800000000003</v>
@@ -42435,7 +44588,7 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K223">
         <v>45.999769999999998</v>
@@ -42457,7 +44610,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K225">
         <v>45.999960000000002</v>
@@ -42490,7 +44643,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K228">
         <v>46.001170000000002</v>
@@ -42501,7 +44654,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K229">
         <v>46.001330000000003</v>
@@ -42512,7 +44665,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K230">
         <v>46.001399999999997</v>
@@ -42534,7 +44687,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K232">
         <v>46.001759999999997</v>
@@ -42545,7 +44698,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K233">
         <v>46.00217</v>
@@ -42556,7 +44709,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K234">
         <v>46.00206</v>
@@ -42567,7 +44720,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K235">
         <v>46.001980000000003</v>
@@ -42578,7 +44731,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="K236">
         <v>46.002079999999999</v>
@@ -42589,7 +44742,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K237">
         <v>46.002220000000001</v>
@@ -42600,7 +44753,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K238">
         <v>46.003270000000001</v>
@@ -42611,7 +44764,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K239">
         <v>46.003369999999997</v>
@@ -42622,7 +44775,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K240">
         <v>46.003700000000002</v>
@@ -42633,7 +44786,7 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K241">
         <v>46.003799999999998</v>
@@ -42644,7 +44797,7 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K242">
         <v>46.003839999999997</v>
@@ -42710,7 +44863,7 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K248">
         <v>46.001829999999998</v>
@@ -42721,7 +44874,7 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K249">
         <v>46.001840000000001</v>
@@ -42732,7 +44885,7 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K250">
         <v>46.001759999999997</v>
@@ -42743,7 +44896,7 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K251">
         <v>46.001910000000002</v>
@@ -42754,7 +44907,7 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K252">
         <v>46.00206</v>
@@ -42765,7 +44918,7 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K253">
         <v>46.00217</v>
@@ -42776,7 +44929,7 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K254">
         <v>46.002220000000001</v>
@@ -42787,7 +44940,7 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K255">
         <v>46.002279999999999</v>
@@ -42798,7 +44951,7 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K256">
         <v>46.002310000000001</v>
@@ -42809,7 +44962,7 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K257">
         <v>46.002479999999998</v>
@@ -42820,7 +44973,7 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K258">
         <v>46.001370000000001</v>
@@ -42831,7 +44984,7 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K259">
         <v>46.001489999999997</v>
@@ -42842,7 +44995,7 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K260">
         <v>46.00159</v>
@@ -42853,7 +45006,7 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K261">
         <v>46.001649999999998</v>
@@ -42864,7 +45017,7 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K262">
         <v>46.001640000000002</v>
@@ -42875,7 +45028,7 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K263">
         <v>46.003430000000002</v>
@@ -42886,7 +45039,7 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K264">
         <v>46.003540000000001</v>
@@ -42897,7 +45050,7 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K265">
         <v>46.003570000000003</v>
@@ -42908,7 +45061,7 @@
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K266">
         <v>46.00365</v>
@@ -42919,7 +45072,7 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K267">
         <v>46.003680000000003</v>
@@ -42930,7 +45083,7 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K268">
         <v>46.000889999999998</v>
@@ -42941,7 +45094,7 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K269">
         <v>46.000950000000003</v>
@@ -42952,7 +45105,7 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K270">
         <v>46.001060000000003</v>
@@ -42963,7 +45116,7 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K271">
         <v>46.001089999999998</v>
@@ -42974,7 +45127,7 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K272">
         <v>46.00121</v>
@@ -42985,7 +45138,7 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K273">
         <v>46.002890000000001</v>
@@ -42996,7 +45149,7 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K274">
         <v>46.003070000000001</v>
@@ -43007,7 +45160,7 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K275">
         <v>46.003010000000003</v>
@@ -43018,7 +45171,7 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K276">
         <v>46.003120000000003</v>
@@ -43029,7 +45182,7 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K277">
         <v>46.003279999999997</v>
@@ -43040,7 +45193,7 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K278">
         <v>46.000720000000001</v>
@@ -43051,7 +45204,7 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K279">
         <v>46.000999999999998</v>
@@ -43062,7 +45215,7 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K280">
         <v>46.00112</v>
@@ -43073,7 +45226,7 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K281">
         <v>46.000990000000002</v>
@@ -43084,7 +45237,7 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K282">
         <v>46.001109999999997</v>
@@ -43095,7 +45248,7 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K283">
         <v>46.00132</v>
@@ -43106,7 +45259,7 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K284">
         <v>46.001469999999998</v>
@@ -43117,7 +45270,7 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K285">
         <v>46.001530000000002</v>
@@ -43128,7 +45281,7 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K286">
         <v>46.001620000000003</v>
@@ -43139,7 +45292,7 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K287">
         <v>46.00159</v>
@@ -43150,7 +45303,7 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K288">
         <v>46.002330000000001</v>
@@ -43161,7 +45314,7 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K289">
         <v>46.00244</v>
@@ -43172,7 +45325,7 @@
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K290">
         <v>46.002470000000002</v>
@@ -43183,7 +45336,7 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K291">
         <v>46.002499999999998</v>
@@ -43194,7 +45347,7 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="K292">
         <v>46.002600000000001</v>
@@ -43205,7 +45358,7 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K293">
         <v>46.000799999999998</v>
@@ -43216,7 +45369,7 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K294">
         <v>46.000909999999998</v>
@@ -43227,7 +45380,7 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K295">
         <v>46.000999999999998</v>
@@ -43238,7 +45391,7 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K296">
         <v>46.001370000000001</v>
@@ -43249,7 +45402,7 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K297">
         <v>46.001220000000004</v>
@@ -43260,7 +45413,7 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K298">
         <v>46.001939999999998</v>
@@ -43271,7 +45424,7 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K299">
         <v>46.001919999999998</v>
@@ -43282,7 +45435,7 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K300">
         <v>46.002000000000002</v>
@@ -43293,7 +45446,7 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K301">
         <v>46.001989999999999</v>
@@ -43304,7 +45457,7 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K302">
         <v>46.002090000000003</v>
@@ -43315,7 +45468,7 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K303">
         <v>46.001330000000003</v>
@@ -43326,7 +45479,7 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K304">
         <v>46.001609999999999</v>
@@ -43337,7 +45490,7 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K305">
         <v>46.00179</v>
@@ -43348,7 +45501,7 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K306">
         <v>46.001939999999998</v>
@@ -43359,7 +45512,7 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K307">
         <v>46.001809999999999</v>
@@ -43370,7 +45523,7 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K308">
         <v>46.00271</v>
@@ -43381,7 +45534,7 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K309">
         <v>46.002839999999999</v>
@@ -43392,7 +45545,7 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K310">
         <v>46.002929999999999</v>
@@ -43403,7 +45556,7 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K311">
         <v>46.003039999999999</v>
@@ -43414,7 +45567,7 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K312">
         <v>46.00311</v>
@@ -43425,7 +45578,7 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K313">
         <v>46.003010000000003</v>
@@ -43436,7 +45589,7 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K314">
         <v>46.003019999999999</v>
@@ -43447,7 +45600,7 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K315">
         <v>46.003219999999999</v>
@@ -43458,7 +45611,7 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K316">
         <v>46.003369999999997</v>
@@ -43469,7 +45622,7 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K317">
         <v>46.003369999999997</v>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -16,6 +16,7 @@
     <sheet name="map_chain" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="Image_J_cut_stump" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="Image_J_subplot_locations" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Recorded_subplot_locations" sheetId="9" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4885" uniqueCount="711">
   <si>
     <t xml:space="preserve">Block</t>
   </si>
@@ -2076,6 +2077,90 @@
   </si>
   <si>
     <t xml:space="preserve">E45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">old_plot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new_plot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chain_ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chain_x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chain_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chain_ref2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chain_x2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chain_y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">azi2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">links2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ft2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nchain_ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nchain_x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nchain_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nazi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nlinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5</t>
   </si>
 </sst>
 </file>
@@ -41726,4 +41811,3939 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:U126"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>684</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>691</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>693</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>695</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <f aca="false">H2*7.92/12</f>
+        <v>48.84</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="P2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="R2" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="S2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="T2" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="U2" s="0" t="n">
+        <f aca="false">T2*7.92/12</f>
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>172</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">N3*7.92/12</f>
+        <v>113.52</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">N4*7.92/12</f>
+        <v>68.64</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>343</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <f aca="false">H5*7.92/12</f>
+        <v>92.4</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>156</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <f aca="false">N5*7.92/12</f>
+        <v>102.96</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="P6" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="S6" s="0" t="n">
+        <v>343</v>
+      </c>
+      <c r="T6" s="0" t="n">
+        <v>134</v>
+      </c>
+      <c r="U6" s="0" t="n">
+        <f aca="false">T6*7.92/12</f>
+        <v>88.44</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="P7" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" s="0" t="n">
+        <v>273</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>119</v>
+      </c>
+      <c r="U7" s="0" t="n">
+        <f aca="false">T7*7.92/12</f>
+        <v>78.54</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>146</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>215</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>226</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>255</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>277</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>591</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <f aca="false">H26*7.92/12</f>
+        <v>130.68</v>
+      </c>
+      <c r="P26" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q26" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="R26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="T26" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="U26" s="0" t="n">
+        <f aca="false">T26*7.92/12</f>
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>234</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <f aca="false">H27*7.92/12</f>
+        <v>154.44</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="O27" s="0" t="n">
+        <f aca="false">N27*7.92/12</f>
+        <v>130.68</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>153</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>202</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <f aca="false">H28*7.92/12</f>
+        <v>133.32</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" s="0" t="n">
+        <v>235</v>
+      </c>
+      <c r="O28" s="0" t="n">
+        <f aca="false">N28*7.92/12</f>
+        <v>155.1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>176</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>163</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <f aca="false">H29*7.92/12</f>
+        <v>107.58</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L29" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M29" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="N29" s="0" t="n">
+        <v>151</v>
+      </c>
+      <c r="O29" s="0" t="n">
+        <f aca="false">N29*7.92/12</f>
+        <v>99.66</v>
+      </c>
+      <c r="P29" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q29" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="R29" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S29" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="T29" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="U29" s="0" t="n">
+        <f aca="false">T29*7.92/12</f>
+        <v>75.9</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>597</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <f aca="false">H30*7.92/12</f>
+        <v>66</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="N30" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="O30" s="0" t="n">
+        <f aca="false">N30*7.92/12</f>
+        <v>81.18</v>
+      </c>
+      <c r="P30" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q30" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="R30" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S30" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="T30" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="U30" s="0" t="n">
+        <f aca="false">T30*7.92/12</f>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="N31" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="O31" s="0" t="n">
+        <f aca="false">N31*7.92/12</f>
+        <v>93.06</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="P33" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q33" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="R33" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="T33" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="U33" s="0" t="n">
+        <f aca="false">T33*7.92/12</f>
+        <v>61.38</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>224</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>281</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>164</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>181</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <f aca="false">H42*7.92/12</f>
+        <v>34.98</v>
+      </c>
+      <c r="P42" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q42" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="R42" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S42" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="T42" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="U42" s="0" t="n">
+        <f aca="false">T42*7.92/12</f>
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <f aca="false">H43*7.92/12</f>
+        <v>75.24</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>253</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <f aca="false">H44*7.92/12</f>
+        <v>35.64</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>277</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>321</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <f aca="false">H46*7.92/12</f>
+        <v>87.12</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>613</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>196</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>357</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>322</v>
+      </c>
+      <c r="I52" s="0" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>318</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <f aca="false">H54*7.92/12</f>
+        <v>93.06</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="O54" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <f aca="false">H55*7.92/12</f>
+        <v>39.6</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L55" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="N55" s="0" t="n">
+        <v>154</v>
+      </c>
+      <c r="O55" s="0" t="n">
+        <f aca="false">N55*7.92/12</f>
+        <v>101.64</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>281</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <f aca="false">H56*7.92/12</f>
+        <v>30.36</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L56" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M56" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="N56" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="O56" s="0" t="n">
+        <f aca="false">N56*7.92/12</f>
+        <v>120.12</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="P57" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q57" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="R57" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="T57" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <f aca="false">T57*7.92/12</f>
+        <v>75.9</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>621</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>622</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>228</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>258</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>705</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="P64" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q64" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="R64" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S64" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="T64" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="U64" s="0" t="n">
+        <f aca="false">T64*7.92/12</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="I66" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E67" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="I67" s="0" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E68" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="I68" s="0" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>625</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E69" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="I69" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="P69" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q69" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="R69" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S69" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="T69" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="U69" s="0" t="n">
+        <f aca="false">T69*7.92/12</f>
+        <v>70.62</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="I70" s="0" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>627</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I71" s="0" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="I72" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>629</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="I73" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>630</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="I74" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>631</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F75" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G75" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="I75" s="0" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>632</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F76" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G76" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="I76" s="0" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F77" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G77" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="H77" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" s="0" t="n">
+        <f aca="false">H77*7.92/12</f>
+        <v>33</v>
+      </c>
+      <c r="P77" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q77" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="R77" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S77" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="T77" s="0" t="n">
+        <v>133</v>
+      </c>
+      <c r="U77" s="0" t="n">
+        <f aca="false">T77*7.92/12</f>
+        <v>87.78</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F78" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G78" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="H78" s="0" t="n">
+        <v>174</v>
+      </c>
+      <c r="I78" s="0" t="n">
+        <f aca="false">H78*7.92/12</f>
+        <v>114.84</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K78" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="L78" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M78" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="N78" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="O78" s="0" t="n">
+        <f aca="false">N78*7.92/12</f>
+        <v>95.04</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>635</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F79" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G79" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="H79" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="I79" s="0" t="n">
+        <f aca="false">H79*7.92/12</f>
+        <v>124.08</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K79" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="L79" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M79" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="N79" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="O79" s="0" t="n">
+        <f aca="false">N79*7.92/12</f>
+        <v>63.36</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F80" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="H80" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="I80" s="0" t="n">
+        <f aca="false">H80*7.92/12</f>
+        <v>44.88</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F81" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="H81" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="I81" s="0" t="n">
+        <f aca="false">H81*7.92/12</f>
+        <v>69.96</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E82" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F82" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G82" s="0" t="n">
+        <v>222</v>
+      </c>
+      <c r="I82" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E83" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F83" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="I83" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>640</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F84" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G84" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="I84" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>641</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E85" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F85" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G85" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="I85" s="0" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E86" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F86" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G86" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="I86" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="E87" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F87" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="I87" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>644</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="E88" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F88" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G88" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P88" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q88" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="R88" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="S88" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="T88" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U88" s="0" t="n">
+        <f aca="false">T88*7.92/12</f>
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>645</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="E89" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F89" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G89" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="I89" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="E90" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F90" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G90" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="I90" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>647</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="E91" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F91" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G91" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="I91" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>648</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E92" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F92" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="0" t="n">
+        <v>196</v>
+      </c>
+      <c r="I92" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>649</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="E93" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F93" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G93" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="I93" s="0" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="E94" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F94" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G94" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="I94" s="0" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>651</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="E95" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F95" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="I95" s="0" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="E96" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F96" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G96" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="0" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E97" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F97" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="I97" s="0" t="n">
+        <v>38.0675443262956</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>654</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E98" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F98" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="I98" s="0" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>655</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E99" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F99" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G99" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="0" t="n">
+        <v>83.3493574337282</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E100" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F100" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="I100" s="0" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>657</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="E101" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F101" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="I101" s="0" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E102" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F102" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G102" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="I102" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E103" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F103" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G103" s="0" t="n">
+        <v>217</v>
+      </c>
+      <c r="I103" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E104" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F104" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G104" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="I104" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>661</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="E105" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="F105" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G105" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="H105" s="0" t="n">
+        <v>148</v>
+      </c>
+      <c r="I105" s="0" t="n">
+        <f aca="false">H105*7.92/12</f>
+        <v>97.68</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="E106" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="F106" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G106" s="0" t="n">
+        <v>262</v>
+      </c>
+      <c r="I106" s="0" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="E107" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F107" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="I107" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="E108" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F108" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="I108" s="0" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>665</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="E109" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F109" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="I109" s="0" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="E110" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F110" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="I110" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="E111" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F111" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="I111" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E112" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F112" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G112" s="0" t="n">
+        <v>224</v>
+      </c>
+      <c r="H112" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="I112" s="0" t="n">
+        <f aca="false">H112*7.92/12</f>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>669</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E113" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F113" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G113" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H113" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="I113" s="0" t="n">
+        <f aca="false">H113*7.92/12</f>
+        <v>27.72</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="E114" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F114" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G114" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="I114" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="E115" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="H115" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="I115" s="0" t="n">
+        <f aca="false">H115*7.92/12</f>
+        <v>121.44</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>672</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="E116" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="H116" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I116" s="0" t="n">
+        <f aca="false">H116*7.92/12</f>
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>673</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E117" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F117" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G117" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="I117" s="0" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E118" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F118" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G118" s="0" t="n">
+        <v>171</v>
+      </c>
+      <c r="I118" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>675</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E119" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F119" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G119" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="I119" s="0" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="C120" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E120" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F120" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G120" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="I120" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>677</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E121" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F121" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G121" s="0" t="n">
+        <v>291</v>
+      </c>
+      <c r="I121" s="0" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="C122" s="0" t="s">
+        <v>678</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E122" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F122" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G122" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="I122" s="0" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="C123" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E123" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F123" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G123" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="I123" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="C124" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E124" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F124" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G124" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="I124" s="0" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="C125" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E125" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F125" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G125" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="I125" s="0" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="C126" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E126" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F126" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G126" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="I126" s="0" t="n">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -30764,7 +30764,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>28</v>
+        <v>28.55</v>
       </c>
       <c r="I4" s="0" t="n">
         <v>-6</v>
@@ -30773,10 +30773,10 @@
         <v>28.55</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>28.55</v>
+        <v>26</v>
       </c>
       <c r="M4" s="0" t="n">
         <v>-4</v>
@@ -30785,13 +30785,19 @@
         <v>26</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>-4</v>
+        <v>-4.4</v>
       </c>
       <c r="P4" s="0" t="n">
-        <v>26</v>
+        <v>22.94</v>
       </c>
       <c r="Q4" s="0" t="n">
         <v>-4.4</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30817,39 +30823,27 @@
         <v>0</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>28.55</v>
+        <v>32.5</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>-6</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>28.55</v>
+        <v>32.25</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>-4</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>32.25</v>
+        <v>28.55</v>
       </c>
       <c r="M5" s="0" t="n">
         <v>-4</v>
       </c>
       <c r="N5" s="0" t="n">
-        <v>32.5</v>
+        <v>28.55</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>-6</v>
-      </c>
-      <c r="P5" s="0" t="n">
-        <v>22.94</v>
-      </c>
-      <c r="Q5" s="0" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="R5" s="0" t="n">
-        <v>22.94</v>
-      </c>
-      <c r="S5" s="0" t="n">
         <v>-6</v>
       </c>
     </row>
@@ -30876,10 +30870,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>32.5</v>
+        <v>32.25</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="J6" s="0" t="n">
         <v>30.5</v>
@@ -31595,13 +31589,13 @@
         <v>22</v>
       </c>
       <c r="M19" s="0" t="n">
-        <v>0.4</v>
+        <v>2.41</v>
       </c>
       <c r="N19" s="0" t="n">
         <v>22</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>2.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4885" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4887" uniqueCount="712">
   <si>
     <t xml:space="preserve">Block</t>
   </si>
@@ -2131,6 +2131,9 @@
   </si>
   <si>
     <t xml:space="preserve">nft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use_note</t>
   </si>
   <si>
     <t xml:space="preserve">C5</t>
@@ -2746,16 +2749,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>55</xdr:col>
-      <xdr:colOff>141840</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>319320</xdr:rowOff>
+      <xdr:col>56</xdr:col>
+      <xdr:colOff>323640</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>142560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>59</xdr:col>
-      <xdr:colOff>20880</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>284040</xdr:rowOff>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>292680</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2764,8 +2767,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="2700000">
-          <a:off x="26167680" y="8872200"/>
-          <a:ext cx="1692720" cy="421920"/>
+          <a:off x="26772480" y="8238240"/>
+          <a:ext cx="421560" cy="1689840"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2828,28 +2831,28 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AP77"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="4.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="5.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="4.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="16" style="0" width="5.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="0" width="4.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="25" style="0" width="5.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="0" width="4.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="9.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="34" style="0" width="5.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="9.85"/>
@@ -9671,7 +9674,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M759"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.33"/>
@@ -27191,12 +27194,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="4.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.15"/>
   </cols>
@@ -27921,7 +27924,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J1048576"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -30538,7 +30541,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -30876,10 +30879,10 @@
         <v>-4</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>-2.5</v>
+        <v>-2.75</v>
       </c>
       <c r="L6" s="0" t="n">
         <v>26</v>
@@ -31424,18 +31427,30 @@
         <v>8</v>
       </c>
       <c r="K16" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="O16" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="P16" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="Q16" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="R16" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="S16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31789,51 +31804,33 @@
         <v>1</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>9.7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="0" t="n">
         <v>4</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>9.7</v>
+        <v>10</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="L23" s="0" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M23" s="0" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="N23" s="0" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P23" s="0" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="0" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R23" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="S23" s="0" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T23" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="U23" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="W23" s="0" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32555,7 +32552,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A3:BS50"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="3" style="0" width="6.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="56" style="0" width="6.42"/>
@@ -37715,7 +37712,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -38528,7 +38525,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -41812,8 +41809,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U126"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:V126"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -41879,6 +41876,9 @@
       <c r="U1" s="0" t="s">
         <v>700</v>
       </c>
+      <c r="V1" s="0" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
@@ -42153,25 +42153,6 @@
       <c r="I7" s="0" t="n">
         <v>123</v>
       </c>
-      <c r="P7" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="R7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" s="0" t="n">
-        <v>273</v>
-      </c>
-      <c r="T7" s="0" t="n">
-        <v>119</v>
-      </c>
-      <c r="U7" s="0" t="n">
-        <f aca="false">T7*7.92/12</f>
-        <v>78.54</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
@@ -42484,6 +42465,25 @@
       <c r="I19" s="0" t="n">
         <v>114</v>
       </c>
+      <c r="P19" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="T19" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="U19" s="0" t="n">
+        <f aca="false">T19*7.92/12</f>
+        <v>118.14</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
@@ -42539,7 +42539,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>443</v>
@@ -42562,10 +42562,29 @@
       <c r="I22" s="0" t="n">
         <v>40</v>
       </c>
+      <c r="P22" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="R22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="U22" s="0" t="n">
+        <f aca="false">T22*7.92/12</f>
+        <v>39.6</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>443</v>
@@ -42591,7 +42610,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>443</v>
@@ -42617,7 +42636,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>443</v>
@@ -42643,7 +42662,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>443</v>
@@ -43242,7 +43261,7 @@
         <v>4</v>
       </c>
       <c r="G41" s="0" t="n">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="I41" s="0" t="n">
         <v>135</v>
@@ -43415,7 +43434,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>379</v>
@@ -43441,7 +43460,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>379</v>
@@ -43467,7 +43486,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>379</v>
@@ -43493,7 +43512,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>379</v>
@@ -43519,7 +43538,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>379</v>
@@ -43895,7 +43914,7 @@
         <v>461</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>225</v>
@@ -43921,7 +43940,7 @@
         <v>461</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>225</v>
@@ -43947,7 +43966,7 @@
         <v>461</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>225</v>
@@ -43992,7 +44011,7 @@
         <v>461</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>225</v>
@@ -44018,7 +44037,7 @@
         <v>461</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>225</v>
@@ -44187,7 +44206,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>449</v>
@@ -44213,7 +44232,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>449</v>
@@ -44239,7 +44258,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>449</v>
@@ -44265,7 +44284,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>449</v>
@@ -44291,7 +44310,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>449</v>
@@ -44933,7 +44952,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>475</v>
@@ -44959,7 +44978,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>475</v>
@@ -44985,7 +45004,7 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>475</v>
@@ -45011,7 +45030,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>475</v>
@@ -45037,7 +45056,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>475</v>
@@ -45603,7 +45622,7 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B122" s="0" t="s">
         <v>452</v>
@@ -45629,7 +45648,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B123" s="0" t="s">
         <v>452</v>
@@ -45655,7 +45674,7 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B124" s="0" t="s">
         <v>452</v>
@@ -45681,7 +45700,7 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B125" s="0" t="s">
         <v>452</v>
@@ -45707,7 +45726,7 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B126" s="0" t="s">
         <v>452</v>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6395" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6753" uniqueCount="718">
   <si>
     <t xml:space="preserve">Block</t>
   </si>
@@ -1237,6 +1237,12 @@
   </si>
   <si>
     <t xml:space="preserve">i.e. T033-218-070-ST-24-99DS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diameter</t>
   </si>
   <si>
     <t xml:space="preserve">hemlock</t>
@@ -32459,8 +32465,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1048576"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L179"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -32470,23 +32476,29 @@
         <v>340</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>347</v>
       </c>
       <c r="F1" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="I1" s="0" t="s">
         <v>350</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
       <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
@@ -32502,6 +32514,12 @@
         <v>8</v>
       </c>
       <c r="F2" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="H2" s="0" t="s">
         <v>384</v>
       </c>
     </row>
@@ -32518,6 +32536,12 @@
       <c r="D3" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F3" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
@@ -32532,6 +32556,12 @@
       <c r="D4" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F4" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
@@ -32546,6 +32576,12 @@
       <c r="D5" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F5" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
@@ -32560,6 +32596,12 @@
       <c r="D6" s="3" t="n">
         <v>9</v>
       </c>
+      <c r="F6" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
@@ -32574,6 +32616,12 @@
       <c r="D7" s="3" t="n">
         <v>17</v>
       </c>
+      <c r="F7" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
@@ -32589,7 +32637,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32605,6 +32659,12 @@
       <c r="D9" s="3" t="n">
         <v>17</v>
       </c>
+      <c r="F9" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
@@ -32619,6 +32679,12 @@
       <c r="D10" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F10" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
@@ -32633,6 +32699,12 @@
       <c r="D11" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F11" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
@@ -32648,7 +32720,13 @@
         <v>14</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32664,6 +32742,12 @@
       <c r="D13" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F13" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
@@ -32678,6 +32762,12 @@
       <c r="D14" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F14" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
@@ -32692,6 +32782,12 @@
       <c r="D15" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F15" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
@@ -32706,6 +32802,12 @@
       <c r="D16" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F16" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
@@ -32720,6 +32822,12 @@
       <c r="D17" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F17" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
@@ -32735,7 +32843,13 @@
         <v>14</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32751,6 +32865,12 @@
       <c r="D19" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="F19" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
@@ -32765,6 +32885,12 @@
       <c r="D20" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F20" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
@@ -32779,6 +32905,12 @@
       <c r="D21" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F21" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
@@ -32793,6 +32925,12 @@
       <c r="D22" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F22" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
@@ -32807,6 +32945,12 @@
       <c r="D23" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F23" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
@@ -32821,6 +32965,12 @@
       <c r="D24" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F24" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
@@ -32835,6 +32985,12 @@
       <c r="D25" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="F25" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
@@ -32849,6 +33005,12 @@
       <c r="D26" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F26" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
@@ -32863,6 +33025,12 @@
       <c r="D27" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F27" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="n">
@@ -32877,6 +33045,12 @@
       <c r="D28" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F28" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
@@ -32891,6 +33065,12 @@
       <c r="D29" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F29" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
@@ -32905,6 +33085,12 @@
       <c r="D30" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F30" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="n">
@@ -32919,6 +33105,12 @@
       <c r="D31" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="F31" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="n">
@@ -32933,6 +33125,12 @@
       <c r="D32" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="F32" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="n">
@@ -32947,6 +33145,12 @@
       <c r="D33" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F33" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="n">
@@ -32961,6 +33165,12 @@
       <c r="D34" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F34" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G34" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="n">
@@ -32975,6 +33185,12 @@
       <c r="D35" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F35" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="n">
@@ -32989,6 +33205,12 @@
       <c r="D36" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F36" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="n">
@@ -33003,6 +33225,12 @@
       <c r="D37" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="F37" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
@@ -33017,6 +33245,12 @@
       <c r="D38" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F38" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="n">
@@ -33032,7 +33266,13 @@
         <v>8</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33048,6 +33288,12 @@
       <c r="D40" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F40" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="n">
@@ -33063,7 +33309,13 @@
         <v>6</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33079,6 +33331,12 @@
       <c r="D42" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="F42" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="n">
@@ -33093,6 +33351,12 @@
       <c r="D43" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F43" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="n">
@@ -33107,6 +33371,12 @@
       <c r="D44" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F44" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
@@ -33121,6 +33391,12 @@
       <c r="D45" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F45" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G45" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="n">
@@ -33135,6 +33411,12 @@
       <c r="D46" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F46" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="n">
@@ -33149,6 +33431,12 @@
       <c r="D47" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F47" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
@@ -33163,6 +33451,12 @@
       <c r="D48" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F48" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
@@ -33177,6 +33471,12 @@
       <c r="D49" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F49" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="n">
@@ -33191,6 +33491,12 @@
       <c r="D50" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F50" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="n">
@@ -33205,6 +33511,12 @@
       <c r="D51" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F51" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
@@ -33219,6 +33531,12 @@
       <c r="D52" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="F52" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="n">
@@ -33233,6 +33551,12 @@
       <c r="D53" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F53" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="n">
@@ -33247,6 +33571,12 @@
       <c r="D54" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F54" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="n">
@@ -33261,6 +33591,12 @@
       <c r="D55" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="F55" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="n">
@@ -33275,6 +33611,12 @@
       <c r="D56" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="F56" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="n">
@@ -33289,6 +33631,12 @@
       <c r="D57" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F57" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="n">
@@ -33303,6 +33651,12 @@
       <c r="D58" s="3" t="n">
         <v>19</v>
       </c>
+      <c r="F58" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="n">
@@ -33317,6 +33671,12 @@
       <c r="D59" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="F59" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="n">
@@ -33331,6 +33691,12 @@
       <c r="D60" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F60" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="n">
@@ -33345,6 +33711,12 @@
       <c r="D61" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="F61" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="n">
@@ -33359,6 +33731,12 @@
       <c r="D62" s="3" t="n">
         <v>19</v>
       </c>
+      <c r="F62" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="n">
@@ -33373,6 +33751,12 @@
       <c r="D63" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F63" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="n">
@@ -33388,7 +33772,13 @@
         <v>10</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33404,6 +33794,12 @@
       <c r="D65" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F65" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="n">
@@ -33418,6 +33814,12 @@
       <c r="D66" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F66" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="n">
@@ -33432,6 +33834,12 @@
       <c r="D67" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F67" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="n">
@@ -33446,6 +33854,12 @@
       <c r="D68" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F68" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="n">
@@ -33460,6 +33874,12 @@
       <c r="D69" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F69" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="n">
@@ -33474,6 +33894,12 @@
       <c r="D70" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F70" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="n">
@@ -33488,6 +33914,12 @@
       <c r="D71" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F71" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="n">
@@ -33502,6 +33934,12 @@
       <c r="D72" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F72" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="n">
@@ -33516,6 +33954,12 @@
       <c r="D73" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F73" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="n">
@@ -33530,6 +33974,12 @@
       <c r="D74" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F74" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="n">
@@ -33544,6 +33994,12 @@
       <c r="D75" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F75" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G75" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="n">
@@ -33558,6 +34014,12 @@
       <c r="D76" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F76" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G76" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="n">
@@ -33573,7 +34035,13 @@
         <v>12</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G77" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33589,6 +34057,12 @@
       <c r="D78" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F78" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="n">
@@ -33603,6 +34077,12 @@
       <c r="D79" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F79" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="n">
@@ -33617,6 +34097,12 @@
       <c r="D80" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F80" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G80" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="n">
@@ -33631,6 +34117,12 @@
       <c r="D81" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F81" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="n">
@@ -33645,6 +34137,12 @@
       <c r="D82" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="F82" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="n">
@@ -33659,6 +34157,12 @@
       <c r="D83" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F83" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="n">
@@ -33673,6 +34177,12 @@
       <c r="D84" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F84" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G84" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="n">
@@ -33687,6 +34197,12 @@
       <c r="D85" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F85" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G85" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="n">
@@ -33701,6 +34217,12 @@
       <c r="D86" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F86" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G86" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="n">
@@ -33715,6 +34237,12 @@
       <c r="D87" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F87" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="n">
@@ -33729,6 +34257,12 @@
       <c r="D88" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F88" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="n">
@@ -33743,6 +34277,12 @@
       <c r="D89" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F89" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="n">
@@ -33757,6 +34297,12 @@
       <c r="D90" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F90" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="n">
@@ -33771,6 +34317,12 @@
       <c r="D91" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F91" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="n">
@@ -33785,6 +34337,12 @@
       <c r="D92" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F92" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G92" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="n">
@@ -33799,6 +34357,12 @@
       <c r="D93" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F93" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="n">
@@ -33813,6 +34377,12 @@
       <c r="D94" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F94" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="n">
@@ -33827,6 +34397,12 @@
       <c r="D95" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G95" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="n">
@@ -33841,6 +34417,12 @@
       <c r="D96" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G96" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="n">
@@ -33855,6 +34437,12 @@
       <c r="D97" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F97" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G97" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="n">
@@ -33870,7 +34458,13 @@
         <v>12</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G98" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33886,6 +34480,12 @@
       <c r="D99" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F99" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G99" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="n">
@@ -33900,6 +34500,12 @@
       <c r="D100" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F100" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G100" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="n">
@@ -33914,6 +34520,12 @@
       <c r="D101" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F101" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G101" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="n">
@@ -33928,6 +34540,12 @@
       <c r="D102" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F102" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="n">
@@ -33942,6 +34560,12 @@
       <c r="D103" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F103" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="n">
@@ -33955,6 +34579,12 @@
       </c>
       <c r="D104" s="3" t="n">
         <v>20</v>
+      </c>
+      <c r="F104" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33970,6 +34600,12 @@
       <c r="D105" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F105" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G105" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="n">
@@ -33984,6 +34620,12 @@
       <c r="D106" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F106" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G106" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="n">
@@ -33998,6 +34640,12 @@
       <c r="D107" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F107" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G107" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="n">
@@ -34012,6 +34660,12 @@
       <c r="D108" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F108" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G108" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="n">
@@ -34026,6 +34680,12 @@
       <c r="D109" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F109" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G109" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="n">
@@ -34040,6 +34700,12 @@
       <c r="D110" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F110" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G110" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="n">
@@ -34054,6 +34720,12 @@
       <c r="D111" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F111" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G111" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="n">
@@ -34068,6 +34740,12 @@
       <c r="D112" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="F112" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G112" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
@@ -34083,7 +34761,13 @@
         <v>14</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G113" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34099,6 +34783,12 @@
       <c r="D114" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F114" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G114" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="n">
@@ -34113,6 +34803,12 @@
       <c r="D115" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F115" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G115" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="n">
@@ -34127,6 +34823,12 @@
       <c r="D116" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F116" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G116" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="n">
@@ -34141,6 +34843,12 @@
       <c r="D117" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F117" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G117" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="n">
@@ -34155,6 +34863,12 @@
       <c r="D118" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F118" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G118" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="n">
@@ -34169,6 +34883,12 @@
       <c r="D119" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F119" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G119" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="n">
@@ -34183,6 +34903,12 @@
       <c r="D120" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F120" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G120" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="n">
@@ -34197,6 +34923,12 @@
       <c r="D121" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F121" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G121" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="n">
@@ -34211,6 +34943,12 @@
       <c r="D122" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F122" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G122" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="n">
@@ -34225,6 +34963,12 @@
       <c r="D123" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F123" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G123" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="n">
@@ -34239,6 +34983,12 @@
       <c r="D124" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F124" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G124" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="n">
@@ -34253,6 +35003,12 @@
       <c r="D125" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F125" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G125" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="n">
@@ -34267,6 +35023,12 @@
       <c r="D126" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F126" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G126" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="n">
@@ -34282,7 +35044,13 @@
         <v>12</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
+      </c>
+      <c r="F127" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G127" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34298,6 +35066,12 @@
       <c r="D128" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F128" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G128" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="n">
@@ -34312,6 +35086,12 @@
       <c r="D129" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F129" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G129" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="n">
@@ -34326,6 +35106,12 @@
       <c r="D130" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F130" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G130" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="n">
@@ -34340,6 +35126,12 @@
       <c r="D131" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F131" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G131" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="n">
@@ -34354,6 +35146,12 @@
       <c r="D132" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F132" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G132" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="n">
@@ -34368,6 +35166,12 @@
       <c r="D133" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F133" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G133" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="n">
@@ -34382,6 +35186,12 @@
       <c r="D134" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F134" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G134" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="n">
@@ -34396,6 +35206,12 @@
       <c r="D135" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F135" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G135" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="n">
@@ -34410,6 +35226,12 @@
       <c r="D136" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F136" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G136" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="n">
@@ -34425,7 +35247,13 @@
         <v>14</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
+      </c>
+      <c r="F137" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G137" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34441,6 +35269,12 @@
       <c r="D138" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F138" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G138" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="n">
@@ -34455,6 +35289,12 @@
       <c r="D139" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F139" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G139" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="n">
@@ -34469,6 +35309,12 @@
       <c r="D140" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F140" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G140" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="n">
@@ -34483,6 +35329,12 @@
       <c r="D141" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F141" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G141" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="n">
@@ -34498,7 +35350,13 @@
         <v>10</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G142" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34514,6 +35372,12 @@
       <c r="D143" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F143" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G143" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="n">
@@ -34528,6 +35392,12 @@
       <c r="D144" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F144" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G144" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="n">
@@ -34542,6 +35412,12 @@
       <c r="D145" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F145" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G145" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="n">
@@ -34556,6 +35432,12 @@
       <c r="D146" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F146" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G146" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="n">
@@ -34571,7 +35453,13 @@
         <v>4</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G147" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34587,6 +35475,12 @@
       <c r="D148" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F148" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G148" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="n">
@@ -34601,6 +35495,12 @@
       <c r="D149" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F149" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G149" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="n">
@@ -34615,6 +35515,12 @@
       <c r="D150" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F150" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G150" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="n">
@@ -34629,6 +35535,12 @@
       <c r="D151" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F151" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G151" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="n">
@@ -34643,6 +35555,12 @@
       <c r="D152" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F152" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G152" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="n">
@@ -34657,6 +35575,12 @@
       <c r="D153" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F153" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G153" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="n">
@@ -34672,7 +35596,13 @@
         <v>8</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F154" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G154" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34689,7 +35619,13 @@
         <v>12</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G155" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34705,6 +35641,12 @@
       <c r="D156" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F156" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G156" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="n">
@@ -34720,7 +35662,13 @@
         <v>10</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F157" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G157" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34736,6 +35684,12 @@
       <c r="D158" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F158" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G158" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="n">
@@ -34750,6 +35704,12 @@
       <c r="D159" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F159" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G159" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="n">
@@ -34764,6 +35724,12 @@
       <c r="D160" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="F160" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G160" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="n">
@@ -34778,6 +35744,12 @@
       <c r="D161" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F161" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G161" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="n">
@@ -34792,6 +35764,12 @@
       <c r="D162" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F162" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G162" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="n">
@@ -34806,6 +35784,12 @@
       <c r="D163" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F163" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G163" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="n">
@@ -34821,7 +35805,13 @@
         <v>8</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="F164" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="G164" s="0" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34837,6 +35827,12 @@
       <c r="D165" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="F165" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G165" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="n">
@@ -34851,6 +35847,12 @@
       <c r="D166" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F166" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G166" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="n">
@@ -34865,6 +35867,12 @@
       <c r="D167" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F167" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G167" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="n">
@@ -34879,6 +35887,12 @@
       <c r="D168" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F168" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G168" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="n">
@@ -34893,6 +35907,12 @@
       <c r="D169" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F169" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G169" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="n">
@@ -34907,6 +35927,12 @@
       <c r="D170" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F170" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G170" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="n">
@@ -34921,6 +35947,12 @@
       <c r="D171" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="F171" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G171" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="n">
@@ -34935,6 +35967,12 @@
       <c r="D172" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F172" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G172" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="n">
@@ -34949,6 +35987,12 @@
       <c r="D173" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F173" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G173" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="n">
@@ -34963,6 +36007,12 @@
       <c r="D174" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F174" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G174" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="n">
@@ -34977,6 +36027,12 @@
       <c r="D175" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="F175" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G175" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="n">
@@ -34991,6 +36047,12 @@
       <c r="D176" s="3" t="n">
         <v>24</v>
       </c>
+      <c r="F176" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G176" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="n">
@@ -35005,6 +36067,12 @@
       <c r="D177" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="F177" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G177" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="n">
@@ -35019,6 +36087,12 @@
       <c r="D178" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="F178" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G178" s="0" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="n">
@@ -35033,33 +36107,13 @@
       <c r="D179" s="3" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="F179" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G179" s="0" t="s">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -35081,13 +36135,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D1" s="0" t="s">
         <v>41</v>
@@ -35096,63 +36150,63 @@
         <v>349</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>30</v>
@@ -35161,7 +36215,7 @@
         <v>-8.72</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E2" s="0" t="s">
         <v>359</v>
@@ -35211,7 +36265,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>30</v>
@@ -35220,7 +36274,7 @@
         <v>-7.48</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>371</v>
@@ -35282,7 +36336,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>28</v>
@@ -35291,10 +36345,10 @@
         <v>-7.48</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>355</v>
@@ -35341,7 +36395,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>22.94</v>
@@ -35350,7 +36404,7 @@
         <v>-6.54</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>380</v>
@@ -35388,7 +36442,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>22.94</v>
@@ -35397,10 +36451,10 @@
         <v>-4.4</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>64</v>
@@ -35435,7 +36489,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>22.94</v>
@@ -35444,10 +36498,10 @@
         <v>-2.43</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>355</v>
@@ -35482,7 +36536,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>22.94</v>
@@ -35491,7 +36545,7 @@
         <v>-6</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>64</v>
@@ -35544,7 +36598,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>26</v>
@@ -35553,10 +36607,10 @@
         <v>-4.4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>389</v>
@@ -35600,7 +36654,7 @@
         <v>-4</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>389</v>
@@ -35659,7 +36713,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>28.55</v>
@@ -35668,10 +36722,10 @@
         <v>-4</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>354</v>
@@ -35706,7 +36760,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>28.55</v>
@@ -35715,7 +36769,7 @@
         <v>-6</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>384</v>
@@ -35780,7 +36834,7 @@
         <v>-6</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>162</v>
@@ -35821,7 +36875,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>32.56</v>
@@ -35830,10 +36884,10 @@
         <v>-6</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>64</v>
@@ -35868,7 +36922,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>32.13</v>
@@ -35877,10 +36931,10 @@
         <v>-4</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>64</v>
@@ -35933,7 +36987,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>26</v>
@@ -35942,10 +36996,10 @@
         <v>-1.29</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>389</v>
@@ -35992,7 +37046,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>24.2</v>
@@ -36001,10 +37055,10 @@
         <v>0.4</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>162</v>
@@ -36057,7 +37111,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>22</v>
@@ -36066,10 +37120,10 @@
         <v>0.4</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>64</v>
@@ -36104,7 +37158,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>19.28</v>
@@ -36113,10 +37167,10 @@
         <v>0.4</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>162</v>
@@ -36151,7 +37205,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>18</v>
@@ -36160,7 +37214,7 @@
         <v>0.4</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>354</v>
@@ -36201,7 +37255,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>16.5</v>
@@ -36210,10 +37264,10 @@
         <v>0.4</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>162</v>
@@ -36272,7 +37326,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>14.55</v>
@@ -36281,10 +37335,10 @@
         <v>0.4</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>354</v>
@@ -36319,7 +37373,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>13.62</v>
@@ -36328,10 +37382,10 @@
         <v>0.4</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>389</v>
@@ -36372,7 +37426,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>12</v>
@@ -36381,10 +37435,10 @@
         <v>0.4</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>355</v>
@@ -36452,10 +37506,10 @@
         <v>162</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>354</v>
@@ -36502,7 +37556,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>8</v>
@@ -36511,10 +37565,10 @@
         <v>162</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>355</v>
@@ -36561,7 +37615,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>9.24</v>
@@ -36570,12 +37624,12 @@
         <v>-2</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>13.62</v>
@@ -36584,7 +37638,7 @@
         <v>-2</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36598,12 +37652,12 @@
         <v>-2</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>16.5</v>
@@ -36612,12 +37666,12 @@
         <v>-2.43</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>16.73</v>
@@ -36626,12 +37680,12 @@
         <v>-2.43</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>19.28</v>
@@ -36640,12 +37694,12 @@
         <v>-2.43</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>20</v>
@@ -36654,12 +37708,12 @@
         <v>-2.43</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>16.73</v>
@@ -36668,7 +37722,7 @@
         <v>-4</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36682,7 +37736,7 @@
         <v>-4</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36696,12 +37750,12 @@
         <v>-4</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>9.55</v>
@@ -36712,7 +37766,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>9.12</v>
@@ -36721,7 +37775,7 @@
         <v>-6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36735,12 +37789,12 @@
         <v>-6</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>14</v>
@@ -36749,12 +37803,12 @@
         <v>-7.66</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>16.73</v>
@@ -36763,12 +37817,12 @@
         <v>-7.4</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>8</v>
@@ -36777,7 +37831,7 @@
         <v>2</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36791,12 +37845,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>12.49</v>
@@ -36805,12 +37859,12 @@
         <v>2</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>12.49</v>
@@ -36819,12 +37873,12 @@
         <v>4</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>8</v>
@@ -36833,7 +37887,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36847,12 +37901,12 @@
         <v>4</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>14.55</v>
@@ -36861,12 +37915,12 @@
         <v>3.54</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>14.55</v>
@@ -36875,12 +37929,12 @@
         <v>2.41</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>17.04</v>
@@ -36889,12 +37943,12 @@
         <v>2.41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>18</v>
@@ -36903,12 +37957,12 @@
         <v>2.41</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>22</v>
@@ -36917,12 +37971,12 @@
         <v>2.41</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>22</v>
@@ -36931,12 +37985,12 @@
         <v>4.37</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>18.65</v>
@@ -36945,12 +37999,12 @@
         <v>4.37</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>17.04</v>
@@ -36959,12 +38013,12 @@
         <v>4.26</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>16.23</v>
@@ -36973,12 +38027,12 @@
         <v>4.26</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>16.23</v>
@@ -36987,12 +38041,12 @@
         <v>4.9</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>14</v>
@@ -37001,12 +38055,12 @@
         <v>4.9</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>14</v>
@@ -37015,12 +38069,12 @@
         <v>6.06</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>18.65</v>
@@ -37040,7 +38094,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37054,12 +38108,12 @@
         <v>8</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>25.5</v>
@@ -37068,7 +38122,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -37536,13 +38590,13 @@
       <c r="BF7" s="28"/>
       <c r="BG7" s="28"/>
       <c r="BH7" s="29" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="BI7" s="29"/>
       <c r="BJ7" s="29"/>
       <c r="BK7" s="29"/>
       <c r="BL7" s="30" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="BM7" s="30"/>
       <c r="BN7" s="30"/>
@@ -37936,25 +38990,25 @@
       <c r="BA11" s="8"/>
       <c r="BB11" s="9"/>
       <c r="BD11" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="BE11" s="33"/>
       <c r="BF11" s="33"/>
       <c r="BG11" s="33"/>
       <c r="BH11" s="30" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="BI11" s="30"/>
       <c r="BJ11" s="30"/>
       <c r="BK11" s="30"/>
       <c r="BL11" s="30" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="BM11" s="30"/>
       <c r="BN11" s="30"/>
       <c r="BO11" s="30"/>
       <c r="BP11" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="BQ11" s="31"/>
       <c r="BR11" s="31"/>
@@ -38384,7 +39438,7 @@
       <c r="BA15" s="8"/>
       <c r="BB15" s="9"/>
       <c r="BD15" s="34" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="BE15" s="34"/>
       <c r="BF15" s="34"/>
@@ -38394,13 +39448,13 @@
       <c r="BJ15" s="35"/>
       <c r="BK15" s="35"/>
       <c r="BL15" s="36" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="BM15" s="36"/>
       <c r="BN15" s="36"/>
       <c r="BO15" s="36"/>
       <c r="BP15" s="37" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="BQ15" s="37"/>
       <c r="BR15" s="37"/>
@@ -39776,7 +40830,7 @@
       </c>
       <c r="BB28" s="17"/>
       <c r="BD28" s="41" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="BE28" s="41"/>
       <c r="BF28" s="41"/>
@@ -42255,22 +43309,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H1" s="0" t="s">
         <v>348</v>
@@ -42279,7 +43333,7 @@
         <v>350</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42306,7 +43360,7 @@
         <v>111.5</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I2" s="0" t="s">
         <v>377</v>
@@ -42336,7 +43390,7 @@
         <v>81.2</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>374</v>
@@ -42366,7 +43420,7 @@
         <v>51.7</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>373</v>
@@ -42396,7 +43450,7 @@
         <v>71.1</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>373</v>
@@ -42426,7 +43480,7 @@
         <v>40.4</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42453,7 +43507,7 @@
         <v>36.4</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>369</v>
@@ -42483,7 +43537,7 @@
         <v>13.5</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>370</v>
@@ -42513,7 +43567,7 @@
         <v>1.5</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42540,7 +43594,7 @@
         <v>-4</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>381</v>
@@ -42570,7 +43624,7 @@
         <v>-19.9</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>381</v>
@@ -42600,7 +43654,7 @@
         <v>-48.3</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42627,7 +43681,7 @@
         <v>-1.9</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>368</v>
@@ -42657,7 +43711,7 @@
         <v>-22.6</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42684,7 +43738,7 @@
         <v>105.3</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42711,10 +43765,10 @@
         <v>81.6</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42741,10 +43795,10 @@
         <v>80.5</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42771,10 +43825,10 @@
         <v>68</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42801,7 +43855,7 @@
         <v>128.9</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42828,7 +43882,7 @@
         <v>9.8</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42851,7 +43905,7 @@
         <v>-55.3</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42874,10 +43928,10 @@
         <v>-86.7</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42900,10 +43954,10 @@
         <v>-86.3</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42926,10 +43980,10 @@
         <v>-84</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42952,10 +44006,10 @@
         <v>-82</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42978,10 +44032,10 @@
         <v>-71</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42998,10 +44052,10 @@
         <v>-6</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I27" s="53" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43018,10 +44072,10 @@
         <v>-6</v>
       </c>
       <c r="H28" s="53" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I28" s="53" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="29" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43038,10 +44092,10 @@
         <v>-6</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I29" s="53" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -43068,25 +44122,25 @@
         <v>350</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43113,7 +44167,7 @@
         <v>52.2</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43140,7 +44194,7 @@
         <v>21.9</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43167,7 +44221,7 @@
         <v>15.5</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43194,7 +44248,7 @@
         <v>-18</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43221,12 +44275,12 @@
         <v>-174.7</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>253</v>
@@ -43248,12 +44302,12 @@
         <v>-108.1</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>253</v>
@@ -43275,12 +44329,12 @@
         <v>-85.4</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>260</v>
@@ -43302,12 +44356,12 @@
         <v>-153.2</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>260</v>
@@ -43329,12 +44383,12 @@
         <v>-75.5</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>297</v>
@@ -43356,12 +44410,12 @@
         <v>-126</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>147</v>
@@ -43383,12 +44437,12 @@
         <v>32</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>150</v>
@@ -43410,12 +44464,12 @@
         <v>-215.1</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>195</v>
@@ -43437,12 +44491,12 @@
         <v>96.5</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>150</v>
@@ -43464,12 +44518,12 @@
         <v>-155.9</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>150</v>
@@ -43491,12 +44545,12 @@
         <v>75.3</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>233</v>
@@ -43518,12 +44572,12 @@
         <v>92.3</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>233</v>
@@ -43545,12 +44599,12 @@
         <v>39.7</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>233</v>
@@ -43572,12 +44626,12 @@
         <v>-6.9</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>233</v>
@@ -43599,12 +44653,12 @@
         <v>-22.3</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>233</v>
@@ -43626,12 +44680,12 @@
         <v>14.9</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>189</v>
@@ -43653,12 +44707,12 @@
         <v>53.6</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>146</v>
@@ -43680,12 +44734,12 @@
         <v>-153.3</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>189</v>
@@ -43707,12 +44761,12 @@
         <v>0.600000000000001</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>189</v>
@@ -43734,12 +44788,12 @@
         <v>25.7</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>146</v>
@@ -43761,12 +44815,12 @@
         <v>-59.4</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>90</v>
@@ -43788,12 +44842,12 @@
         <v>118</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>90</v>
@@ -43815,12 +44869,12 @@
         <v>100.2</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>90</v>
@@ -43842,12 +44896,12 @@
         <v>69.4</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>90</v>
@@ -43869,12 +44923,12 @@
         <v>70.3</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>90</v>
@@ -43896,12 +44950,12 @@
         <v>26.8</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>329</v>
@@ -43923,12 +44977,12 @@
         <v>-41.2</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>329</v>
@@ -43950,12 +45004,12 @@
         <v>7</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>329</v>
@@ -43977,7 +45031,7 @@
         <v>-27.9</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44004,12 +45058,12 @@
         <v>48.4</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>312</v>
@@ -44031,12 +45085,12 @@
         <v>-182.5</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>280</v>
@@ -44058,12 +45112,12 @@
         <v>-120.4</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>280</v>
@@ -44085,12 +45139,12 @@
         <v>-84</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>280</v>
@@ -44112,7 +45166,7 @@
         <v>25.5</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44139,12 +45193,12 @@
         <v>1</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>253</v>
@@ -44166,12 +45220,12 @@
         <v>-156.5</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>96</v>
@@ -44193,12 +45247,12 @@
         <v>87.4</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>96</v>
@@ -44220,12 +45274,12 @@
         <v>44.4</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>96</v>
@@ -44247,12 +45301,12 @@
         <v>-103.8</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>101</v>
@@ -44274,12 +45328,12 @@
         <v>-188.4</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>101</v>
@@ -44301,12 +45355,12 @@
         <v>122.5</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>114</v>
@@ -44328,12 +45382,12 @@
         <v>91.6</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>114</v>
@@ -44355,12 +45409,12 @@
         <v>64.3</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>75</v>
@@ -44382,12 +45436,12 @@
         <v>102.7</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>75</v>
@@ -44409,12 +45463,12 @@
         <v>77.2</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>75</v>
@@ -44436,7 +45490,7 @@
         <v>37.6</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44463,7 +45517,7 @@
         <v>99.9</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44490,12 +45544,12 @@
         <v>51.6</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>65</v>
@@ -44517,7 +45571,7 @@
         <v>-148.2</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44544,12 +45598,12 @@
         <v>-171.6</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>65</v>
@@ -44571,12 +45625,12 @@
         <v>-76.8</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>249</v>
@@ -44598,12 +45652,12 @@
         <v>68.8</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>249</v>
@@ -44625,12 +45679,12 @@
         <v>23.6</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>249</v>
@@ -44652,12 +45706,12 @@
         <v>-75.8</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>253</v>
@@ -44679,12 +45733,12 @@
         <v>-205.7</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>249</v>
@@ -44706,12 +45760,12 @@
         <v>4.5</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>214</v>
@@ -44733,12 +45787,12 @@
         <v>118.9</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>214</v>
@@ -44760,12 +45814,12 @@
         <v>111.3</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>214</v>
@@ -44787,12 +45841,12 @@
         <v>68.3</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>214</v>
@@ -44814,12 +45868,12 @@
         <v>-16.1</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>214</v>
@@ -44841,12 +45895,12 @@
         <v>24.3</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>114</v>
@@ -44868,12 +45922,12 @@
         <v>2.3</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>114</v>
@@ -44895,12 +45949,12 @@
         <v>-104.7</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>75</v>
@@ -44922,12 +45976,12 @@
         <v>-167.3</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>75</v>
@@ -44949,12 +46003,12 @@
         <v>-134.8</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>75</v>
@@ -44976,12 +46030,12 @@
         <v>-145.9</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>45</v>
@@ -45003,12 +46057,12 @@
         <v>-139.1</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>45</v>
@@ -45030,12 +46084,12 @@
         <v>-119.3</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>45</v>
@@ -45057,12 +46111,12 @@
         <v>-86.6</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>45</v>
@@ -45084,12 +46138,12 @@
         <v>-84.5</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>83</v>
@@ -45111,12 +46165,12 @@
         <v>-10.5</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>106</v>
@@ -45138,12 +46192,12 @@
         <v>-139.7</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>106</v>
@@ -45165,12 +46219,12 @@
         <v>40.7</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>106</v>
@@ -45192,12 +46246,12 @@
         <v>-91.1</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>106</v>
@@ -45219,12 +46273,12 @@
         <v>-64.5</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>106</v>
@@ -45246,12 +46300,12 @@
         <v>-83.2</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>312</v>
@@ -45273,12 +46327,12 @@
         <v>86.7</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>277</v>
@@ -45300,12 +46354,12 @@
         <v>81.9</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>277</v>
@@ -45327,12 +46381,12 @@
         <v>37.4</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>277</v>
@@ -45354,12 +46408,12 @@
         <v>-82.3</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>277</v>
@@ -45381,12 +46435,12 @@
         <v>-24.5</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>214</v>
@@ -45408,12 +46462,12 @@
         <v>-179.3</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>245</v>
@@ -45435,12 +46489,12 @@
         <v>113.7</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>245</v>
@@ -45462,12 +46516,12 @@
         <v>88.3</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>245</v>
@@ -45489,12 +46543,12 @@
         <v>51.4</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>245</v>
@@ -45516,12 +46570,12 @@
         <v>4.1</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>260</v>
@@ -45543,12 +46597,12 @@
         <v>35.9</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>260</v>
@@ -45570,12 +46624,12 @@
         <v>40.3</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>260</v>
@@ -45597,12 +46651,12 @@
         <v>9.1</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>260</v>
@@ -45624,12 +46678,12 @@
         <v>-20.4</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>260</v>
@@ -45651,12 +46705,12 @@
         <v>-0.5</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>83</v>
@@ -45678,12 +46732,12 @@
         <v>-200.9</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>83</v>
@@ -45705,12 +46759,12 @@
         <v>-170.2</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>83</v>
@@ -45732,12 +46786,12 @@
         <v>-120.8</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>90</v>
@@ -45759,12 +46813,12 @@
         <v>-183.6</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>90</v>
@@ -45786,12 +46840,12 @@
         <v>-175.1</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>189</v>
@@ -45813,12 +46867,12 @@
         <v>-91.5</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B103" s="0" t="s">
         <v>222</v>
@@ -45840,12 +46894,12 @@
         <v>-55.1</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B104" s="0" t="s">
         <v>222</v>
@@ -45867,12 +46921,12 @@
         <v>-80.5</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B105" s="0" t="s">
         <v>222</v>
@@ -45894,12 +46948,12 @@
         <v>-32</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B106" s="0" t="s">
         <v>222</v>
@@ -45921,12 +46975,12 @@
         <v>25.1</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>138</v>
@@ -45948,12 +47002,12 @@
         <v>-135.2</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B108" s="0" t="s">
         <v>138</v>
@@ -45975,12 +47029,12 @@
         <v>12.4</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>138</v>
@@ -46002,12 +47056,12 @@
         <v>32.2</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>143</v>
@@ -46029,12 +47083,12 @@
         <v>-201.6</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B111" s="0" t="s">
         <v>143</v>
@@ -46056,12 +47110,12 @@
         <v>-137.9</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>192</v>
@@ -46083,12 +47137,12 @@
         <v>115.2</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>150</v>
@@ -46110,12 +47164,12 @@
         <v>-97.6</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B114" s="0" t="s">
         <v>150</v>
@@ -46137,12 +47191,12 @@
         <v>-79.8</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B115" s="0" t="s">
         <v>192</v>
@@ -46164,12 +47218,12 @@
         <v>10.4</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B116" s="0" t="s">
         <v>157</v>
@@ -46191,12 +47245,12 @@
         <v>-172.4</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B117" s="0" t="s">
         <v>150</v>
@@ -46218,12 +47272,12 @@
         <v>17.1</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B118" s="0" t="s">
         <v>150</v>
@@ -46245,12 +47299,12 @@
         <v>-15.5</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B119" s="0" t="s">
         <v>114</v>
@@ -46272,12 +47326,12 @@
         <v>-104.3</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B120" s="0" t="s">
         <v>157</v>
@@ -46299,12 +47353,12 @@
         <v>65.5</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B121" s="0" t="s">
         <v>157</v>
@@ -46326,7 +47380,7 @@
         <v>57.8</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -46350,75 +47404,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="G1" s="0" t="s">
+        <v>569</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="I1" s="0" t="s">
         <v>567</v>
       </c>
-      <c r="H1" s="0" t="s">
-        <v>692</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>565</v>
-      </c>
       <c r="J1" s="0" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>359</v>
@@ -46482,7 +47536,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>359</v>
@@ -46527,7 +47581,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>359</v>
@@ -46572,7 +47626,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>359</v>
@@ -46621,7 +47675,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>359</v>
@@ -46666,13 +47720,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>260</v>
@@ -46692,13 +47746,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>260</v>
@@ -46718,13 +47772,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>260</v>
@@ -46744,13 +47798,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>260</v>
@@ -46770,13 +47824,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>260</v>
@@ -46796,13 +47850,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>150</v>
@@ -46822,13 +47876,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>150</v>
@@ -46848,13 +47902,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>150</v>
@@ -46874,13 +47928,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>150</v>
@@ -46900,13 +47954,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>150</v>
@@ -46929,10 +47983,10 @@
         <v>384</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>202</v>
@@ -46955,10 +48009,10 @@
         <v>384</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>202</v>
@@ -46981,10 +48035,10 @@
         <v>384</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>202</v>
@@ -47026,10 +48080,10 @@
         <v>384</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>202</v>
@@ -47052,10 +48106,10 @@
         <v>384</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>202</v>
@@ -47075,13 +48129,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>189</v>
@@ -47120,13 +48174,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>189</v>
@@ -47146,13 +48200,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>189</v>
@@ -47172,13 +48226,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>189</v>
@@ -47198,13 +48252,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>189</v>
@@ -47247,13 +48301,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>59</v>
@@ -47296,13 +48350,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>59</v>
@@ -47345,13 +48399,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>59</v>
@@ -47413,13 +48467,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>59</v>
@@ -47481,13 +48535,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>59</v>
@@ -47526,13 +48580,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>329</v>
@@ -47552,13 +48606,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>329</v>
@@ -47597,13 +48651,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>329</v>
@@ -47623,10 +48677,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>112</v>
@@ -47649,13 +48703,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>308</v>
@@ -47675,13 +48729,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>280</v>
@@ -47701,13 +48755,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>280</v>
@@ -47727,13 +48781,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>249</v>
@@ -47753,10 +48807,10 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>223</v>
@@ -47779,13 +48833,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>249</v>
@@ -47805,13 +48859,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>96</v>
@@ -47854,13 +48908,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>96</v>
@@ -47884,13 +48938,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>96</v>
@@ -47914,13 +48968,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>96</v>
@@ -47940,13 +48994,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>96</v>
@@ -47970,13 +49024,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>71</v>
@@ -47996,13 +49050,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>71</v>
@@ -48022,13 +49076,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>71</v>
@@ -48048,13 +49102,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>71</v>
@@ -48074,13 +49128,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>71</v>
@@ -48100,7 +49154,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>371</v>
@@ -48126,7 +49180,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>371</v>
@@ -48152,13 +49206,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>371</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>65</v>
@@ -48197,7 +49251,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>371</v>
@@ -48246,13 +49300,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>371</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>65</v>
@@ -48295,13 +49349,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>249</v>
@@ -48340,13 +49394,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>249</v>
@@ -48366,13 +49420,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>249</v>
@@ -48392,13 +49446,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>249</v>
@@ -48418,13 +49472,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>249</v>
@@ -48444,13 +49498,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>225</v>
@@ -48470,13 +49524,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>225</v>
@@ -48496,13 +49550,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>225</v>
@@ -48541,13 +49595,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>225</v>
@@ -48567,13 +49621,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>225</v>
@@ -48593,13 +49647,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>214</v>
@@ -48619,13 +49673,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>214</v>
@@ -48645,13 +49699,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>214</v>
@@ -48690,13 +49744,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>214</v>
@@ -48716,13 +49770,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>214</v>
@@ -48742,13 +49796,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>71</v>
@@ -48768,13 +49822,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>71</v>
@@ -48794,13 +49848,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>71</v>
@@ -48820,13 +49874,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>71</v>
@@ -48846,13 +49900,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>71</v>
@@ -48872,13 +49926,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>45</v>
@@ -48921,13 +49975,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>83</v>
@@ -48970,13 +50024,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>83</v>
@@ -49019,13 +50073,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>83</v>
@@ -49049,13 +50103,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>83</v>
@@ -49079,13 +50133,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>106</v>
@@ -49105,13 +50159,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>106</v>
@@ -49131,13 +50185,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D84" s="0" t="s">
         <v>106</v>
@@ -49157,13 +50211,13 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>106</v>
@@ -49183,13 +50237,13 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D86" s="0" t="s">
         <v>106</v>
@@ -49209,13 +50263,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>277</v>
@@ -49235,13 +50289,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D88" s="0" t="s">
         <v>277</v>
@@ -49280,13 +50334,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D89" s="0" t="s">
         <v>277</v>
@@ -49306,13 +50360,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D90" s="0" t="s">
         <v>277</v>
@@ -49332,13 +50386,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D91" s="0" t="s">
         <v>277</v>
@@ -49358,13 +50412,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D92" s="0" t="s">
         <v>214</v>
@@ -49384,13 +50438,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D93" s="0" t="s">
         <v>245</v>
@@ -49410,13 +50464,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D94" s="0" t="s">
         <v>245</v>
@@ -49436,13 +50490,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D95" s="0" t="s">
         <v>245</v>
@@ -49462,13 +50516,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D96" s="0" t="s">
         <v>245</v>
@@ -49488,13 +50542,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D97" s="0" t="s">
         <v>260</v>
@@ -49514,13 +50568,13 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D98" s="0" t="s">
         <v>260</v>
@@ -49540,13 +50594,13 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D99" s="0" t="s">
         <v>260</v>
@@ -49566,13 +50620,13 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D100" s="0" t="s">
         <v>260</v>
@@ -49592,13 +50646,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D101" s="0" t="s">
         <v>260</v>
@@ -49618,13 +50672,13 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D102" s="0" t="s">
         <v>83</v>
@@ -49644,13 +50698,13 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D103" s="0" t="s">
         <v>83</v>
@@ -49670,13 +50724,13 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D104" s="0" t="s">
         <v>83</v>
@@ -49696,13 +50750,13 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D105" s="0" t="s">
         <v>87</v>
@@ -49726,13 +50780,13 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D106" s="0" t="s">
         <v>87</v>
@@ -49752,13 +50806,13 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>222</v>
@@ -49778,13 +50832,13 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D108" s="0" t="s">
         <v>222</v>
@@ -49804,13 +50858,13 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>222</v>
@@ -49830,13 +50884,13 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D110" s="0" t="s">
         <v>222</v>
@@ -49856,13 +50910,13 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D111" s="0" t="s">
         <v>222</v>
@@ -49882,13 +50936,13 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D112" s="0" t="s">
         <v>138</v>
@@ -49912,13 +50966,13 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D113" s="0" t="s">
         <v>138</v>
@@ -49942,13 +50996,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D114" s="0" t="s">
         <v>138</v>
@@ -49968,13 +51022,13 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>186</v>
@@ -49998,13 +51052,13 @@
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>186</v>
@@ -50028,13 +51082,13 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D117" s="0" t="s">
         <v>153</v>
@@ -50054,13 +51108,13 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>153</v>
@@ -50080,13 +51134,13 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>153</v>
@@ -50106,13 +51160,13 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>153</v>
@@ -50132,13 +51186,13 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>153</v>
@@ -50158,13 +51212,13 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D122" s="0" t="s">
         <v>153</v>
@@ -50184,13 +51238,13 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D123" s="0" t="s">
         <v>153</v>
@@ -50210,13 +51264,13 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D124" s="0" t="s">
         <v>153</v>
@@ -50236,13 +51290,13 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D125" s="0" t="s">
         <v>153</v>
@@ -50262,13 +51316,13 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D126" s="0" t="s">
         <v>153</v>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -17,6 +17,7 @@
     <sheet name="Image_J_cut_stump" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="Image_J_subplot_locations" sheetId="8" state="visible" r:id="rId9"/>
     <sheet name="Recorded_subplot_locations" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Block_numbers" sheetId="10" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6753" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6707" uniqueCount="718">
   <si>
     <t xml:space="preserve">Block</t>
   </si>
@@ -1737,13 +1738,157 @@
     <t xml:space="preserve">angle</t>
   </si>
   <si>
+    <t xml:space="preserve">image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_2chain</t>
+  </si>
+  <si>
     <t xml:space="preserve">azi</t>
   </si>
   <si>
-    <t xml:space="preserve">Azi= - angle -  45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
+    <t xml:space="preserve">LL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B45</t>
   </si>
   <si>
     <t xml:space="preserve">C03</t>
@@ -1752,156 +1897,6 @@
     <t xml:space="preserve">C05</t>
   </si>
   <si>
-    <t xml:space="preserve">DI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DI5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B45</t>
-  </si>
-  <si>
     <t xml:space="preserve">C11</t>
   </si>
   <si>
@@ -2182,6 +2177,12 @@
   </si>
   <si>
     <t xml:space="preserve">D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLY</t>
   </si>
 </sst>
 </file>
@@ -2687,7 +2688,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9686,6 +9687,1114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C99"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -32508,7 +33617,7 @@
         <v>119</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8</v>
@@ -43301,7 +44410,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43327,13 +44436,10 @@
         <v>569</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>348</v>
+        <v>570</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>350</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43349,22 +44455,6 @@
       <c r="D2" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="E2" s="0" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>-156.5</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <f aca="false">-F2-45</f>
-        <v>111.5</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>377</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
@@ -43379,22 +44469,6 @@
       <c r="D3" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="E3" s="0" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>-126.2</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <f aca="false">-F3-45</f>
-        <v>81.2</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>374</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
@@ -43409,22 +44483,6 @@
       <c r="D4" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>-96.7</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <f aca="false">-F4-45</f>
-        <v>51.7</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>373</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
@@ -43439,22 +44497,6 @@
       <c r="D5" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E5" s="0" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>-116.1</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <f aca="false">-F5-45</f>
-        <v>71.1</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>373</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
@@ -43469,19 +44511,6 @@
       <c r="D6" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E6" s="0" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>-85.4</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <f aca="false">-F6-45</f>
-        <v>40.4</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
@@ -43496,22 +44525,6 @@
       <c r="D7" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E7" s="0" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>-81.4</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <f aca="false">-F7-45</f>
-        <v>36.4</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>369</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
@@ -43526,22 +44539,6 @@
       <c r="D8" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>125</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>-58.5</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <f aca="false">-F8-45</f>
-        <v>13.5</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
@@ -43556,19 +44553,6 @@
       <c r="D9" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E9" s="0" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>-46.5</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <f aca="false">-F9-45</f>
-        <v>1.5</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
@@ -43583,22 +44567,6 @@
       <c r="D10" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E10" s="0" t="n">
-        <v>77.4</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>-41</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <f aca="false">-F10-45</f>
-        <v>-4</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
@@ -43613,22 +44581,6 @@
       <c r="D11" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>-25.1</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <f aca="false">-F11-45</f>
-        <v>-19.9</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
@@ -43643,19 +44595,6 @@
       <c r="D12" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="E12" s="0" t="n">
-        <v>85.9</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <f aca="false">-F12-45</f>
-        <v>-48.3</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
@@ -43670,22 +44609,6 @@
       <c r="D13" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E13" s="0" t="n">
-        <v>97.1</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>-43.1</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <f aca="false">-F13-45</f>
-        <v>-1.9</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>368</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
@@ -43700,19 +44623,6 @@
       <c r="D14" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E14" s="0" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>-22.4</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <f aca="false">-F14-45</f>
-        <v>-22.6</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
@@ -43727,19 +44637,6 @@
       <c r="D15" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E15" s="0" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>-150.3</v>
-      </c>
-      <c r="G15" s="0" t="n">
-        <f aca="false">-F15-45</f>
-        <v>105.3</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
@@ -43754,22 +44651,6 @@
       <c r="D16" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E16" s="0" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>-126.6</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <f aca="false">-F16-45</f>
-        <v>81.6</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>572</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
@@ -43784,22 +44665,6 @@
       <c r="D17" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E17" s="0" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>-125.5</v>
-      </c>
-      <c r="G17" s="0" t="n">
-        <f aca="false">-F17-45</f>
-        <v>80.5</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I17" s="0" t="s">
-        <v>572</v>
-      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
@@ -43814,22 +44679,6 @@
       <c r="D18" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E18" s="0" t="n">
-        <v>65.1</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>-113</v>
-      </c>
-      <c r="G18" s="0" t="n">
-        <f aca="false">-F18-45</f>
-        <v>68</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>572</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
@@ -43844,19 +44693,6 @@
       <c r="D19" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E19" s="0" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <v>-173.9</v>
-      </c>
-      <c r="G19" s="0" t="n">
-        <f aca="false">-F19-45</f>
-        <v>128.9</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
@@ -43871,19 +44707,6 @@
       <c r="D20" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E20" s="0" t="n">
-        <v>72.4</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>-54.8</v>
-      </c>
-      <c r="G20" s="0" t="n">
-        <f aca="false">-F20-45</f>
-        <v>9.8</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
@@ -43898,15 +44721,6 @@
       <c r="D21" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E21" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>-55.3</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
@@ -43921,18 +44735,6 @@
       <c r="D22" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E22" s="0" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="F22" s="0" t="n">
-        <v>-86.7</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I22" s="0" t="s">
-        <v>573</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
@@ -43947,18 +44749,6 @@
       <c r="D23" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E23" s="0" t="n">
-        <v>116.7</v>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>-86.3</v>
-      </c>
-      <c r="H23" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I23" s="0" t="s">
-        <v>573</v>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
@@ -43973,18 +44763,6 @@
       <c r="D24" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E24" s="0" t="n">
-        <v>108.3</v>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>-84</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>573</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
@@ -43999,18 +44777,6 @@
       <c r="D25" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E25" s="0" t="n">
-        <v>108.8</v>
-      </c>
-      <c r="F25" s="0" t="n">
-        <v>-82</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>573</v>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
@@ -44025,18 +44791,6 @@
       <c r="D26" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E26" s="0" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>-71</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>573</v>
-      </c>
     </row>
     <row r="27" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="53" t="n">
@@ -44051,12 +44805,6 @@
       <c r="D27" s="53" t="n">
         <v>-6</v>
       </c>
-      <c r="H27" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="I27" s="53" t="s">
-        <v>574</v>
-      </c>
     </row>
     <row r="28" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="53" t="n">
@@ -44071,12 +44819,6 @@
       <c r="D28" s="53" t="n">
         <v>-6</v>
       </c>
-      <c r="H28" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="I28" s="53" t="s">
-        <v>575</v>
-      </c>
     </row>
     <row r="29" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="53" t="n">
@@ -44090,12 +44832,6 @@
       </c>
       <c r="D29" s="53" t="n">
         <v>-6</v>
-      </c>
-      <c r="H29" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="I29" s="53" t="s">
-        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -44137,10 +44873,10 @@
         <v>568</v>
       </c>
       <c r="G1" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>569</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44167,7 +44903,7 @@
         <v>52.2</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44194,7 +44930,7 @@
         <v>21.9</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44221,7 +44957,7 @@
         <v>15.5</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44248,7 +44984,7 @@
         <v>-18</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44275,12 +45011,12 @@
         <v>-174.7</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>253</v>
@@ -44302,12 +45038,12 @@
         <v>-108.1</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>253</v>
@@ -44329,12 +45065,12 @@
         <v>-85.4</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>260</v>
@@ -44356,12 +45092,12 @@
         <v>-153.2</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>260</v>
@@ -44383,12 +45119,12 @@
         <v>-75.5</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>297</v>
@@ -44410,12 +45146,12 @@
         <v>-126</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>147</v>
@@ -44437,12 +45173,12 @@
         <v>32</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>150</v>
@@ -44464,12 +45200,12 @@
         <v>-215.1</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>195</v>
@@ -44491,12 +45227,12 @@
         <v>96.5</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>150</v>
@@ -44518,12 +45254,12 @@
         <v>-155.9</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>150</v>
@@ -44545,12 +45281,12 @@
         <v>75.3</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>233</v>
@@ -44572,12 +45308,12 @@
         <v>92.3</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>233</v>
@@ -44599,12 +45335,12 @@
         <v>39.7</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>233</v>
@@ -44626,12 +45362,12 @@
         <v>-6.9</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>233</v>
@@ -44653,12 +45389,12 @@
         <v>-22.3</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>233</v>
@@ -44680,12 +45416,12 @@
         <v>14.9</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>189</v>
@@ -44707,12 +45443,12 @@
         <v>53.6</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>146</v>
@@ -44734,12 +45470,12 @@
         <v>-153.3</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>189</v>
@@ -44761,12 +45497,12 @@
         <v>0.600000000000001</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>189</v>
@@ -44788,12 +45524,12 @@
         <v>25.7</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>146</v>
@@ -44815,12 +45551,12 @@
         <v>-59.4</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>90</v>
@@ -44842,12 +45578,12 @@
         <v>118</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>90</v>
@@ -44869,12 +45605,12 @@
         <v>100.2</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>90</v>
@@ -44896,12 +45632,12 @@
         <v>69.4</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>90</v>
@@ -44923,12 +45659,12 @@
         <v>70.3</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>90</v>
@@ -44950,12 +45686,12 @@
         <v>26.8</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>329</v>
@@ -44977,12 +45713,12 @@
         <v>-41.2</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>329</v>
@@ -45004,12 +45740,12 @@
         <v>7</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>329</v>
@@ -45031,7 +45767,7 @@
         <v>-27.9</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45058,12 +45794,12 @@
         <v>48.4</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>312</v>
@@ -45085,12 +45821,12 @@
         <v>-182.5</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>280</v>
@@ -45112,12 +45848,12 @@
         <v>-120.4</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>280</v>
@@ -45139,12 +45875,12 @@
         <v>-84</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>280</v>
@@ -45166,7 +45902,7 @@
         <v>25.5</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45193,12 +45929,12 @@
         <v>1</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>253</v>
@@ -45220,12 +45956,12 @@
         <v>-156.5</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>96</v>
@@ -45247,12 +45983,12 @@
         <v>87.4</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>96</v>
@@ -45274,12 +46010,12 @@
         <v>44.4</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>96</v>
@@ -45301,12 +46037,12 @@
         <v>-103.8</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>101</v>
@@ -45328,12 +46064,12 @@
         <v>-188.4</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>101</v>
@@ -45355,12 +46091,12 @@
         <v>122.5</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>114</v>
@@ -45382,12 +46118,12 @@
         <v>91.6</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>114</v>
@@ -45409,12 +46145,12 @@
         <v>64.3</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>75</v>
@@ -45436,12 +46172,12 @@
         <v>102.7</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>75</v>
@@ -45463,12 +46199,12 @@
         <v>77.2</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>75</v>
@@ -45490,7 +46226,7 @@
         <v>37.6</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45517,7 +46253,7 @@
         <v>99.9</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45544,12 +46280,12 @@
         <v>51.6</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>65</v>
@@ -45571,7 +46307,7 @@
         <v>-148.2</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45598,12 +46334,12 @@
         <v>-171.6</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>573</v>
+        <v>621</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>65</v>
@@ -45625,12 +46361,12 @@
         <v>-76.8</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>249</v>
@@ -45652,12 +46388,12 @@
         <v>68.8</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>249</v>
@@ -45679,12 +46415,12 @@
         <v>23.6</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>249</v>
@@ -45706,12 +46442,12 @@
         <v>-75.8</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>253</v>
@@ -45733,12 +46469,12 @@
         <v>-205.7</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>249</v>
@@ -45760,12 +46496,12 @@
         <v>4.5</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>214</v>
@@ -45787,12 +46523,12 @@
         <v>118.9</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>214</v>
@@ -45814,12 +46550,12 @@
         <v>111.3</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>214</v>
@@ -45841,12 +46577,12 @@
         <v>68.3</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>214</v>
@@ -45868,12 +46604,12 @@
         <v>-16.1</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>214</v>
@@ -45895,12 +46631,12 @@
         <v>24.3</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>114</v>
@@ -45922,12 +46658,12 @@
         <v>2.3</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>114</v>
@@ -45949,12 +46685,12 @@
         <v>-104.7</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>75</v>
@@ -45976,12 +46712,12 @@
         <v>-167.3</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>75</v>
@@ -46003,12 +46739,12 @@
         <v>-134.8</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>75</v>
@@ -46030,12 +46766,12 @@
         <v>-145.9</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>45</v>
@@ -46057,12 +46793,12 @@
         <v>-139.1</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>45</v>
@@ -46084,12 +46820,12 @@
         <v>-119.3</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>45</v>
@@ -46111,12 +46847,12 @@
         <v>-86.6</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>45</v>
@@ -46138,12 +46874,12 @@
         <v>-84.5</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>83</v>
@@ -46165,12 +46901,12 @@
         <v>-10.5</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>106</v>
@@ -46192,12 +46928,12 @@
         <v>-139.7</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>106</v>
@@ -46219,12 +46955,12 @@
         <v>40.7</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>106</v>
@@ -46246,12 +46982,12 @@
         <v>-91.1</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>106</v>
@@ -46273,12 +47009,12 @@
         <v>-64.5</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>106</v>
@@ -46300,12 +47036,12 @@
         <v>-83.2</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>312</v>
@@ -46327,12 +47063,12 @@
         <v>86.7</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>277</v>
@@ -46354,12 +47090,12 @@
         <v>81.9</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>277</v>
@@ -46381,12 +47117,12 @@
         <v>37.4</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>277</v>
@@ -46408,12 +47144,12 @@
         <v>-82.3</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>277</v>
@@ -46435,12 +47171,12 @@
         <v>-24.5</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>214</v>
@@ -46462,12 +47198,12 @@
         <v>-179.3</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>245</v>
@@ -46489,12 +47225,12 @@
         <v>113.7</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>245</v>
@@ -46516,12 +47252,12 @@
         <v>88.3</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>245</v>
@@ -46543,12 +47279,12 @@
         <v>51.4</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>245</v>
@@ -46570,12 +47306,12 @@
         <v>4.1</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>260</v>
@@ -46597,12 +47333,12 @@
         <v>35.9</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>260</v>
@@ -46624,12 +47360,12 @@
         <v>40.3</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>260</v>
@@ -46651,12 +47387,12 @@
         <v>9.1</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>260</v>
@@ -46678,12 +47414,12 @@
         <v>-20.4</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>260</v>
@@ -46705,12 +47441,12 @@
         <v>-0.5</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>83</v>
@@ -46732,12 +47468,12 @@
         <v>-200.9</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>83</v>
@@ -46759,12 +47495,12 @@
         <v>-170.2</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>83</v>
@@ -46786,12 +47522,12 @@
         <v>-120.8</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>90</v>
@@ -46813,12 +47549,12 @@
         <v>-183.6</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>90</v>
@@ -46840,12 +47576,12 @@
         <v>-175.1</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>189</v>
@@ -46867,12 +47603,12 @@
         <v>-91.5</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B103" s="0" t="s">
         <v>222</v>
@@ -46894,12 +47630,12 @@
         <v>-55.1</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B104" s="0" t="s">
         <v>222</v>
@@ -46921,12 +47657,12 @@
         <v>-80.5</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B105" s="0" t="s">
         <v>222</v>
@@ -46948,12 +47684,12 @@
         <v>-32</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B106" s="0" t="s">
         <v>222</v>
@@ -46975,12 +47711,12 @@
         <v>25.1</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>138</v>
@@ -47002,12 +47738,12 @@
         <v>-135.2</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B108" s="0" t="s">
         <v>138</v>
@@ -47029,12 +47765,12 @@
         <v>12.4</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>138</v>
@@ -47056,12 +47792,12 @@
         <v>32.2</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>143</v>
@@ -47083,12 +47819,12 @@
         <v>-201.6</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B111" s="0" t="s">
         <v>143</v>
@@ -47110,12 +47846,12 @@
         <v>-137.9</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>192</v>
@@ -47137,12 +47873,12 @@
         <v>115.2</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>150</v>
@@ -47164,12 +47900,12 @@
         <v>-97.6</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B114" s="0" t="s">
         <v>150</v>
@@ -47191,12 +47927,12 @@
         <v>-79.8</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B115" s="0" t="s">
         <v>192</v>
@@ -47218,12 +47954,12 @@
         <v>10.4</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B116" s="0" t="s">
         <v>157</v>
@@ -47245,12 +47981,12 @@
         <v>-172.4</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B117" s="0" t="s">
         <v>150</v>
@@ -47272,12 +48008,12 @@
         <v>17.1</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B118" s="0" t="s">
         <v>150</v>
@@ -47299,12 +48035,12 @@
         <v>-15.5</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B119" s="0" t="s">
         <v>114</v>
@@ -47326,12 +48062,12 @@
         <v>-104.3</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B120" s="0" t="s">
         <v>157</v>
@@ -47353,12 +48089,12 @@
         <v>65.5</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B121" s="0" t="s">
         <v>157</v>
@@ -47380,7 +48116,7 @@
         <v>57.8</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -47404,70 +48140,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D1" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="F1" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="G1" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>692</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>694</v>
       </c>
       <c r="I1" s="0" t="s">
         <v>567</v>
       </c>
       <c r="J1" s="0" t="s">
+        <v>693</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="L1" s="0" t="s">
         <v>695</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="M1" s="0" t="s">
         <v>696</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="N1" s="0" t="s">
         <v>697</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="O1" s="0" t="s">
         <v>698</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="P1" s="0" t="s">
         <v>699</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="Q1" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="R1" s="0" t="s">
         <v>701</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="S1" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="T1" s="0" t="s">
         <v>703</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="U1" s="0" t="s">
         <v>704</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="V1" s="0" t="s">
         <v>705</v>
-      </c>
-      <c r="U1" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="V1" s="0" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47726,7 +48462,7 @@
         <v>484</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>260</v>
@@ -47752,7 +48488,7 @@
         <v>484</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>260</v>
@@ -47778,7 +48514,7 @@
         <v>484</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>260</v>
@@ -47804,7 +48540,7 @@
         <v>484</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>260</v>
@@ -47830,7 +48566,7 @@
         <v>484</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>260</v>
@@ -47856,7 +48592,7 @@
         <v>450</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>150</v>
@@ -47882,7 +48618,7 @@
         <v>450</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>150</v>
@@ -47908,7 +48644,7 @@
         <v>450</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>150</v>
@@ -47934,7 +48670,7 @@
         <v>450</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>150</v>
@@ -47960,7 +48696,7 @@
         <v>450</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>150</v>
@@ -47986,7 +48722,7 @@
         <v>464</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>202</v>
@@ -48012,7 +48748,7 @@
         <v>464</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>202</v>
@@ -48038,7 +48774,7 @@
         <v>464</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>202</v>
@@ -48083,7 +48819,7 @@
         <v>464</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>202</v>
@@ -48109,7 +48845,7 @@
         <v>464</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>202</v>
@@ -48129,13 +48865,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>449</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>189</v>
@@ -48174,13 +48910,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>449</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>189</v>
@@ -48200,13 +48936,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>449</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>189</v>
@@ -48226,13 +48962,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>449</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>189</v>
@@ -48252,13 +48988,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>449</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>189</v>
@@ -48307,7 +49043,7 @@
         <v>436</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>59</v>
@@ -48356,7 +49092,7 @@
         <v>436</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>59</v>
@@ -48405,7 +49141,7 @@
         <v>436</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>59</v>
@@ -48473,7 +49209,7 @@
         <v>436</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>59</v>
@@ -48541,7 +49277,7 @@
         <v>436</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>59</v>
@@ -48586,7 +49322,7 @@
         <v>492</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>329</v>
@@ -48612,7 +49348,7 @@
         <v>492</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>329</v>
@@ -48657,7 +49393,7 @@
         <v>492</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>329</v>
@@ -48709,7 +49445,7 @@
         <v>492</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>308</v>
@@ -48735,7 +49471,7 @@
         <v>487</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>280</v>
@@ -48761,7 +49497,7 @@
         <v>487</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>280</v>
@@ -48787,7 +49523,7 @@
         <v>487</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>249</v>
@@ -48839,7 +49575,7 @@
         <v>487</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>249</v>
@@ -48865,7 +49601,7 @@
         <v>444</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>96</v>
@@ -48914,7 +49650,7 @@
         <v>444</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>96</v>
@@ -48944,7 +49680,7 @@
         <v>444</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>96</v>
@@ -48974,7 +49710,7 @@
         <v>444</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>96</v>
@@ -49000,7 +49736,7 @@
         <v>444</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>96</v>
@@ -49024,13 +49760,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>71</v>
@@ -49050,13 +49786,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>71</v>
@@ -49076,13 +49812,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>71</v>
@@ -49102,13 +49838,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>71</v>
@@ -49128,13 +49864,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>71</v>
@@ -49212,7 +49948,7 @@
         <v>371</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>65</v>
@@ -49306,7 +50042,7 @@
         <v>371</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>573</v>
+        <v>621</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>65</v>
@@ -49355,7 +50091,7 @@
         <v>478</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>249</v>
@@ -49400,7 +50136,7 @@
         <v>478</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>249</v>
@@ -49426,7 +50162,7 @@
         <v>478</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>249</v>
@@ -49452,7 +50188,7 @@
         <v>478</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>249</v>
@@ -49478,7 +50214,7 @@
         <v>478</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>249</v>
@@ -49504,7 +50240,7 @@
         <v>467</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>225</v>
@@ -49530,7 +50266,7 @@
         <v>467</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>225</v>
@@ -49556,7 +50292,7 @@
         <v>467</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>225</v>
@@ -49601,7 +50337,7 @@
         <v>467</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>225</v>
@@ -49627,7 +50363,7 @@
         <v>467</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>225</v>
@@ -49653,7 +50389,7 @@
         <v>473</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>214</v>
@@ -49679,7 +50415,7 @@
         <v>473</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>214</v>
@@ -49705,7 +50441,7 @@
         <v>473</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>214</v>
@@ -49750,7 +50486,7 @@
         <v>473</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>214</v>
@@ -49776,7 +50512,7 @@
         <v>473</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>214</v>
@@ -49796,13 +50532,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>455</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>71</v>
@@ -49822,13 +50558,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>455</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>71</v>
@@ -49848,13 +50584,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>455</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>71</v>
@@ -49874,13 +50610,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>455</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>71</v>
@@ -49900,13 +50636,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>455</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>71</v>
@@ -49932,7 +50668,7 @@
         <v>380</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>45</v>
@@ -49981,7 +50717,7 @@
         <v>380</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>83</v>
@@ -50030,7 +50766,7 @@
         <v>380</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>83</v>
@@ -50079,7 +50815,7 @@
         <v>380</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>83</v>
@@ -50109,7 +50845,7 @@
         <v>380</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>83</v>
@@ -50139,7 +50875,7 @@
         <v>452</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>106</v>
@@ -50165,7 +50901,7 @@
         <v>452</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>106</v>
@@ -50191,7 +50927,7 @@
         <v>452</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D84" s="0" t="s">
         <v>106</v>
@@ -50217,7 +50953,7 @@
         <v>452</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>106</v>
@@ -50243,7 +50979,7 @@
         <v>452</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D86" s="0" t="s">
         <v>106</v>
@@ -50269,7 +51005,7 @@
         <v>489</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>277</v>
@@ -50295,7 +51031,7 @@
         <v>489</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D88" s="0" t="s">
         <v>277</v>
@@ -50340,7 +51076,7 @@
         <v>489</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D89" s="0" t="s">
         <v>277</v>
@@ -50366,7 +51102,7 @@
         <v>489</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D90" s="0" t="s">
         <v>277</v>
@@ -50392,7 +51128,7 @@
         <v>489</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D91" s="0" t="s">
         <v>277</v>
@@ -50418,7 +51154,7 @@
         <v>475</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D92" s="0" t="s">
         <v>214</v>
@@ -50444,7 +51180,7 @@
         <v>475</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D93" s="0" t="s">
         <v>245</v>
@@ -50470,7 +51206,7 @@
         <v>475</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D94" s="0" t="s">
         <v>245</v>
@@ -50496,7 +51232,7 @@
         <v>475</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D95" s="0" t="s">
         <v>245</v>
@@ -50522,7 +51258,7 @@
         <v>475</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D96" s="0" t="s">
         <v>245</v>
@@ -50542,13 +51278,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>481</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D97" s="0" t="s">
         <v>260</v>
@@ -50568,13 +51304,13 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>481</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D98" s="0" t="s">
         <v>260</v>
@@ -50594,13 +51330,13 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>481</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D99" s="0" t="s">
         <v>260</v>
@@ -50620,13 +51356,13 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>481</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D100" s="0" t="s">
         <v>260</v>
@@ -50646,13 +51382,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>481</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D101" s="0" t="s">
         <v>260</v>
@@ -50678,7 +51414,7 @@
         <v>441</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D102" s="0" t="s">
         <v>83</v>
@@ -50704,7 +51440,7 @@
         <v>441</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D103" s="0" t="s">
         <v>83</v>
@@ -50730,7 +51466,7 @@
         <v>441</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D104" s="0" t="s">
         <v>83</v>
@@ -50756,7 +51492,7 @@
         <v>441</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D105" s="0" t="s">
         <v>87</v>
@@ -50786,7 +51522,7 @@
         <v>441</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D106" s="0" t="s">
         <v>87</v>
@@ -50812,7 +51548,7 @@
         <v>470</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>222</v>
@@ -50838,7 +51574,7 @@
         <v>470</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D108" s="0" t="s">
         <v>222</v>
@@ -50864,7 +51600,7 @@
         <v>470</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>222</v>
@@ -50890,7 +51626,7 @@
         <v>470</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D110" s="0" t="s">
         <v>222</v>
@@ -50916,7 +51652,7 @@
         <v>470</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D111" s="0" t="s">
         <v>222</v>
@@ -50942,7 +51678,7 @@
         <v>446</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D112" s="0" t="s">
         <v>138</v>
@@ -50972,7 +51708,7 @@
         <v>446</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D113" s="0" t="s">
         <v>138</v>
@@ -51002,7 +51738,7 @@
         <v>446</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D114" s="0" t="s">
         <v>138</v>
@@ -51028,7 +51764,7 @@
         <v>446</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>186</v>
@@ -51058,7 +51794,7 @@
         <v>446</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>186</v>
@@ -51088,7 +51824,7 @@
         <v>461</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D117" s="0" t="s">
         <v>153</v>
@@ -51114,7 +51850,7 @@
         <v>461</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>153</v>
@@ -51140,7 +51876,7 @@
         <v>461</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>153</v>
@@ -51166,7 +51902,7 @@
         <v>461</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>153</v>
@@ -51192,7 +51928,7 @@
         <v>461</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>153</v>
@@ -51212,13 +51948,13 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B122" s="0" t="s">
         <v>458</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D122" s="0" t="s">
         <v>153</v>
@@ -51238,13 +51974,13 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B123" s="0" t="s">
         <v>458</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D123" s="0" t="s">
         <v>153</v>
@@ -51264,13 +52000,13 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B124" s="0" t="s">
         <v>458</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D124" s="0" t="s">
         <v>153</v>
@@ -51290,13 +52026,13 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B125" s="0" t="s">
         <v>458</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D125" s="0" t="s">
         <v>153</v>
@@ -51316,13 +52052,13 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B126" s="0" t="s">
         <v>458</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D126" s="0" t="s">
         <v>153</v>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6707" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="734">
   <si>
     <t xml:space="preserve">Block</t>
   </si>
@@ -1237,6 +1237,12 @@
     <t xml:space="preserve">alder, not diseased tree</t>
   </si>
   <si>
+    <t xml:space="preserve">condition blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition “?”</t>
+  </si>
+  <si>
     <t xml:space="preserve">i.e. T033-218-070-ST-24-99DS</t>
   </si>
   <si>
@@ -1741,18 +1747,63 @@
     <t xml:space="preserve">image</t>
   </si>
   <si>
-    <t xml:space="preserve">image_angle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image_2chain</t>
+    <t xml:space="preserve">image_diag_angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_diag_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_diag_ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">px_per_ft</t>
   </si>
   <si>
     <t xml:space="preserve">azi</t>
   </si>
   <si>
+    <t xml:space="preserve">3,1</t>
+  </si>
+  <si>
     <t xml:space="preserve">LL</t>
   </si>
   <si>
+    <t xml:space="preserve">1,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,1</t>
+  </si>
+  <si>
     <t xml:space="preserve">A11</t>
   </si>
   <si>
@@ -1772,9 +1823,6 @@
   </si>
   <si>
     <t xml:space="preserve">A21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR</t>
   </si>
   <si>
     <t xml:space="preserve">A22</t>
@@ -9700,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32701,6 +32749,9 @@
       <c r="H754" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="I754" s="0" t="s">
+        <v>402</v>
+      </c>
       <c r="M754" s="0" t="s">
         <v>63</v>
       </c>
@@ -32722,13 +32773,16 @@
         <v>60</v>
       </c>
       <c r="F755" s="0" t="s">
-        <v>355</v>
+        <v>162</v>
       </c>
       <c r="G755" s="0" t="s">
         <v>356</v>
       </c>
       <c r="H755" s="0" t="n">
         <v>10</v>
+      </c>
+      <c r="I755" s="0" t="s">
+        <v>403</v>
       </c>
       <c r="M755" s="0" t="s">
         <v>63</v>
@@ -32806,7 +32860,7 @@
         <v>24</v>
       </c>
       <c r="I758" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J758" s="5"/>
     </row>
@@ -33585,10 +33639,10 @@
         <v>340</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>347</v>
@@ -33746,7 +33800,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>361</v>
@@ -33829,7 +33883,7 @@
         <v>14</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>356</v>
@@ -33952,7 +34006,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>361</v>
@@ -34375,7 +34429,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>361</v>
@@ -34418,7 +34472,7 @@
         <v>6</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>361</v>
@@ -34881,7 +34935,7 @@
         <v>10</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F64" s="0" t="s">
         <v>361</v>
@@ -35144,7 +35198,7 @@
         <v>12</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>361</v>
@@ -35567,7 +35621,7 @@
         <v>12</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F98" s="0" t="s">
         <v>361</v>
@@ -35870,7 +35924,7 @@
         <v>14</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F113" s="0" t="s">
         <v>361</v>
@@ -36153,7 +36207,7 @@
         <v>12</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>356</v>
@@ -36356,7 +36410,7 @@
         <v>14</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>356</v>
@@ -36459,7 +36513,7 @@
         <v>10</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F142" s="0" t="s">
         <v>361</v>
@@ -36562,7 +36616,7 @@
         <v>4</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F147" s="0" t="s">
         <v>361</v>
@@ -36705,7 +36759,7 @@
         <v>8</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F154" s="0" t="s">
         <v>361</v>
@@ -36728,7 +36782,7 @@
         <v>12</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>361</v>
@@ -36771,7 +36825,7 @@
         <v>10</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F157" s="0" t="s">
         <v>361</v>
@@ -36914,7 +36968,7 @@
         <v>8</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F164" s="0" t="s">
         <v>361</v>
@@ -37244,13 +37298,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D1" s="0" t="s">
         <v>41</v>
@@ -37259,63 +37313,63 @@
         <v>349</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>30</v>
@@ -37324,7 +37378,7 @@
         <v>-8.72</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E2" s="0" t="s">
         <v>359</v>
@@ -37374,7 +37428,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>30</v>
@@ -37383,7 +37437,7 @@
         <v>-7.48</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>371</v>
@@ -37445,7 +37499,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>28</v>
@@ -37454,10 +37508,10 @@
         <v>-7.48</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>355</v>
@@ -37504,7 +37558,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>22.94</v>
@@ -37513,7 +37567,7 @@
         <v>-6.54</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>380</v>
@@ -37551,7 +37605,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>22.94</v>
@@ -37560,10 +37614,10 @@
         <v>-4.4</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>64</v>
@@ -37598,7 +37652,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>22.94</v>
@@ -37607,10 +37661,10 @@
         <v>-2.43</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>355</v>
@@ -37645,7 +37699,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>22.94</v>
@@ -37654,7 +37708,7 @@
         <v>-6</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>64</v>
@@ -37707,7 +37761,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>26</v>
@@ -37716,10 +37770,10 @@
         <v>-4.4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>389</v>
@@ -37763,7 +37817,7 @@
         <v>-4</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>389</v>
@@ -37822,7 +37876,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>28.55</v>
@@ -37831,10 +37885,10 @@
         <v>-4</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>354</v>
@@ -37869,7 +37923,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>28.55</v>
@@ -37878,7 +37932,7 @@
         <v>-6</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>384</v>
@@ -37943,7 +37997,7 @@
         <v>-6</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>162</v>
@@ -37984,7 +38038,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>32.56</v>
@@ -37993,10 +38047,10 @@
         <v>-6</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>64</v>
@@ -38031,7 +38085,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>32.13</v>
@@ -38040,10 +38094,10 @@
         <v>-4</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>64</v>
@@ -38096,7 +38150,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>26</v>
@@ -38105,10 +38159,10 @@
         <v>-1.29</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>389</v>
@@ -38155,7 +38209,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>24.2</v>
@@ -38164,10 +38218,10 @@
         <v>0.4</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>162</v>
@@ -38220,7 +38274,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>22</v>
@@ -38229,10 +38283,10 @@
         <v>0.4</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>64</v>
@@ -38267,7 +38321,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>19.28</v>
@@ -38276,10 +38330,10 @@
         <v>0.4</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>162</v>
@@ -38314,7 +38368,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>18</v>
@@ -38323,7 +38377,7 @@
         <v>0.4</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>354</v>
@@ -38364,7 +38418,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>16.5</v>
@@ -38373,10 +38427,10 @@
         <v>0.4</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>162</v>
@@ -38435,7 +38489,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>14.55</v>
@@ -38444,10 +38498,10 @@
         <v>0.4</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>354</v>
@@ -38482,7 +38536,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>13.62</v>
@@ -38491,10 +38545,10 @@
         <v>0.4</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>389</v>
@@ -38535,7 +38589,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>12</v>
@@ -38544,10 +38598,10 @@
         <v>0.4</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>355</v>
@@ -38615,10 +38669,10 @@
         <v>162</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>354</v>
@@ -38665,7 +38719,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>8</v>
@@ -38674,10 +38728,10 @@
         <v>162</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>355</v>
@@ -38724,7 +38778,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>9.24</v>
@@ -38733,12 +38787,12 @@
         <v>-2</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>13.62</v>
@@ -38747,7 +38801,7 @@
         <v>-2</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38761,12 +38815,12 @@
         <v>-2</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>16.5</v>
@@ -38775,12 +38829,12 @@
         <v>-2.43</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>16.73</v>
@@ -38789,12 +38843,12 @@
         <v>-2.43</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>19.28</v>
@@ -38803,12 +38857,12 @@
         <v>-2.43</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>20</v>
@@ -38817,12 +38871,12 @@
         <v>-2.43</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>16.73</v>
@@ -38831,7 +38885,7 @@
         <v>-4</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38845,7 +38899,7 @@
         <v>-4</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38859,12 +38913,12 @@
         <v>-4</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>9.55</v>
@@ -38875,7 +38929,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>9.12</v>
@@ -38884,7 +38938,7 @@
         <v>-6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38898,12 +38952,12 @@
         <v>-6</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>14</v>
@@ -38912,12 +38966,12 @@
         <v>-7.66</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>16.73</v>
@@ -38926,12 +38980,12 @@
         <v>-7.4</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>8</v>
@@ -38940,7 +38994,7 @@
         <v>2</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38954,12 +39008,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>12.49</v>
@@ -38968,12 +39022,12 @@
         <v>2</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>12.49</v>
@@ -38982,12 +39036,12 @@
         <v>4</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>8</v>
@@ -38996,7 +39050,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39010,12 +39064,12 @@
         <v>4</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>14.55</v>
@@ -39024,12 +39078,12 @@
         <v>3.54</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>14.55</v>
@@ -39038,12 +39092,12 @@
         <v>2.41</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>17.04</v>
@@ -39052,12 +39106,12 @@
         <v>2.41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>18</v>
@@ -39066,12 +39120,12 @@
         <v>2.41</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>22</v>
@@ -39080,12 +39134,12 @@
         <v>2.41</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>22</v>
@@ -39094,12 +39148,12 @@
         <v>4.37</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>18.65</v>
@@ -39108,12 +39162,12 @@
         <v>4.37</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>17.04</v>
@@ -39122,12 +39176,12 @@
         <v>4.26</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>16.23</v>
@@ -39136,12 +39190,12 @@
         <v>4.26</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>16.23</v>
@@ -39150,12 +39204,12 @@
         <v>4.9</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>14</v>
@@ -39164,12 +39218,12 @@
         <v>4.9</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>14</v>
@@ -39178,12 +39232,12 @@
         <v>6.06</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>18.65</v>
@@ -39203,7 +39257,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39217,12 +39271,12 @@
         <v>8</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>25.5</v>
@@ -39231,7 +39285,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -39699,13 +39753,13 @@
       <c r="BF7" s="28"/>
       <c r="BG7" s="28"/>
       <c r="BH7" s="29" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="BI7" s="29"/>
       <c r="BJ7" s="29"/>
       <c r="BK7" s="29"/>
       <c r="BL7" s="30" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="BM7" s="30"/>
       <c r="BN7" s="30"/>
@@ -40099,25 +40153,25 @@
       <c r="BA11" s="8"/>
       <c r="BB11" s="9"/>
       <c r="BD11" s="33" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="BE11" s="33"/>
       <c r="BF11" s="33"/>
       <c r="BG11" s="33"/>
       <c r="BH11" s="30" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="BI11" s="30"/>
       <c r="BJ11" s="30"/>
       <c r="BK11" s="30"/>
       <c r="BL11" s="30" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="BM11" s="30"/>
       <c r="BN11" s="30"/>
       <c r="BO11" s="30"/>
       <c r="BP11" s="31" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="BQ11" s="31"/>
       <c r="BR11" s="31"/>
@@ -40547,7 +40601,7 @@
       <c r="BA15" s="8"/>
       <c r="BB15" s="9"/>
       <c r="BD15" s="34" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="BE15" s="34"/>
       <c r="BF15" s="34"/>
@@ -40557,13 +40611,13 @@
       <c r="BJ15" s="35"/>
       <c r="BK15" s="35"/>
       <c r="BL15" s="36" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="BM15" s="36"/>
       <c r="BN15" s="36"/>
       <c r="BO15" s="36"/>
       <c r="BP15" s="37" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="BQ15" s="37"/>
       <c r="BR15" s="37"/>
@@ -41939,7 +41993,7 @@
       </c>
       <c r="BB28" s="17"/>
       <c r="BD28" s="41" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="BE28" s="41"/>
       <c r="BF28" s="41"/>
@@ -44410,7 +44464,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:AMJ65"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44418,28 +44472,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44447,13 +44510,39 @@
         <v>3</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>55</v>
+        <v>577</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>-8</v>
+        <v>1</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-125.43</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <f aca="false">SQRT(2*(I2^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <f aca="false">-(F2-H2)</f>
+        <v>80.855</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44461,13 +44550,39 @@
         <v>3</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>55</v>
+        <v>577</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>-8</v>
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-156.61</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <f aca="false">SQRT(2*(I3^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <f aca="false">-(F3-H3)</f>
+        <v>112.035</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44475,13 +44590,39 @@
         <v>5</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-116.09</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <f aca="false">SQRT(2*(I4^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <f aca="false">-(F4-H4)</f>
+        <v>71.515</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44489,13 +44630,39 @@
         <v>5</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-97.24</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <f aca="false">SQRT(2*(I5^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <f aca="false">-(F5-H5)</f>
+        <v>52.665</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44503,13 +44670,39 @@
         <v>6</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-86.31</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <f aca="false">SQRT(2*(I6^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <f aca="false">-(F6-H6)</f>
+        <v>41.735</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44517,13 +44710,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>70.96</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-81.11</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <f aca="false">SQRT(2*(I7^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <f aca="false">-(F7-H7)</f>
+        <v>36.535</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44531,13 +44750,39 @@
         <v>6</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>-45.99</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <f aca="false">SQRT(2*(I8^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <f aca="false">-(F8-H8)</f>
+        <v>1.415</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44545,13 +44790,39 @@
         <v>6</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>-40.84</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <f aca="false">SQRT(2*(I9^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <f aca="false">-(F9-H9)</f>
+        <v>-3.735</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44559,13 +44830,39 @@
         <v>6</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>-58.38</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <f aca="false">SQRT(2*(I10^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <f aca="false">-(F10-H10)</f>
+        <v>13.805</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44573,13 +44870,39 @@
         <v>6</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>45</v>
+        <v>579</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>111.09</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>-25.03</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <f aca="false">SQRT(2*(I11^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">-(F11-H11)</f>
+        <v>-19.545</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44587,13 +44910,39 @@
         <v>7</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>-8</v>
+        <v>2</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>-43.26</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <f aca="false">SQRT(2*(I12^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">-(F12-H12)</f>
+        <v>-1.315</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44601,27 +44950,79 @@
         <v>7</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>156.14</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>-55.11</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <f aca="false">SQRT(2*(I13^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <f aca="false">-(F13-H13)</f>
+        <v>10.535</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>50</v>
+        <v>580</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>-100.67</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <f aca="false">SQRT(2*(I14^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">-(F14-H14)</f>
+        <v>56.095</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44629,13 +45030,39 @@
         <v>8</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>59</v>
+        <v>580</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <f aca="false">SQRT(2*(I15^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">-(F15-H15)</f>
+        <v>-29.625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44643,13 +45070,39 @@
         <v>8</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>59</v>
+        <v>581</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>-150.83</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <f aca="false">SQRT(2*(I16^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">-(F16-H16)</f>
+        <v>106.255</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44657,13 +45110,39 @@
         <v>8</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>59</v>
+        <v>581</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>-126.51</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <f aca="false">SQRT(2*(I17^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <f aca="false">-(F17-H17)</f>
+        <v>81.935</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44671,13 +45150,39 @@
         <v>8</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>59</v>
+        <v>581</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>-125.88</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <f aca="false">SQRT(2*(I18^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K18" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <f aca="false">-(F18-H18)</f>
+        <v>81.305</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44685,13 +45190,39 @@
         <v>8</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>59</v>
+        <v>581</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>-112.85</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <f aca="false">SQRT(2*(I19^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <f aca="false">-(F19-H19)</f>
+        <v>68.275</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44699,13 +45230,39 @@
         <v>9</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>59</v>
+        <v>581</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>-58.17</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <f aca="false">SQRT(2*(I20^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L20" s="0" t="n">
+        <f aca="false">-(F20-H20)</f>
+        <v>13.595</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44713,125 +45270,1805 @@
         <v>9</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>59</v>
+        <v>581</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>-6</v>
+        <v>2</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>-55.11</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <f aca="false">SQRT(2*(I21^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L21" s="0" t="n">
+        <f aca="false">-(F21-H21)</f>
+        <v>10.535</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>59</v>
+        <v>582</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>73.29</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>-93.6</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <f aca="false">SQRT(2*(I22^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <f aca="false">-(F22-H22)</f>
+        <v>49.025</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>59</v>
+        <v>582</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>83.21</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>-82.77</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <f aca="false">SQRT(2*(I23^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <f aca="false">-(F23-H23)</f>
+        <v>38.195</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>59</v>
+        <v>582</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>148.45</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>-54.42</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <f aca="false">SQRT(2*(I24^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <f aca="false">-(F24-H24)</f>
+        <v>9.845</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>59</v>
+        <v>582</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>-49.87</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <f aca="false">SQRT(2*(I25^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <f aca="false">-(F25-H25)</f>
+        <v>5.29499999999999</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>59</v>
+        <v>582</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>-46</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <f aca="false">SQRT(2*(I26^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <f aca="false">-(F26-H26)</f>
+        <v>1.425</v>
       </c>
     </row>
     <row r="27" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="53" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>106</v>
+        <v>583</v>
       </c>
       <c r="C27" s="53" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D27" s="53" t="n">
-        <v>-6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E27" s="53" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F27" s="53" t="n">
+        <v>-123.65</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <f aca="false">SQRT(2*(I27^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <f aca="false">-(F27-H27)</f>
+        <v>79.075</v>
+      </c>
+      <c r="AMI27" s="0"/>
+      <c r="AMJ27" s="0"/>
     </row>
     <row r="28" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="53" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>106</v>
+        <v>583</v>
       </c>
       <c r="C28" s="53" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D28" s="53" t="n">
-        <v>-6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E28" s="53" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="F28" s="53" t="n">
+        <v>-96.39</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <f aca="false">SQRT(2*(I28^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <f aca="false">-(F28-H28)</f>
+        <v>51.815</v>
+      </c>
+      <c r="AMI28" s="0"/>
+      <c r="AMJ28" s="0"/>
     </row>
     <row r="29" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="53" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>106</v>
+        <v>583</v>
       </c>
       <c r="C29" s="53" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D29" s="53" t="n">
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="E29" s="53" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="F29" s="53" t="n">
+        <v>-134.93</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <f aca="false">SQRT(2*(I29^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L29" s="0" t="n">
+        <f aca="false">-(F29-H29)</f>
+        <v>90.355</v>
+      </c>
+      <c r="AMI29" s="0"/>
+      <c r="AMJ29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>583</v>
+      </c>
+      <c r="C30" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>-22.83</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <f aca="false">SQRT(2*(I30^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <f aca="false">-(F30-H30)</f>
+        <v>-21.745</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>583</v>
+      </c>
+      <c r="C31" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>75.93</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>-17.64</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <f aca="false">SQRT(2*(I31^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <f aca="false">-(F31-H31)</f>
+        <v>-26.935</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>88.64</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>-153.07</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <f aca="false">SQRT(2*(I32^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <f aca="false">-(F32-H32)</f>
+        <v>108.495</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>110.77</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>-142.54</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <f aca="false">SQRT(2*(I33^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <f aca="false">-(F33-H33)</f>
+        <v>97.965</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>99.26</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>-120.21</v>
+      </c>
+      <c r="G34" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <f aca="false">SQRT(2*(I34^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L34" s="0" t="n">
+        <f aca="false">-(F34-H34)</f>
+        <v>75.635</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>-119.68</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" s="0" t="n">
+        <f aca="false">SQRT(2*(I35^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <f aca="false">-(F35-H35)</f>
+        <v>75.105</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="0" t="n">
+        <f aca="false">SQRT(2*(I36^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <f aca="false">-(F36-H36)</f>
+        <v>-51.915</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>-132.41</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="0" t="n">
+        <f aca="false">SQRT(2*(I37^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <f aca="false">-(F37-H37)</f>
+        <v>87.835</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>-136.6</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" s="0" t="n">
+        <f aca="false">SQRT(2*(I38^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <f aca="false">-(F38-H38)</f>
+        <v>92.025</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>-98.45</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" s="0" t="n">
+        <f aca="false">SQRT(2*(I39^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K39" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L39" s="0" t="n">
+        <f aca="false">-(F39-H39)</f>
+        <v>53.875</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>80.85</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>-103.54</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <f aca="false">SQRT(2*(I40^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L40" s="0" t="n">
+        <f aca="false">-(F40-H40)</f>
+        <v>58.965</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>-81.53</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <f aca="false">SQRT(2*(I41^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L41" s="0" t="n">
+        <f aca="false">-(F41-H41)</f>
+        <v>36.955</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" s="0" t="n">
+        <f aca="false">SQRT(2*(I42^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L42" s="0" t="n">
+        <f aca="false">-(F42-H42)</f>
+        <v>-40.145</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J43" s="0" t="n">
+        <f aca="false">SQRT(2*(I43^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K43" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L43" s="0" t="n">
+        <f aca="false">-(F43-H43)</f>
+        <v>-74.675</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="0" t="n">
+        <f aca="false">SQRT(2*(I44^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L44" s="0" t="n">
+        <f aca="false">-(F44-H44)</f>
+        <v>-57.905</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>-179.01</v>
+      </c>
+      <c r="G45" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" s="0" t="n">
+        <f aca="false">SQRT(2*(I45^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L45" s="0" t="n">
+        <f aca="false">-(F45-H45)</f>
+        <v>134.435</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>-13.49</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J46" s="0" t="n">
+        <f aca="false">SQRT(2*(I46^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L46" s="0" t="n">
+        <f aca="false">-(F46-H46)</f>
+        <v>-31.085</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>142.77</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="0" t="n">
+        <f aca="false">SQRT(2*(I47^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K47" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L47" s="0" t="n">
+        <f aca="false">-(F47-H47)</f>
+        <v>-187.345</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>131.66</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" s="0" t="n">
+        <f aca="false">SQRT(2*(I48^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K48" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L48" s="0" t="n">
+        <f aca="false">-(F48-H48)</f>
+        <v>-176.235</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>149.69</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" s="0" t="n">
+        <f aca="false">SQRT(2*(I49^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L49" s="0" t="n">
+        <f aca="false">-(F49-H49)</f>
+        <v>-194.265</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>154.35</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="0" t="n">
+        <f aca="false">SQRT(2*(I50^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L50" s="0" t="n">
+        <f aca="false">-(F50-H50)</f>
+        <v>-198.925</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>81.18</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>172.27</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="0" t="n">
+        <f aca="false">SQRT(2*(I51^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L51" s="0" t="n">
+        <f aca="false">-(F51-H51)</f>
+        <v>-216.845</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>76.85</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>174.37</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I52" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <f aca="false">SQRT(2*(I52^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L52" s="0" t="n">
+        <f aca="false">-(F52-H52)</f>
+        <v>-218.945</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>-79.3</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <f aca="false">SQRT(2*(I53^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <f aca="false">-(F53-H53)</f>
+        <v>34.725</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>151.61</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <f aca="false">SQRT(2*(I54^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <f aca="false">-(F54-H54)</f>
+        <v>-196.185</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>105.43</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>-95.33</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" s="0" t="n">
+        <f aca="false">SQRT(2*(I55^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L55" s="0" t="n">
+        <f aca="false">-(F55-H55)</f>
+        <v>50.755</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>-28.79</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>-44.575</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <f aca="false">SQRT(2*(I56^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="L56" s="0" t="n">
+        <f aca="false">-(F56-H56)</f>
+        <v>-15.785</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>-44.346</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="0" t="n">
+        <f aca="false">SQRT(2*(I57^2))*132</f>
+        <v>560.028570699746</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="L57" s="0" t="n">
+        <f aca="false">-(F57-H57)</f>
+        <v>-34.686</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>-44.346</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="0" t="n">
+        <f aca="false">SQRT(2*(I58^2))*132</f>
+        <v>560.028570699746</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="L58" s="0" t="n">
+        <f aca="false">-(F58-H58)</f>
+        <v>-74.276</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>-44.346</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="0" t="n">
+        <f aca="false">SQRT(2*(I59^2))*132</f>
+        <v>560.028570699746</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="L59" s="0" t="n">
+        <f aca="false">-(F59-H59)</f>
+        <v>-86.646</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>-44.346</v>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="0" t="n">
+        <f aca="false">SQRT(2*(I60^2))*132</f>
+        <v>560.028570699746</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="L60" s="0" t="n">
+        <f aca="false">-(F60-H60)</f>
+        <v>-111.566</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" s="0" t="n">
+        <f aca="false">SQRT(2*(I61^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>2.5526</v>
+      </c>
+      <c r="L61" s="0" t="n">
+        <f aca="false">-(F61-H61)</f>
+        <v>-71.46</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J62" s="0" t="n">
+        <f aca="false">SQRT(2*(I62^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K62" s="0" t="n">
+        <v>2.5526</v>
+      </c>
+      <c r="L62" s="0" t="n">
+        <f aca="false">-(F62-H62)</f>
+        <v>-94.44</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" s="0" t="n">
+        <f aca="false">SQRT(2*(I63^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K63" s="0" t="n">
+        <v>2.5526</v>
+      </c>
+      <c r="L63" s="0" t="n">
+        <f aca="false">-(F63-H63)</f>
+        <v>-102.6</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" s="0" t="n">
+        <f aca="false">SQRT(2*(I64^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>2.5526</v>
+      </c>
+      <c r="L64" s="0" t="n">
+        <f aca="false">-(F64-H64)</f>
+        <v>-116.96</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="0" t="n">
+        <f aca="false">SQRT(2*(I65^2))*132</f>
+        <v>746.704760932994</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>2.5526</v>
+      </c>
+      <c r="L65" s="0" t="n">
+        <f aca="false">-(F65-H65)</f>
+        <v>-97.64</v>
       </c>
     </row>
   </sheetData>
@@ -44858,25 +47095,25 @@
         <v>350</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44903,7 +47140,7 @@
         <v>52.2</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44930,7 +47167,7 @@
         <v>21.9</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44957,7 +47194,7 @@
         <v>15.5</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44984,7 +47221,7 @@
         <v>-18</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45011,12 +47248,12 @@
         <v>-174.7</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>253</v>
@@ -45038,12 +47275,12 @@
         <v>-108.1</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>253</v>
@@ -45065,12 +47302,12 @@
         <v>-85.4</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>260</v>
@@ -45092,12 +47329,12 @@
         <v>-153.2</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>260</v>
@@ -45119,12 +47356,12 @@
         <v>-75.5</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>297</v>
@@ -45146,12 +47383,12 @@
         <v>-126</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>147</v>
@@ -45173,12 +47410,12 @@
         <v>32</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>150</v>
@@ -45200,12 +47437,12 @@
         <v>-215.1</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>195</v>
@@ -45227,12 +47464,12 @@
         <v>96.5</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>150</v>
@@ -45254,12 +47491,12 @@
         <v>-155.9</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>150</v>
@@ -45281,12 +47518,12 @@
         <v>75.3</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>233</v>
@@ -45308,12 +47545,12 @@
         <v>92.3</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>233</v>
@@ -45335,12 +47572,12 @@
         <v>39.7</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>233</v>
@@ -45362,12 +47599,12 @@
         <v>-6.9</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>233</v>
@@ -45389,12 +47626,12 @@
         <v>-22.3</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>233</v>
@@ -45416,12 +47653,12 @@
         <v>14.9</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>189</v>
@@ -45443,12 +47680,12 @@
         <v>53.6</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>146</v>
@@ -45470,12 +47707,12 @@
         <v>-153.3</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>189</v>
@@ -45497,12 +47734,12 @@
         <v>0.600000000000001</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>189</v>
@@ -45524,12 +47761,12 @@
         <v>25.7</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>146</v>
@@ -45551,12 +47788,12 @@
         <v>-59.4</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>90</v>
@@ -45578,12 +47815,12 @@
         <v>118</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>90</v>
@@ -45605,12 +47842,12 @@
         <v>100.2</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>90</v>
@@ -45632,12 +47869,12 @@
         <v>69.4</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>90</v>
@@ -45659,12 +47896,12 @@
         <v>70.3</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>90</v>
@@ -45686,12 +47923,12 @@
         <v>26.8</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>329</v>
@@ -45713,12 +47950,12 @@
         <v>-41.2</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>329</v>
@@ -45740,12 +47977,12 @@
         <v>7</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>329</v>
@@ -45767,7 +48004,7 @@
         <v>-27.9</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45794,12 +48031,12 @@
         <v>48.4</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>312</v>
@@ -45821,12 +48058,12 @@
         <v>-182.5</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>280</v>
@@ -45848,12 +48085,12 @@
         <v>-120.4</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>280</v>
@@ -45875,12 +48112,12 @@
         <v>-84</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>280</v>
@@ -45902,7 +48139,7 @@
         <v>25.5</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45929,12 +48166,12 @@
         <v>1</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>253</v>
@@ -45956,12 +48193,12 @@
         <v>-156.5</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>96</v>
@@ -45983,12 +48220,12 @@
         <v>87.4</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>96</v>
@@ -46010,12 +48247,12 @@
         <v>44.4</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>96</v>
@@ -46037,12 +48274,12 @@
         <v>-103.8</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>101</v>
@@ -46064,12 +48301,12 @@
         <v>-188.4</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>101</v>
@@ -46091,12 +48328,12 @@
         <v>122.5</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>114</v>
@@ -46118,12 +48355,12 @@
         <v>91.6</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>114</v>
@@ -46145,12 +48382,12 @@
         <v>64.3</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>75</v>
@@ -46172,12 +48409,12 @@
         <v>102.7</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>75</v>
@@ -46199,12 +48436,12 @@
         <v>77.2</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>75</v>
@@ -46226,7 +48463,7 @@
         <v>37.6</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46253,7 +48490,7 @@
         <v>99.9</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46280,12 +48517,12 @@
         <v>51.6</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>65</v>
@@ -46307,7 +48544,7 @@
         <v>-148.2</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46334,12 +48571,12 @@
         <v>-171.6</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>65</v>
@@ -46361,12 +48598,12 @@
         <v>-76.8</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>249</v>
@@ -46388,12 +48625,12 @@
         <v>68.8</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>249</v>
@@ -46415,12 +48652,12 @@
         <v>23.6</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>249</v>
@@ -46442,12 +48679,12 @@
         <v>-75.8</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>253</v>
@@ -46469,12 +48706,12 @@
         <v>-205.7</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>249</v>
@@ -46496,12 +48733,12 @@
         <v>4.5</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>214</v>
@@ -46523,12 +48760,12 @@
         <v>118.9</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>214</v>
@@ -46550,12 +48787,12 @@
         <v>111.3</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>214</v>
@@ -46577,12 +48814,12 @@
         <v>68.3</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>214</v>
@@ -46604,12 +48841,12 @@
         <v>-16.1</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>214</v>
@@ -46631,12 +48868,12 @@
         <v>24.3</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>114</v>
@@ -46658,12 +48895,12 @@
         <v>2.3</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>114</v>
@@ -46685,12 +48922,12 @@
         <v>-104.7</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>75</v>
@@ -46712,12 +48949,12 @@
         <v>-167.3</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>75</v>
@@ -46739,12 +48976,12 @@
         <v>-134.8</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>75</v>
@@ -46766,12 +49003,12 @@
         <v>-145.9</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>45</v>
@@ -46793,12 +49030,12 @@
         <v>-139.1</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>45</v>
@@ -46820,12 +49057,12 @@
         <v>-119.3</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>45</v>
@@ -46847,12 +49084,12 @@
         <v>-86.6</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>45</v>
@@ -46874,12 +49111,12 @@
         <v>-84.5</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>83</v>
@@ -46901,12 +49138,12 @@
         <v>-10.5</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>106</v>
@@ -46928,12 +49165,12 @@
         <v>-139.7</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>106</v>
@@ -46955,12 +49192,12 @@
         <v>40.7</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>106</v>
@@ -46982,12 +49219,12 @@
         <v>-91.1</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>106</v>
@@ -47009,12 +49246,12 @@
         <v>-64.5</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>106</v>
@@ -47036,12 +49273,12 @@
         <v>-83.2</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>312</v>
@@ -47063,12 +49300,12 @@
         <v>86.7</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>277</v>
@@ -47090,12 +49327,12 @@
         <v>81.9</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>277</v>
@@ -47117,12 +49354,12 @@
         <v>37.4</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>277</v>
@@ -47144,12 +49381,12 @@
         <v>-82.3</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>277</v>
@@ -47171,12 +49408,12 @@
         <v>-24.5</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>214</v>
@@ -47198,12 +49435,12 @@
         <v>-179.3</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>245</v>
@@ -47225,12 +49462,12 @@
         <v>113.7</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>245</v>
@@ -47252,12 +49489,12 @@
         <v>88.3</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>245</v>
@@ -47279,12 +49516,12 @@
         <v>51.4</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>245</v>
@@ -47306,12 +49543,12 @@
         <v>4.1</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>260</v>
@@ -47333,12 +49570,12 @@
         <v>35.9</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>260</v>
@@ -47360,12 +49597,12 @@
         <v>40.3</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>260</v>
@@ -47387,12 +49624,12 @@
         <v>9.1</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>260</v>
@@ -47414,12 +49651,12 @@
         <v>-20.4</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>260</v>
@@ -47441,12 +49678,12 @@
         <v>-0.5</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>83</v>
@@ -47468,12 +49705,12 @@
         <v>-200.9</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>83</v>
@@ -47495,12 +49732,12 @@
         <v>-170.2</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>83</v>
@@ -47522,12 +49759,12 @@
         <v>-120.8</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>90</v>
@@ -47549,12 +49786,12 @@
         <v>-183.6</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>90</v>
@@ -47576,12 +49813,12 @@
         <v>-175.1</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>189</v>
@@ -47603,12 +49840,12 @@
         <v>-91.5</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="B103" s="0" t="s">
         <v>222</v>
@@ -47630,12 +49867,12 @@
         <v>-55.1</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="B104" s="0" t="s">
         <v>222</v>
@@ -47657,12 +49894,12 @@
         <v>-80.5</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="B105" s="0" t="s">
         <v>222</v>
@@ -47684,12 +49921,12 @@
         <v>-32</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="B106" s="0" t="s">
         <v>222</v>
@@ -47711,12 +49948,12 @@
         <v>25.1</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>138</v>
@@ -47738,12 +49975,12 @@
         <v>-135.2</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="B108" s="0" t="s">
         <v>138</v>
@@ -47765,12 +50002,12 @@
         <v>12.4</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>138</v>
@@ -47792,12 +50029,12 @@
         <v>32.2</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>143</v>
@@ -47819,12 +50056,12 @@
         <v>-201.6</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="B111" s="0" t="s">
         <v>143</v>
@@ -47846,12 +50083,12 @@
         <v>-137.9</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>192</v>
@@ -47873,12 +50110,12 @@
         <v>115.2</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>150</v>
@@ -47900,12 +50137,12 @@
         <v>-97.6</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="B114" s="0" t="s">
         <v>150</v>
@@ -47927,12 +50164,12 @@
         <v>-79.8</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="B115" s="0" t="s">
         <v>192</v>
@@ -47954,12 +50191,12 @@
         <v>10.4</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="B116" s="0" t="s">
         <v>157</v>
@@ -47981,12 +50218,12 @@
         <v>-172.4</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="B117" s="0" t="s">
         <v>150</v>
@@ -48008,12 +50245,12 @@
         <v>17.1</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="B118" s="0" t="s">
         <v>150</v>
@@ -48035,12 +50272,12 @@
         <v>-15.5</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="B119" s="0" t="s">
         <v>114</v>
@@ -48062,12 +50299,12 @@
         <v>-104.3</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="B120" s="0" t="s">
         <v>157</v>
@@ -48089,12 +50326,12 @@
         <v>65.5</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="B121" s="0" t="s">
         <v>157</v>
@@ -48116,7 +50353,7 @@
         <v>57.8</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -48140,75 +50377,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>359</v>
@@ -48272,7 +50509,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>359</v>
@@ -48317,7 +50554,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>359</v>
@@ -48362,7 +50599,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>359</v>
@@ -48411,7 +50648,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>359</v>
@@ -48456,13 +50693,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>260</v>
@@ -48482,13 +50719,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>260</v>
@@ -48508,13 +50745,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>260</v>
@@ -48534,13 +50771,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>260</v>
@@ -48560,13 +50797,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>260</v>
@@ -48586,13 +50823,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>150</v>
@@ -48612,13 +50849,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>150</v>
@@ -48638,13 +50875,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>150</v>
@@ -48664,13 +50901,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>150</v>
@@ -48690,13 +50927,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>150</v>
@@ -48719,10 +50956,10 @@
         <v>384</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>202</v>
@@ -48745,10 +50982,10 @@
         <v>384</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>202</v>
@@ -48771,10 +51008,10 @@
         <v>384</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>202</v>
@@ -48816,10 +51053,10 @@
         <v>384</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>202</v>
@@ -48842,10 +51079,10 @@
         <v>384</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>202</v>
@@ -48865,13 +51102,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>189</v>
@@ -48910,13 +51147,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>189</v>
@@ -48936,13 +51173,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>189</v>
@@ -48962,13 +51199,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>189</v>
@@ -48988,13 +51225,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>189</v>
@@ -49037,13 +51274,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>59</v>
@@ -49086,13 +51323,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>59</v>
@@ -49135,13 +51372,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>59</v>
@@ -49203,13 +51440,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>59</v>
@@ -49271,13 +51508,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>59</v>
@@ -49316,13 +51553,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>329</v>
@@ -49342,13 +51579,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>329</v>
@@ -49387,13 +51624,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>329</v>
@@ -49413,10 +51650,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>112</v>
@@ -49439,13 +51676,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>308</v>
@@ -49465,13 +51702,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>280</v>
@@ -49491,13 +51728,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>280</v>
@@ -49517,13 +51754,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>249</v>
@@ -49543,10 +51780,10 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>223</v>
@@ -49569,13 +51806,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>249</v>
@@ -49595,13 +51832,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>96</v>
@@ -49644,13 +51881,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>96</v>
@@ -49674,13 +51911,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>96</v>
@@ -49704,13 +51941,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>96</v>
@@ -49730,13 +51967,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>96</v>
@@ -49760,13 +51997,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>71</v>
@@ -49786,13 +52023,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>71</v>
@@ -49812,13 +52049,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>71</v>
@@ -49838,13 +52075,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>71</v>
@@ -49864,13 +52101,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>384</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>71</v>
@@ -49890,7 +52127,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>371</v>
@@ -49916,7 +52153,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>371</v>
@@ -49942,13 +52179,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>371</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>65</v>
@@ -49987,7 +52224,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>371</v>
@@ -50036,13 +52273,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>371</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>65</v>
@@ -50085,13 +52322,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>249</v>
@@ -50130,13 +52367,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>249</v>
@@ -50156,13 +52393,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>249</v>
@@ -50182,13 +52419,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>249</v>
@@ -50208,13 +52445,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>249</v>
@@ -50234,13 +52471,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>225</v>
@@ -50260,13 +52497,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>225</v>
@@ -50286,13 +52523,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>225</v>
@@ -50331,13 +52568,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>225</v>
@@ -50357,13 +52594,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>225</v>
@@ -50383,13 +52620,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>214</v>
@@ -50409,13 +52646,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>214</v>
@@ -50435,13 +52672,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>214</v>
@@ -50480,13 +52717,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>214</v>
@@ -50506,13 +52743,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>214</v>
@@ -50532,13 +52769,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>71</v>
@@ -50558,13 +52795,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>71</v>
@@ -50584,13 +52821,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>71</v>
@@ -50610,13 +52847,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>71</v>
@@ -50636,13 +52873,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>71</v>
@@ -50662,13 +52899,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>45</v>
@@ -50711,13 +52948,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>83</v>
@@ -50760,13 +52997,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>83</v>
@@ -50809,13 +53046,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>83</v>
@@ -50839,13 +53076,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>380</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>83</v>
@@ -50869,13 +53106,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>106</v>
@@ -50895,13 +53132,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>106</v>
@@ -50921,13 +53158,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
       <c r="D84" s="0" t="s">
         <v>106</v>
@@ -50947,13 +53184,13 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>106</v>
@@ -50973,13 +53210,13 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="D86" s="0" t="s">
         <v>106</v>
@@ -50999,13 +53236,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>277</v>
@@ -51025,13 +53262,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="D88" s="0" t="s">
         <v>277</v>
@@ -51070,13 +53307,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="D89" s="0" t="s">
         <v>277</v>
@@ -51096,13 +53333,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="D90" s="0" t="s">
         <v>277</v>
@@ -51122,13 +53359,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="D91" s="0" t="s">
         <v>277</v>
@@ -51148,13 +53385,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="D92" s="0" t="s">
         <v>214</v>
@@ -51174,13 +53411,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="D93" s="0" t="s">
         <v>245</v>
@@ -51200,13 +53437,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="D94" s="0" t="s">
         <v>245</v>
@@ -51226,13 +53463,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="D95" s="0" t="s">
         <v>245</v>
@@ -51252,13 +53489,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
       <c r="D96" s="0" t="s">
         <v>245</v>
@@ -51278,13 +53515,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="D97" s="0" t="s">
         <v>260</v>
@@ -51304,13 +53541,13 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="D98" s="0" t="s">
         <v>260</v>
@@ -51330,13 +53567,13 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="D99" s="0" t="s">
         <v>260</v>
@@ -51356,13 +53593,13 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="D100" s="0" t="s">
         <v>260</v>
@@ -51382,13 +53619,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="D101" s="0" t="s">
         <v>260</v>
@@ -51408,13 +53645,13 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="D102" s="0" t="s">
         <v>83</v>
@@ -51434,13 +53671,13 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="D103" s="0" t="s">
         <v>83</v>
@@ -51460,13 +53697,13 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="D104" s="0" t="s">
         <v>83</v>
@@ -51486,13 +53723,13 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="D105" s="0" t="s">
         <v>87</v>
@@ -51516,13 +53753,13 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="D106" s="0" t="s">
         <v>87</v>
@@ -51542,13 +53779,13 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>222</v>
@@ -51568,13 +53805,13 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="D108" s="0" t="s">
         <v>222</v>
@@ -51594,13 +53831,13 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>222</v>
@@ -51620,13 +53857,13 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="D110" s="0" t="s">
         <v>222</v>
@@ -51646,13 +53883,13 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="D111" s="0" t="s">
         <v>222</v>
@@ -51672,13 +53909,13 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="D112" s="0" t="s">
         <v>138</v>
@@ -51702,13 +53939,13 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="D113" s="0" t="s">
         <v>138</v>
@@ -51732,13 +53969,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="D114" s="0" t="s">
         <v>138</v>
@@ -51758,13 +53995,13 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>186</v>
@@ -51788,13 +54025,13 @@
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>186</v>
@@ -51818,13 +54055,13 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="D117" s="0" t="s">
         <v>153</v>
@@ -51844,13 +54081,13 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>153</v>
@@ -51870,13 +54107,13 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>153</v>
@@ -51896,13 +54133,13 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>153</v>
@@ -51922,13 +54159,13 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>153</v>
@@ -51948,13 +54185,13 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="D122" s="0" t="s">
         <v>153</v>
@@ -51974,13 +54211,13 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="D123" s="0" t="s">
         <v>153</v>
@@ -52000,13 +54237,13 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D124" s="0" t="s">
         <v>153</v>
@@ -52026,13 +54263,13 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="D125" s="0" t="s">
         <v>153</v>
@@ -52052,13 +54289,13 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="D126" s="0" t="s">
         <v>153</v>

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -1219,6 +1219,15 @@
     <t xml:space="preserve">SS</t>
   </si>
   <si>
+    <t xml:space="preserve">condition blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition “?”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i.e. T033-218-070-ST-24-99DS</t>
+  </si>
+  <si>
     <t xml:space="preserve">NP</t>
   </si>
   <si>
@@ -1235,15 +1244,6 @@
   </si>
   <si>
     <t xml:space="preserve">alder, not diseased tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">condition blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condition “?”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i.e. T033-218-070-ST-24-99DS</t>
   </si>
   <si>
     <t xml:space="preserve">Dist</t>
@@ -2523,7 +2523,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2736,10 +2736,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2816,16 +2812,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>56</xdr:col>
-      <xdr:colOff>323640</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>142560</xdr:rowOff>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>142560</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>319320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>57</xdr:col>
-      <xdr:colOff>292680</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>3600</xdr:rowOff>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>21240</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>283680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2834,8 +2830,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="2700000">
-          <a:off x="26772480" y="8238240"/>
-          <a:ext cx="421560" cy="1689840"/>
+          <a:off x="26142840" y="8872200"/>
+          <a:ext cx="1689480" cy="421560"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2898,7 +2894,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AP77"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.13"/>
@@ -9741,7 +9737,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C99"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -10849,7 +10845,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O759"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.33"/>
@@ -32660,227 +32656,227 @@
     </row>
     <row r="750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B750" s="0" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C750" s="0" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D750" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F750" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="G750" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="H750" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I750" s="0" t="s">
         <v>396</v>
       </c>
-      <c r="I750" s="0" t="s">
-        <v>397</v>
-      </c>
-      <c r="J750" s="5"/>
+      <c r="M750" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="N750" s="0" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="O750" s="0" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B751" s="0" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C751" s="0" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D751" s="0" t="s">
-        <v>396</v>
+        <v>60</v>
+      </c>
+      <c r="F751" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="G751" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="H751" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="I751" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="J751" s="5"/>
+        <v>397</v>
+      </c>
+      <c r="M751" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="N751" s="0" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="O751" s="0" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="B752" s="0" t="n">
-        <v>349</v>
+        <v>122</v>
       </c>
       <c r="C752" s="0" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D752" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="I752" s="0" t="s">
-        <v>400</v>
-      </c>
-      <c r="J752" s="5"/>
+        <v>386</v>
+      </c>
+      <c r="F752" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="G752" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="H752" s="0" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>335</v>
+        <v>130</v>
       </c>
       <c r="B753" s="0" t="n">
-        <v>347</v>
+        <v>255</v>
       </c>
       <c r="C753" s="0" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D753" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="I753" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="J753" s="5"/>
+        <v>386</v>
+      </c>
+      <c r="F753" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="G753" s="0" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>95</v>
+        <v>130</v>
+      </c>
+      <c r="B754" s="0" t="n">
+        <v>218</v>
       </c>
       <c r="C754" s="0" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D754" s="0" t="s">
-        <v>60</v>
+        <v>386</v>
       </c>
       <c r="F754" s="0" t="s">
-        <v>355</v>
+        <v>162</v>
       </c>
       <c r="G754" s="0" t="s">
         <v>356</v>
       </c>
       <c r="H754" s="0" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I754" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="M754" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="N754" s="0" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="O754" s="0" t="s">
-        <v>61</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="J754" s="5"/>
     </row>
     <row r="755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="C755" s="0" t="n">
-        <v>42</v>
-      </c>
-      <c r="D755" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="F755" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="G755" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="H755" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I755" s="0" t="s">
-        <v>403</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D755" s="2"/>
       <c r="M755" s="0" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N755" s="0" t="n">
-        <v>30.5</v>
+        <v>60.5</v>
       </c>
       <c r="O755" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="B756" s="0" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="C756" s="0" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D756" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="F756" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="G756" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="H756" s="0" t="n">
-        <v>28</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="I756" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="J756" s="5"/>
     </row>
     <row r="757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="B757" s="0" t="n">
-        <v>255</v>
+        <v>173</v>
       </c>
       <c r="C757" s="0" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D757" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="F757" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="G757" s="0" t="s">
-        <v>356</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="I757" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="J757" s="5"/>
     </row>
     <row r="758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="B758" s="0" t="n">
-        <v>218</v>
+        <v>349</v>
       </c>
       <c r="C758" s="0" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D758" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="F758" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="G758" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="H758" s="0" t="n">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="I758" s="0" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J758" s="5"/>
     </row>
     <row r="759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>142</v>
+        <v>335</v>
+      </c>
+      <c r="B759" s="0" t="n">
+        <v>347</v>
       </c>
       <c r="C759" s="0" t="n">
-        <v>53</v>
-      </c>
-      <c r="D759" s="2"/>
-      <c r="M759" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="N759" s="0" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="O759" s="0" t="s">
-        <v>64</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D759" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="I759" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="J759" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -32899,12 +32895,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="4.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.15"/>
   </cols>
@@ -33629,7 +33625,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L179"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -37294,7 +37290,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -39305,7 +39301,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A3:BS50"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="3" style="0" width="6.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="56" style="0" width="6.42"/>
@@ -44464,8 +44460,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ65"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -45505,23 +45501,23 @@
         <v>1.425</v>
       </c>
     </row>
-    <row r="27" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="53" t="n">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="C27" s="53" t="n">
+      <c r="C27" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="53" t="n">
+      <c r="D27" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="53" t="n">
+      <c r="E27" s="0" t="n">
         <v>51.2</v>
       </c>
-      <c r="F27" s="53" t="n">
+      <c r="F27" s="0" t="n">
         <v>-123.65</v>
       </c>
       <c r="G27" s="0" t="s">
@@ -45544,26 +45540,24 @@
         <f aca="false">-(F27-H27)</f>
         <v>79.075</v>
       </c>
-      <c r="AMI27" s="0"/>
-      <c r="AMJ27" s="0"/>
-    </row>
-    <row r="28" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="53" t="n">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="C28" s="53" t="n">
+      <c r="C28" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="53" t="n">
+      <c r="D28" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="53" t="n">
+      <c r="E28" s="0" t="n">
         <v>40.23</v>
       </c>
-      <c r="F28" s="53" t="n">
+      <c r="F28" s="0" t="n">
         <v>-96.39</v>
       </c>
       <c r="G28" s="0" t="s">
@@ -45586,26 +45580,24 @@
         <f aca="false">-(F28-H28)</f>
         <v>51.815</v>
       </c>
-      <c r="AMI28" s="0"/>
-      <c r="AMJ28" s="0"/>
-    </row>
-    <row r="29" s="53" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="53" t="n">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="C29" s="53" t="n">
+      <c r="C29" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="53" t="n">
+      <c r="D29" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="53" t="n">
+      <c r="E29" s="0" t="n">
         <v>28.39</v>
       </c>
-      <c r="F29" s="53" t="n">
+      <c r="F29" s="0" t="n">
         <v>-134.93</v>
       </c>
       <c r="G29" s="0" t="s">
@@ -45628,20 +45620,18 @@
         <f aca="false">-(F29-H29)</f>
         <v>90.355</v>
       </c>
-      <c r="AMI29" s="0"/>
-      <c r="AMJ29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="C30" s="53" t="n">
+      <c r="C30" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="53" t="n">
+      <c r="D30" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E30" s="0" t="n">
@@ -45675,13 +45665,13 @@
       <c r="A31" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="C31" s="53" t="n">
+      <c r="C31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="53" t="n">
+      <c r="D31" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E31" s="0" t="n">
@@ -47088,7 +47078,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -50373,7 +50363,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V126"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">

--- a/Poria_survey_70s.xlsx
+++ b/Poria_survey_70s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Poria_compass_points" sheetId="1" state="visible" r:id="rId2"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6811" uniqueCount="734">
   <si>
     <t xml:space="preserve">Block</t>
   </si>
@@ -2812,16 +2812,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>55</xdr:col>
-      <xdr:colOff>142560</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>319320</xdr:rowOff>
+      <xdr:col>56</xdr:col>
+      <xdr:colOff>324360</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>142560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>59</xdr:col>
-      <xdr:colOff>21240</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>283680</xdr:rowOff>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>292680</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2830,8 +2830,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="2700000">
-          <a:off x="26142840" y="8872200"/>
-          <a:ext cx="1689480" cy="421560"/>
+          <a:off x="26781120" y="8238240"/>
+          <a:ext cx="421200" cy="1689480"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2894,7 +2894,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AP77"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.13"/>
@@ -9737,7 +9737,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C99"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -10845,7 +10845,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O759"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.33"/>
@@ -32895,7 +32895,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="4.71"/>
@@ -33625,7 +33625,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L179"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -37290,7 +37290,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -39301,7 +39301,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A3:BS50"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="3" style="0" width="6.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="56" style="0" width="6.42"/>
@@ -44461,7 +44461,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L65"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -47078,7 +47078,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -50363,7 +50363,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V126"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -51241,25 +51241,6 @@
       <c r="I26" s="0" t="n">
         <f aca="false">H26*7.92/12</f>
         <v>130.68</v>
-      </c>
-      <c r="P26" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q26" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="R26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="0" t="n">
-        <v>110</v>
-      </c>
-      <c r="T26" s="0" t="n">
-        <v>60</v>
-      </c>
-      <c r="U26" s="0" t="n">
-        <f aca="false">T26*7.92/12</f>
-        <v>39.6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
